--- a/secretario.xlsx
+++ b/secretario.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5105" uniqueCount="1767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5204" uniqueCount="1792">
   <si>
     <t xml:space="preserve">DATA</t>
   </si>
@@ -5098,6 +5098,7 @@
         <color theme="1"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">, Balneário Camboriú, SC, Brasil</t>
     </r>
@@ -6872,6 +6873,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">, Balneário Camboriú, SC, Brasil</t>
     </r>
@@ -6939,6 +6941,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">, Balneário Camboriú, SC, Brasil</t>
     </r>
@@ -6972,6 +6975,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">, Balneário Camboriú, SC, Brasil</t>
     </r>
@@ -7027,6 +7031,7 @@
         <color theme="1"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">, Balneário Camboriú, SC, Brasil</t>
     </r>
@@ -7081,6 +7086,154 @@
         <color theme="1"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, Balneário Camboriú, SC, Brasil</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">BO-00600.2026.0026758 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://drive.google.com/file/d/1W_am9MaOOI65g3nsKiYYMH7lt4OzqGUX/view?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Masculino arrombou porta da residencia e furtou um relógio e R$ 200,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R. Indonésia</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rua Indonésia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, Balneário Camboriú, SC, Brasil</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">BO-00549.2026.0005655 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://drive.google.com/file/d/1hig1FQLF6sA96C74Z1ZgCF-O92edfvL9/view?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Furto de bicicleta e uma bolsa com celular  em frente ao supermercado Bistek </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supermercado Bistek – 4ª Avenida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO-00600.2026.0026785 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://drive.google.com/file/d/1xEjM_FyW1sm-7PY92yzKA7_FLys2meZS/view?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Furto de botijão de gás e aparelho de ar condicionado na residencia</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rua 2850</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">, Balneário Camboriú, SC, Brasil</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">BO-00600.2026.0026795 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://drive.google.com/file/d/1-h6fkuS1PgQk8yRYON73tKJQJgPfotUg/view?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Furto de bicicleta na garagem da residencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R. Canelinha</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rua Canelinha</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">, Balneário Camboriú, SC, Brasil</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">BO-00600.2026.0027288 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://drive.google.com/file/d/1ScXvUAvpfWdl2N1IwhLh9EL0FyIxalkN/view?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Furto de fiação elétrica numa obra na Av. Alvin Bauer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOCOP-02317.2026.0002570 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://drive.google.com/file/d/1TLgHuUwEjBLYnXqXqQj-psKBmo7t9Yyv/view?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Furto de bicicleta de dentro do patio da residencia</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rua Dom Miguel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
       </rPr>
       <t xml:space="preserve">, Balneário Camboriú, SC, Brasil</t>
     </r>
@@ -7200,17 +7353,17 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -7294,7 +7447,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="78">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7471,47 +7624,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7583,12 +7696,48 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -7601,10 +7750,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -24848,58 +24993,58 @@
       <c r="V325" s="5"/>
       <c r="XFD325" s="5"/>
     </row>
-    <row r="326" s="47" customFormat="true" ht="40.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A326" s="44" t="n">
+    <row r="326" s="14" customFormat="true" ht="40.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A326" s="26" t="n">
         <v>28</v>
       </c>
-      <c r="B326" s="45" t="s">
+      <c r="B326" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C326" s="45" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D326" s="46" t="n">
+      <c r="C326" s="15" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D326" s="36" t="n">
         <v>0.0666666666666667</v>
       </c>
-      <c r="E326" s="44" t="s">
+      <c r="E326" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="F326" s="47" t="s">
+      <c r="F326" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="G326" s="48" t="s">
+      <c r="G326" s="35" t="s">
         <v>1317</v>
       </c>
-      <c r="H326" s="49" t="s">
+      <c r="H326" s="17" t="s">
         <v>1318</v>
       </c>
-      <c r="I326" s="50" t="s">
-        <v>22</v>
-      </c>
-      <c r="J326" s="50" t="s">
+      <c r="I326" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="J326" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="K326" s="51" t="s">
+      <c r="K326" s="20" t="s">
         <v>1319</v>
       </c>
-      <c r="L326" s="51"/>
-      <c r="M326" s="48" t="s">
+      <c r="L326" s="20"/>
+      <c r="M326" s="35" t="s">
         <v>1320</v>
       </c>
-      <c r="N326" s="52" t="s">
+      <c r="N326" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="O326" s="48" t="s">
+      <c r="O326" s="35" t="s">
         <v>1321</v>
       </c>
-      <c r="P326" s="48" t="s">
+      <c r="P326" s="35" t="s">
         <v>1322</v>
       </c>
-      <c r="S326" s="53"/>
-      <c r="T326" s="53"/>
-      <c r="U326" s="53"/>
-      <c r="V326" s="53"/>
-      <c r="XFD326" s="53"/>
+      <c r="S326" s="5"/>
+      <c r="T326" s="5"/>
+      <c r="U326" s="5"/>
+      <c r="V326" s="5"/>
+      <c r="XFD326" s="5"/>
     </row>
     <row r="327" s="14" customFormat="true" ht="40.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="26" t="n">
@@ -24947,7 +25092,7 @@
       <c r="O327" s="25" t="s">
         <v>792</v>
       </c>
-      <c r="P327" s="54" t="s">
+      <c r="P327" s="44" t="s">
         <v>1327</v>
       </c>
       <c r="S327" s="2"/>
@@ -25019,7 +25164,7 @@
       <c r="C329" s="15" t="n">
         <v>2026</v>
       </c>
-      <c r="D329" s="55" t="n">
+      <c r="D329" s="45" t="n">
         <v>0.34375</v>
       </c>
       <c r="E329" s="26" t="s">
@@ -25869,7 +26014,7 @@
       <c r="C345" s="15" t="n">
         <v>2026</v>
       </c>
-      <c r="D345" s="55" t="n">
+      <c r="D345" s="45" t="n">
         <v>0.166666666666667</v>
       </c>
       <c r="E345" s="26" t="s">
@@ -26032,7 +26177,7 @@
       <c r="C348" s="15" t="n">
         <v>2026</v>
       </c>
-      <c r="D348" s="56" t="n">
+      <c r="D348" s="46" t="n">
         <v>0.277777777777778</v>
       </c>
       <c r="E348" s="26" t="s">
@@ -26085,7 +26230,7 @@
       <c r="C349" s="15" t="n">
         <v>2026</v>
       </c>
-      <c r="D349" s="56" t="n">
+      <c r="D349" s="46" t="n">
         <v>1.27777777777778</v>
       </c>
       <c r="E349" s="26" t="s">
@@ -26138,7 +26283,7 @@
       <c r="C350" s="15" t="n">
         <v>2026</v>
       </c>
-      <c r="D350" s="56" t="n">
+      <c r="D350" s="46" t="n">
         <v>2.27777777777778</v>
       </c>
       <c r="E350" s="26" t="s">
@@ -26191,7 +26336,7 @@
       <c r="C351" s="15" t="n">
         <v>2026</v>
       </c>
-      <c r="D351" s="56" t="n">
+      <c r="D351" s="46" t="n">
         <v>3.27777777777778</v>
       </c>
       <c r="E351" s="26" t="s">
@@ -26509,7 +26654,7 @@
       <c r="C357" s="15" t="n">
         <v>2026</v>
       </c>
-      <c r="D357" s="55" t="n">
+      <c r="D357" s="45" t="n">
         <v>0.875</v>
       </c>
       <c r="E357" s="26" t="s">
@@ -27132,7 +27277,7 @@
       <c r="M368" s="38" t="s">
         <v>203</v>
       </c>
-      <c r="N368" s="57" t="s">
+      <c r="N368" s="47" t="s">
         <v>128</v>
       </c>
       <c r="O368" s="35" t="s">
@@ -27190,7 +27335,7 @@
       <c r="M369" s="35" t="s">
         <v>1497</v>
       </c>
-      <c r="N369" s="57" t="s">
+      <c r="N369" s="47" t="s">
         <v>26</v>
       </c>
       <c r="O369" s="35" t="s">
@@ -27306,7 +27451,7 @@
       <c r="M371" s="35" t="s">
         <v>1510</v>
       </c>
-      <c r="N371" s="57" t="s">
+      <c r="N371" s="47" t="s">
         <v>66</v>
       </c>
       <c r="O371" s="35" t="s">
@@ -27361,13 +27506,13 @@
       <c r="M372" s="35" t="s">
         <v>1516</v>
       </c>
-      <c r="N372" s="57" t="s">
+      <c r="N372" s="47" t="s">
         <v>26</v>
       </c>
       <c r="O372" s="35" t="s">
         <v>1517</v>
       </c>
-      <c r="P372" s="57" t="s">
+      <c r="P372" s="47" t="s">
         <v>1518</v>
       </c>
       <c r="S372" s="2"/>
@@ -27414,7 +27559,7 @@
       <c r="M373" s="35" t="s">
         <v>438</v>
       </c>
-      <c r="N373" s="57" t="s">
+      <c r="N373" s="47" t="s">
         <v>26</v>
       </c>
       <c r="O373" s="35" t="s">
@@ -27628,13 +27773,13 @@
       <c r="M377" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="N377" s="57" t="s">
+      <c r="N377" s="47" t="s">
         <v>26</v>
       </c>
       <c r="O377" s="35" t="s">
         <v>1535</v>
       </c>
-      <c r="P377" s="57" t="s">
+      <c r="P377" s="47" t="s">
         <v>88</v>
       </c>
       <c r="S377" s="2"/>
@@ -27734,7 +27879,7 @@
       <c r="M379" s="38" t="s">
         <v>1542</v>
       </c>
-      <c r="N379" s="57" t="s">
+      <c r="N379" s="47" t="s">
         <v>26</v>
       </c>
       <c r="O379" s="38" t="s">
@@ -27842,7 +27987,7 @@
       <c r="M381" s="35" t="s">
         <v>566</v>
       </c>
-      <c r="N381" s="57" t="s">
+      <c r="N381" s="47" t="s">
         <v>26</v>
       </c>
       <c r="O381" s="35" t="s">
@@ -27897,7 +28042,7 @@
       <c r="M382" s="38" t="s">
         <v>203</v>
       </c>
-      <c r="N382" s="57" t="s">
+      <c r="N382" s="47" t="s">
         <v>26</v>
       </c>
       <c r="O382" s="35" t="s">
@@ -27953,7 +28098,7 @@
       <c r="M383" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="N383" s="57" t="s">
+      <c r="N383" s="47" t="s">
         <v>273</v>
       </c>
       <c r="O383" s="39" t="s">
@@ -28006,7 +28151,7 @@
       <c r="M384" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="N384" s="57" t="s">
+      <c r="N384" s="47" t="s">
         <v>26</v>
       </c>
       <c r="O384" s="39" t="s">
@@ -28057,7 +28202,7 @@
       <c r="M385" s="38" t="s">
         <v>203</v>
       </c>
-      <c r="N385" s="57" t="s">
+      <c r="N385" s="47" t="s">
         <v>52</v>
       </c>
       <c r="O385" s="32" t="s">
@@ -28269,7 +28414,7 @@
       <c r="M389" s="35" t="s">
         <v>1582</v>
       </c>
-      <c r="N389" s="57" t="s">
+      <c r="N389" s="47" t="s">
         <v>192</v>
       </c>
       <c r="O389" s="35" t="s">
@@ -28333,693 +28478,693 @@
       <c r="R390" s="38"/>
       <c r="S390" s="2"/>
     </row>
-    <row r="391" s="66" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A391" s="58" t="n">
+    <row r="391" s="56" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A391" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="B391" s="59" t="s">
+      <c r="B391" s="49" t="s">
         <v>1453</v>
       </c>
-      <c r="C391" s="59" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D391" s="60" t="n">
+      <c r="C391" s="49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D391" s="50" t="n">
         <v>0.971527777777778</v>
       </c>
-      <c r="E391" s="58" t="s">
+      <c r="E391" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="F391" s="61" t="s">
+      <c r="F391" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="G391" s="62" t="s">
+      <c r="G391" s="52" t="s">
         <v>1589</v>
       </c>
-      <c r="H391" s="62" t="s">
+      <c r="H391" s="52" t="s">
         <v>1590</v>
       </c>
-      <c r="I391" s="61" t="s">
-        <v>22</v>
-      </c>
-      <c r="J391" s="63" t="s">
+      <c r="I391" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="J391" s="53" t="s">
         <v>136</v>
       </c>
-      <c r="K391" s="62" t="s">
+      <c r="K391" s="52" t="s">
         <v>1591</v>
       </c>
-      <c r="L391" s="62" t="s">
+      <c r="L391" s="52" t="s">
         <v>1592</v>
       </c>
-      <c r="M391" s="62" t="s">
+      <c r="M391" s="52" t="s">
         <v>1593</v>
       </c>
-      <c r="N391" s="64" t="s">
+      <c r="N391" s="54" t="s">
         <v>179</v>
       </c>
-      <c r="O391" s="62" t="s">
+      <c r="O391" s="52" t="s">
         <v>1594</v>
       </c>
-      <c r="P391" s="62" t="s">
+      <c r="P391" s="52" t="s">
         <v>1595</v>
       </c>
-      <c r="Q391" s="61"/>
-      <c r="R391" s="62" t="s">
+      <c r="Q391" s="51"/>
+      <c r="R391" s="52" t="s">
         <v>1596</v>
       </c>
-      <c r="S391" s="65"/>
-    </row>
-    <row r="392" s="66" customFormat="true" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A392" s="58" t="n">
+      <c r="S391" s="55"/>
+    </row>
+    <row r="392" s="56" customFormat="true" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A392" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="B392" s="59" t="s">
+      <c r="B392" s="49" t="s">
         <v>1453</v>
       </c>
-      <c r="C392" s="59" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D392" s="60" t="n">
+      <c r="C392" s="49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D392" s="50" t="n">
         <v>0.0416666666666667</v>
       </c>
-      <c r="E392" s="58" t="s">
+      <c r="E392" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="F392" s="61" t="s">
+      <c r="F392" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="G392" s="62" t="s">
+      <c r="G392" s="52" t="s">
         <v>1597</v>
       </c>
-      <c r="H392" s="62" t="s">
+      <c r="H392" s="52" t="s">
         <v>1598</v>
       </c>
-      <c r="I392" s="61" t="s">
-        <v>22</v>
-      </c>
-      <c r="J392" s="61" t="s">
+      <c r="I392" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="J392" s="51" t="s">
         <v>325</v>
       </c>
-      <c r="K392" s="62" t="s">
+      <c r="K392" s="52" t="s">
         <v>1599</v>
       </c>
-      <c r="L392" s="67" t="s">
+      <c r="L392" s="57" t="s">
         <v>327</v>
       </c>
-      <c r="M392" s="61" t="s">
+      <c r="M392" s="51" t="s">
         <v>263</v>
       </c>
-      <c r="N392" s="64" t="s">
+      <c r="N392" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="O392" s="61" t="s">
+      <c r="O392" s="51" t="s">
         <v>1600</v>
       </c>
-      <c r="P392" s="64" t="s">
+      <c r="P392" s="54" t="s">
         <v>265</v>
       </c>
-      <c r="Q392" s="61"/>
-      <c r="R392" s="62" t="s">
+      <c r="Q392" s="51"/>
+      <c r="R392" s="52" t="s">
         <v>1601</v>
       </c>
-      <c r="S392" s="65"/>
-    </row>
-    <row r="393" s="66" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A393" s="58" t="n">
+      <c r="S392" s="55"/>
+    </row>
+    <row r="393" s="56" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A393" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="B393" s="59" t="s">
+      <c r="B393" s="49" t="s">
         <v>1453</v>
       </c>
-      <c r="C393" s="59" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D393" s="60" t="n">
+      <c r="C393" s="49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D393" s="50" t="n">
         <v>0.0854166666666667</v>
       </c>
-      <c r="E393" s="58" t="s">
+      <c r="E393" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="F393" s="61" t="s">
+      <c r="F393" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="G393" s="62" t="s">
+      <c r="G393" s="52" t="s">
         <v>1602</v>
       </c>
-      <c r="H393" s="62" t="s">
+      <c r="H393" s="52" t="s">
         <v>1603</v>
       </c>
-      <c r="I393" s="61" t="s">
-        <v>22</v>
-      </c>
-      <c r="J393" s="61" t="s">
+      <c r="I393" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="J393" s="51" t="s">
         <v>325</v>
       </c>
-      <c r="K393" s="62" t="s">
+      <c r="K393" s="52" t="s">
         <v>1604</v>
       </c>
-      <c r="L393" s="68" t="s">
+      <c r="L393" s="58" t="s">
         <v>1076</v>
       </c>
-      <c r="M393" s="69" t="s">
+      <c r="M393" s="59" t="s">
         <v>428</v>
       </c>
-      <c r="N393" s="67" t="s">
+      <c r="N393" s="57" t="s">
         <v>429</v>
       </c>
-      <c r="O393" s="67" t="s">
+      <c r="O393" s="57" t="s">
         <v>430</v>
       </c>
-      <c r="P393" s="67" t="s">
+      <c r="P393" s="57" t="s">
         <v>431</v>
       </c>
-      <c r="Q393" s="61"/>
-      <c r="R393" s="62" t="s">
+      <c r="Q393" s="51"/>
+      <c r="R393" s="52" t="s">
         <v>1605</v>
       </c>
-      <c r="S393" s="65"/>
-    </row>
-    <row r="394" s="66" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A394" s="58" t="n">
+      <c r="S393" s="55"/>
+    </row>
+    <row r="394" s="56" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A394" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="B394" s="59" t="s">
+      <c r="B394" s="49" t="s">
         <v>1453</v>
       </c>
-      <c r="C394" s="59" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D394" s="60" t="n">
+      <c r="C394" s="49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D394" s="50" t="n">
         <v>0.930555555555556</v>
       </c>
-      <c r="E394" s="58" t="s">
+      <c r="E394" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="F394" s="61" t="s">
+      <c r="F394" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="G394" s="62" t="s">
+      <c r="G394" s="52" t="s">
         <v>1606</v>
       </c>
-      <c r="H394" s="62" t="s">
+      <c r="H394" s="52" t="s">
         <v>1607</v>
       </c>
-      <c r="I394" s="61" t="s">
+      <c r="I394" s="51" t="s">
         <v>410</v>
       </c>
-      <c r="J394" s="61" t="s">
+      <c r="J394" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="K394" s="62" t="s">
+      <c r="K394" s="52" t="s">
         <v>1608</v>
       </c>
-      <c r="L394" s="70" t="s">
+      <c r="L394" s="60" t="s">
         <v>72</v>
       </c>
-      <c r="M394" s="61" t="s">
+      <c r="M394" s="51" t="s">
         <v>1609</v>
       </c>
-      <c r="N394" s="64" t="s">
+      <c r="N394" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="O394" s="62" t="s">
+      <c r="O394" s="52" t="s">
         <v>1610</v>
       </c>
-      <c r="P394" s="61" t="s">
+      <c r="P394" s="51" t="s">
         <v>1611</v>
       </c>
-      <c r="Q394" s="61"/>
-      <c r="R394" s="61"/>
-      <c r="S394" s="65"/>
-    </row>
-    <row r="395" s="66" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A395" s="58" t="n">
+      <c r="Q394" s="51"/>
+      <c r="R394" s="51"/>
+      <c r="S394" s="55"/>
+    </row>
+    <row r="395" s="56" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A395" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="B395" s="59" t="s">
+      <c r="B395" s="49" t="s">
         <v>1453</v>
       </c>
-      <c r="C395" s="59" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D395" s="60" t="n">
+      <c r="C395" s="49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D395" s="50" t="n">
         <v>0.818055555555556</v>
       </c>
-      <c r="E395" s="58" t="s">
+      <c r="E395" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="F395" s="61" t="s">
+      <c r="F395" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="G395" s="62" t="s">
+      <c r="G395" s="52" t="s">
         <v>1612</v>
       </c>
-      <c r="H395" s="62" t="s">
+      <c r="H395" s="52" t="s">
         <v>1613</v>
       </c>
-      <c r="I395" s="61" t="s">
-        <v>22</v>
-      </c>
-      <c r="J395" s="70" t="s">
+      <c r="I395" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="J395" s="60" t="s">
         <v>163</v>
       </c>
-      <c r="K395" s="62" t="s">
+      <c r="K395" s="52" t="s">
         <v>1614</v>
       </c>
-      <c r="L395" s="62" t="s">
+      <c r="L395" s="52" t="s">
         <v>1615</v>
       </c>
-      <c r="M395" s="61" t="s">
+      <c r="M395" s="51" t="s">
         <v>203</v>
       </c>
-      <c r="N395" s="64" t="s">
+      <c r="N395" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="O395" s="62" t="s">
+      <c r="O395" s="52" t="s">
         <v>1616</v>
       </c>
-      <c r="P395" s="67" t="s">
+      <c r="P395" s="57" t="s">
         <v>205</v>
       </c>
-      <c r="Q395" s="61"/>
-      <c r="R395" s="61"/>
-      <c r="S395" s="65"/>
-    </row>
-    <row r="396" s="66" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A396" s="58" t="n">
+      <c r="Q395" s="51"/>
+      <c r="R395" s="51"/>
+      <c r="S395" s="55"/>
+    </row>
+    <row r="396" s="56" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A396" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="B396" s="59" t="s">
+      <c r="B396" s="49" t="s">
         <v>1453</v>
       </c>
-      <c r="C396" s="59" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D396" s="60" t="n">
+      <c r="C396" s="49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D396" s="50" t="n">
         <v>0.305555555555556</v>
       </c>
-      <c r="E396" s="58" t="s">
+      <c r="E396" s="48" t="s">
         <v>123</v>
       </c>
-      <c r="F396" s="61" t="s">
+      <c r="F396" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="G396" s="62" t="s">
+      <c r="G396" s="52" t="s">
         <v>1617</v>
       </c>
-      <c r="H396" s="62" t="s">
+      <c r="H396" s="52" t="s">
         <v>1618</v>
       </c>
-      <c r="I396" s="61" t="s">
+      <c r="I396" s="51" t="s">
         <v>810</v>
       </c>
-      <c r="J396" s="61" t="s">
+      <c r="J396" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="K396" s="62" t="s">
+      <c r="K396" s="52" t="s">
         <v>1619</v>
       </c>
-      <c r="M396" s="61" t="s">
+      <c r="M396" s="51" t="s">
         <v>1516</v>
       </c>
-      <c r="N396" s="64" t="s">
+      <c r="N396" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="O396" s="62" t="s">
+      <c r="O396" s="52" t="s">
         <v>1620</v>
       </c>
-      <c r="P396" s="64" t="s">
+      <c r="P396" s="54" t="s">
         <v>1518</v>
       </c>
-      <c r="Q396" s="61"/>
-      <c r="R396" s="61"/>
-      <c r="S396" s="65"/>
-    </row>
-    <row r="397" s="66" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A397" s="58" t="n">
+      <c r="Q396" s="51"/>
+      <c r="R396" s="51"/>
+      <c r="S396" s="55"/>
+    </row>
+    <row r="397" s="56" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A397" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="B397" s="59" t="s">
+      <c r="B397" s="49" t="s">
         <v>1453</v>
       </c>
-      <c r="C397" s="59" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D397" s="60" t="n">
+      <c r="C397" s="49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D397" s="50" t="n">
         <v>0.302083333333333</v>
       </c>
-      <c r="E397" s="58" t="s">
+      <c r="E397" s="48" t="s">
         <v>123</v>
       </c>
-      <c r="F397" s="61" t="s">
+      <c r="F397" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="G397" s="62" t="s">
+      <c r="G397" s="52" t="s">
         <v>1621</v>
       </c>
-      <c r="H397" s="62" t="s">
+      <c r="H397" s="52" t="s">
         <v>1622</v>
       </c>
-      <c r="I397" s="61" t="s">
+      <c r="I397" s="51" t="s">
         <v>410</v>
       </c>
-      <c r="J397" s="61" t="s">
+      <c r="J397" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="K397" s="62" t="s">
+      <c r="K397" s="52" t="s">
         <v>1608</v>
       </c>
-      <c r="L397" s="67" t="s">
+      <c r="L397" s="57" t="s">
         <v>187</v>
       </c>
-      <c r="M397" s="61" t="s">
+      <c r="M397" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="N397" s="64" t="s">
+      <c r="N397" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="O397" s="62" t="s">
+      <c r="O397" s="52" t="s">
         <v>1623</v>
       </c>
-      <c r="P397" s="71" t="s">
+      <c r="P397" s="61" t="s">
         <v>1371</v>
       </c>
-      <c r="Q397" s="61"/>
-      <c r="R397" s="61"/>
-      <c r="S397" s="65"/>
-    </row>
-    <row r="398" s="66" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A398" s="58" t="n">
+      <c r="Q397" s="51"/>
+      <c r="R397" s="51"/>
+      <c r="S397" s="55"/>
+    </row>
+    <row r="398" s="56" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A398" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="B398" s="59" t="s">
+      <c r="B398" s="49" t="s">
         <v>1453</v>
       </c>
-      <c r="C398" s="59" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D398" s="60" t="n">
+      <c r="C398" s="49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D398" s="50" t="n">
         <v>0.572916666666667</v>
       </c>
-      <c r="E398" s="58" t="s">
+      <c r="E398" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="F398" s="61" t="s">
+      <c r="F398" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="G398" s="62" t="s">
+      <c r="G398" s="52" t="s">
         <v>1624</v>
       </c>
-      <c r="H398" s="62" t="s">
+      <c r="H398" s="52" t="s">
         <v>1625</v>
       </c>
-      <c r="I398" s="61" t="s">
-        <v>22</v>
-      </c>
-      <c r="J398" s="61" t="s">
+      <c r="I398" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="J398" s="51" t="s">
         <v>1626</v>
       </c>
-      <c r="K398" s="62" t="s">
+      <c r="K398" s="52" t="s">
         <v>1627</v>
       </c>
-      <c r="L398" s="62"/>
-      <c r="M398" s="61" t="s">
+      <c r="L398" s="52"/>
+      <c r="M398" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="N398" s="64" t="s">
+      <c r="N398" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="O398" s="62" t="s">
+      <c r="O398" s="52" t="s">
         <v>1628</v>
       </c>
-      <c r="P398" s="71" t="s">
+      <c r="P398" s="61" t="s">
         <v>1371</v>
       </c>
-      <c r="Q398" s="61"/>
-      <c r="R398" s="61"/>
-      <c r="S398" s="65"/>
-    </row>
-    <row r="399" s="66" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A399" s="58" t="n">
+      <c r="Q398" s="51"/>
+      <c r="R398" s="51"/>
+      <c r="S398" s="55"/>
+    </row>
+    <row r="399" s="56" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A399" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="B399" s="59" t="s">
+      <c r="B399" s="49" t="s">
         <v>1453</v>
       </c>
-      <c r="C399" s="59" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D399" s="60" t="n">
+      <c r="C399" s="49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D399" s="50" t="n">
         <v>0.470833333333333</v>
       </c>
-      <c r="E399" s="58" t="s">
+      <c r="E399" s="48" t="s">
         <v>123</v>
       </c>
-      <c r="F399" s="61" t="s">
+      <c r="F399" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="G399" s="62" t="s">
+      <c r="G399" s="52" t="s">
         <v>1629</v>
       </c>
-      <c r="H399" s="62" t="s">
+      <c r="H399" s="52" t="s">
         <v>1630</v>
       </c>
-      <c r="I399" s="61" t="s">
+      <c r="I399" s="51" t="s">
         <v>810</v>
       </c>
-      <c r="J399" s="61" t="s">
+      <c r="J399" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="K399" s="62" t="s">
+      <c r="K399" s="52" t="s">
         <v>1631</v>
       </c>
-      <c r="L399" s="67" t="s">
+      <c r="L399" s="57" t="s">
         <v>260</v>
       </c>
-      <c r="M399" s="61" t="s">
+      <c r="M399" s="51" t="s">
         <v>1632</v>
       </c>
-      <c r="N399" s="64" t="s">
+      <c r="N399" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="O399" s="62" t="s">
+      <c r="O399" s="52" t="s">
         <v>1633</v>
       </c>
-      <c r="P399" s="64" t="s">
+      <c r="P399" s="54" t="s">
         <v>1634</v>
       </c>
-      <c r="Q399" s="61"/>
-      <c r="R399" s="61"/>
-      <c r="S399" s="65"/>
-    </row>
-    <row r="400" s="66" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A400" s="58" t="n">
+      <c r="Q399" s="51"/>
+      <c r="R399" s="51"/>
+      <c r="S399" s="55"/>
+    </row>
+    <row r="400" s="56" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A400" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="B400" s="59" t="s">
+      <c r="B400" s="49" t="s">
         <v>1453</v>
       </c>
-      <c r="C400" s="59" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D400" s="60" t="n">
+      <c r="C400" s="49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D400" s="50" t="n">
         <v>0.697916666666667</v>
       </c>
-      <c r="E400" s="58" t="s">
+      <c r="E400" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="F400" s="61" t="s">
+      <c r="F400" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="G400" s="62" t="s">
+      <c r="G400" s="52" t="s">
         <v>1635</v>
       </c>
-      <c r="H400" s="62" t="s">
+      <c r="H400" s="52" t="s">
         <v>1636</v>
       </c>
-      <c r="I400" s="61" t="s">
-        <v>22</v>
-      </c>
-      <c r="J400" s="61" t="s">
+      <c r="I400" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="J400" s="51" t="s">
         <v>581</v>
       </c>
-      <c r="K400" s="62" t="s">
+      <c r="K400" s="52" t="s">
         <v>1637</v>
       </c>
-      <c r="L400" s="62"/>
-      <c r="M400" s="61" t="s">
+      <c r="L400" s="52"/>
+      <c r="M400" s="51" t="s">
         <v>188</v>
       </c>
-      <c r="N400" s="64" t="s">
+      <c r="N400" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="O400" s="62" t="s">
+      <c r="O400" s="52" t="s">
         <v>1638</v>
       </c>
-      <c r="P400" s="61" t="s">
+      <c r="P400" s="51" t="s">
         <v>1639</v>
       </c>
-      <c r="Q400" s="61"/>
-      <c r="R400" s="61"/>
-      <c r="S400" s="65"/>
-    </row>
-    <row r="401" s="66" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A401" s="58" t="n">
+      <c r="Q400" s="51"/>
+      <c r="R400" s="51"/>
+      <c r="S400" s="55"/>
+    </row>
+    <row r="401" s="56" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A401" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="B401" s="59" t="s">
+      <c r="B401" s="49" t="s">
         <v>1453</v>
       </c>
-      <c r="C401" s="59" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D401" s="60" t="n">
+      <c r="C401" s="49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D401" s="50" t="n">
         <v>0.208333333333333</v>
       </c>
-      <c r="E401" s="58" t="s">
+      <c r="E401" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="F401" s="61" t="s">
+      <c r="F401" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="G401" s="62" t="s">
+      <c r="G401" s="52" t="s">
         <v>1640</v>
       </c>
-      <c r="H401" s="62" t="s">
+      <c r="H401" s="52" t="s">
         <v>1641</v>
       </c>
-      <c r="I401" s="61" t="s">
-        <v>22</v>
-      </c>
-      <c r="J401" s="70" t="s">
+      <c r="I401" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="J401" s="60" t="s">
         <v>163</v>
       </c>
-      <c r="K401" s="62" t="s">
+      <c r="K401" s="52" t="s">
         <v>1642</v>
       </c>
-      <c r="L401" s="62"/>
-      <c r="M401" s="62" t="s">
+      <c r="L401" s="52"/>
+      <c r="M401" s="52" t="s">
         <v>1643</v>
       </c>
-      <c r="N401" s="64" t="s">
+      <c r="N401" s="54" t="s">
         <v>192</v>
       </c>
-      <c r="O401" s="62" t="s">
+      <c r="O401" s="52" t="s">
         <v>1644</v>
       </c>
-      <c r="P401" s="62" t="s">
+      <c r="P401" s="52" t="s">
         <v>1584</v>
       </c>
-      <c r="Q401" s="61"/>
-      <c r="R401" s="61"/>
-      <c r="S401" s="65"/>
-    </row>
-    <row r="402" s="66" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A402" s="58" t="n">
+      <c r="Q401" s="51"/>
+      <c r="R401" s="51"/>
+      <c r="S401" s="55"/>
+    </row>
+    <row r="402" s="56" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A402" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="B402" s="59" t="s">
+      <c r="B402" s="49" t="s">
         <v>1453</v>
       </c>
-      <c r="C402" s="59" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D402" s="60" t="n">
+      <c r="C402" s="49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D402" s="50" t="n">
         <v>0.958333333333333</v>
       </c>
-      <c r="E402" s="58" t="s">
+      <c r="E402" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="F402" s="61" t="s">
+      <c r="F402" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="G402" s="62" t="s">
+      <c r="G402" s="52" t="s">
         <v>1645</v>
       </c>
-      <c r="H402" s="62" t="s">
+      <c r="H402" s="52" t="s">
         <v>1646</v>
       </c>
-      <c r="I402" s="61" t="s">
-        <v>22</v>
-      </c>
-      <c r="J402" s="70" t="s">
+      <c r="I402" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="J402" s="60" t="s">
         <v>55</v>
       </c>
-      <c r="K402" s="62" t="s">
+      <c r="K402" s="52" t="s">
         <v>1647</v>
       </c>
-      <c r="L402" s="67" t="s">
+      <c r="L402" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="M402" s="67" t="s">
+      <c r="M402" s="57" t="s">
         <v>54</v>
       </c>
-      <c r="N402" s="64" t="s">
+      <c r="N402" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="O402" s="67" t="s">
+      <c r="O402" s="57" t="s">
         <v>155</v>
       </c>
-      <c r="P402" s="67" t="s">
+      <c r="P402" s="57" t="s">
         <v>54</v>
       </c>
-      <c r="Q402" s="62" t="n">
+      <c r="Q402" s="52" t="n">
         <v>350636599723647</v>
       </c>
-      <c r="R402" s="61"/>
-      <c r="S402" s="65"/>
-    </row>
-    <row r="403" s="66" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A403" s="58" t="n">
+      <c r="R402" s="51"/>
+      <c r="S402" s="55"/>
+    </row>
+    <row r="403" s="56" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A403" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="B403" s="59" t="s">
+      <c r="B403" s="49" t="s">
         <v>1453</v>
       </c>
-      <c r="C403" s="59" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D403" s="72" t="n">
+      <c r="C403" s="49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D403" s="62" t="n">
         <v>0.798611111111111</v>
       </c>
-      <c r="E403" s="58" t="s">
+      <c r="E403" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="F403" s="61" t="s">
+      <c r="F403" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="G403" s="73" t="s">
+      <c r="G403" s="63" t="s">
         <v>1648</v>
       </c>
-      <c r="H403" s="62" t="s">
+      <c r="H403" s="52" t="s">
         <v>1649</v>
       </c>
-      <c r="I403" s="61" t="s">
+      <c r="I403" s="51" t="s">
         <v>410</v>
       </c>
-      <c r="J403" s="70" t="s">
+      <c r="J403" s="60" t="s">
         <v>55</v>
       </c>
-      <c r="K403" s="62" t="s">
+      <c r="K403" s="52" t="s">
         <v>1650</v>
       </c>
-      <c r="L403" s="67" t="s">
+      <c r="L403" s="57" t="s">
         <v>72</v>
       </c>
-      <c r="M403" s="67" t="s">
+      <c r="M403" s="57" t="s">
         <v>896</v>
       </c>
-      <c r="N403" s="64" t="s">
+      <c r="N403" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="O403" s="67" t="s">
+      <c r="O403" s="57" t="s">
         <v>896</v>
       </c>
-      <c r="P403" s="67" t="s">
+      <c r="P403" s="57" t="s">
         <v>1651</v>
       </c>
-      <c r="Q403" s="62"/>
-      <c r="R403" s="61"/>
-      <c r="S403" s="65"/>
+      <c r="Q403" s="52"/>
+      <c r="R403" s="51"/>
+      <c r="S403" s="55"/>
     </row>
     <row r="404" s="38" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="37" t="n">
@@ -29061,7 +29206,7 @@
       <c r="M404" s="35" t="s">
         <v>1655</v>
       </c>
-      <c r="N404" s="57" t="s">
+      <c r="N404" s="47" t="s">
         <v>26</v>
       </c>
       <c r="O404" s="35" t="s">
@@ -29163,7 +29308,7 @@
       <c r="M406" s="35" t="s">
         <v>1664</v>
       </c>
-      <c r="N406" s="57" t="s">
+      <c r="N406" s="47" t="s">
         <v>26</v>
       </c>
       <c r="O406" s="35" t="s">
@@ -29217,7 +29362,7 @@
       <c r="M407" s="35" t="s">
         <v>1671</v>
       </c>
-      <c r="N407" s="57" t="s">
+      <c r="N407" s="47" t="s">
         <v>192</v>
       </c>
       <c r="O407" s="35" t="s">
@@ -29268,7 +29413,7 @@
       <c r="M408" s="35" t="s">
         <v>1671</v>
       </c>
-      <c r="N408" s="57" t="s">
+      <c r="N408" s="47" t="s">
         <v>192</v>
       </c>
       <c r="O408" s="35" t="s">
@@ -29317,13 +29462,13 @@
       <c r="M409" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="N409" s="57" t="s">
+      <c r="N409" s="47" t="s">
         <v>52</v>
       </c>
       <c r="O409" s="35" t="s">
         <v>1677</v>
       </c>
-      <c r="P409" s="57" t="s">
+      <c r="P409" s="47" t="s">
         <v>174</v>
       </c>
       <c r="S409" s="2"/>
@@ -29366,7 +29511,7 @@
       <c r="M410" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="N410" s="57" t="s">
+      <c r="N410" s="47" t="s">
         <v>159</v>
       </c>
       <c r="O410" s="35" t="s">
@@ -29415,13 +29560,13 @@
       <c r="M411" s="38" t="s">
         <v>203</v>
       </c>
-      <c r="N411" s="57" t="s">
+      <c r="N411" s="47" t="s">
         <v>52</v>
       </c>
       <c r="O411" s="35" t="s">
         <v>1686</v>
       </c>
-      <c r="P411" s="57" t="s">
+      <c r="P411" s="47" t="s">
         <v>205</v>
       </c>
       <c r="S411" s="2"/>
@@ -29466,7 +29611,7 @@
       <c r="M412" s="35" t="s">
         <v>1690</v>
       </c>
-      <c r="N412" s="57" t="s">
+      <c r="N412" s="47" t="s">
         <v>33</v>
       </c>
       <c r="O412" s="35" t="s">
@@ -29517,13 +29662,13 @@
       <c r="M413" s="35" t="s">
         <v>1516</v>
       </c>
-      <c r="N413" s="57" t="s">
+      <c r="N413" s="47" t="s">
         <v>26</v>
       </c>
       <c r="O413" s="35" t="s">
         <v>1517</v>
       </c>
-      <c r="P413" s="57" t="s">
+      <c r="P413" s="47" t="s">
         <v>1518</v>
       </c>
       <c r="S413" s="2"/>
@@ -29566,10 +29711,10 @@
       <c r="M414" s="32" t="s">
         <v>679</v>
       </c>
-      <c r="N414" s="57" t="s">
+      <c r="N414" s="47" t="s">
         <v>1699</v>
       </c>
-      <c r="O414" s="57" t="s">
+      <c r="O414" s="47" t="s">
         <v>1700</v>
       </c>
       <c r="P414" s="28" t="s">
@@ -29671,7 +29816,7 @@
       <c r="M416" s="32" t="s">
         <v>679</v>
       </c>
-      <c r="N416" s="57" t="s">
+      <c r="N416" s="47" t="s">
         <v>1699</v>
       </c>
       <c r="O416" s="35" t="s">
@@ -29722,7 +29867,7 @@
       <c r="M417" s="35" t="s">
         <v>1711</v>
       </c>
-      <c r="N417" s="57" t="s">
+      <c r="N417" s="47" t="s">
         <v>26</v>
       </c>
       <c r="O417" s="35" t="s">
@@ -29822,7 +29967,7 @@
       <c r="M419" s="32" t="s">
         <v>679</v>
       </c>
-      <c r="N419" s="57" t="s">
+      <c r="N419" s="47" t="s">
         <v>192</v>
       </c>
       <c r="O419" s="38" t="s">
@@ -29884,4259 +30029,4597 @@
       </c>
       <c r="S420" s="2"/>
     </row>
-    <row r="421" s="76" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A421" s="58" t="n">
+    <row r="421" s="67" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A421" s="64" t="n">
         <v>7</v>
       </c>
-      <c r="B421" s="59" t="s">
+      <c r="B421" s="65" t="s">
         <v>1453</v>
       </c>
-      <c r="C421" s="59" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D421" s="74" t="n">
+      <c r="C421" s="65" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D421" s="66" t="n">
         <v>0.0625</v>
       </c>
-      <c r="E421" s="58" t="s">
+      <c r="E421" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="F421" s="66" t="s">
+      <c r="F421" s="67" t="s">
         <v>216</v>
       </c>
-      <c r="G421" s="75" t="s">
+      <c r="G421" s="68" t="s">
         <v>1723</v>
       </c>
-      <c r="H421" s="62" t="s">
+      <c r="H421" s="68" t="s">
         <v>1724</v>
       </c>
-      <c r="I421" s="66" t="s">
-        <v>22</v>
-      </c>
-      <c r="J421" s="66" t="s">
+      <c r="I421" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="J421" s="67" t="s">
         <v>136</v>
       </c>
-      <c r="K421" s="62" t="s">
+      <c r="K421" s="68" t="s">
         <v>1725</v>
       </c>
-      <c r="L421" s="62" t="s">
+      <c r="L421" s="68" t="s">
         <v>144</v>
       </c>
-      <c r="M421" s="75" t="s">
+      <c r="M421" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="N421" s="64" t="s">
+      <c r="N421" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="O421" s="75" t="s">
+      <c r="O421" s="68" t="s">
         <v>1726</v>
       </c>
-      <c r="P421" s="75" t="s">
+      <c r="P421" s="68" t="s">
         <v>1727</v>
       </c>
-      <c r="Q421" s="66"/>
-      <c r="R421" s="75" t="s">
+      <c r="R421" s="68" t="s">
         <v>1728</v>
       </c>
-      <c r="S421" s="66"/>
-      <c r="T421" s="66"/>
-      <c r="U421" s="66"/>
-      <c r="V421" s="66"/>
-    </row>
-    <row r="422" s="76" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A422" s="58" t="n">
+    </row>
+    <row r="422" s="67" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A422" s="64" t="n">
         <v>7</v>
       </c>
-      <c r="B422" s="59" t="s">
+      <c r="B422" s="65" t="s">
         <v>1453</v>
       </c>
-      <c r="C422" s="59" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D422" s="74" t="n">
+      <c r="C422" s="65" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D422" s="66" t="n">
         <v>0.125</v>
       </c>
-      <c r="E422" s="58" t="s">
+      <c r="E422" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="F422" s="66" t="s">
+      <c r="F422" s="67" t="s">
         <v>216</v>
       </c>
-      <c r="G422" s="75" t="s">
+      <c r="G422" s="68" t="s">
         <v>1729</v>
       </c>
-      <c r="H422" s="62" t="s">
+      <c r="H422" s="68" t="s">
         <v>1730</v>
       </c>
-      <c r="I422" s="66" t="s">
-        <v>22</v>
-      </c>
-      <c r="J422" s="66" t="s">
+      <c r="I422" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="J422" s="67" t="s">
         <v>325</v>
       </c>
-      <c r="K422" s="62" t="s">
+      <c r="K422" s="68" t="s">
         <v>1731</v>
       </c>
-      <c r="L422" s="75" t="s">
+      <c r="L422" s="68" t="s">
         <v>1732</v>
       </c>
-      <c r="M422" s="66" t="s">
+      <c r="M422" s="67" t="s">
         <v>203</v>
       </c>
-      <c r="N422" s="64" t="s">
+      <c r="N422" s="69" t="s">
         <v>52</v>
       </c>
-      <c r="O422" s="62" t="s">
+      <c r="O422" s="68" t="s">
         <v>1733</v>
       </c>
-      <c r="P422" s="64" t="s">
+      <c r="P422" s="69" t="s">
         <v>205</v>
       </c>
-      <c r="Q422" s="66"/>
-      <c r="R422" s="75" t="s">
+      <c r="R422" s="68" t="s">
         <v>1734</v>
       </c>
-      <c r="S422" s="66"/>
-      <c r="T422" s="66"/>
-      <c r="U422" s="66"/>
-      <c r="V422" s="66"/>
-    </row>
-    <row r="423" s="76" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A423" s="58" t="n">
+    </row>
+    <row r="423" s="67" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A423" s="64" t="n">
         <v>7</v>
       </c>
-      <c r="B423" s="59" t="s">
+      <c r="B423" s="65" t="s">
         <v>1453</v>
       </c>
-      <c r="C423" s="59" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D423" s="74" t="n">
+      <c r="C423" s="65" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D423" s="66" t="n">
         <v>0.729166666666667</v>
       </c>
-      <c r="E423" s="58" t="s">
+      <c r="E423" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="F423" s="66" t="s">
+      <c r="F423" s="67" t="s">
         <v>216</v>
       </c>
-      <c r="G423" s="75" t="s">
+      <c r="G423" s="68" t="s">
         <v>1735</v>
       </c>
-      <c r="H423" s="62" t="s">
+      <c r="H423" s="68" t="s">
         <v>1736</v>
       </c>
-      <c r="I423" s="66" t="s">
-        <v>22</v>
-      </c>
-      <c r="J423" s="66" t="s">
+      <c r="I423" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="J423" s="67" t="s">
         <v>37</v>
       </c>
-      <c r="K423" s="62" t="s">
+      <c r="K423" s="68" t="s">
         <v>1737</v>
       </c>
-      <c r="L423" s="75" t="s">
+      <c r="L423" s="68" t="s">
         <v>1738</v>
       </c>
-      <c r="M423" s="75" t="s">
+      <c r="M423" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="N423" s="64" t="s">
+      <c r="N423" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="O423" s="75" t="s">
+      <c r="O423" s="68" t="s">
         <v>1739</v>
       </c>
-      <c r="P423" s="75" t="s">
+      <c r="P423" s="68" t="s">
         <v>1740</v>
       </c>
-      <c r="Q423" s="66"/>
-      <c r="R423" s="66"/>
-      <c r="S423" s="66"/>
-      <c r="T423" s="66"/>
-      <c r="U423" s="66"/>
-      <c r="V423" s="66"/>
-    </row>
-    <row r="424" s="76" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A424" s="58" t="n">
+    </row>
+    <row r="424" s="67" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A424" s="64" t="n">
         <v>7</v>
       </c>
-      <c r="B424" s="59" t="s">
+      <c r="B424" s="65" t="s">
         <v>1453</v>
       </c>
-      <c r="C424" s="59" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D424" s="74" t="n">
+      <c r="C424" s="65" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D424" s="66" t="n">
         <v>0.604166666666667</v>
       </c>
-      <c r="E424" s="58" t="s">
+      <c r="E424" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="F424" s="66" t="s">
+      <c r="F424" s="67" t="s">
         <v>216</v>
       </c>
-      <c r="G424" s="75" t="s">
+      <c r="G424" s="68" t="s">
         <v>1741</v>
       </c>
-      <c r="H424" s="62" t="s">
+      <c r="H424" s="68" t="s">
         <v>1742</v>
       </c>
-      <c r="I424" s="66" t="s">
-        <v>22</v>
-      </c>
-      <c r="J424" s="66" t="s">
+      <c r="I424" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="J424" s="67" t="s">
         <v>723</v>
       </c>
-      <c r="K424" s="62" t="s">
+      <c r="K424" s="68" t="s">
         <v>1743</v>
       </c>
-      <c r="L424" s="62"/>
-      <c r="M424" s="75" t="s">
+      <c r="L424" s="68"/>
+      <c r="M424" s="68" t="s">
         <v>1744</v>
       </c>
-      <c r="N424" s="64" t="s">
+      <c r="N424" s="69" t="s">
         <v>120</v>
       </c>
-      <c r="O424" s="75" t="s">
+      <c r="O424" s="68" t="s">
         <v>1744</v>
       </c>
-      <c r="P424" s="75" t="s">
+      <c r="P424" s="68" t="s">
         <v>1745</v>
       </c>
-      <c r="Q424" s="66"/>
-      <c r="R424" s="66"/>
-      <c r="S424" s="66"/>
-      <c r="T424" s="66"/>
-      <c r="U424" s="66"/>
-      <c r="V424" s="66"/>
-    </row>
-    <row r="425" s="76" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A425" s="58" t="n">
+    </row>
+    <row r="425" s="67" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A425" s="64" t="n">
         <v>7</v>
       </c>
-      <c r="B425" s="59" t="s">
+      <c r="B425" s="65" t="s">
         <v>1453</v>
       </c>
-      <c r="C425" s="59" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D425" s="74" t="n">
+      <c r="C425" s="65" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D425" s="66" t="n">
         <v>0.347222222222222</v>
       </c>
-      <c r="E425" s="58" t="s">
+      <c r="E425" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="F425" s="66" t="s">
+      <c r="F425" s="67" t="s">
         <v>216</v>
       </c>
-      <c r="G425" s="75" t="s">
+      <c r="G425" s="68" t="s">
         <v>1746</v>
       </c>
-      <c r="H425" s="62" t="s">
+      <c r="H425" s="68" t="s">
         <v>1747</v>
       </c>
-      <c r="I425" s="66" t="s">
-        <v>22</v>
-      </c>
-      <c r="J425" s="66" t="s">
+      <c r="I425" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="J425" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="K425" s="62" t="s">
+      <c r="K425" s="68" t="s">
         <v>1748</v>
       </c>
-      <c r="L425" s="62" t="s">
+      <c r="L425" s="68" t="s">
         <v>267</v>
       </c>
-      <c r="M425" s="66" t="s">
+      <c r="M425" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="N425" s="64" t="s">
+      <c r="N425" s="69" t="s">
         <v>128</v>
       </c>
-      <c r="O425" s="75" t="s">
+      <c r="O425" s="68" t="s">
         <v>1749</v>
       </c>
-      <c r="P425" s="71" t="s">
+      <c r="P425" s="70" t="s">
         <v>1371</v>
       </c>
-      <c r="Q425" s="66"/>
-      <c r="R425" s="66"/>
-      <c r="S425" s="66"/>
-      <c r="T425" s="66"/>
-      <c r="U425" s="66"/>
-      <c r="V425" s="66"/>
-    </row>
-    <row r="426" s="76" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A426" s="58" t="n">
+    </row>
+    <row r="426" s="67" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A426" s="64" t="n">
         <v>7</v>
       </c>
-      <c r="B426" s="59" t="s">
+      <c r="B426" s="65" t="s">
         <v>1453</v>
       </c>
-      <c r="C426" s="59" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D426" s="74" t="n">
+      <c r="C426" s="65" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D426" s="66" t="n">
         <v>0.263888888888889</v>
       </c>
-      <c r="E426" s="58" t="s">
+      <c r="E426" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="F426" s="66" t="s">
+      <c r="F426" s="67" t="s">
         <v>216</v>
       </c>
-      <c r="G426" s="75" t="s">
+      <c r="G426" s="68" t="s">
         <v>1750</v>
       </c>
-      <c r="H426" s="62" t="s">
+      <c r="H426" s="68" t="s">
         <v>1751</v>
       </c>
-      <c r="I426" s="66" t="s">
+      <c r="I426" s="67" t="s">
         <v>303</v>
       </c>
-      <c r="J426" s="66" t="s">
+      <c r="J426" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="K426" s="62" t="s">
+      <c r="K426" s="68" t="s">
         <v>1752</v>
       </c>
-      <c r="L426" s="62"/>
-      <c r="M426" s="66" t="s">
+      <c r="L426" s="68"/>
+      <c r="M426" s="67" t="s">
         <v>1132</v>
       </c>
-      <c r="N426" s="64" t="s">
+      <c r="N426" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="O426" s="75" t="s">
+      <c r="O426" s="68" t="s">
         <v>1753</v>
       </c>
-      <c r="P426" s="66" t="s">
+      <c r="P426" s="67" t="s">
         <v>1754</v>
       </c>
-      <c r="Q426" s="66"/>
-      <c r="R426" s="66"/>
-      <c r="S426" s="66"/>
-      <c r="T426" s="66"/>
-      <c r="U426" s="66"/>
-      <c r="V426" s="66"/>
-    </row>
-    <row r="427" s="76" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A427" s="58" t="n">
+    </row>
+    <row r="427" s="67" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A427" s="64" t="n">
         <v>7</v>
       </c>
-      <c r="B427" s="59" t="s">
+      <c r="B427" s="65" t="s">
         <v>1453</v>
       </c>
-      <c r="C427" s="59" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D427" s="74" t="n">
+      <c r="C427" s="65" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D427" s="66" t="n">
         <v>0.125</v>
       </c>
-      <c r="E427" s="58" t="s">
+      <c r="E427" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="F427" s="66" t="s">
+      <c r="F427" s="67" t="s">
         <v>216</v>
       </c>
-      <c r="G427" s="75" t="s">
+      <c r="G427" s="68" t="s">
         <v>1755</v>
       </c>
-      <c r="H427" s="62" t="s">
+      <c r="H427" s="68" t="s">
         <v>1756</v>
       </c>
-      <c r="I427" s="66" t="s">
-        <v>22</v>
-      </c>
-      <c r="J427" s="66" t="s">
+      <c r="I427" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="J427" s="67" t="s">
         <v>913</v>
       </c>
-      <c r="K427" s="62" t="s">
+      <c r="K427" s="68" t="s">
         <v>1757</v>
       </c>
-      <c r="L427" s="62"/>
-      <c r="M427" s="66" t="s">
+      <c r="L427" s="68"/>
+      <c r="M427" s="67" t="s">
         <v>746</v>
       </c>
-      <c r="N427" s="64" t="s">
+      <c r="N427" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="O427" s="62" t="s">
+      <c r="O427" s="68" t="s">
         <v>1758</v>
       </c>
-      <c r="P427" s="64" t="s">
+      <c r="P427" s="69" t="s">
         <v>748</v>
       </c>
-      <c r="Q427" s="66"/>
-      <c r="R427" s="66"/>
-      <c r="S427" s="66"/>
-      <c r="T427" s="66"/>
-      <c r="U427" s="66"/>
-      <c r="V427" s="66"/>
-    </row>
-    <row r="428" s="76" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A428" s="58" t="n">
+    </row>
+    <row r="428" s="67" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A428" s="64" t="n">
         <v>7</v>
       </c>
-      <c r="B428" s="59" t="s">
+      <c r="B428" s="65" t="s">
         <v>1453</v>
       </c>
-      <c r="C428" s="59" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D428" s="74" t="n">
+      <c r="C428" s="65" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D428" s="66" t="n">
         <v>0.0416666666666667</v>
       </c>
-      <c r="E428" s="58" t="s">
+      <c r="E428" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="F428" s="66" t="s">
+      <c r="F428" s="67" t="s">
         <v>216</v>
       </c>
-      <c r="G428" s="75" t="s">
+      <c r="G428" s="68" t="s">
         <v>1759</v>
       </c>
-      <c r="H428" s="62" t="s">
+      <c r="H428" s="68" t="s">
         <v>1760</v>
       </c>
-      <c r="I428" s="66" t="s">
+      <c r="I428" s="67" t="s">
         <v>810</v>
       </c>
-      <c r="J428" s="66" t="s">
+      <c r="J428" s="67" t="s">
         <v>113</v>
       </c>
-      <c r="K428" s="62" t="s">
+      <c r="K428" s="68" t="s">
         <v>1761</v>
       </c>
-      <c r="L428" s="62"/>
-      <c r="M428" s="68" t="s">
+      <c r="L428" s="68"/>
+      <c r="M428" s="71" t="s">
         <v>679</v>
       </c>
-      <c r="N428" s="64" t="s">
+      <c r="N428" s="69" t="s">
         <v>192</v>
       </c>
-      <c r="O428" s="61" t="s">
+      <c r="O428" s="67" t="s">
         <v>679</v>
       </c>
-      <c r="P428" s="77" t="s">
+      <c r="P428" s="72" t="s">
         <v>682</v>
       </c>
-      <c r="Q428" s="66"/>
-      <c r="R428" s="66"/>
-      <c r="S428" s="66"/>
-      <c r="T428" s="66"/>
-      <c r="U428" s="66"/>
-      <c r="V428" s="66"/>
-    </row>
-    <row r="429" s="76" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A429" s="58" t="n">
+    </row>
+    <row r="429" s="67" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A429" s="64" t="n">
         <v>7</v>
       </c>
-      <c r="B429" s="59" t="s">
+      <c r="B429" s="65" t="s">
         <v>1453</v>
       </c>
-      <c r="C429" s="59" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D429" s="74" t="n">
+      <c r="C429" s="65" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D429" s="66" t="n">
         <v>0</v>
       </c>
-      <c r="E429" s="58" t="s">
+      <c r="E429" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="F429" s="66" t="s">
+      <c r="F429" s="67" t="s">
         <v>216</v>
       </c>
-      <c r="G429" s="75" t="s">
+      <c r="G429" s="68" t="s">
         <v>1762</v>
       </c>
-      <c r="H429" s="62" t="s">
+      <c r="H429" s="68" t="s">
         <v>1763</v>
       </c>
-      <c r="I429" s="66" t="s">
-        <v>22</v>
-      </c>
-      <c r="J429" s="66" t="s">
+      <c r="I429" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="J429" s="67" t="s">
         <v>113</v>
       </c>
-      <c r="K429" s="62" t="s">
+      <c r="K429" s="68" t="s">
         <v>1764</v>
       </c>
-      <c r="L429" s="62"/>
-      <c r="M429" s="75" t="s">
+      <c r="L429" s="68"/>
+      <c r="M429" s="68" t="s">
         <v>1765</v>
       </c>
-      <c r="N429" s="64" t="s">
+      <c r="N429" s="69" t="s">
         <v>52</v>
       </c>
-      <c r="O429" s="62" t="s">
+      <c r="O429" s="68" t="s">
         <v>198</v>
       </c>
-      <c r="P429" s="75" t="s">
+      <c r="P429" s="68" t="s">
         <v>1766</v>
       </c>
-      <c r="Q429" s="66"/>
-      <c r="R429" s="66"/>
-      <c r="S429" s="66"/>
-      <c r="T429" s="66"/>
-      <c r="U429" s="66"/>
-      <c r="V429" s="66"/>
-    </row>
-    <row r="430" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A430" s="78"/>
-      <c r="E430" s="78"/>
-      <c r="N430" s="79"/>
-      <c r="P430" s="79"/>
-    </row>
-    <row r="431" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A431" s="78"/>
-      <c r="E431" s="78"/>
-      <c r="N431" s="79"/>
-      <c r="P431" s="79"/>
-    </row>
-    <row r="432" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A432" s="78"/>
-      <c r="E432" s="78"/>
-      <c r="N432" s="79"/>
-      <c r="P432" s="79"/>
-    </row>
-    <row r="433" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A433" s="78"/>
-      <c r="E433" s="78"/>
-      <c r="N433" s="79"/>
-      <c r="P433" s="79"/>
-    </row>
-    <row r="434" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A434" s="78"/>
-      <c r="E434" s="78"/>
-      <c r="N434" s="79"/>
-      <c r="P434" s="79"/>
-    </row>
-    <row r="435" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A435" s="78"/>
-      <c r="E435" s="78"/>
-      <c r="N435" s="79"/>
-      <c r="P435" s="79"/>
-    </row>
-    <row r="436" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A436" s="78"/>
-      <c r="E436" s="78"/>
-      <c r="N436" s="79"/>
-      <c r="P436" s="79"/>
-    </row>
-    <row r="437" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A437" s="78"/>
-      <c r="E437" s="78"/>
-      <c r="N437" s="79"/>
-      <c r="P437" s="79"/>
+    </row>
+    <row r="430" s="75" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A430" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="B430" s="49" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C430" s="49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D430" s="73" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E430" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="F430" s="51" t="s">
+        <v>250</v>
+      </c>
+      <c r="G430" s="74" t="s">
+        <v>1767</v>
+      </c>
+      <c r="H430" s="52" t="s">
+        <v>1768</v>
+      </c>
+      <c r="I430" s="51" t="s">
+        <v>303</v>
+      </c>
+      <c r="J430" s="51" t="s">
+        <v>125</v>
+      </c>
+      <c r="K430" s="52" t="s">
+        <v>1769</v>
+      </c>
+      <c r="L430" s="52"/>
+      <c r="M430" s="74" t="s">
+        <v>1770</v>
+      </c>
+      <c r="N430" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="O430" s="74" t="s">
+        <v>1770</v>
+      </c>
+      <c r="P430" s="74" t="s">
+        <v>1771</v>
+      </c>
+      <c r="Q430" s="51"/>
+      <c r="R430" s="51"/>
+      <c r="S430" s="51"/>
+      <c r="T430" s="51"/>
+      <c r="U430" s="51"/>
+      <c r="V430" s="51"/>
+    </row>
+    <row r="431" s="75" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A431" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="B431" s="49" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C431" s="49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D431" s="73" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="E431" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="F431" s="51" t="s">
+        <v>250</v>
+      </c>
+      <c r="G431" s="74" t="s">
+        <v>1772</v>
+      </c>
+      <c r="H431" s="52" t="s">
+        <v>1773</v>
+      </c>
+      <c r="I431" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="J431" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="K431" s="52" t="s">
+        <v>1774</v>
+      </c>
+      <c r="L431" s="52" t="s">
+        <v>1092</v>
+      </c>
+      <c r="M431" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="N431" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="O431" s="52" t="s">
+        <v>1775</v>
+      </c>
+      <c r="P431" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q431" s="51"/>
+      <c r="R431" s="51"/>
+      <c r="S431" s="51"/>
+      <c r="T431" s="51"/>
+      <c r="U431" s="51"/>
+      <c r="V431" s="51"/>
+    </row>
+    <row r="432" s="75" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A432" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="B432" s="49" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C432" s="49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D432" s="73" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="E432" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="F432" s="51" t="s">
+        <v>250</v>
+      </c>
+      <c r="G432" s="74" t="s">
+        <v>1772</v>
+      </c>
+      <c r="H432" s="52" t="s">
+        <v>1773</v>
+      </c>
+      <c r="I432" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="J432" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="K432" s="52" t="s">
+        <v>1774</v>
+      </c>
+      <c r="L432" s="52" t="s">
+        <v>218</v>
+      </c>
+      <c r="M432" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="N432" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="O432" s="52" t="s">
+        <v>1775</v>
+      </c>
+      <c r="P432" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q432" s="51"/>
+      <c r="R432" s="51"/>
+      <c r="S432" s="51"/>
+      <c r="T432" s="51"/>
+      <c r="U432" s="51"/>
+      <c r="V432" s="51"/>
+    </row>
+    <row r="433" s="75" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A433" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="B433" s="49" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C433" s="49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D433" s="73" t="n">
+        <v>0.345833333333333</v>
+      </c>
+      <c r="E433" s="48" t="s">
+        <v>123</v>
+      </c>
+      <c r="F433" s="51" t="s">
+        <v>250</v>
+      </c>
+      <c r="G433" s="74" t="s">
+        <v>1776</v>
+      </c>
+      <c r="H433" s="52" t="s">
+        <v>1777</v>
+      </c>
+      <c r="I433" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="J433" s="51" t="s">
+        <v>125</v>
+      </c>
+      <c r="K433" s="52" t="s">
+        <v>1778</v>
+      </c>
+      <c r="L433" s="52"/>
+      <c r="M433" s="74" t="s">
+        <v>462</v>
+      </c>
+      <c r="N433" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="O433" s="74" t="s">
+        <v>462</v>
+      </c>
+      <c r="P433" s="74" t="s">
+        <v>1779</v>
+      </c>
+      <c r="Q433" s="51"/>
+      <c r="R433" s="51"/>
+      <c r="S433" s="51"/>
+      <c r="T433" s="51"/>
+      <c r="U433" s="51"/>
+      <c r="V433" s="51"/>
+    </row>
+    <row r="434" s="75" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A434" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="B434" s="49" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C434" s="49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D434" s="73" t="n">
+        <v>0.345833333333333</v>
+      </c>
+      <c r="E434" s="48" t="s">
+        <v>123</v>
+      </c>
+      <c r="F434" s="51" t="s">
+        <v>250</v>
+      </c>
+      <c r="G434" s="74" t="s">
+        <v>1776</v>
+      </c>
+      <c r="H434" s="52" t="s">
+        <v>1777</v>
+      </c>
+      <c r="I434" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="J434" s="51" t="s">
+        <v>125</v>
+      </c>
+      <c r="K434" s="52" t="s">
+        <v>1778</v>
+      </c>
+      <c r="L434" s="52"/>
+      <c r="M434" s="74" t="s">
+        <v>462</v>
+      </c>
+      <c r="N434" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="O434" s="74" t="s">
+        <v>462</v>
+      </c>
+      <c r="P434" s="74" t="s">
+        <v>1779</v>
+      </c>
+      <c r="Q434" s="51"/>
+      <c r="R434" s="51"/>
+      <c r="S434" s="51"/>
+      <c r="T434" s="51"/>
+      <c r="U434" s="51"/>
+      <c r="V434" s="51"/>
+    </row>
+    <row r="435" s="75" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A435" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="B435" s="49" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C435" s="49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D435" s="73" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E435" s="48" t="s">
+        <v>123</v>
+      </c>
+      <c r="F435" s="51" t="s">
+        <v>250</v>
+      </c>
+      <c r="G435" s="74" t="s">
+        <v>1780</v>
+      </c>
+      <c r="H435" s="52" t="s">
+        <v>1781</v>
+      </c>
+      <c r="I435" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="J435" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="K435" s="52" t="s">
+        <v>1782</v>
+      </c>
+      <c r="L435" s="52"/>
+      <c r="M435" s="74" t="s">
+        <v>1783</v>
+      </c>
+      <c r="N435" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="O435" s="74" t="s">
+        <v>1783</v>
+      </c>
+      <c r="P435" s="74" t="s">
+        <v>1784</v>
+      </c>
+      <c r="Q435" s="51"/>
+      <c r="R435" s="51"/>
+      <c r="S435" s="51"/>
+      <c r="T435" s="51"/>
+      <c r="U435" s="51"/>
+      <c r="V435" s="51"/>
+    </row>
+    <row r="436" s="75" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A436" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="B436" s="49" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C436" s="49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D436" s="73" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="E436" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="F436" s="51" t="s">
+        <v>250</v>
+      </c>
+      <c r="G436" s="74" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H436" s="52" t="s">
+        <v>1786</v>
+      </c>
+      <c r="I436" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="J436" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="K436" s="52" t="s">
+        <v>1787</v>
+      </c>
+      <c r="L436" s="52"/>
+      <c r="M436" s="51" t="s">
+        <v>746</v>
+      </c>
+      <c r="N436" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="O436" s="51" t="s">
+        <v>746</v>
+      </c>
+      <c r="P436" s="54" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q436" s="51"/>
+      <c r="R436" s="51"/>
+      <c r="S436" s="51"/>
+      <c r="T436" s="51"/>
+      <c r="U436" s="51"/>
+      <c r="V436" s="51"/>
+    </row>
+    <row r="437" s="75" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A437" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="B437" s="49" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C437" s="49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D437" s="73" t="n">
+        <v>0.111111111111111</v>
+      </c>
+      <c r="E437" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="F437" s="51" t="s">
+        <v>250</v>
+      </c>
+      <c r="G437" s="74" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H437" s="52" t="s">
+        <v>1789</v>
+      </c>
+      <c r="I437" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="J437" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="K437" s="52" t="s">
+        <v>1790</v>
+      </c>
+      <c r="L437" s="52" t="s">
+        <v>247</v>
+      </c>
+      <c r="M437" s="74" t="s">
+        <v>305</v>
+      </c>
+      <c r="N437" s="54" t="s">
+        <v>223</v>
+      </c>
+      <c r="O437" s="74" t="s">
+        <v>305</v>
+      </c>
+      <c r="P437" s="74" t="s">
+        <v>1791</v>
+      </c>
+      <c r="Q437" s="51"/>
+      <c r="R437" s="51"/>
+      <c r="S437" s="51"/>
+      <c r="T437" s="51"/>
+      <c r="U437" s="51"/>
+      <c r="V437" s="51"/>
     </row>
     <row r="438" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A438" s="78"/>
-      <c r="E438" s="78"/>
-      <c r="N438" s="79"/>
-      <c r="P438" s="79"/>
+      <c r="A438" s="76"/>
+      <c r="E438" s="76"/>
+      <c r="N438" s="77"/>
+      <c r="P438" s="77"/>
     </row>
     <row r="439" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A439" s="78"/>
-      <c r="E439" s="78"/>
-      <c r="N439" s="79"/>
-      <c r="P439" s="79"/>
+      <c r="A439" s="76"/>
+      <c r="E439" s="76"/>
+      <c r="N439" s="77"/>
+      <c r="P439" s="77"/>
     </row>
     <row r="440" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A440" s="78"/>
-      <c r="E440" s="78"/>
-      <c r="N440" s="79"/>
-      <c r="P440" s="79"/>
+      <c r="A440" s="76"/>
+      <c r="E440" s="76"/>
+      <c r="N440" s="77"/>
+      <c r="P440" s="77"/>
     </row>
     <row r="441" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A441" s="78"/>
-      <c r="E441" s="78"/>
-      <c r="N441" s="79"/>
-      <c r="P441" s="79"/>
+      <c r="A441" s="76"/>
+      <c r="E441" s="76"/>
+      <c r="N441" s="77"/>
+      <c r="P441" s="77"/>
     </row>
     <row r="442" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A442" s="78"/>
-      <c r="E442" s="78"/>
-      <c r="N442" s="79"/>
-      <c r="P442" s="79"/>
+      <c r="A442" s="76"/>
+      <c r="E442" s="76"/>
+      <c r="N442" s="77"/>
+      <c r="P442" s="77"/>
     </row>
     <row r="443" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A443" s="78"/>
-      <c r="E443" s="78"/>
-      <c r="N443" s="79"/>
-      <c r="P443" s="79"/>
+      <c r="A443" s="76"/>
+      <c r="E443" s="76"/>
+      <c r="N443" s="77"/>
+      <c r="P443" s="77"/>
     </row>
     <row r="444" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A444" s="78"/>
-      <c r="E444" s="78"/>
-      <c r="N444" s="79"/>
-      <c r="P444" s="79"/>
+      <c r="A444" s="76"/>
+      <c r="E444" s="76"/>
+      <c r="N444" s="77"/>
+      <c r="P444" s="77"/>
     </row>
     <row r="445" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A445" s="78"/>
-      <c r="E445" s="78"/>
-      <c r="N445" s="79"/>
-      <c r="P445" s="79"/>
+      <c r="A445" s="76"/>
+      <c r="E445" s="76"/>
+      <c r="N445" s="77"/>
+      <c r="P445" s="77"/>
     </row>
     <row r="446" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A446" s="78"/>
-      <c r="E446" s="78"/>
-      <c r="N446" s="79"/>
-      <c r="P446" s="79"/>
+      <c r="A446" s="76"/>
+      <c r="E446" s="76"/>
+      <c r="N446" s="77"/>
+      <c r="P446" s="77"/>
     </row>
     <row r="447" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A447" s="78"/>
-      <c r="E447" s="78"/>
-      <c r="N447" s="79"/>
-      <c r="P447" s="79"/>
+      <c r="A447" s="76"/>
+      <c r="E447" s="76"/>
+      <c r="N447" s="77"/>
+      <c r="P447" s="77"/>
     </row>
     <row r="448" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A448" s="78"/>
-      <c r="E448" s="78"/>
-      <c r="N448" s="79"/>
-      <c r="P448" s="79"/>
+      <c r="A448" s="76"/>
+      <c r="E448" s="76"/>
+      <c r="N448" s="77"/>
+      <c r="P448" s="77"/>
     </row>
     <row r="449" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A449" s="78"/>
-      <c r="E449" s="78"/>
-      <c r="N449" s="79"/>
-      <c r="P449" s="79"/>
+      <c r="A449" s="76"/>
+      <c r="E449" s="76"/>
+      <c r="N449" s="77"/>
+      <c r="P449" s="77"/>
     </row>
     <row r="450" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A450" s="78"/>
-      <c r="E450" s="78"/>
-      <c r="N450" s="79"/>
-      <c r="P450" s="79"/>
+      <c r="A450" s="76"/>
+      <c r="E450" s="76"/>
+      <c r="N450" s="77"/>
+      <c r="P450" s="77"/>
     </row>
     <row r="451" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A451" s="78"/>
-      <c r="E451" s="78"/>
-      <c r="N451" s="79"/>
-      <c r="P451" s="79"/>
+      <c r="A451" s="76"/>
+      <c r="E451" s="76"/>
+      <c r="N451" s="77"/>
+      <c r="P451" s="77"/>
     </row>
     <row r="452" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A452" s="78"/>
-      <c r="E452" s="78"/>
-      <c r="N452" s="79"/>
-      <c r="P452" s="79"/>
+      <c r="A452" s="76"/>
+      <c r="E452" s="76"/>
+      <c r="N452" s="77"/>
+      <c r="P452" s="77"/>
     </row>
     <row r="453" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A453" s="78"/>
-      <c r="E453" s="78"/>
-      <c r="N453" s="79"/>
-      <c r="P453" s="79"/>
+      <c r="A453" s="76"/>
+      <c r="E453" s="76"/>
+      <c r="N453" s="77"/>
+      <c r="P453" s="77"/>
     </row>
     <row r="454" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A454" s="78"/>
-      <c r="E454" s="78"/>
-      <c r="N454" s="79"/>
-      <c r="P454" s="79"/>
+      <c r="A454" s="76"/>
+      <c r="E454" s="76"/>
+      <c r="N454" s="77"/>
+      <c r="P454" s="77"/>
     </row>
     <row r="455" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A455" s="78"/>
-      <c r="E455" s="78"/>
-      <c r="N455" s="79"/>
-      <c r="P455" s="79"/>
+      <c r="A455" s="76"/>
+      <c r="E455" s="76"/>
+      <c r="N455" s="77"/>
+      <c r="P455" s="77"/>
     </row>
     <row r="456" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A456" s="78"/>
-      <c r="E456" s="78"/>
-      <c r="N456" s="79"/>
-      <c r="P456" s="79"/>
+      <c r="A456" s="76"/>
+      <c r="E456" s="76"/>
+      <c r="N456" s="77"/>
+      <c r="P456" s="77"/>
     </row>
     <row r="457" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A457" s="78"/>
-      <c r="E457" s="78"/>
-      <c r="N457" s="79"/>
-      <c r="P457" s="79"/>
+      <c r="A457" s="76"/>
+      <c r="E457" s="76"/>
+      <c r="N457" s="77"/>
+      <c r="P457" s="77"/>
     </row>
     <row r="458" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A458" s="78"/>
-      <c r="E458" s="78"/>
-      <c r="N458" s="79"/>
-      <c r="P458" s="79"/>
+      <c r="A458" s="76"/>
+      <c r="E458" s="76"/>
+      <c r="N458" s="77"/>
+      <c r="P458" s="77"/>
     </row>
     <row r="459" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A459" s="78"/>
-      <c r="E459" s="78"/>
-      <c r="N459" s="79"/>
-      <c r="P459" s="79"/>
+      <c r="A459" s="76"/>
+      <c r="E459" s="76"/>
+      <c r="N459" s="77"/>
+      <c r="P459" s="77"/>
     </row>
     <row r="460" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A460" s="78"/>
-      <c r="E460" s="78"/>
-      <c r="N460" s="79"/>
-      <c r="P460" s="79"/>
+      <c r="A460" s="76"/>
+      <c r="E460" s="76"/>
+      <c r="N460" s="77"/>
+      <c r="P460" s="77"/>
     </row>
     <row r="461" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A461" s="78"/>
-      <c r="E461" s="78"/>
-      <c r="N461" s="79"/>
-      <c r="P461" s="79"/>
+      <c r="A461" s="76"/>
+      <c r="E461" s="76"/>
+      <c r="N461" s="77"/>
+      <c r="P461" s="77"/>
     </row>
     <row r="462" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A462" s="78"/>
-      <c r="E462" s="78"/>
-      <c r="N462" s="79"/>
-      <c r="P462" s="79"/>
+      <c r="A462" s="76"/>
+      <c r="E462" s="76"/>
+      <c r="N462" s="77"/>
+      <c r="P462" s="77"/>
     </row>
     <row r="463" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A463" s="78"/>
-      <c r="E463" s="78"/>
-      <c r="N463" s="79"/>
-      <c r="P463" s="79"/>
+      <c r="A463" s="76"/>
+      <c r="E463" s="76"/>
+      <c r="N463" s="77"/>
+      <c r="P463" s="77"/>
     </row>
     <row r="464" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A464" s="78"/>
-      <c r="E464" s="78"/>
-      <c r="N464" s="79"/>
-      <c r="P464" s="79"/>
+      <c r="A464" s="76"/>
+      <c r="E464" s="76"/>
+      <c r="N464" s="77"/>
+      <c r="P464" s="77"/>
     </row>
     <row r="465" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A465" s="78"/>
-      <c r="E465" s="78"/>
-      <c r="N465" s="79"/>
-      <c r="P465" s="79"/>
+      <c r="A465" s="76"/>
+      <c r="E465" s="76"/>
+      <c r="N465" s="77"/>
+      <c r="P465" s="77"/>
     </row>
     <row r="466" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A466" s="78"/>
-      <c r="E466" s="78"/>
-      <c r="N466" s="79"/>
-      <c r="P466" s="79"/>
+      <c r="A466" s="76"/>
+      <c r="E466" s="76"/>
+      <c r="N466" s="77"/>
+      <c r="P466" s="77"/>
     </row>
     <row r="467" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A467" s="78"/>
-      <c r="E467" s="78"/>
-      <c r="N467" s="79"/>
-      <c r="P467" s="79"/>
+      <c r="A467" s="76"/>
+      <c r="E467" s="76"/>
+      <c r="N467" s="77"/>
+      <c r="P467" s="77"/>
     </row>
     <row r="468" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A468" s="78"/>
-      <c r="E468" s="78"/>
-      <c r="N468" s="79"/>
-      <c r="P468" s="79"/>
+      <c r="A468" s="76"/>
+      <c r="E468" s="76"/>
+      <c r="N468" s="77"/>
+      <c r="P468" s="77"/>
     </row>
     <row r="469" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A469" s="78"/>
-      <c r="E469" s="78"/>
-      <c r="N469" s="79"/>
-      <c r="P469" s="79"/>
+      <c r="A469" s="76"/>
+      <c r="E469" s="76"/>
+      <c r="N469" s="77"/>
+      <c r="P469" s="77"/>
     </row>
     <row r="470" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A470" s="78"/>
-      <c r="E470" s="78"/>
-      <c r="N470" s="79"/>
-      <c r="P470" s="79"/>
+      <c r="A470" s="76"/>
+      <c r="E470" s="76"/>
+      <c r="N470" s="77"/>
+      <c r="P470" s="77"/>
     </row>
     <row r="471" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A471" s="78"/>
-      <c r="E471" s="78"/>
-      <c r="N471" s="79"/>
-      <c r="P471" s="79"/>
+      <c r="A471" s="76"/>
+      <c r="E471" s="76"/>
+      <c r="N471" s="77"/>
+      <c r="P471" s="77"/>
     </row>
     <row r="472" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A472" s="78"/>
-      <c r="E472" s="78"/>
-      <c r="N472" s="79"/>
-      <c r="P472" s="79"/>
+      <c r="A472" s="76"/>
+      <c r="E472" s="76"/>
+      <c r="N472" s="77"/>
+      <c r="P472" s="77"/>
     </row>
     <row r="473" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A473" s="78"/>
-      <c r="E473" s="78"/>
-      <c r="N473" s="79"/>
-      <c r="P473" s="79"/>
+      <c r="A473" s="76"/>
+      <c r="E473" s="76"/>
+      <c r="N473" s="77"/>
+      <c r="P473" s="77"/>
     </row>
     <row r="474" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A474" s="78"/>
-      <c r="E474" s="78"/>
-      <c r="N474" s="79"/>
-      <c r="P474" s="79"/>
+      <c r="A474" s="76"/>
+      <c r="E474" s="76"/>
+      <c r="N474" s="77"/>
+      <c r="P474" s="77"/>
     </row>
     <row r="475" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A475" s="78"/>
-      <c r="E475" s="78"/>
-      <c r="N475" s="79"/>
-      <c r="P475" s="79"/>
+      <c r="A475" s="76"/>
+      <c r="E475" s="76"/>
+      <c r="N475" s="77"/>
+      <c r="P475" s="77"/>
     </row>
     <row r="476" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A476" s="78"/>
-      <c r="E476" s="78"/>
-      <c r="N476" s="79"/>
-      <c r="P476" s="79"/>
+      <c r="A476" s="76"/>
+      <c r="E476" s="76"/>
+      <c r="N476" s="77"/>
+      <c r="P476" s="77"/>
     </row>
     <row r="477" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A477" s="78"/>
-      <c r="E477" s="78"/>
-      <c r="N477" s="79"/>
-      <c r="P477" s="79"/>
+      <c r="A477" s="76"/>
+      <c r="E477" s="76"/>
+      <c r="N477" s="77"/>
+      <c r="P477" s="77"/>
     </row>
     <row r="478" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A478" s="78"/>
-      <c r="E478" s="78"/>
-      <c r="N478" s="79"/>
-      <c r="P478" s="79"/>
+      <c r="A478" s="76"/>
+      <c r="E478" s="76"/>
+      <c r="N478" s="77"/>
+      <c r="P478" s="77"/>
     </row>
     <row r="479" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A479" s="78"/>
-      <c r="E479" s="78"/>
-      <c r="N479" s="79"/>
-      <c r="P479" s="79"/>
+      <c r="A479" s="76"/>
+      <c r="E479" s="76"/>
+      <c r="N479" s="77"/>
+      <c r="P479" s="77"/>
     </row>
     <row r="480" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A480" s="78"/>
-      <c r="E480" s="78"/>
-      <c r="N480" s="79"/>
-      <c r="P480" s="79"/>
+      <c r="A480" s="76"/>
+      <c r="E480" s="76"/>
+      <c r="N480" s="77"/>
+      <c r="P480" s="77"/>
     </row>
     <row r="481" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A481" s="78"/>
-      <c r="E481" s="78"/>
-      <c r="N481" s="79"/>
-      <c r="P481" s="79"/>
+      <c r="A481" s="76"/>
+      <c r="E481" s="76"/>
+      <c r="N481" s="77"/>
+      <c r="P481" s="77"/>
     </row>
     <row r="482" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A482" s="78"/>
-      <c r="E482" s="78"/>
-      <c r="N482" s="79"/>
-      <c r="P482" s="79"/>
+      <c r="A482" s="76"/>
+      <c r="E482" s="76"/>
+      <c r="N482" s="77"/>
+      <c r="P482" s="77"/>
     </row>
     <row r="483" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A483" s="78"/>
-      <c r="E483" s="78"/>
-      <c r="N483" s="79"/>
-      <c r="P483" s="79"/>
+      <c r="A483" s="76"/>
+      <c r="E483" s="76"/>
+      <c r="N483" s="77"/>
+      <c r="P483" s="77"/>
     </row>
     <row r="484" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A484" s="78"/>
-      <c r="E484" s="78"/>
-      <c r="N484" s="79"/>
-      <c r="P484" s="79"/>
+      <c r="A484" s="76"/>
+      <c r="E484" s="76"/>
+      <c r="N484" s="77"/>
+      <c r="P484" s="77"/>
     </row>
     <row r="485" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A485" s="78"/>
-      <c r="E485" s="78"/>
-      <c r="N485" s="79"/>
-      <c r="P485" s="79"/>
+      <c r="A485" s="76"/>
+      <c r="E485" s="76"/>
+      <c r="N485" s="77"/>
+      <c r="P485" s="77"/>
     </row>
     <row r="486" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A486" s="78"/>
-      <c r="E486" s="78"/>
-      <c r="N486" s="79"/>
-      <c r="P486" s="79"/>
+      <c r="A486" s="76"/>
+      <c r="E486" s="76"/>
+      <c r="N486" s="77"/>
+      <c r="P486" s="77"/>
     </row>
     <row r="487" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A487" s="78"/>
-      <c r="E487" s="78"/>
-      <c r="N487" s="79"/>
-      <c r="P487" s="79"/>
+      <c r="A487" s="76"/>
+      <c r="E487" s="76"/>
+      <c r="N487" s="77"/>
+      <c r="P487" s="77"/>
     </row>
     <row r="488" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A488" s="78"/>
-      <c r="E488" s="78"/>
-      <c r="N488" s="79"/>
-      <c r="P488" s="79"/>
+      <c r="A488" s="76"/>
+      <c r="E488" s="76"/>
+      <c r="N488" s="77"/>
+      <c r="P488" s="77"/>
     </row>
     <row r="489" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A489" s="78"/>
-      <c r="E489" s="78"/>
-      <c r="N489" s="79"/>
-      <c r="P489" s="79"/>
+      <c r="A489" s="76"/>
+      <c r="E489" s="76"/>
+      <c r="N489" s="77"/>
+      <c r="P489" s="77"/>
     </row>
     <row r="490" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A490" s="78"/>
-      <c r="E490" s="78"/>
-      <c r="N490" s="79"/>
-      <c r="P490" s="79"/>
+      <c r="A490" s="76"/>
+      <c r="E490" s="76"/>
+      <c r="N490" s="77"/>
+      <c r="P490" s="77"/>
     </row>
     <row r="491" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A491" s="78"/>
-      <c r="E491" s="78"/>
-      <c r="N491" s="79"/>
-      <c r="P491" s="79"/>
+      <c r="A491" s="76"/>
+      <c r="E491" s="76"/>
+      <c r="N491" s="77"/>
+      <c r="P491" s="77"/>
     </row>
     <row r="492" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A492" s="78"/>
-      <c r="E492" s="78"/>
-      <c r="N492" s="79"/>
-      <c r="P492" s="79"/>
+      <c r="A492" s="76"/>
+      <c r="E492" s="76"/>
+      <c r="N492" s="77"/>
+      <c r="P492" s="77"/>
     </row>
     <row r="493" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A493" s="78"/>
-      <c r="E493" s="78"/>
-      <c r="N493" s="79"/>
-      <c r="P493" s="79"/>
+      <c r="A493" s="76"/>
+      <c r="E493" s="76"/>
+      <c r="N493" s="77"/>
+      <c r="P493" s="77"/>
     </row>
     <row r="494" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A494" s="78"/>
-      <c r="E494" s="78"/>
-      <c r="N494" s="79"/>
-      <c r="P494" s="79"/>
+      <c r="A494" s="76"/>
+      <c r="E494" s="76"/>
+      <c r="N494" s="77"/>
+      <c r="P494" s="77"/>
     </row>
     <row r="495" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A495" s="78"/>
-      <c r="E495" s="78"/>
-      <c r="N495" s="79"/>
-      <c r="P495" s="79"/>
+      <c r="A495" s="76"/>
+      <c r="E495" s="76"/>
+      <c r="N495" s="77"/>
+      <c r="P495" s="77"/>
     </row>
     <row r="496" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A496" s="78"/>
-      <c r="E496" s="78"/>
-      <c r="N496" s="79"/>
-      <c r="P496" s="79"/>
+      <c r="A496" s="76"/>
+      <c r="E496" s="76"/>
+      <c r="N496" s="77"/>
+      <c r="P496" s="77"/>
     </row>
     <row r="497" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A497" s="78"/>
-      <c r="E497" s="78"/>
-      <c r="N497" s="79"/>
-      <c r="P497" s="79"/>
+      <c r="A497" s="76"/>
+      <c r="E497" s="76"/>
+      <c r="N497" s="77"/>
+      <c r="P497" s="77"/>
     </row>
     <row r="498" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A498" s="78"/>
-      <c r="E498" s="78"/>
-      <c r="N498" s="79"/>
-      <c r="P498" s="79"/>
+      <c r="A498" s="76"/>
+      <c r="E498" s="76"/>
+      <c r="N498" s="77"/>
+      <c r="P498" s="77"/>
     </row>
     <row r="499" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A499" s="78"/>
-      <c r="E499" s="78"/>
-      <c r="N499" s="79"/>
-      <c r="P499" s="79"/>
+      <c r="A499" s="76"/>
+      <c r="E499" s="76"/>
+      <c r="N499" s="77"/>
+      <c r="P499" s="77"/>
     </row>
     <row r="500" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A500" s="78"/>
-      <c r="E500" s="78"/>
-      <c r="N500" s="79"/>
-      <c r="P500" s="79"/>
+      <c r="A500" s="76"/>
+      <c r="E500" s="76"/>
+      <c r="N500" s="77"/>
+      <c r="P500" s="77"/>
     </row>
     <row r="501" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A501" s="78"/>
-      <c r="E501" s="78"/>
-      <c r="N501" s="79"/>
-      <c r="P501" s="79"/>
+      <c r="A501" s="76"/>
+      <c r="E501" s="76"/>
+      <c r="N501" s="77"/>
+      <c r="P501" s="77"/>
     </row>
     <row r="502" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A502" s="78"/>
-      <c r="E502" s="78"/>
-      <c r="N502" s="79"/>
-      <c r="P502" s="79"/>
+      <c r="A502" s="76"/>
+      <c r="E502" s="76"/>
+      <c r="N502" s="77"/>
+      <c r="P502" s="77"/>
     </row>
     <row r="503" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A503" s="78"/>
-      <c r="E503" s="78"/>
-      <c r="N503" s="79"/>
-      <c r="P503" s="79"/>
+      <c r="A503" s="76"/>
+      <c r="E503" s="76"/>
+      <c r="N503" s="77"/>
+      <c r="P503" s="77"/>
     </row>
     <row r="504" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A504" s="78"/>
-      <c r="E504" s="78"/>
-      <c r="N504" s="79"/>
-      <c r="P504" s="79"/>
+      <c r="A504" s="76"/>
+      <c r="E504" s="76"/>
+      <c r="N504" s="77"/>
+      <c r="P504" s="77"/>
     </row>
     <row r="505" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A505" s="78"/>
-      <c r="E505" s="78"/>
-      <c r="N505" s="79"/>
-      <c r="P505" s="79"/>
+      <c r="A505" s="76"/>
+      <c r="E505" s="76"/>
+      <c r="N505" s="77"/>
+      <c r="P505" s="77"/>
     </row>
     <row r="506" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A506" s="78"/>
-      <c r="E506" s="78"/>
-      <c r="N506" s="79"/>
-      <c r="P506" s="79"/>
+      <c r="A506" s="76"/>
+      <c r="E506" s="76"/>
+      <c r="N506" s="77"/>
+      <c r="P506" s="77"/>
     </row>
     <row r="507" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A507" s="78"/>
-      <c r="E507" s="78"/>
-      <c r="N507" s="79"/>
-      <c r="P507" s="79"/>
+      <c r="A507" s="76"/>
+      <c r="E507" s="76"/>
+      <c r="N507" s="77"/>
+      <c r="P507" s="77"/>
     </row>
     <row r="508" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A508" s="78"/>
-      <c r="E508" s="78"/>
-      <c r="N508" s="79"/>
-      <c r="P508" s="79"/>
+      <c r="A508" s="76"/>
+      <c r="E508" s="76"/>
+      <c r="N508" s="77"/>
+      <c r="P508" s="77"/>
     </row>
     <row r="509" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A509" s="78"/>
-      <c r="E509" s="78"/>
-      <c r="N509" s="79"/>
-      <c r="P509" s="79"/>
+      <c r="A509" s="76"/>
+      <c r="E509" s="76"/>
+      <c r="N509" s="77"/>
+      <c r="P509" s="77"/>
     </row>
     <row r="510" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A510" s="78"/>
-      <c r="E510" s="78"/>
-      <c r="N510" s="79"/>
-      <c r="P510" s="79"/>
+      <c r="A510" s="76"/>
+      <c r="E510" s="76"/>
+      <c r="N510" s="77"/>
+      <c r="P510" s="77"/>
     </row>
     <row r="511" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A511" s="78"/>
-      <c r="E511" s="78"/>
-      <c r="N511" s="79"/>
-      <c r="P511" s="79"/>
+      <c r="A511" s="76"/>
+      <c r="E511" s="76"/>
+      <c r="N511" s="77"/>
+      <c r="P511" s="77"/>
     </row>
     <row r="512" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A512" s="78"/>
-      <c r="E512" s="78"/>
-      <c r="N512" s="79"/>
-      <c r="P512" s="79"/>
+      <c r="A512" s="76"/>
+      <c r="E512" s="76"/>
+      <c r="N512" s="77"/>
+      <c r="P512" s="77"/>
     </row>
     <row r="513" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A513" s="78"/>
-      <c r="E513" s="78"/>
-      <c r="N513" s="79"/>
-      <c r="P513" s="79"/>
+      <c r="A513" s="76"/>
+      <c r="E513" s="76"/>
+      <c r="N513" s="77"/>
+      <c r="P513" s="77"/>
     </row>
     <row r="514" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A514" s="78"/>
-      <c r="E514" s="78"/>
-      <c r="N514" s="79"/>
-      <c r="P514" s="79"/>
+      <c r="A514" s="76"/>
+      <c r="E514" s="76"/>
+      <c r="N514" s="77"/>
+      <c r="P514" s="77"/>
     </row>
     <row r="515" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A515" s="78"/>
-      <c r="E515" s="78"/>
-      <c r="N515" s="79"/>
-      <c r="P515" s="79"/>
+      <c r="A515" s="76"/>
+      <c r="E515" s="76"/>
+      <c r="N515" s="77"/>
+      <c r="P515" s="77"/>
     </row>
     <row r="516" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A516" s="78"/>
-      <c r="E516" s="78"/>
-      <c r="N516" s="79"/>
-      <c r="P516" s="79"/>
+      <c r="A516" s="76"/>
+      <c r="E516" s="76"/>
+      <c r="N516" s="77"/>
+      <c r="P516" s="77"/>
     </row>
     <row r="517" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A517" s="78"/>
-      <c r="E517" s="78"/>
-      <c r="N517" s="79"/>
-      <c r="P517" s="79"/>
+      <c r="A517" s="76"/>
+      <c r="E517" s="76"/>
+      <c r="N517" s="77"/>
+      <c r="P517" s="77"/>
     </row>
     <row r="518" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A518" s="78"/>
-      <c r="E518" s="78"/>
-      <c r="N518" s="79"/>
-      <c r="P518" s="79"/>
+      <c r="A518" s="76"/>
+      <c r="E518" s="76"/>
+      <c r="N518" s="77"/>
+      <c r="P518" s="77"/>
     </row>
     <row r="519" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A519" s="78"/>
-      <c r="E519" s="78"/>
-      <c r="N519" s="79"/>
-      <c r="P519" s="79"/>
+      <c r="A519" s="76"/>
+      <c r="E519" s="76"/>
+      <c r="N519" s="77"/>
+      <c r="P519" s="77"/>
     </row>
     <row r="520" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A520" s="78"/>
-      <c r="E520" s="78"/>
-      <c r="N520" s="79"/>
-      <c r="P520" s="79"/>
+      <c r="A520" s="76"/>
+      <c r="E520" s="76"/>
+      <c r="N520" s="77"/>
+      <c r="P520" s="77"/>
     </row>
     <row r="521" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A521" s="78"/>
-      <c r="E521" s="78"/>
-      <c r="N521" s="79"/>
-      <c r="P521" s="79"/>
+      <c r="A521" s="76"/>
+      <c r="E521" s="76"/>
+      <c r="N521" s="77"/>
+      <c r="P521" s="77"/>
     </row>
     <row r="522" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A522" s="78"/>
-      <c r="E522" s="78"/>
-      <c r="N522" s="79"/>
-      <c r="P522" s="79"/>
+      <c r="A522" s="76"/>
+      <c r="E522" s="76"/>
+      <c r="N522" s="77"/>
+      <c r="P522" s="77"/>
     </row>
     <row r="523" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A523" s="78"/>
-      <c r="E523" s="78"/>
-      <c r="N523" s="79"/>
-      <c r="P523" s="79"/>
+      <c r="A523" s="76"/>
+      <c r="E523" s="76"/>
+      <c r="N523" s="77"/>
+      <c r="P523" s="77"/>
     </row>
     <row r="524" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A524" s="78"/>
-      <c r="E524" s="78"/>
-      <c r="N524" s="79"/>
-      <c r="P524" s="79"/>
+      <c r="A524" s="76"/>
+      <c r="E524" s="76"/>
+      <c r="N524" s="77"/>
+      <c r="P524" s="77"/>
     </row>
     <row r="525" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A525" s="78"/>
-      <c r="E525" s="78"/>
-      <c r="N525" s="79"/>
-      <c r="P525" s="79"/>
+      <c r="A525" s="76"/>
+      <c r="E525" s="76"/>
+      <c r="N525" s="77"/>
+      <c r="P525" s="77"/>
     </row>
     <row r="526" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A526" s="78"/>
-      <c r="E526" s="78"/>
-      <c r="N526" s="79"/>
-      <c r="P526" s="79"/>
+      <c r="A526" s="76"/>
+      <c r="E526" s="76"/>
+      <c r="N526" s="77"/>
+      <c r="P526" s="77"/>
     </row>
     <row r="527" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A527" s="78"/>
-      <c r="E527" s="78"/>
-      <c r="N527" s="79"/>
-      <c r="P527" s="79"/>
+      <c r="A527" s="76"/>
+      <c r="E527" s="76"/>
+      <c r="N527" s="77"/>
+      <c r="P527" s="77"/>
     </row>
     <row r="528" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A528" s="78"/>
-      <c r="E528" s="78"/>
-      <c r="N528" s="79"/>
-      <c r="P528" s="79"/>
+      <c r="A528" s="76"/>
+      <c r="E528" s="76"/>
+      <c r="N528" s="77"/>
+      <c r="P528" s="77"/>
     </row>
     <row r="529" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A529" s="78"/>
-      <c r="E529" s="78"/>
-      <c r="N529" s="79"/>
-      <c r="P529" s="79"/>
+      <c r="A529" s="76"/>
+      <c r="E529" s="76"/>
+      <c r="N529" s="77"/>
+      <c r="P529" s="77"/>
     </row>
     <row r="530" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A530" s="78"/>
-      <c r="E530" s="78"/>
-      <c r="N530" s="79"/>
-      <c r="P530" s="79"/>
+      <c r="A530" s="76"/>
+      <c r="E530" s="76"/>
+      <c r="N530" s="77"/>
+      <c r="P530" s="77"/>
     </row>
     <row r="531" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A531" s="78"/>
-      <c r="E531" s="78"/>
-      <c r="N531" s="79"/>
-      <c r="P531" s="79"/>
+      <c r="A531" s="76"/>
+      <c r="E531" s="76"/>
+      <c r="N531" s="77"/>
+      <c r="P531" s="77"/>
     </row>
     <row r="532" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A532" s="78"/>
-      <c r="E532" s="78"/>
-      <c r="N532" s="79"/>
-      <c r="P532" s="79"/>
+      <c r="A532" s="76"/>
+      <c r="E532" s="76"/>
+      <c r="N532" s="77"/>
+      <c r="P532" s="77"/>
     </row>
     <row r="533" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A533" s="78"/>
-      <c r="E533" s="78"/>
-      <c r="N533" s="79"/>
-      <c r="P533" s="79"/>
+      <c r="A533" s="76"/>
+      <c r="E533" s="76"/>
+      <c r="N533" s="77"/>
+      <c r="P533" s="77"/>
     </row>
     <row r="534" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A534" s="78"/>
-      <c r="E534" s="78"/>
-      <c r="N534" s="79"/>
-      <c r="P534" s="79"/>
+      <c r="A534" s="76"/>
+      <c r="E534" s="76"/>
+      <c r="N534" s="77"/>
+      <c r="P534" s="77"/>
     </row>
     <row r="535" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A535" s="78"/>
-      <c r="E535" s="78"/>
-      <c r="N535" s="79"/>
-      <c r="P535" s="79"/>
+      <c r="A535" s="76"/>
+      <c r="E535" s="76"/>
+      <c r="N535" s="77"/>
+      <c r="P535" s="77"/>
     </row>
     <row r="536" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A536" s="78"/>
-      <c r="E536" s="78"/>
-      <c r="N536" s="79"/>
-      <c r="P536" s="79"/>
+      <c r="A536" s="76"/>
+      <c r="E536" s="76"/>
+      <c r="N536" s="77"/>
+      <c r="P536" s="77"/>
     </row>
     <row r="537" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A537" s="78"/>
-      <c r="E537" s="78"/>
-      <c r="N537" s="79"/>
-      <c r="P537" s="79"/>
+      <c r="A537" s="76"/>
+      <c r="E537" s="76"/>
+      <c r="N537" s="77"/>
+      <c r="P537" s="77"/>
     </row>
     <row r="538" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A538" s="78"/>
-      <c r="E538" s="78"/>
-      <c r="N538" s="79"/>
-      <c r="P538" s="79"/>
+      <c r="A538" s="76"/>
+      <c r="E538" s="76"/>
+      <c r="N538" s="77"/>
+      <c r="P538" s="77"/>
     </row>
     <row r="539" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A539" s="78"/>
-      <c r="E539" s="78"/>
-      <c r="N539" s="79"/>
-      <c r="P539" s="79"/>
+      <c r="A539" s="76"/>
+      <c r="E539" s="76"/>
+      <c r="N539" s="77"/>
+      <c r="P539" s="77"/>
     </row>
     <row r="540" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A540" s="78"/>
-      <c r="E540" s="78"/>
-      <c r="N540" s="79"/>
-      <c r="P540" s="79"/>
+      <c r="A540" s="76"/>
+      <c r="E540" s="76"/>
+      <c r="N540" s="77"/>
+      <c r="P540" s="77"/>
     </row>
     <row r="541" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A541" s="78"/>
-      <c r="E541" s="78"/>
-      <c r="N541" s="79"/>
-      <c r="P541" s="79"/>
+      <c r="A541" s="76"/>
+      <c r="E541" s="76"/>
+      <c r="N541" s="77"/>
+      <c r="P541" s="77"/>
     </row>
     <row r="542" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A542" s="78"/>
-      <c r="E542" s="78"/>
-      <c r="N542" s="79"/>
-      <c r="P542" s="79"/>
+      <c r="A542" s="76"/>
+      <c r="E542" s="76"/>
+      <c r="N542" s="77"/>
+      <c r="P542" s="77"/>
     </row>
     <row r="543" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A543" s="78"/>
-      <c r="E543" s="78"/>
-      <c r="N543" s="79"/>
-      <c r="P543" s="79"/>
+      <c r="A543" s="76"/>
+      <c r="E543" s="76"/>
+      <c r="N543" s="77"/>
+      <c r="P543" s="77"/>
     </row>
     <row r="544" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A544" s="78"/>
-      <c r="E544" s="78"/>
-      <c r="N544" s="79"/>
-      <c r="P544" s="79"/>
+      <c r="A544" s="76"/>
+      <c r="E544" s="76"/>
+      <c r="N544" s="77"/>
+      <c r="P544" s="77"/>
     </row>
     <row r="545" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A545" s="78"/>
-      <c r="E545" s="78"/>
-      <c r="N545" s="79"/>
-      <c r="P545" s="79"/>
+      <c r="A545" s="76"/>
+      <c r="E545" s="76"/>
+      <c r="N545" s="77"/>
+      <c r="P545" s="77"/>
     </row>
     <row r="546" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A546" s="78"/>
-      <c r="E546" s="78"/>
-      <c r="N546" s="79"/>
-      <c r="P546" s="79"/>
+      <c r="A546" s="76"/>
+      <c r="E546" s="76"/>
+      <c r="N546" s="77"/>
+      <c r="P546" s="77"/>
     </row>
     <row r="547" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A547" s="78"/>
-      <c r="E547" s="78"/>
-      <c r="N547" s="79"/>
-      <c r="P547" s="79"/>
+      <c r="A547" s="76"/>
+      <c r="E547" s="76"/>
+      <c r="N547" s="77"/>
+      <c r="P547" s="77"/>
     </row>
     <row r="548" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A548" s="78"/>
-      <c r="E548" s="78"/>
-      <c r="N548" s="79"/>
-      <c r="P548" s="79"/>
+      <c r="A548" s="76"/>
+      <c r="E548" s="76"/>
+      <c r="N548" s="77"/>
+      <c r="P548" s="77"/>
     </row>
     <row r="549" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A549" s="78"/>
-      <c r="E549" s="78"/>
-      <c r="N549" s="79"/>
-      <c r="P549" s="79"/>
+      <c r="A549" s="76"/>
+      <c r="E549" s="76"/>
+      <c r="N549" s="77"/>
+      <c r="P549" s="77"/>
     </row>
     <row r="550" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A550" s="78"/>
-      <c r="E550" s="78"/>
-      <c r="N550" s="79"/>
-      <c r="P550" s="79"/>
+      <c r="A550" s="76"/>
+      <c r="E550" s="76"/>
+      <c r="N550" s="77"/>
+      <c r="P550" s="77"/>
     </row>
     <row r="551" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A551" s="78"/>
-      <c r="E551" s="78"/>
-      <c r="N551" s="79"/>
-      <c r="P551" s="79"/>
+      <c r="A551" s="76"/>
+      <c r="E551" s="76"/>
+      <c r="N551" s="77"/>
+      <c r="P551" s="77"/>
     </row>
     <row r="552" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A552" s="78"/>
-      <c r="E552" s="78"/>
-      <c r="N552" s="79"/>
-      <c r="P552" s="79"/>
+      <c r="A552" s="76"/>
+      <c r="E552" s="76"/>
+      <c r="N552" s="77"/>
+      <c r="P552" s="77"/>
     </row>
     <row r="553" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A553" s="78"/>
-      <c r="E553" s="78"/>
-      <c r="N553" s="79"/>
-      <c r="P553" s="79"/>
+      <c r="A553" s="76"/>
+      <c r="E553" s="76"/>
+      <c r="N553" s="77"/>
+      <c r="P553" s="77"/>
     </row>
     <row r="554" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A554" s="78"/>
-      <c r="E554" s="78"/>
-      <c r="N554" s="79"/>
-      <c r="P554" s="79"/>
+      <c r="A554" s="76"/>
+      <c r="E554" s="76"/>
+      <c r="N554" s="77"/>
+      <c r="P554" s="77"/>
     </row>
     <row r="555" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A555" s="78"/>
-      <c r="E555" s="78"/>
-      <c r="N555" s="79"/>
-      <c r="P555" s="79"/>
+      <c r="A555" s="76"/>
+      <c r="E555" s="76"/>
+      <c r="N555" s="77"/>
+      <c r="P555" s="77"/>
     </row>
     <row r="556" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A556" s="78"/>
-      <c r="E556" s="78"/>
-      <c r="N556" s="79"/>
-      <c r="P556" s="79"/>
+      <c r="A556" s="76"/>
+      <c r="E556" s="76"/>
+      <c r="N556" s="77"/>
+      <c r="P556" s="77"/>
     </row>
     <row r="557" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A557" s="78"/>
-      <c r="E557" s="78"/>
-      <c r="N557" s="79"/>
-      <c r="P557" s="79"/>
+      <c r="A557" s="76"/>
+      <c r="E557" s="76"/>
+      <c r="N557" s="77"/>
+      <c r="P557" s="77"/>
     </row>
     <row r="558" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A558" s="78"/>
-      <c r="E558" s="78"/>
-      <c r="N558" s="79"/>
-      <c r="P558" s="79"/>
+      <c r="A558" s="76"/>
+      <c r="E558" s="76"/>
+      <c r="N558" s="77"/>
+      <c r="P558" s="77"/>
     </row>
     <row r="559" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A559" s="78"/>
-      <c r="E559" s="78"/>
-      <c r="N559" s="79"/>
-      <c r="P559" s="79"/>
+      <c r="A559" s="76"/>
+      <c r="E559" s="76"/>
+      <c r="N559" s="77"/>
+      <c r="P559" s="77"/>
     </row>
     <row r="560" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A560" s="78"/>
-      <c r="E560" s="78"/>
-      <c r="N560" s="79"/>
-      <c r="P560" s="79"/>
+      <c r="A560" s="76"/>
+      <c r="E560" s="76"/>
+      <c r="N560" s="77"/>
+      <c r="P560" s="77"/>
     </row>
     <row r="561" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A561" s="78"/>
-      <c r="E561" s="78"/>
-      <c r="N561" s="79"/>
-      <c r="P561" s="79"/>
+      <c r="A561" s="76"/>
+      <c r="E561" s="76"/>
+      <c r="N561" s="77"/>
+      <c r="P561" s="77"/>
     </row>
     <row r="562" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A562" s="78"/>
-      <c r="E562" s="78"/>
-      <c r="N562" s="79"/>
-      <c r="P562" s="79"/>
+      <c r="A562" s="76"/>
+      <c r="E562" s="76"/>
+      <c r="N562" s="77"/>
+      <c r="P562" s="77"/>
     </row>
     <row r="563" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A563" s="78"/>
-      <c r="E563" s="78"/>
-      <c r="N563" s="79"/>
-      <c r="P563" s="79"/>
+      <c r="A563" s="76"/>
+      <c r="E563" s="76"/>
+      <c r="N563" s="77"/>
+      <c r="P563" s="77"/>
     </row>
     <row r="564" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A564" s="78"/>
-      <c r="E564" s="78"/>
-      <c r="N564" s="79"/>
-      <c r="P564" s="79"/>
+      <c r="A564" s="76"/>
+      <c r="E564" s="76"/>
+      <c r="N564" s="77"/>
+      <c r="P564" s="77"/>
     </row>
     <row r="565" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A565" s="78"/>
-      <c r="E565" s="78"/>
-      <c r="N565" s="79"/>
-      <c r="P565" s="79"/>
+      <c r="A565" s="76"/>
+      <c r="E565" s="76"/>
+      <c r="N565" s="77"/>
+      <c r="P565" s="77"/>
     </row>
     <row r="566" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A566" s="78"/>
-      <c r="E566" s="78"/>
-      <c r="N566" s="79"/>
-      <c r="P566" s="79"/>
+      <c r="A566" s="76"/>
+      <c r="E566" s="76"/>
+      <c r="N566" s="77"/>
+      <c r="P566" s="77"/>
     </row>
     <row r="567" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A567" s="78"/>
-      <c r="E567" s="78"/>
-      <c r="N567" s="79"/>
-      <c r="P567" s="79"/>
+      <c r="A567" s="76"/>
+      <c r="E567" s="76"/>
+      <c r="N567" s="77"/>
+      <c r="P567" s="77"/>
     </row>
     <row r="568" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A568" s="78"/>
-      <c r="E568" s="78"/>
-      <c r="N568" s="79"/>
-      <c r="P568" s="79"/>
+      <c r="A568" s="76"/>
+      <c r="E568" s="76"/>
+      <c r="N568" s="77"/>
+      <c r="P568" s="77"/>
     </row>
     <row r="569" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A569" s="78"/>
-      <c r="E569" s="78"/>
-      <c r="N569" s="79"/>
-      <c r="P569" s="79"/>
+      <c r="A569" s="76"/>
+      <c r="E569" s="76"/>
+      <c r="N569" s="77"/>
+      <c r="P569" s="77"/>
     </row>
     <row r="570" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A570" s="78"/>
-      <c r="E570" s="78"/>
-      <c r="N570" s="79"/>
-      <c r="P570" s="79"/>
+      <c r="A570" s="76"/>
+      <c r="E570" s="76"/>
+      <c r="N570" s="77"/>
+      <c r="P570" s="77"/>
     </row>
     <row r="571" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A571" s="78"/>
-      <c r="E571" s="78"/>
-      <c r="N571" s="79"/>
-      <c r="P571" s="79"/>
+      <c r="A571" s="76"/>
+      <c r="E571" s="76"/>
+      <c r="N571" s="77"/>
+      <c r="P571" s="77"/>
     </row>
     <row r="572" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A572" s="78"/>
-      <c r="E572" s="78"/>
-      <c r="N572" s="79"/>
-      <c r="P572" s="79"/>
+      <c r="A572" s="76"/>
+      <c r="E572" s="76"/>
+      <c r="N572" s="77"/>
+      <c r="P572" s="77"/>
     </row>
     <row r="573" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A573" s="78"/>
-      <c r="E573" s="78"/>
-      <c r="N573" s="79"/>
-      <c r="P573" s="79"/>
+      <c r="A573" s="76"/>
+      <c r="E573" s="76"/>
+      <c r="N573" s="77"/>
+      <c r="P573" s="77"/>
     </row>
     <row r="574" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A574" s="78"/>
-      <c r="E574" s="78"/>
-      <c r="N574" s="79"/>
-      <c r="P574" s="79"/>
+      <c r="A574" s="76"/>
+      <c r="E574" s="76"/>
+      <c r="N574" s="77"/>
+      <c r="P574" s="77"/>
     </row>
     <row r="575" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A575" s="78"/>
-      <c r="E575" s="78"/>
-      <c r="N575" s="79"/>
-      <c r="P575" s="79"/>
+      <c r="A575" s="76"/>
+      <c r="E575" s="76"/>
+      <c r="N575" s="77"/>
+      <c r="P575" s="77"/>
     </row>
     <row r="576" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A576" s="78"/>
-      <c r="E576" s="78"/>
-      <c r="N576" s="79"/>
-      <c r="P576" s="79"/>
+      <c r="A576" s="76"/>
+      <c r="E576" s="76"/>
+      <c r="N576" s="77"/>
+      <c r="P576" s="77"/>
     </row>
     <row r="577" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A577" s="78"/>
-      <c r="E577" s="78"/>
-      <c r="N577" s="79"/>
-      <c r="P577" s="79"/>
+      <c r="A577" s="76"/>
+      <c r="E577" s="76"/>
+      <c r="N577" s="77"/>
+      <c r="P577" s="77"/>
     </row>
     <row r="578" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A578" s="78"/>
-      <c r="E578" s="78"/>
-      <c r="N578" s="79"/>
-      <c r="P578" s="79"/>
+      <c r="A578" s="76"/>
+      <c r="E578" s="76"/>
+      <c r="N578" s="77"/>
+      <c r="P578" s="77"/>
     </row>
     <row r="579" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A579" s="78"/>
-      <c r="E579" s="78"/>
-      <c r="N579" s="79"/>
-      <c r="P579" s="79"/>
+      <c r="A579" s="76"/>
+      <c r="E579" s="76"/>
+      <c r="N579" s="77"/>
+      <c r="P579" s="77"/>
     </row>
     <row r="580" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A580" s="78"/>
-      <c r="E580" s="78"/>
-      <c r="N580" s="79"/>
-      <c r="P580" s="79"/>
+      <c r="A580" s="76"/>
+      <c r="E580" s="76"/>
+      <c r="N580" s="77"/>
+      <c r="P580" s="77"/>
     </row>
     <row r="581" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A581" s="78"/>
-      <c r="E581" s="78"/>
-      <c r="N581" s="79"/>
-      <c r="P581" s="79"/>
+      <c r="A581" s="76"/>
+      <c r="E581" s="76"/>
+      <c r="N581" s="77"/>
+      <c r="P581" s="77"/>
     </row>
     <row r="582" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A582" s="78"/>
-      <c r="E582" s="78"/>
-      <c r="N582" s="79"/>
-      <c r="P582" s="79"/>
+      <c r="A582" s="76"/>
+      <c r="E582" s="76"/>
+      <c r="N582" s="77"/>
+      <c r="P582" s="77"/>
     </row>
     <row r="583" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A583" s="78"/>
-      <c r="E583" s="78"/>
-      <c r="N583" s="79"/>
-      <c r="P583" s="79"/>
+      <c r="A583" s="76"/>
+      <c r="E583" s="76"/>
+      <c r="N583" s="77"/>
+      <c r="P583" s="77"/>
     </row>
     <row r="584" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A584" s="78"/>
-      <c r="E584" s="78"/>
-      <c r="N584" s="79"/>
-      <c r="P584" s="79"/>
+      <c r="A584" s="76"/>
+      <c r="E584" s="76"/>
+      <c r="N584" s="77"/>
+      <c r="P584" s="77"/>
     </row>
     <row r="585" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A585" s="78"/>
-      <c r="E585" s="78"/>
-      <c r="N585" s="79"/>
-      <c r="P585" s="79"/>
+      <c r="A585" s="76"/>
+      <c r="E585" s="76"/>
+      <c r="N585" s="77"/>
+      <c r="P585" s="77"/>
     </row>
     <row r="586" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A586" s="78"/>
-      <c r="E586" s="78"/>
-      <c r="N586" s="79"/>
-      <c r="P586" s="79"/>
+      <c r="A586" s="76"/>
+      <c r="E586" s="76"/>
+      <c r="N586" s="77"/>
+      <c r="P586" s="77"/>
     </row>
     <row r="587" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A587" s="78"/>
-      <c r="E587" s="78"/>
-      <c r="N587" s="79"/>
-      <c r="P587" s="79"/>
+      <c r="A587" s="76"/>
+      <c r="E587" s="76"/>
+      <c r="N587" s="77"/>
+      <c r="P587" s="77"/>
     </row>
     <row r="588" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A588" s="78"/>
-      <c r="E588" s="78"/>
-      <c r="N588" s="79"/>
-      <c r="P588" s="79"/>
+      <c r="A588" s="76"/>
+      <c r="E588" s="76"/>
+      <c r="N588" s="77"/>
+      <c r="P588" s="77"/>
     </row>
     <row r="589" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A589" s="78"/>
-      <c r="E589" s="78"/>
-      <c r="N589" s="79"/>
-      <c r="P589" s="79"/>
+      <c r="A589" s="76"/>
+      <c r="E589" s="76"/>
+      <c r="N589" s="77"/>
+      <c r="P589" s="77"/>
     </row>
     <row r="590" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A590" s="78"/>
-      <c r="E590" s="78"/>
-      <c r="N590" s="79"/>
-      <c r="P590" s="79"/>
+      <c r="A590" s="76"/>
+      <c r="E590" s="76"/>
+      <c r="N590" s="77"/>
+      <c r="P590" s="77"/>
     </row>
     <row r="591" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A591" s="78"/>
-      <c r="E591" s="78"/>
-      <c r="N591" s="79"/>
-      <c r="P591" s="79"/>
+      <c r="A591" s="76"/>
+      <c r="E591" s="76"/>
+      <c r="N591" s="77"/>
+      <c r="P591" s="77"/>
     </row>
     <row r="592" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A592" s="78"/>
-      <c r="E592" s="78"/>
-      <c r="N592" s="79"/>
-      <c r="P592" s="79"/>
+      <c r="A592" s="76"/>
+      <c r="E592" s="76"/>
+      <c r="N592" s="77"/>
+      <c r="P592" s="77"/>
     </row>
     <row r="593" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A593" s="78"/>
-      <c r="E593" s="78"/>
-      <c r="N593" s="79"/>
-      <c r="P593" s="79"/>
+      <c r="A593" s="76"/>
+      <c r="E593" s="76"/>
+      <c r="N593" s="77"/>
+      <c r="P593" s="77"/>
     </row>
     <row r="594" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A594" s="78"/>
-      <c r="E594" s="78"/>
-      <c r="N594" s="79"/>
-      <c r="P594" s="79"/>
+      <c r="A594" s="76"/>
+      <c r="E594" s="76"/>
+      <c r="N594" s="77"/>
+      <c r="P594" s="77"/>
     </row>
     <row r="595" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A595" s="78"/>
-      <c r="E595" s="78"/>
-      <c r="N595" s="79"/>
-      <c r="P595" s="79"/>
+      <c r="A595" s="76"/>
+      <c r="E595" s="76"/>
+      <c r="N595" s="77"/>
+      <c r="P595" s="77"/>
     </row>
     <row r="596" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A596" s="78"/>
-      <c r="E596" s="78"/>
-      <c r="N596" s="79"/>
-      <c r="P596" s="79"/>
+      <c r="A596" s="76"/>
+      <c r="E596" s="76"/>
+      <c r="N596" s="77"/>
+      <c r="P596" s="77"/>
     </row>
     <row r="597" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A597" s="78"/>
-      <c r="E597" s="78"/>
-      <c r="N597" s="79"/>
-      <c r="P597" s="79"/>
+      <c r="A597" s="76"/>
+      <c r="E597" s="76"/>
+      <c r="N597" s="77"/>
+      <c r="P597" s="77"/>
     </row>
     <row r="598" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A598" s="78"/>
-      <c r="E598" s="78"/>
-      <c r="N598" s="79"/>
-      <c r="P598" s="79"/>
+      <c r="A598" s="76"/>
+      <c r="E598" s="76"/>
+      <c r="N598" s="77"/>
+      <c r="P598" s="77"/>
     </row>
     <row r="599" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A599" s="78"/>
-      <c r="E599" s="78"/>
-      <c r="N599" s="79"/>
-      <c r="P599" s="79"/>
+      <c r="A599" s="76"/>
+      <c r="E599" s="76"/>
+      <c r="N599" s="77"/>
+      <c r="P599" s="77"/>
     </row>
     <row r="600" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A600" s="78"/>
-      <c r="E600" s="78"/>
-      <c r="N600" s="79"/>
-      <c r="P600" s="79"/>
+      <c r="A600" s="76"/>
+      <c r="E600" s="76"/>
+      <c r="N600" s="77"/>
+      <c r="P600" s="77"/>
     </row>
     <row r="601" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A601" s="78"/>
-      <c r="E601" s="78"/>
-      <c r="N601" s="79"/>
-      <c r="P601" s="79"/>
+      <c r="A601" s="76"/>
+      <c r="E601" s="76"/>
+      <c r="N601" s="77"/>
+      <c r="P601" s="77"/>
     </row>
     <row r="602" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A602" s="78"/>
-      <c r="E602" s="78"/>
-      <c r="N602" s="79"/>
-      <c r="P602" s="79"/>
+      <c r="A602" s="76"/>
+      <c r="E602" s="76"/>
+      <c r="N602" s="77"/>
+      <c r="P602" s="77"/>
     </row>
     <row r="603" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A603" s="78"/>
-      <c r="E603" s="78"/>
-      <c r="N603" s="79"/>
-      <c r="P603" s="79"/>
+      <c r="A603" s="76"/>
+      <c r="E603" s="76"/>
+      <c r="N603" s="77"/>
+      <c r="P603" s="77"/>
     </row>
     <row r="604" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A604" s="78"/>
-      <c r="E604" s="78"/>
-      <c r="N604" s="79"/>
-      <c r="P604" s="79"/>
+      <c r="A604" s="76"/>
+      <c r="E604" s="76"/>
+      <c r="N604" s="77"/>
+      <c r="P604" s="77"/>
     </row>
     <row r="605" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A605" s="78"/>
-      <c r="E605" s="78"/>
-      <c r="N605" s="79"/>
-      <c r="P605" s="79"/>
+      <c r="A605" s="76"/>
+      <c r="E605" s="76"/>
+      <c r="N605" s="77"/>
+      <c r="P605" s="77"/>
     </row>
     <row r="606" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A606" s="78"/>
-      <c r="E606" s="78"/>
-      <c r="N606" s="79"/>
-      <c r="P606" s="79"/>
+      <c r="A606" s="76"/>
+      <c r="E606" s="76"/>
+      <c r="N606" s="77"/>
+      <c r="P606" s="77"/>
     </row>
     <row r="607" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A607" s="78"/>
-      <c r="E607" s="78"/>
-      <c r="N607" s="79"/>
-      <c r="P607" s="79"/>
+      <c r="A607" s="76"/>
+      <c r="E607" s="76"/>
+      <c r="N607" s="77"/>
+      <c r="P607" s="77"/>
     </row>
     <row r="608" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A608" s="78"/>
-      <c r="E608" s="78"/>
-      <c r="N608" s="79"/>
-      <c r="P608" s="79"/>
+      <c r="A608" s="76"/>
+      <c r="E608" s="76"/>
+      <c r="N608" s="77"/>
+      <c r="P608" s="77"/>
     </row>
     <row r="609" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A609" s="78"/>
-      <c r="E609" s="78"/>
-      <c r="N609" s="79"/>
-      <c r="P609" s="79"/>
+      <c r="A609" s="76"/>
+      <c r="E609" s="76"/>
+      <c r="N609" s="77"/>
+      <c r="P609" s="77"/>
     </row>
     <row r="610" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A610" s="78"/>
-      <c r="E610" s="78"/>
-      <c r="N610" s="79"/>
-      <c r="P610" s="79"/>
+      <c r="A610" s="76"/>
+      <c r="E610" s="76"/>
+      <c r="N610" s="77"/>
+      <c r="P610" s="77"/>
     </row>
     <row r="611" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A611" s="78"/>
-      <c r="E611" s="78"/>
-      <c r="N611" s="79"/>
-      <c r="P611" s="79"/>
+      <c r="A611" s="76"/>
+      <c r="E611" s="76"/>
+      <c r="N611" s="77"/>
+      <c r="P611" s="77"/>
     </row>
     <row r="612" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A612" s="78"/>
-      <c r="E612" s="78"/>
-      <c r="N612" s="79"/>
-      <c r="P612" s="79"/>
+      <c r="A612" s="76"/>
+      <c r="E612" s="76"/>
+      <c r="N612" s="77"/>
+      <c r="P612" s="77"/>
     </row>
     <row r="613" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A613" s="78"/>
-      <c r="E613" s="78"/>
-      <c r="N613" s="79"/>
-      <c r="P613" s="79"/>
+      <c r="A613" s="76"/>
+      <c r="E613" s="76"/>
+      <c r="N613" s="77"/>
+      <c r="P613" s="77"/>
     </row>
     <row r="614" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A614" s="78"/>
-      <c r="E614" s="78"/>
-      <c r="N614" s="79"/>
-      <c r="P614" s="79"/>
+      <c r="A614" s="76"/>
+      <c r="E614" s="76"/>
+      <c r="N614" s="77"/>
+      <c r="P614" s="77"/>
     </row>
     <row r="615" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A615" s="78"/>
-      <c r="E615" s="78"/>
-      <c r="N615" s="79"/>
-      <c r="P615" s="79"/>
+      <c r="A615" s="76"/>
+      <c r="E615" s="76"/>
+      <c r="N615" s="77"/>
+      <c r="P615" s="77"/>
     </row>
     <row r="616" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A616" s="78"/>
-      <c r="E616" s="78"/>
-      <c r="N616" s="79"/>
-      <c r="P616" s="79"/>
+      <c r="A616" s="76"/>
+      <c r="E616" s="76"/>
+      <c r="N616" s="77"/>
+      <c r="P616" s="77"/>
     </row>
     <row r="617" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A617" s="78"/>
-      <c r="E617" s="78"/>
-      <c r="N617" s="79"/>
-      <c r="P617" s="79"/>
+      <c r="A617" s="76"/>
+      <c r="E617" s="76"/>
+      <c r="N617" s="77"/>
+      <c r="P617" s="77"/>
     </row>
     <row r="618" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A618" s="78"/>
-      <c r="E618" s="78"/>
-      <c r="N618" s="79"/>
-      <c r="P618" s="79"/>
+      <c r="A618" s="76"/>
+      <c r="E618" s="76"/>
+      <c r="N618" s="77"/>
+      <c r="P618" s="77"/>
     </row>
     <row r="619" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A619" s="78"/>
-      <c r="E619" s="78"/>
-      <c r="N619" s="79"/>
-      <c r="P619" s="79"/>
+      <c r="A619" s="76"/>
+      <c r="E619" s="76"/>
+      <c r="N619" s="77"/>
+      <c r="P619" s="77"/>
     </row>
     <row r="620" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A620" s="78"/>
-      <c r="E620" s="78"/>
-      <c r="N620" s="79"/>
-      <c r="P620" s="79"/>
+      <c r="A620" s="76"/>
+      <c r="E620" s="76"/>
+      <c r="N620" s="77"/>
+      <c r="P620" s="77"/>
     </row>
     <row r="621" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A621" s="78"/>
-      <c r="E621" s="78"/>
-      <c r="N621" s="79"/>
-      <c r="P621" s="79"/>
+      <c r="A621" s="76"/>
+      <c r="E621" s="76"/>
+      <c r="N621" s="77"/>
+      <c r="P621" s="77"/>
     </row>
     <row r="622" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A622" s="78"/>
-      <c r="E622" s="78"/>
-      <c r="N622" s="79"/>
-      <c r="P622" s="79"/>
+      <c r="A622" s="76"/>
+      <c r="E622" s="76"/>
+      <c r="N622" s="77"/>
+      <c r="P622" s="77"/>
     </row>
     <row r="623" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A623" s="78"/>
-      <c r="E623" s="78"/>
-      <c r="N623" s="79"/>
-      <c r="P623" s="79"/>
+      <c r="A623" s="76"/>
+      <c r="E623" s="76"/>
+      <c r="N623" s="77"/>
+      <c r="P623" s="77"/>
     </row>
     <row r="624" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A624" s="78"/>
-      <c r="E624" s="78"/>
-      <c r="N624" s="79"/>
-      <c r="P624" s="79"/>
+      <c r="A624" s="76"/>
+      <c r="E624" s="76"/>
+      <c r="N624" s="77"/>
+      <c r="P624" s="77"/>
     </row>
     <row r="625" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A625" s="78"/>
-      <c r="E625" s="78"/>
-      <c r="N625" s="79"/>
-      <c r="P625" s="79"/>
+      <c r="A625" s="76"/>
+      <c r="E625" s="76"/>
+      <c r="N625" s="77"/>
+      <c r="P625" s="77"/>
     </row>
     <row r="626" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A626" s="78"/>
-      <c r="E626" s="78"/>
-      <c r="N626" s="79"/>
-      <c r="P626" s="79"/>
+      <c r="A626" s="76"/>
+      <c r="E626" s="76"/>
+      <c r="N626" s="77"/>
+      <c r="P626" s="77"/>
     </row>
     <row r="627" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A627" s="78"/>
-      <c r="E627" s="78"/>
-      <c r="N627" s="79"/>
-      <c r="P627" s="79"/>
+      <c r="A627" s="76"/>
+      <c r="E627" s="76"/>
+      <c r="N627" s="77"/>
+      <c r="P627" s="77"/>
     </row>
     <row r="628" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A628" s="78"/>
-      <c r="E628" s="78"/>
-      <c r="N628" s="79"/>
-      <c r="P628" s="79"/>
+      <c r="A628" s="76"/>
+      <c r="E628" s="76"/>
+      <c r="N628" s="77"/>
+      <c r="P628" s="77"/>
     </row>
     <row r="629" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A629" s="78"/>
-      <c r="E629" s="78"/>
-      <c r="N629" s="79"/>
-      <c r="P629" s="79"/>
+      <c r="A629" s="76"/>
+      <c r="E629" s="76"/>
+      <c r="N629" s="77"/>
+      <c r="P629" s="77"/>
     </row>
     <row r="630" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A630" s="78"/>
-      <c r="E630" s="78"/>
-      <c r="N630" s="79"/>
-      <c r="P630" s="79"/>
+      <c r="A630" s="76"/>
+      <c r="E630" s="76"/>
+      <c r="N630" s="77"/>
+      <c r="P630" s="77"/>
     </row>
     <row r="631" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A631" s="78"/>
-      <c r="E631" s="78"/>
-      <c r="N631" s="79"/>
-      <c r="P631" s="79"/>
+      <c r="A631" s="76"/>
+      <c r="E631" s="76"/>
+      <c r="N631" s="77"/>
+      <c r="P631" s="77"/>
     </row>
     <row r="632" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A632" s="78"/>
-      <c r="E632" s="78"/>
-      <c r="N632" s="79"/>
-      <c r="P632" s="79"/>
+      <c r="A632" s="76"/>
+      <c r="E632" s="76"/>
+      <c r="N632" s="77"/>
+      <c r="P632" s="77"/>
     </row>
     <row r="633" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A633" s="78"/>
-      <c r="E633" s="78"/>
-      <c r="N633" s="79"/>
-      <c r="P633" s="79"/>
+      <c r="A633" s="76"/>
+      <c r="E633" s="76"/>
+      <c r="N633" s="77"/>
+      <c r="P633" s="77"/>
     </row>
     <row r="634" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A634" s="78"/>
-      <c r="E634" s="78"/>
-      <c r="N634" s="79"/>
-      <c r="P634" s="79"/>
+      <c r="A634" s="76"/>
+      <c r="E634" s="76"/>
+      <c r="N634" s="77"/>
+      <c r="P634" s="77"/>
     </row>
     <row r="635" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A635" s="78"/>
-      <c r="E635" s="78"/>
-      <c r="N635" s="79"/>
-      <c r="P635" s="79"/>
+      <c r="A635" s="76"/>
+      <c r="E635" s="76"/>
+      <c r="N635" s="77"/>
+      <c r="P635" s="77"/>
     </row>
     <row r="636" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A636" s="78"/>
-      <c r="E636" s="78"/>
-      <c r="N636" s="79"/>
-      <c r="P636" s="79"/>
+      <c r="A636" s="76"/>
+      <c r="E636" s="76"/>
+      <c r="N636" s="77"/>
+      <c r="P636" s="77"/>
     </row>
     <row r="637" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A637" s="78"/>
-      <c r="E637" s="78"/>
-      <c r="N637" s="79"/>
-      <c r="P637" s="79"/>
+      <c r="A637" s="76"/>
+      <c r="E637" s="76"/>
+      <c r="N637" s="77"/>
+      <c r="P637" s="77"/>
     </row>
     <row r="638" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A638" s="78"/>
-      <c r="E638" s="78"/>
-      <c r="N638" s="79"/>
-      <c r="P638" s="79"/>
+      <c r="A638" s="76"/>
+      <c r="E638" s="76"/>
+      <c r="N638" s="77"/>
+      <c r="P638" s="77"/>
     </row>
     <row r="639" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A639" s="78"/>
-      <c r="E639" s="78"/>
-      <c r="N639" s="79"/>
-      <c r="P639" s="79"/>
+      <c r="A639" s="76"/>
+      <c r="E639" s="76"/>
+      <c r="N639" s="77"/>
+      <c r="P639" s="77"/>
     </row>
     <row r="640" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A640" s="78"/>
-      <c r="E640" s="78"/>
-      <c r="N640" s="79"/>
-      <c r="P640" s="79"/>
+      <c r="A640" s="76"/>
+      <c r="E640" s="76"/>
+      <c r="N640" s="77"/>
+      <c r="P640" s="77"/>
     </row>
     <row r="641" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A641" s="78"/>
-      <c r="E641" s="78"/>
-      <c r="N641" s="79"/>
-      <c r="P641" s="79"/>
+      <c r="A641" s="76"/>
+      <c r="E641" s="76"/>
+      <c r="N641" s="77"/>
+      <c r="P641" s="77"/>
     </row>
     <row r="642" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A642" s="78"/>
-      <c r="E642" s="78"/>
-      <c r="N642" s="79"/>
-      <c r="P642" s="79"/>
+      <c r="A642" s="76"/>
+      <c r="E642" s="76"/>
+      <c r="N642" s="77"/>
+      <c r="P642" s="77"/>
     </row>
     <row r="643" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A643" s="78"/>
-      <c r="E643" s="78"/>
-      <c r="N643" s="79"/>
-      <c r="P643" s="79"/>
+      <c r="A643" s="76"/>
+      <c r="E643" s="76"/>
+      <c r="N643" s="77"/>
+      <c r="P643" s="77"/>
     </row>
     <row r="644" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A644" s="78"/>
-      <c r="E644" s="78"/>
-      <c r="N644" s="79"/>
-      <c r="P644" s="79"/>
+      <c r="A644" s="76"/>
+      <c r="E644" s="76"/>
+      <c r="N644" s="77"/>
+      <c r="P644" s="77"/>
     </row>
     <row r="645" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A645" s="78"/>
-      <c r="E645" s="78"/>
-      <c r="N645" s="79"/>
-      <c r="P645" s="79"/>
+      <c r="A645" s="76"/>
+      <c r="E645" s="76"/>
+      <c r="N645" s="77"/>
+      <c r="P645" s="77"/>
     </row>
     <row r="646" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A646" s="78"/>
-      <c r="E646" s="78"/>
-      <c r="N646" s="79"/>
-      <c r="P646" s="79"/>
+      <c r="A646" s="76"/>
+      <c r="E646" s="76"/>
+      <c r="N646" s="77"/>
+      <c r="P646" s="77"/>
     </row>
     <row r="647" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A647" s="78"/>
-      <c r="E647" s="78"/>
-      <c r="N647" s="79"/>
-      <c r="P647" s="79"/>
+      <c r="A647" s="76"/>
+      <c r="E647" s="76"/>
+      <c r="N647" s="77"/>
+      <c r="P647" s="77"/>
     </row>
     <row r="648" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A648" s="78"/>
-      <c r="E648" s="78"/>
-      <c r="N648" s="79"/>
-      <c r="P648" s="79"/>
+      <c r="A648" s="76"/>
+      <c r="E648" s="76"/>
+      <c r="N648" s="77"/>
+      <c r="P648" s="77"/>
     </row>
     <row r="649" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A649" s="78"/>
-      <c r="E649" s="78"/>
-      <c r="N649" s="79"/>
-      <c r="P649" s="79"/>
+      <c r="A649" s="76"/>
+      <c r="E649" s="76"/>
+      <c r="N649" s="77"/>
+      <c r="P649" s="77"/>
     </row>
     <row r="650" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A650" s="78"/>
-      <c r="E650" s="78"/>
-      <c r="N650" s="79"/>
-      <c r="P650" s="79"/>
+      <c r="A650" s="76"/>
+      <c r="E650" s="76"/>
+      <c r="N650" s="77"/>
+      <c r="P650" s="77"/>
     </row>
     <row r="651" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A651" s="78"/>
-      <c r="E651" s="78"/>
-      <c r="N651" s="79"/>
-      <c r="P651" s="79"/>
+      <c r="A651" s="76"/>
+      <c r="E651" s="76"/>
+      <c r="N651" s="77"/>
+      <c r="P651" s="77"/>
     </row>
     <row r="652" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A652" s="78"/>
-      <c r="E652" s="78"/>
-      <c r="N652" s="79"/>
-      <c r="P652" s="79"/>
+      <c r="A652" s="76"/>
+      <c r="E652" s="76"/>
+      <c r="N652" s="77"/>
+      <c r="P652" s="77"/>
     </row>
     <row r="653" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A653" s="78"/>
-      <c r="E653" s="78"/>
-      <c r="N653" s="79"/>
-      <c r="P653" s="79"/>
+      <c r="A653" s="76"/>
+      <c r="E653" s="76"/>
+      <c r="N653" s="77"/>
+      <c r="P653" s="77"/>
     </row>
     <row r="654" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A654" s="78"/>
-      <c r="E654" s="78"/>
-      <c r="N654" s="79"/>
-      <c r="P654" s="79"/>
+      <c r="A654" s="76"/>
+      <c r="E654" s="76"/>
+      <c r="N654" s="77"/>
+      <c r="P654" s="77"/>
     </row>
     <row r="655" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A655" s="78"/>
-      <c r="E655" s="78"/>
-      <c r="N655" s="79"/>
-      <c r="P655" s="79"/>
+      <c r="A655" s="76"/>
+      <c r="E655" s="76"/>
+      <c r="N655" s="77"/>
+      <c r="P655" s="77"/>
     </row>
     <row r="656" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A656" s="78"/>
-      <c r="E656" s="78"/>
-      <c r="N656" s="79"/>
-      <c r="P656" s="79"/>
+      <c r="A656" s="76"/>
+      <c r="E656" s="76"/>
+      <c r="N656" s="77"/>
+      <c r="P656" s="77"/>
     </row>
     <row r="657" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A657" s="78"/>
-      <c r="E657" s="78"/>
-      <c r="N657" s="79"/>
-      <c r="P657" s="79"/>
+      <c r="A657" s="76"/>
+      <c r="E657" s="76"/>
+      <c r="N657" s="77"/>
+      <c r="P657" s="77"/>
     </row>
     <row r="658" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A658" s="78"/>
-      <c r="E658" s="78"/>
-      <c r="N658" s="79"/>
-      <c r="P658" s="79"/>
+      <c r="A658" s="76"/>
+      <c r="E658" s="76"/>
+      <c r="N658" s="77"/>
+      <c r="P658" s="77"/>
     </row>
     <row r="659" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A659" s="78"/>
-      <c r="E659" s="78"/>
-      <c r="N659" s="79"/>
-      <c r="P659" s="79"/>
+      <c r="A659" s="76"/>
+      <c r="E659" s="76"/>
+      <c r="N659" s="77"/>
+      <c r="P659" s="77"/>
     </row>
     <row r="660" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A660" s="78"/>
-      <c r="E660" s="78"/>
-      <c r="N660" s="79"/>
-      <c r="P660" s="79"/>
+      <c r="A660" s="76"/>
+      <c r="E660" s="76"/>
+      <c r="N660" s="77"/>
+      <c r="P660" s="77"/>
     </row>
     <row r="661" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A661" s="78"/>
-      <c r="E661" s="78"/>
-      <c r="N661" s="79"/>
-      <c r="P661" s="79"/>
+      <c r="A661" s="76"/>
+      <c r="E661" s="76"/>
+      <c r="N661" s="77"/>
+      <c r="P661" s="77"/>
     </row>
     <row r="662" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A662" s="78"/>
-      <c r="E662" s="78"/>
-      <c r="N662" s="79"/>
-      <c r="P662" s="79"/>
+      <c r="A662" s="76"/>
+      <c r="E662" s="76"/>
+      <c r="N662" s="77"/>
+      <c r="P662" s="77"/>
     </row>
     <row r="663" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A663" s="78"/>
-      <c r="E663" s="78"/>
-      <c r="N663" s="79"/>
-      <c r="P663" s="79"/>
+      <c r="A663" s="76"/>
+      <c r="E663" s="76"/>
+      <c r="N663" s="77"/>
+      <c r="P663" s="77"/>
     </row>
     <row r="664" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A664" s="78"/>
-      <c r="E664" s="78"/>
-      <c r="N664" s="79"/>
-      <c r="P664" s="79"/>
+      <c r="A664" s="76"/>
+      <c r="E664" s="76"/>
+      <c r="N664" s="77"/>
+      <c r="P664" s="77"/>
     </row>
     <row r="665" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A665" s="78"/>
-      <c r="E665" s="78"/>
-      <c r="N665" s="79"/>
-      <c r="P665" s="79"/>
+      <c r="A665" s="76"/>
+      <c r="E665" s="76"/>
+      <c r="N665" s="77"/>
+      <c r="P665" s="77"/>
     </row>
     <row r="666" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A666" s="78"/>
-      <c r="E666" s="78"/>
-      <c r="N666" s="79"/>
-      <c r="P666" s="79"/>
+      <c r="A666" s="76"/>
+      <c r="E666" s="76"/>
+      <c r="N666" s="77"/>
+      <c r="P666" s="77"/>
     </row>
     <row r="667" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A667" s="78"/>
-      <c r="E667" s="78"/>
-      <c r="N667" s="79"/>
-      <c r="P667" s="79"/>
+      <c r="A667" s="76"/>
+      <c r="E667" s="76"/>
+      <c r="N667" s="77"/>
+      <c r="P667" s="77"/>
     </row>
     <row r="668" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A668" s="78"/>
-      <c r="E668" s="78"/>
-      <c r="N668" s="79"/>
-      <c r="P668" s="79"/>
+      <c r="A668" s="76"/>
+      <c r="E668" s="76"/>
+      <c r="N668" s="77"/>
+      <c r="P668" s="77"/>
     </row>
     <row r="669" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A669" s="78"/>
-      <c r="E669" s="78"/>
-      <c r="N669" s="79"/>
-      <c r="P669" s="79"/>
+      <c r="A669" s="76"/>
+      <c r="E669" s="76"/>
+      <c r="N669" s="77"/>
+      <c r="P669" s="77"/>
     </row>
     <row r="670" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A670" s="78"/>
-      <c r="E670" s="78"/>
-      <c r="N670" s="79"/>
-      <c r="P670" s="79"/>
+      <c r="A670" s="76"/>
+      <c r="E670" s="76"/>
+      <c r="N670" s="77"/>
+      <c r="P670" s="77"/>
     </row>
     <row r="671" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A671" s="78"/>
-      <c r="E671" s="78"/>
-      <c r="N671" s="79"/>
-      <c r="P671" s="79"/>
+      <c r="A671" s="76"/>
+      <c r="E671" s="76"/>
+      <c r="N671" s="77"/>
+      <c r="P671" s="77"/>
     </row>
     <row r="672" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A672" s="78"/>
-      <c r="E672" s="78"/>
-      <c r="N672" s="79"/>
-      <c r="P672" s="79"/>
+      <c r="A672" s="76"/>
+      <c r="E672" s="76"/>
+      <c r="N672" s="77"/>
+      <c r="P672" s="77"/>
     </row>
     <row r="673" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A673" s="78"/>
-      <c r="E673" s="78"/>
-      <c r="N673" s="79"/>
-      <c r="P673" s="79"/>
+      <c r="A673" s="76"/>
+      <c r="E673" s="76"/>
+      <c r="N673" s="77"/>
+      <c r="P673" s="77"/>
     </row>
     <row r="674" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A674" s="78"/>
-      <c r="E674" s="78"/>
-      <c r="N674" s="79"/>
-      <c r="P674" s="79"/>
+      <c r="A674" s="76"/>
+      <c r="E674" s="76"/>
+      <c r="N674" s="77"/>
+      <c r="P674" s="77"/>
     </row>
     <row r="675" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A675" s="78"/>
-      <c r="E675" s="78"/>
-      <c r="N675" s="79"/>
-      <c r="P675" s="79"/>
+      <c r="A675" s="76"/>
+      <c r="E675" s="76"/>
+      <c r="N675" s="77"/>
+      <c r="P675" s="77"/>
     </row>
     <row r="676" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A676" s="78"/>
-      <c r="E676" s="78"/>
-      <c r="N676" s="79"/>
-      <c r="P676" s="79"/>
+      <c r="A676" s="76"/>
+      <c r="E676" s="76"/>
+      <c r="N676" s="77"/>
+      <c r="P676" s="77"/>
     </row>
     <row r="677" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A677" s="78"/>
-      <c r="E677" s="78"/>
-      <c r="N677" s="79"/>
-      <c r="P677" s="79"/>
+      <c r="A677" s="76"/>
+      <c r="E677" s="76"/>
+      <c r="N677" s="77"/>
+      <c r="P677" s="77"/>
     </row>
     <row r="678" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A678" s="78"/>
-      <c r="E678" s="78"/>
-      <c r="N678" s="79"/>
-      <c r="P678" s="79"/>
+      <c r="A678" s="76"/>
+      <c r="E678" s="76"/>
+      <c r="N678" s="77"/>
+      <c r="P678" s="77"/>
     </row>
     <row r="679" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A679" s="78"/>
-      <c r="E679" s="78"/>
-      <c r="N679" s="79"/>
-      <c r="P679" s="79"/>
+      <c r="A679" s="76"/>
+      <c r="E679" s="76"/>
+      <c r="N679" s="77"/>
+      <c r="P679" s="77"/>
     </row>
     <row r="680" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A680" s="78"/>
-      <c r="E680" s="78"/>
-      <c r="N680" s="79"/>
-      <c r="P680" s="79"/>
+      <c r="A680" s="76"/>
+      <c r="E680" s="76"/>
+      <c r="N680" s="77"/>
+      <c r="P680" s="77"/>
     </row>
     <row r="681" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A681" s="78"/>
-      <c r="E681" s="78"/>
-      <c r="N681" s="79"/>
-      <c r="P681" s="79"/>
+      <c r="A681" s="76"/>
+      <c r="E681" s="76"/>
+      <c r="N681" s="77"/>
+      <c r="P681" s="77"/>
     </row>
     <row r="682" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A682" s="78"/>
-      <c r="E682" s="78"/>
-      <c r="N682" s="79"/>
-      <c r="P682" s="79"/>
+      <c r="A682" s="76"/>
+      <c r="E682" s="76"/>
+      <c r="N682" s="77"/>
+      <c r="P682" s="77"/>
     </row>
     <row r="683" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A683" s="78"/>
-      <c r="E683" s="78"/>
-      <c r="N683" s="79"/>
-      <c r="P683" s="79"/>
+      <c r="A683" s="76"/>
+      <c r="E683" s="76"/>
+      <c r="N683" s="77"/>
+      <c r="P683" s="77"/>
     </row>
     <row r="684" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A684" s="78"/>
-      <c r="E684" s="78"/>
-      <c r="N684" s="79"/>
-      <c r="P684" s="79"/>
+      <c r="A684" s="76"/>
+      <c r="E684" s="76"/>
+      <c r="N684" s="77"/>
+      <c r="P684" s="77"/>
     </row>
     <row r="685" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A685" s="78"/>
-      <c r="E685" s="78"/>
-      <c r="N685" s="79"/>
-      <c r="P685" s="79"/>
+      <c r="A685" s="76"/>
+      <c r="E685" s="76"/>
+      <c r="N685" s="77"/>
+      <c r="P685" s="77"/>
     </row>
     <row r="686" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A686" s="78"/>
-      <c r="E686" s="78"/>
-      <c r="N686" s="79"/>
-      <c r="P686" s="79"/>
+      <c r="A686" s="76"/>
+      <c r="E686" s="76"/>
+      <c r="N686" s="77"/>
+      <c r="P686" s="77"/>
     </row>
     <row r="687" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A687" s="78"/>
-      <c r="E687" s="78"/>
-      <c r="N687" s="79"/>
-      <c r="P687" s="79"/>
+      <c r="A687" s="76"/>
+      <c r="E687" s="76"/>
+      <c r="N687" s="77"/>
+      <c r="P687" s="77"/>
     </row>
     <row r="688" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A688" s="78"/>
-      <c r="E688" s="78"/>
-      <c r="N688" s="79"/>
-      <c r="P688" s="79"/>
+      <c r="A688" s="76"/>
+      <c r="E688" s="76"/>
+      <c r="N688" s="77"/>
+      <c r="P688" s="77"/>
     </row>
     <row r="689" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A689" s="78"/>
-      <c r="E689" s="78"/>
-      <c r="N689" s="79"/>
-      <c r="P689" s="79"/>
+      <c r="A689" s="76"/>
+      <c r="E689" s="76"/>
+      <c r="N689" s="77"/>
+      <c r="P689" s="77"/>
     </row>
     <row r="690" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A690" s="78"/>
-      <c r="E690" s="78"/>
-      <c r="N690" s="79"/>
-      <c r="P690" s="79"/>
+      <c r="A690" s="76"/>
+      <c r="E690" s="76"/>
+      <c r="N690" s="77"/>
+      <c r="P690" s="77"/>
     </row>
     <row r="691" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A691" s="78"/>
-      <c r="E691" s="78"/>
-      <c r="N691" s="79"/>
-      <c r="P691" s="79"/>
+      <c r="A691" s="76"/>
+      <c r="E691" s="76"/>
+      <c r="N691" s="77"/>
+      <c r="P691" s="77"/>
     </row>
     <row r="692" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A692" s="78"/>
-      <c r="E692" s="78"/>
-      <c r="N692" s="79"/>
-      <c r="P692" s="79"/>
+      <c r="A692" s="76"/>
+      <c r="E692" s="76"/>
+      <c r="N692" s="77"/>
+      <c r="P692" s="77"/>
     </row>
     <row r="693" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A693" s="78"/>
-      <c r="E693" s="78"/>
-      <c r="N693" s="79"/>
-      <c r="P693" s="79"/>
+      <c r="A693" s="76"/>
+      <c r="E693" s="76"/>
+      <c r="N693" s="77"/>
+      <c r="P693" s="77"/>
     </row>
     <row r="694" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A694" s="78"/>
-      <c r="E694" s="78"/>
-      <c r="N694" s="79"/>
-      <c r="P694" s="79"/>
+      <c r="A694" s="76"/>
+      <c r="E694" s="76"/>
+      <c r="N694" s="77"/>
+      <c r="P694" s="77"/>
     </row>
     <row r="695" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A695" s="78"/>
-      <c r="E695" s="78"/>
-      <c r="N695" s="79"/>
-      <c r="P695" s="79"/>
+      <c r="A695" s="76"/>
+      <c r="E695" s="76"/>
+      <c r="N695" s="77"/>
+      <c r="P695" s="77"/>
     </row>
     <row r="696" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A696" s="78"/>
-      <c r="E696" s="78"/>
-      <c r="N696" s="79"/>
-      <c r="P696" s="79"/>
+      <c r="A696" s="76"/>
+      <c r="E696" s="76"/>
+      <c r="N696" s="77"/>
+      <c r="P696" s="77"/>
     </row>
     <row r="697" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A697" s="78"/>
-      <c r="E697" s="78"/>
-      <c r="N697" s="79"/>
-      <c r="P697" s="79"/>
+      <c r="A697" s="76"/>
+      <c r="E697" s="76"/>
+      <c r="N697" s="77"/>
+      <c r="P697" s="77"/>
     </row>
     <row r="698" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A698" s="78"/>
-      <c r="E698" s="78"/>
-      <c r="N698" s="79"/>
-      <c r="P698" s="79"/>
+      <c r="A698" s="76"/>
+      <c r="E698" s="76"/>
+      <c r="N698" s="77"/>
+      <c r="P698" s="77"/>
     </row>
     <row r="699" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A699" s="78"/>
-      <c r="E699" s="78"/>
-      <c r="N699" s="79"/>
-      <c r="P699" s="79"/>
+      <c r="A699" s="76"/>
+      <c r="E699" s="76"/>
+      <c r="N699" s="77"/>
+      <c r="P699" s="77"/>
     </row>
     <row r="700" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A700" s="78"/>
-      <c r="E700" s="78"/>
-      <c r="N700" s="79"/>
-      <c r="P700" s="79"/>
+      <c r="A700" s="76"/>
+      <c r="E700" s="76"/>
+      <c r="N700" s="77"/>
+      <c r="P700" s="77"/>
     </row>
     <row r="701" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A701" s="78"/>
-      <c r="E701" s="78"/>
-      <c r="N701" s="79"/>
-      <c r="P701" s="79"/>
+      <c r="A701" s="76"/>
+      <c r="E701" s="76"/>
+      <c r="N701" s="77"/>
+      <c r="P701" s="77"/>
     </row>
     <row r="702" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A702" s="78"/>
-      <c r="E702" s="78"/>
-      <c r="N702" s="79"/>
-      <c r="P702" s="79"/>
+      <c r="A702" s="76"/>
+      <c r="E702" s="76"/>
+      <c r="N702" s="77"/>
+      <c r="P702" s="77"/>
     </row>
     <row r="703" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A703" s="78"/>
-      <c r="E703" s="78"/>
-      <c r="N703" s="79"/>
-      <c r="P703" s="79"/>
+      <c r="A703" s="76"/>
+      <c r="E703" s="76"/>
+      <c r="N703" s="77"/>
+      <c r="P703" s="77"/>
     </row>
     <row r="704" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A704" s="78"/>
-      <c r="E704" s="78"/>
-      <c r="N704" s="79"/>
-      <c r="P704" s="79"/>
+      <c r="A704" s="76"/>
+      <c r="E704" s="76"/>
+      <c r="N704" s="77"/>
+      <c r="P704" s="77"/>
     </row>
     <row r="705" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A705" s="78"/>
-      <c r="E705" s="78"/>
-      <c r="N705" s="79"/>
-      <c r="P705" s="79"/>
+      <c r="A705" s="76"/>
+      <c r="E705" s="76"/>
+      <c r="N705" s="77"/>
+      <c r="P705" s="77"/>
     </row>
     <row r="706" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A706" s="78"/>
-      <c r="E706" s="78"/>
-      <c r="N706" s="79"/>
-      <c r="P706" s="79"/>
+      <c r="A706" s="76"/>
+      <c r="E706" s="76"/>
+      <c r="N706" s="77"/>
+      <c r="P706" s="77"/>
     </row>
     <row r="707" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A707" s="78"/>
-      <c r="E707" s="78"/>
-      <c r="N707" s="79"/>
-      <c r="P707" s="79"/>
+      <c r="A707" s="76"/>
+      <c r="E707" s="76"/>
+      <c r="N707" s="77"/>
+      <c r="P707" s="77"/>
     </row>
     <row r="708" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A708" s="78"/>
-      <c r="E708" s="78"/>
-      <c r="N708" s="79"/>
-      <c r="P708" s="79"/>
+      <c r="A708" s="76"/>
+      <c r="E708" s="76"/>
+      <c r="N708" s="77"/>
+      <c r="P708" s="77"/>
     </row>
     <row r="709" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A709" s="78"/>
-      <c r="E709" s="78"/>
-      <c r="N709" s="79"/>
-      <c r="P709" s="79"/>
+      <c r="A709" s="76"/>
+      <c r="E709" s="76"/>
+      <c r="N709" s="77"/>
+      <c r="P709" s="77"/>
     </row>
     <row r="710" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A710" s="78"/>
-      <c r="E710" s="78"/>
-      <c r="N710" s="79"/>
-      <c r="P710" s="79"/>
+      <c r="A710" s="76"/>
+      <c r="E710" s="76"/>
+      <c r="N710" s="77"/>
+      <c r="P710" s="77"/>
     </row>
     <row r="711" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A711" s="78"/>
-      <c r="E711" s="78"/>
-      <c r="N711" s="79"/>
-      <c r="P711" s="79"/>
+      <c r="A711" s="76"/>
+      <c r="E711" s="76"/>
+      <c r="N711" s="77"/>
+      <c r="P711" s="77"/>
     </row>
     <row r="712" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A712" s="78"/>
-      <c r="E712" s="78"/>
-      <c r="N712" s="79"/>
-      <c r="P712" s="79"/>
+      <c r="A712" s="76"/>
+      <c r="E712" s="76"/>
+      <c r="N712" s="77"/>
+      <c r="P712" s="77"/>
     </row>
     <row r="713" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A713" s="78"/>
-      <c r="E713" s="78"/>
-      <c r="N713" s="79"/>
-      <c r="P713" s="79"/>
+      <c r="A713" s="76"/>
+      <c r="E713" s="76"/>
+      <c r="N713" s="77"/>
+      <c r="P713" s="77"/>
     </row>
     <row r="714" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A714" s="78"/>
-      <c r="E714" s="78"/>
-      <c r="N714" s="79"/>
-      <c r="P714" s="79"/>
+      <c r="A714" s="76"/>
+      <c r="E714" s="76"/>
+      <c r="N714" s="77"/>
+      <c r="P714" s="77"/>
     </row>
     <row r="715" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A715" s="78"/>
-      <c r="E715" s="78"/>
-      <c r="N715" s="79"/>
-      <c r="P715" s="79"/>
+      <c r="A715" s="76"/>
+      <c r="E715" s="76"/>
+      <c r="N715" s="77"/>
+      <c r="P715" s="77"/>
     </row>
     <row r="716" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A716" s="78"/>
-      <c r="E716" s="78"/>
-      <c r="N716" s="79"/>
-      <c r="P716" s="79"/>
+      <c r="A716" s="76"/>
+      <c r="E716" s="76"/>
+      <c r="N716" s="77"/>
+      <c r="P716" s="77"/>
     </row>
     <row r="717" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A717" s="78"/>
-      <c r="E717" s="78"/>
-      <c r="N717" s="79"/>
-      <c r="P717" s="79"/>
+      <c r="A717" s="76"/>
+      <c r="E717" s="76"/>
+      <c r="N717" s="77"/>
+      <c r="P717" s="77"/>
     </row>
     <row r="718" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A718" s="78"/>
-      <c r="E718" s="78"/>
-      <c r="N718" s="79"/>
-      <c r="P718" s="79"/>
+      <c r="A718" s="76"/>
+      <c r="E718" s="76"/>
+      <c r="N718" s="77"/>
+      <c r="P718" s="77"/>
     </row>
     <row r="719" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A719" s="78"/>
-      <c r="E719" s="78"/>
-      <c r="N719" s="79"/>
-      <c r="P719" s="79"/>
+      <c r="A719" s="76"/>
+      <c r="E719" s="76"/>
+      <c r="N719" s="77"/>
+      <c r="P719" s="77"/>
     </row>
     <row r="720" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A720" s="78"/>
-      <c r="E720" s="78"/>
-      <c r="N720" s="79"/>
-      <c r="P720" s="79"/>
+      <c r="A720" s="76"/>
+      <c r="E720" s="76"/>
+      <c r="N720" s="77"/>
+      <c r="P720" s="77"/>
     </row>
     <row r="721" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A721" s="78"/>
-      <c r="E721" s="78"/>
-      <c r="N721" s="79"/>
-      <c r="P721" s="79"/>
+      <c r="A721" s="76"/>
+      <c r="E721" s="76"/>
+      <c r="N721" s="77"/>
+      <c r="P721" s="77"/>
     </row>
     <row r="722" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A722" s="78"/>
-      <c r="E722" s="78"/>
-      <c r="N722" s="79"/>
-      <c r="P722" s="79"/>
+      <c r="A722" s="76"/>
+      <c r="E722" s="76"/>
+      <c r="N722" s="77"/>
+      <c r="P722" s="77"/>
     </row>
     <row r="723" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A723" s="78"/>
-      <c r="E723" s="78"/>
-      <c r="N723" s="79"/>
-      <c r="P723" s="79"/>
+      <c r="A723" s="76"/>
+      <c r="E723" s="76"/>
+      <c r="N723" s="77"/>
+      <c r="P723" s="77"/>
     </row>
     <row r="724" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A724" s="78"/>
-      <c r="E724" s="78"/>
-      <c r="N724" s="79"/>
-      <c r="P724" s="79"/>
+      <c r="A724" s="76"/>
+      <c r="E724" s="76"/>
+      <c r="N724" s="77"/>
+      <c r="P724" s="77"/>
     </row>
     <row r="725" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A725" s="78"/>
-      <c r="E725" s="78"/>
-      <c r="N725" s="79"/>
-      <c r="P725" s="79"/>
+      <c r="A725" s="76"/>
+      <c r="E725" s="76"/>
+      <c r="N725" s="77"/>
+      <c r="P725" s="77"/>
     </row>
     <row r="726" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A726" s="78"/>
-      <c r="E726" s="78"/>
-      <c r="N726" s="79"/>
-      <c r="P726" s="79"/>
+      <c r="A726" s="76"/>
+      <c r="E726" s="76"/>
+      <c r="N726" s="77"/>
+      <c r="P726" s="77"/>
     </row>
     <row r="727" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A727" s="78"/>
-      <c r="E727" s="78"/>
-      <c r="N727" s="79"/>
-      <c r="P727" s="79"/>
+      <c r="A727" s="76"/>
+      <c r="E727" s="76"/>
+      <c r="N727" s="77"/>
+      <c r="P727" s="77"/>
     </row>
     <row r="728" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A728" s="78"/>
-      <c r="E728" s="78"/>
-      <c r="N728" s="79"/>
-      <c r="P728" s="79"/>
+      <c r="A728" s="76"/>
+      <c r="E728" s="76"/>
+      <c r="N728" s="77"/>
+      <c r="P728" s="77"/>
     </row>
     <row r="729" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A729" s="78"/>
-      <c r="E729" s="78"/>
-      <c r="N729" s="79"/>
-      <c r="P729" s="79"/>
+      <c r="A729" s="76"/>
+      <c r="E729" s="76"/>
+      <c r="N729" s="77"/>
+      <c r="P729" s="77"/>
     </row>
     <row r="730" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A730" s="78"/>
-      <c r="E730" s="78"/>
-      <c r="N730" s="79"/>
-      <c r="P730" s="79"/>
+      <c r="A730" s="76"/>
+      <c r="E730" s="76"/>
+      <c r="N730" s="77"/>
+      <c r="P730" s="77"/>
     </row>
     <row r="731" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A731" s="78"/>
-      <c r="E731" s="78"/>
-      <c r="N731" s="79"/>
-      <c r="P731" s="79"/>
+      <c r="A731" s="76"/>
+      <c r="E731" s="76"/>
+      <c r="N731" s="77"/>
+      <c r="P731" s="77"/>
     </row>
     <row r="732" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A732" s="78"/>
-      <c r="E732" s="78"/>
-      <c r="N732" s="79"/>
-      <c r="P732" s="79"/>
+      <c r="A732" s="76"/>
+      <c r="E732" s="76"/>
+      <c r="N732" s="77"/>
+      <c r="P732" s="77"/>
     </row>
     <row r="733" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A733" s="78"/>
-      <c r="E733" s="78"/>
-      <c r="N733" s="79"/>
-      <c r="P733" s="79"/>
+      <c r="A733" s="76"/>
+      <c r="E733" s="76"/>
+      <c r="N733" s="77"/>
+      <c r="P733" s="77"/>
     </row>
     <row r="734" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A734" s="78"/>
-      <c r="E734" s="78"/>
-      <c r="N734" s="79"/>
-      <c r="P734" s="79"/>
+      <c r="A734" s="76"/>
+      <c r="E734" s="76"/>
+      <c r="N734" s="77"/>
+      <c r="P734" s="77"/>
     </row>
     <row r="735" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A735" s="78"/>
-      <c r="E735" s="78"/>
-      <c r="N735" s="79"/>
-      <c r="P735" s="79"/>
+      <c r="A735" s="76"/>
+      <c r="E735" s="76"/>
+      <c r="N735" s="77"/>
+      <c r="P735" s="77"/>
     </row>
     <row r="736" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A736" s="78"/>
-      <c r="E736" s="78"/>
-      <c r="N736" s="79"/>
-      <c r="P736" s="79"/>
+      <c r="A736" s="76"/>
+      <c r="E736" s="76"/>
+      <c r="N736" s="77"/>
+      <c r="P736" s="77"/>
     </row>
     <row r="737" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A737" s="78"/>
-      <c r="E737" s="78"/>
-      <c r="N737" s="79"/>
-      <c r="P737" s="79"/>
+      <c r="A737" s="76"/>
+      <c r="E737" s="76"/>
+      <c r="N737" s="77"/>
+      <c r="P737" s="77"/>
     </row>
     <row r="738" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A738" s="78"/>
-      <c r="E738" s="78"/>
-      <c r="N738" s="79"/>
-      <c r="P738" s="79"/>
+      <c r="A738" s="76"/>
+      <c r="E738" s="76"/>
+      <c r="N738" s="77"/>
+      <c r="P738" s="77"/>
     </row>
     <row r="739" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A739" s="78"/>
-      <c r="E739" s="78"/>
-      <c r="N739" s="79"/>
-      <c r="P739" s="79"/>
+      <c r="A739" s="76"/>
+      <c r="E739" s="76"/>
+      <c r="N739" s="77"/>
+      <c r="P739" s="77"/>
     </row>
     <row r="740" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A740" s="78"/>
-      <c r="E740" s="78"/>
-      <c r="N740" s="79"/>
-      <c r="P740" s="79"/>
+      <c r="A740" s="76"/>
+      <c r="E740" s="76"/>
+      <c r="N740" s="77"/>
+      <c r="P740" s="77"/>
     </row>
     <row r="741" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A741" s="78"/>
-      <c r="E741" s="78"/>
-      <c r="N741" s="79"/>
-      <c r="P741" s="79"/>
+      <c r="A741" s="76"/>
+      <c r="E741" s="76"/>
+      <c r="N741" s="77"/>
+      <c r="P741" s="77"/>
     </row>
     <row r="742" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A742" s="78"/>
-      <c r="E742" s="78"/>
-      <c r="N742" s="79"/>
-      <c r="P742" s="79"/>
+      <c r="A742" s="76"/>
+      <c r="E742" s="76"/>
+      <c r="N742" s="77"/>
+      <c r="P742" s="77"/>
     </row>
     <row r="743" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A743" s="78"/>
-      <c r="E743" s="78"/>
-      <c r="N743" s="79"/>
-      <c r="P743" s="79"/>
+      <c r="A743" s="76"/>
+      <c r="E743" s="76"/>
+      <c r="N743" s="77"/>
+      <c r="P743" s="77"/>
     </row>
     <row r="744" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A744" s="78"/>
-      <c r="E744" s="78"/>
-      <c r="N744" s="79"/>
-      <c r="P744" s="79"/>
+      <c r="A744" s="76"/>
+      <c r="E744" s="76"/>
+      <c r="N744" s="77"/>
+      <c r="P744" s="77"/>
     </row>
     <row r="745" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A745" s="78"/>
-      <c r="E745" s="78"/>
-      <c r="N745" s="79"/>
-      <c r="P745" s="79"/>
+      <c r="A745" s="76"/>
+      <c r="E745" s="76"/>
+      <c r="N745" s="77"/>
+      <c r="P745" s="77"/>
     </row>
     <row r="746" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A746" s="78"/>
-      <c r="E746" s="78"/>
-      <c r="N746" s="79"/>
-      <c r="P746" s="79"/>
+      <c r="A746" s="76"/>
+      <c r="E746" s="76"/>
+      <c r="N746" s="77"/>
+      <c r="P746" s="77"/>
     </row>
     <row r="747" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A747" s="78"/>
-      <c r="E747" s="78"/>
-      <c r="N747" s="79"/>
-      <c r="P747" s="79"/>
+      <c r="A747" s="76"/>
+      <c r="E747" s="76"/>
+      <c r="N747" s="77"/>
+      <c r="P747" s="77"/>
     </row>
     <row r="748" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A748" s="78"/>
-      <c r="E748" s="78"/>
-      <c r="N748" s="79"/>
-      <c r="P748" s="79"/>
+      <c r="A748" s="76"/>
+      <c r="E748" s="76"/>
+      <c r="N748" s="77"/>
+      <c r="P748" s="77"/>
     </row>
     <row r="749" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A749" s="78"/>
-      <c r="E749" s="78"/>
-      <c r="N749" s="79"/>
-      <c r="P749" s="79"/>
+      <c r="A749" s="76"/>
+      <c r="E749" s="76"/>
+      <c r="N749" s="77"/>
+      <c r="P749" s="77"/>
     </row>
     <row r="750" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A750" s="78"/>
-      <c r="E750" s="78"/>
-      <c r="N750" s="79"/>
-      <c r="P750" s="79"/>
+      <c r="A750" s="76"/>
+      <c r="E750" s="76"/>
+      <c r="N750" s="77"/>
+      <c r="P750" s="77"/>
     </row>
     <row r="751" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A751" s="78"/>
-      <c r="E751" s="78"/>
-      <c r="N751" s="79"/>
-      <c r="P751" s="79"/>
+      <c r="A751" s="76"/>
+      <c r="E751" s="76"/>
+      <c r="N751" s="77"/>
+      <c r="P751" s="77"/>
     </row>
     <row r="752" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A752" s="78"/>
-      <c r="E752" s="78"/>
-      <c r="N752" s="79"/>
-      <c r="P752" s="79"/>
+      <c r="A752" s="76"/>
+      <c r="E752" s="76"/>
+      <c r="N752" s="77"/>
+      <c r="P752" s="77"/>
     </row>
     <row r="753" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A753" s="78"/>
-      <c r="E753" s="78"/>
-      <c r="N753" s="79"/>
-      <c r="P753" s="79"/>
+      <c r="A753" s="76"/>
+      <c r="E753" s="76"/>
+      <c r="N753" s="77"/>
+      <c r="P753" s="77"/>
     </row>
     <row r="754" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A754" s="78"/>
-      <c r="E754" s="78"/>
-      <c r="N754" s="79"/>
-      <c r="P754" s="79"/>
+      <c r="A754" s="76"/>
+      <c r="E754" s="76"/>
+      <c r="N754" s="77"/>
+      <c r="P754" s="77"/>
     </row>
     <row r="755" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A755" s="78"/>
-      <c r="E755" s="78"/>
-      <c r="N755" s="79"/>
-      <c r="P755" s="79"/>
+      <c r="A755" s="76"/>
+      <c r="E755" s="76"/>
+      <c r="N755" s="77"/>
+      <c r="P755" s="77"/>
     </row>
     <row r="756" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A756" s="78"/>
-      <c r="E756" s="78"/>
-      <c r="N756" s="79"/>
-      <c r="P756" s="79"/>
+      <c r="A756" s="76"/>
+      <c r="E756" s="76"/>
+      <c r="N756" s="77"/>
+      <c r="P756" s="77"/>
     </row>
     <row r="757" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A757" s="78"/>
-      <c r="E757" s="78"/>
-      <c r="N757" s="79"/>
-      <c r="P757" s="79"/>
+      <c r="A757" s="76"/>
+      <c r="E757" s="76"/>
+      <c r="N757" s="77"/>
+      <c r="P757" s="77"/>
     </row>
     <row r="758" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A758" s="78"/>
-      <c r="E758" s="78"/>
-      <c r="N758" s="79"/>
-      <c r="P758" s="79"/>
+      <c r="A758" s="76"/>
+      <c r="E758" s="76"/>
+      <c r="N758" s="77"/>
+      <c r="P758" s="77"/>
     </row>
     <row r="759" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A759" s="78"/>
-      <c r="E759" s="78"/>
-      <c r="N759" s="79"/>
-      <c r="P759" s="79"/>
+      <c r="A759" s="76"/>
+      <c r="E759" s="76"/>
+      <c r="N759" s="77"/>
+      <c r="P759" s="77"/>
     </row>
     <row r="760" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A760" s="78"/>
-      <c r="E760" s="78"/>
-      <c r="N760" s="79"/>
-      <c r="P760" s="79"/>
+      <c r="A760" s="76"/>
+      <c r="E760" s="76"/>
+      <c r="N760" s="77"/>
+      <c r="P760" s="77"/>
     </row>
     <row r="761" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A761" s="78"/>
-      <c r="E761" s="78"/>
-      <c r="N761" s="79"/>
-      <c r="P761" s="79"/>
+      <c r="A761" s="76"/>
+      <c r="E761" s="76"/>
+      <c r="N761" s="77"/>
+      <c r="P761" s="77"/>
     </row>
     <row r="762" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A762" s="78"/>
-      <c r="E762" s="78"/>
-      <c r="N762" s="79"/>
-      <c r="P762" s="79"/>
+      <c r="A762" s="76"/>
+      <c r="E762" s="76"/>
+      <c r="N762" s="77"/>
+      <c r="P762" s="77"/>
     </row>
     <row r="763" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A763" s="78"/>
-      <c r="E763" s="78"/>
-      <c r="N763" s="79"/>
-      <c r="P763" s="79"/>
+      <c r="A763" s="76"/>
+      <c r="E763" s="76"/>
+      <c r="N763" s="77"/>
+      <c r="P763" s="77"/>
     </row>
     <row r="764" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A764" s="78"/>
-      <c r="E764" s="78"/>
-      <c r="N764" s="79"/>
-      <c r="P764" s="79"/>
+      <c r="A764" s="76"/>
+      <c r="E764" s="76"/>
+      <c r="N764" s="77"/>
+      <c r="P764" s="77"/>
     </row>
     <row r="765" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A765" s="78"/>
-      <c r="E765" s="78"/>
-      <c r="N765" s="79"/>
-      <c r="P765" s="79"/>
+      <c r="A765" s="76"/>
+      <c r="E765" s="76"/>
+      <c r="N765" s="77"/>
+      <c r="P765" s="77"/>
     </row>
     <row r="766" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A766" s="78"/>
-      <c r="E766" s="78"/>
-      <c r="N766" s="79"/>
-      <c r="P766" s="79"/>
+      <c r="A766" s="76"/>
+      <c r="E766" s="76"/>
+      <c r="N766" s="77"/>
+      <c r="P766" s="77"/>
     </row>
     <row r="767" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A767" s="78"/>
-      <c r="E767" s="78"/>
-      <c r="N767" s="79"/>
-      <c r="P767" s="79"/>
+      <c r="A767" s="76"/>
+      <c r="E767" s="76"/>
+      <c r="N767" s="77"/>
+      <c r="P767" s="77"/>
     </row>
     <row r="768" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A768" s="78"/>
-      <c r="E768" s="78"/>
-      <c r="N768" s="79"/>
-      <c r="P768" s="79"/>
+      <c r="A768" s="76"/>
+      <c r="E768" s="76"/>
+      <c r="N768" s="77"/>
+      <c r="P768" s="77"/>
     </row>
     <row r="769" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A769" s="78"/>
-      <c r="E769" s="78"/>
-      <c r="N769" s="79"/>
-      <c r="P769" s="79"/>
+      <c r="A769" s="76"/>
+      <c r="E769" s="76"/>
+      <c r="N769" s="77"/>
+      <c r="P769" s="77"/>
     </row>
     <row r="770" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A770" s="78"/>
-      <c r="E770" s="78"/>
-      <c r="N770" s="79"/>
-      <c r="P770" s="79"/>
+      <c r="A770" s="76"/>
+      <c r="E770" s="76"/>
+      <c r="N770" s="77"/>
+      <c r="P770" s="77"/>
     </row>
     <row r="771" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A771" s="78"/>
-      <c r="E771" s="78"/>
-      <c r="N771" s="79"/>
-      <c r="P771" s="79"/>
+      <c r="A771" s="76"/>
+      <c r="E771" s="76"/>
+      <c r="N771" s="77"/>
+      <c r="P771" s="77"/>
     </row>
     <row r="772" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A772" s="78"/>
-      <c r="E772" s="78"/>
-      <c r="N772" s="79"/>
-      <c r="P772" s="79"/>
+      <c r="A772" s="76"/>
+      <c r="E772" s="76"/>
+      <c r="N772" s="77"/>
+      <c r="P772" s="77"/>
     </row>
     <row r="773" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A773" s="78"/>
-      <c r="E773" s="78"/>
-      <c r="N773" s="79"/>
-      <c r="P773" s="79"/>
+      <c r="A773" s="76"/>
+      <c r="E773" s="76"/>
+      <c r="N773" s="77"/>
+      <c r="P773" s="77"/>
     </row>
     <row r="774" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A774" s="78"/>
-      <c r="E774" s="78"/>
-      <c r="N774" s="79"/>
-      <c r="P774" s="79"/>
+      <c r="A774" s="76"/>
+      <c r="E774" s="76"/>
+      <c r="N774" s="77"/>
+      <c r="P774" s="77"/>
     </row>
     <row r="775" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A775" s="78"/>
-      <c r="E775" s="78"/>
-      <c r="N775" s="79"/>
-      <c r="P775" s="79"/>
+      <c r="A775" s="76"/>
+      <c r="E775" s="76"/>
+      <c r="N775" s="77"/>
+      <c r="P775" s="77"/>
     </row>
     <row r="776" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A776" s="78"/>
-      <c r="E776" s="78"/>
-      <c r="N776" s="79"/>
-      <c r="P776" s="79"/>
+      <c r="A776" s="76"/>
+      <c r="E776" s="76"/>
+      <c r="N776" s="77"/>
+      <c r="P776" s="77"/>
     </row>
     <row r="777" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A777" s="78"/>
-      <c r="E777" s="78"/>
-      <c r="N777" s="79"/>
-      <c r="P777" s="79"/>
+      <c r="A777" s="76"/>
+      <c r="E777" s="76"/>
+      <c r="N777" s="77"/>
+      <c r="P777" s="77"/>
     </row>
     <row r="778" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A778" s="78"/>
-      <c r="E778" s="78"/>
-      <c r="N778" s="79"/>
-      <c r="P778" s="79"/>
+      <c r="A778" s="76"/>
+      <c r="E778" s="76"/>
+      <c r="N778" s="77"/>
+      <c r="P778" s="77"/>
     </row>
     <row r="779" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A779" s="78"/>
-      <c r="E779" s="78"/>
-      <c r="N779" s="79"/>
-      <c r="P779" s="79"/>
+      <c r="A779" s="76"/>
+      <c r="E779" s="76"/>
+      <c r="N779" s="77"/>
+      <c r="P779" s="77"/>
     </row>
     <row r="780" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A780" s="78"/>
-      <c r="E780" s="78"/>
-      <c r="N780" s="79"/>
-      <c r="P780" s="79"/>
+      <c r="A780" s="76"/>
+      <c r="E780" s="76"/>
+      <c r="N780" s="77"/>
+      <c r="P780" s="77"/>
     </row>
     <row r="781" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A781" s="78"/>
-      <c r="E781" s="78"/>
-      <c r="N781" s="79"/>
-      <c r="P781" s="79"/>
+      <c r="A781" s="76"/>
+      <c r="E781" s="76"/>
+      <c r="N781" s="77"/>
+      <c r="P781" s="77"/>
     </row>
     <row r="782" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A782" s="78"/>
-      <c r="E782" s="78"/>
-      <c r="N782" s="79"/>
-      <c r="P782" s="79"/>
+      <c r="A782" s="76"/>
+      <c r="E782" s="76"/>
+      <c r="N782" s="77"/>
+      <c r="P782" s="77"/>
     </row>
     <row r="783" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A783" s="78"/>
-      <c r="E783" s="78"/>
-      <c r="N783" s="79"/>
-      <c r="P783" s="79"/>
+      <c r="A783" s="76"/>
+      <c r="E783" s="76"/>
+      <c r="N783" s="77"/>
+      <c r="P783" s="77"/>
     </row>
     <row r="784" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A784" s="78"/>
-      <c r="E784" s="78"/>
-      <c r="N784" s="79"/>
-      <c r="P784" s="79"/>
+      <c r="A784" s="76"/>
+      <c r="E784" s="76"/>
+      <c r="N784" s="77"/>
+      <c r="P784" s="77"/>
     </row>
     <row r="785" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A785" s="78"/>
-      <c r="E785" s="78"/>
-      <c r="N785" s="79"/>
-      <c r="P785" s="79"/>
+      <c r="A785" s="76"/>
+      <c r="E785" s="76"/>
+      <c r="N785" s="77"/>
+      <c r="P785" s="77"/>
     </row>
     <row r="786" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A786" s="78"/>
-      <c r="E786" s="78"/>
-      <c r="N786" s="79"/>
-      <c r="P786" s="79"/>
+      <c r="A786" s="76"/>
+      <c r="E786" s="76"/>
+      <c r="N786" s="77"/>
+      <c r="P786" s="77"/>
     </row>
     <row r="787" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A787" s="78"/>
-      <c r="E787" s="78"/>
-      <c r="N787" s="79"/>
-      <c r="P787" s="79"/>
+      <c r="A787" s="76"/>
+      <c r="E787" s="76"/>
+      <c r="N787" s="77"/>
+      <c r="P787" s="77"/>
     </row>
     <row r="788" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A788" s="78"/>
-      <c r="E788" s="78"/>
-      <c r="N788" s="79"/>
-      <c r="P788" s="79"/>
+      <c r="A788" s="76"/>
+      <c r="E788" s="76"/>
+      <c r="N788" s="77"/>
+      <c r="P788" s="77"/>
     </row>
     <row r="789" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A789" s="78"/>
-      <c r="E789" s="78"/>
-      <c r="N789" s="79"/>
-      <c r="P789" s="79"/>
+      <c r="A789" s="76"/>
+      <c r="E789" s="76"/>
+      <c r="N789" s="77"/>
+      <c r="P789" s="77"/>
     </row>
     <row r="790" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A790" s="78"/>
-      <c r="E790" s="78"/>
-      <c r="N790" s="79"/>
-      <c r="P790" s="79"/>
+      <c r="A790" s="76"/>
+      <c r="E790" s="76"/>
+      <c r="N790" s="77"/>
+      <c r="P790" s="77"/>
     </row>
     <row r="791" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A791" s="78"/>
-      <c r="E791" s="78"/>
-      <c r="N791" s="79"/>
-      <c r="P791" s="79"/>
+      <c r="A791" s="76"/>
+      <c r="E791" s="76"/>
+      <c r="N791" s="77"/>
+      <c r="P791" s="77"/>
     </row>
     <row r="792" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A792" s="78"/>
-      <c r="E792" s="78"/>
-      <c r="N792" s="79"/>
-      <c r="P792" s="79"/>
+      <c r="A792" s="76"/>
+      <c r="E792" s="76"/>
+      <c r="N792" s="77"/>
+      <c r="P792" s="77"/>
     </row>
     <row r="793" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A793" s="78"/>
-      <c r="E793" s="78"/>
-      <c r="N793" s="79"/>
-      <c r="P793" s="79"/>
+      <c r="A793" s="76"/>
+      <c r="E793" s="76"/>
+      <c r="N793" s="77"/>
+      <c r="P793" s="77"/>
     </row>
     <row r="794" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A794" s="78"/>
-      <c r="E794" s="78"/>
-      <c r="N794" s="79"/>
-      <c r="P794" s="79"/>
+      <c r="A794" s="76"/>
+      <c r="E794" s="76"/>
+      <c r="N794" s="77"/>
+      <c r="P794" s="77"/>
     </row>
     <row r="795" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A795" s="78"/>
-      <c r="E795" s="78"/>
-      <c r="N795" s="79"/>
-      <c r="P795" s="79"/>
+      <c r="A795" s="76"/>
+      <c r="E795" s="76"/>
+      <c r="N795" s="77"/>
+      <c r="P795" s="77"/>
     </row>
     <row r="796" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A796" s="78"/>
-      <c r="E796" s="78"/>
-      <c r="N796" s="79"/>
-      <c r="P796" s="79"/>
+      <c r="A796" s="76"/>
+      <c r="E796" s="76"/>
+      <c r="N796" s="77"/>
+      <c r="P796" s="77"/>
     </row>
     <row r="797" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A797" s="78"/>
-      <c r="E797" s="78"/>
-      <c r="N797" s="79"/>
-      <c r="P797" s="79"/>
+      <c r="A797" s="76"/>
+      <c r="E797" s="76"/>
+      <c r="N797" s="77"/>
+      <c r="P797" s="77"/>
     </row>
     <row r="798" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A798" s="78"/>
-      <c r="E798" s="78"/>
-      <c r="N798" s="79"/>
-      <c r="P798" s="79"/>
+      <c r="A798" s="76"/>
+      <c r="E798" s="76"/>
+      <c r="N798" s="77"/>
+      <c r="P798" s="77"/>
     </row>
     <row r="799" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A799" s="78"/>
-      <c r="E799" s="78"/>
-      <c r="N799" s="79"/>
-      <c r="P799" s="79"/>
+      <c r="A799" s="76"/>
+      <c r="E799" s="76"/>
+      <c r="N799" s="77"/>
+      <c r="P799" s="77"/>
     </row>
     <row r="800" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A800" s="78"/>
-      <c r="E800" s="78"/>
-      <c r="N800" s="79"/>
-      <c r="P800" s="79"/>
+      <c r="A800" s="76"/>
+      <c r="E800" s="76"/>
+      <c r="N800" s="77"/>
+      <c r="P800" s="77"/>
     </row>
     <row r="801" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A801" s="78"/>
-      <c r="E801" s="78"/>
-      <c r="N801" s="79"/>
-      <c r="P801" s="79"/>
+      <c r="A801" s="76"/>
+      <c r="E801" s="76"/>
+      <c r="N801" s="77"/>
+      <c r="P801" s="77"/>
     </row>
     <row r="802" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A802" s="78"/>
-      <c r="E802" s="78"/>
-      <c r="N802" s="79"/>
-      <c r="P802" s="79"/>
+      <c r="A802" s="76"/>
+      <c r="E802" s="76"/>
+      <c r="N802" s="77"/>
+      <c r="P802" s="77"/>
     </row>
     <row r="803" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A803" s="78"/>
-      <c r="E803" s="78"/>
-      <c r="N803" s="79"/>
-      <c r="P803" s="79"/>
+      <c r="A803" s="76"/>
+      <c r="E803" s="76"/>
+      <c r="N803" s="77"/>
+      <c r="P803" s="77"/>
     </row>
     <row r="804" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A804" s="78"/>
-      <c r="E804" s="78"/>
-      <c r="N804" s="79"/>
-      <c r="P804" s="79"/>
+      <c r="A804" s="76"/>
+      <c r="E804" s="76"/>
+      <c r="N804" s="77"/>
+      <c r="P804" s="77"/>
     </row>
     <row r="805" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A805" s="78"/>
-      <c r="E805" s="78"/>
-      <c r="N805" s="79"/>
-      <c r="P805" s="79"/>
+      <c r="A805" s="76"/>
+      <c r="E805" s="76"/>
+      <c r="N805" s="77"/>
+      <c r="P805" s="77"/>
     </row>
     <row r="806" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A806" s="78"/>
-      <c r="E806" s="78"/>
-      <c r="N806" s="79"/>
-      <c r="P806" s="79"/>
+      <c r="A806" s="76"/>
+      <c r="E806" s="76"/>
+      <c r="N806" s="77"/>
+      <c r="P806" s="77"/>
     </row>
     <row r="807" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A807" s="78"/>
-      <c r="E807" s="78"/>
-      <c r="N807" s="79"/>
-      <c r="P807" s="79"/>
+      <c r="A807" s="76"/>
+      <c r="E807" s="76"/>
+      <c r="N807" s="77"/>
+      <c r="P807" s="77"/>
     </row>
     <row r="808" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A808" s="78"/>
-      <c r="E808" s="78"/>
-      <c r="N808" s="79"/>
-      <c r="P808" s="79"/>
+      <c r="A808" s="76"/>
+      <c r="E808" s="76"/>
+      <c r="N808" s="77"/>
+      <c r="P808" s="77"/>
     </row>
     <row r="809" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A809" s="78"/>
-      <c r="E809" s="78"/>
-      <c r="N809" s="79"/>
-      <c r="P809" s="79"/>
+      <c r="A809" s="76"/>
+      <c r="E809" s="76"/>
+      <c r="N809" s="77"/>
+      <c r="P809" s="77"/>
     </row>
     <row r="810" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A810" s="78"/>
-      <c r="E810" s="78"/>
-      <c r="N810" s="79"/>
-      <c r="P810" s="79"/>
+      <c r="A810" s="76"/>
+      <c r="E810" s="76"/>
+      <c r="N810" s="77"/>
+      <c r="P810" s="77"/>
     </row>
     <row r="811" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A811" s="78"/>
-      <c r="E811" s="78"/>
-      <c r="N811" s="79"/>
-      <c r="P811" s="79"/>
+      <c r="A811" s="76"/>
+      <c r="E811" s="76"/>
+      <c r="N811" s="77"/>
+      <c r="P811" s="77"/>
     </row>
     <row r="812" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A812" s="78"/>
-      <c r="E812" s="78"/>
-      <c r="N812" s="79"/>
-      <c r="P812" s="79"/>
+      <c r="A812" s="76"/>
+      <c r="E812" s="76"/>
+      <c r="N812" s="77"/>
+      <c r="P812" s="77"/>
     </row>
     <row r="813" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A813" s="78"/>
-      <c r="E813" s="78"/>
-      <c r="N813" s="79"/>
-      <c r="P813" s="79"/>
+      <c r="A813" s="76"/>
+      <c r="E813" s="76"/>
+      <c r="N813" s="77"/>
+      <c r="P813" s="77"/>
     </row>
     <row r="814" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A814" s="78"/>
-      <c r="E814" s="78"/>
-      <c r="N814" s="79"/>
-      <c r="P814" s="79"/>
+      <c r="A814" s="76"/>
+      <c r="E814" s="76"/>
+      <c r="N814" s="77"/>
+      <c r="P814" s="77"/>
     </row>
     <row r="815" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A815" s="78"/>
-      <c r="E815" s="78"/>
-      <c r="N815" s="79"/>
-      <c r="P815" s="79"/>
+      <c r="A815" s="76"/>
+      <c r="E815" s="76"/>
+      <c r="N815" s="77"/>
+      <c r="P815" s="77"/>
     </row>
     <row r="816" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A816" s="78"/>
-      <c r="E816" s="78"/>
-      <c r="N816" s="79"/>
-      <c r="P816" s="79"/>
+      <c r="A816" s="76"/>
+      <c r="E816" s="76"/>
+      <c r="N816" s="77"/>
+      <c r="P816" s="77"/>
     </row>
     <row r="817" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A817" s="78"/>
-      <c r="E817" s="78"/>
-      <c r="N817" s="79"/>
-      <c r="P817" s="79"/>
+      <c r="A817" s="76"/>
+      <c r="E817" s="76"/>
+      <c r="N817" s="77"/>
+      <c r="P817" s="77"/>
     </row>
     <row r="818" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A818" s="78"/>
-      <c r="E818" s="78"/>
-      <c r="N818" s="79"/>
-      <c r="P818" s="79"/>
+      <c r="A818" s="76"/>
+      <c r="E818" s="76"/>
+      <c r="N818" s="77"/>
+      <c r="P818" s="77"/>
     </row>
     <row r="819" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A819" s="78"/>
-      <c r="E819" s="78"/>
-      <c r="N819" s="79"/>
-      <c r="P819" s="79"/>
+      <c r="A819" s="76"/>
+      <c r="E819" s="76"/>
+      <c r="N819" s="77"/>
+      <c r="P819" s="77"/>
     </row>
     <row r="820" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A820" s="78"/>
-      <c r="E820" s="78"/>
-      <c r="N820" s="79"/>
-      <c r="P820" s="79"/>
+      <c r="A820" s="76"/>
+      <c r="E820" s="76"/>
+      <c r="N820" s="77"/>
+      <c r="P820" s="77"/>
     </row>
     <row r="821" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A821" s="78"/>
-      <c r="E821" s="78"/>
-      <c r="N821" s="79"/>
-      <c r="P821" s="79"/>
+      <c r="A821" s="76"/>
+      <c r="E821" s="76"/>
+      <c r="N821" s="77"/>
+      <c r="P821" s="77"/>
     </row>
     <row r="822" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A822" s="78"/>
-      <c r="E822" s="78"/>
-      <c r="N822" s="79"/>
-      <c r="P822" s="79"/>
+      <c r="A822" s="76"/>
+      <c r="E822" s="76"/>
+      <c r="N822" s="77"/>
+      <c r="P822" s="77"/>
     </row>
     <row r="823" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A823" s="78"/>
-      <c r="E823" s="78"/>
-      <c r="N823" s="79"/>
-      <c r="P823" s="79"/>
+      <c r="A823" s="76"/>
+      <c r="E823" s="76"/>
+      <c r="N823" s="77"/>
+      <c r="P823" s="77"/>
     </row>
     <row r="824" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A824" s="78"/>
-      <c r="E824" s="78"/>
-      <c r="N824" s="79"/>
-      <c r="P824" s="79"/>
+      <c r="A824" s="76"/>
+      <c r="E824" s="76"/>
+      <c r="N824" s="77"/>
+      <c r="P824" s="77"/>
     </row>
     <row r="825" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A825" s="78"/>
-      <c r="E825" s="78"/>
-      <c r="N825" s="79"/>
-      <c r="P825" s="79"/>
+      <c r="A825" s="76"/>
+      <c r="E825" s="76"/>
+      <c r="N825" s="77"/>
+      <c r="P825" s="77"/>
     </row>
     <row r="826" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A826" s="78"/>
-      <c r="E826" s="78"/>
-      <c r="N826" s="79"/>
-      <c r="P826" s="79"/>
+      <c r="A826" s="76"/>
+      <c r="E826" s="76"/>
+      <c r="N826" s="77"/>
+      <c r="P826" s="77"/>
     </row>
     <row r="827" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A827" s="78"/>
-      <c r="E827" s="78"/>
-      <c r="N827" s="79"/>
-      <c r="P827" s="79"/>
+      <c r="A827" s="76"/>
+      <c r="E827" s="76"/>
+      <c r="N827" s="77"/>
+      <c r="P827" s="77"/>
     </row>
     <row r="828" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A828" s="78"/>
-      <c r="E828" s="78"/>
-      <c r="N828" s="79"/>
-      <c r="P828" s="79"/>
+      <c r="A828" s="76"/>
+      <c r="E828" s="76"/>
+      <c r="N828" s="77"/>
+      <c r="P828" s="77"/>
     </row>
     <row r="829" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A829" s="78"/>
-      <c r="E829" s="78"/>
-      <c r="N829" s="79"/>
-      <c r="P829" s="79"/>
+      <c r="A829" s="76"/>
+      <c r="E829" s="76"/>
+      <c r="N829" s="77"/>
+      <c r="P829" s="77"/>
     </row>
     <row r="830" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A830" s="78"/>
-      <c r="E830" s="78"/>
-      <c r="N830" s="79"/>
-      <c r="P830" s="79"/>
+      <c r="A830" s="76"/>
+      <c r="E830" s="76"/>
+      <c r="N830" s="77"/>
+      <c r="P830" s="77"/>
     </row>
     <row r="831" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A831" s="78"/>
-      <c r="E831" s="78"/>
-      <c r="N831" s="79"/>
-      <c r="P831" s="79"/>
+      <c r="A831" s="76"/>
+      <c r="E831" s="76"/>
+      <c r="N831" s="77"/>
+      <c r="P831" s="77"/>
     </row>
     <row r="832" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A832" s="78"/>
-      <c r="E832" s="78"/>
-      <c r="N832" s="79"/>
-      <c r="P832" s="79"/>
+      <c r="A832" s="76"/>
+      <c r="E832" s="76"/>
+      <c r="N832" s="77"/>
+      <c r="P832" s="77"/>
     </row>
     <row r="833" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A833" s="78"/>
-      <c r="E833" s="78"/>
-      <c r="N833" s="79"/>
-      <c r="P833" s="79"/>
+      <c r="A833" s="76"/>
+      <c r="E833" s="76"/>
+      <c r="N833" s="77"/>
+      <c r="P833" s="77"/>
     </row>
     <row r="834" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A834" s="78"/>
-      <c r="E834" s="78"/>
-      <c r="N834" s="79"/>
-      <c r="P834" s="79"/>
+      <c r="A834" s="76"/>
+      <c r="E834" s="76"/>
+      <c r="N834" s="77"/>
+      <c r="P834" s="77"/>
     </row>
     <row r="835" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A835" s="78"/>
-      <c r="E835" s="78"/>
-      <c r="N835" s="79"/>
-      <c r="P835" s="79"/>
+      <c r="A835" s="76"/>
+      <c r="E835" s="76"/>
+      <c r="N835" s="77"/>
+      <c r="P835" s="77"/>
     </row>
     <row r="836" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A836" s="78"/>
-      <c r="E836" s="78"/>
-      <c r="N836" s="79"/>
-      <c r="P836" s="79"/>
+      <c r="A836" s="76"/>
+      <c r="E836" s="76"/>
+      <c r="N836" s="77"/>
+      <c r="P836" s="77"/>
     </row>
     <row r="837" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A837" s="78"/>
-      <c r="E837" s="78"/>
-      <c r="N837" s="79"/>
-      <c r="P837" s="79"/>
+      <c r="A837" s="76"/>
+      <c r="E837" s="76"/>
+      <c r="N837" s="77"/>
+      <c r="P837" s="77"/>
     </row>
     <row r="838" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A838" s="78"/>
-      <c r="E838" s="78"/>
-      <c r="N838" s="79"/>
-      <c r="P838" s="79"/>
+      <c r="A838" s="76"/>
+      <c r="E838" s="76"/>
+      <c r="N838" s="77"/>
+      <c r="P838" s="77"/>
     </row>
     <row r="839" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A839" s="78"/>
-      <c r="E839" s="78"/>
-      <c r="N839" s="79"/>
-      <c r="P839" s="79"/>
+      <c r="A839" s="76"/>
+      <c r="E839" s="76"/>
+      <c r="N839" s="77"/>
+      <c r="P839" s="77"/>
     </row>
     <row r="840" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A840" s="78"/>
-      <c r="E840" s="78"/>
-      <c r="N840" s="79"/>
-      <c r="P840" s="79"/>
+      <c r="A840" s="76"/>
+      <c r="E840" s="76"/>
+      <c r="N840" s="77"/>
+      <c r="P840" s="77"/>
     </row>
     <row r="841" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A841" s="78"/>
-      <c r="E841" s="78"/>
-      <c r="N841" s="79"/>
-      <c r="P841" s="79"/>
+      <c r="A841" s="76"/>
+      <c r="E841" s="76"/>
+      <c r="N841" s="77"/>
+      <c r="P841" s="77"/>
     </row>
     <row r="842" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A842" s="78"/>
-      <c r="E842" s="78"/>
-      <c r="N842" s="79"/>
-      <c r="P842" s="79"/>
+      <c r="A842" s="76"/>
+      <c r="E842" s="76"/>
+      <c r="N842" s="77"/>
+      <c r="P842" s="77"/>
     </row>
     <row r="843" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A843" s="78"/>
-      <c r="E843" s="78"/>
-      <c r="N843" s="79"/>
-      <c r="P843" s="79"/>
+      <c r="A843" s="76"/>
+      <c r="E843" s="76"/>
+      <c r="N843" s="77"/>
+      <c r="P843" s="77"/>
     </row>
     <row r="844" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A844" s="78"/>
-      <c r="E844" s="78"/>
-      <c r="N844" s="79"/>
-      <c r="P844" s="79"/>
+      <c r="A844" s="76"/>
+      <c r="E844" s="76"/>
+      <c r="N844" s="77"/>
+      <c r="P844" s="77"/>
     </row>
     <row r="845" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A845" s="78"/>
-      <c r="E845" s="78"/>
-      <c r="N845" s="79"/>
-      <c r="P845" s="79"/>
+      <c r="A845" s="76"/>
+      <c r="E845" s="76"/>
+      <c r="N845" s="77"/>
+      <c r="P845" s="77"/>
     </row>
     <row r="846" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A846" s="78"/>
-      <c r="E846" s="78"/>
-      <c r="N846" s="79"/>
-      <c r="P846" s="79"/>
+      <c r="A846" s="76"/>
+      <c r="E846" s="76"/>
+      <c r="N846" s="77"/>
+      <c r="P846" s="77"/>
     </row>
     <row r="847" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A847" s="78"/>
-      <c r="E847" s="78"/>
-      <c r="N847" s="79"/>
-      <c r="P847" s="79"/>
+      <c r="A847" s="76"/>
+      <c r="E847" s="76"/>
+      <c r="N847" s="77"/>
+      <c r="P847" s="77"/>
     </row>
     <row r="848" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A848" s="78"/>
-      <c r="E848" s="78"/>
-      <c r="N848" s="79"/>
-      <c r="P848" s="79"/>
+      <c r="A848" s="76"/>
+      <c r="E848" s="76"/>
+      <c r="N848" s="77"/>
+      <c r="P848" s="77"/>
     </row>
     <row r="849" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A849" s="78"/>
-      <c r="E849" s="78"/>
-      <c r="N849" s="79"/>
-      <c r="P849" s="79"/>
+      <c r="A849" s="76"/>
+      <c r="E849" s="76"/>
+      <c r="N849" s="77"/>
+      <c r="P849" s="77"/>
     </row>
     <row r="850" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A850" s="78"/>
-      <c r="E850" s="78"/>
-      <c r="N850" s="79"/>
-      <c r="P850" s="79"/>
+      <c r="A850" s="76"/>
+      <c r="E850" s="76"/>
+      <c r="N850" s="77"/>
+      <c r="P850" s="77"/>
     </row>
     <row r="851" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A851" s="78"/>
-      <c r="E851" s="78"/>
-      <c r="N851" s="79"/>
-      <c r="P851" s="79"/>
+      <c r="A851" s="76"/>
+      <c r="E851" s="76"/>
+      <c r="N851" s="77"/>
+      <c r="P851" s="77"/>
     </row>
     <row r="852" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A852" s="78"/>
-      <c r="E852" s="78"/>
-      <c r="N852" s="79"/>
-      <c r="P852" s="79"/>
+      <c r="A852" s="76"/>
+      <c r="E852" s="76"/>
+      <c r="N852" s="77"/>
+      <c r="P852" s="77"/>
     </row>
     <row r="853" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A853" s="78"/>
-      <c r="E853" s="78"/>
-      <c r="N853" s="79"/>
-      <c r="P853" s="79"/>
+      <c r="A853" s="76"/>
+      <c r="E853" s="76"/>
+      <c r="N853" s="77"/>
+      <c r="P853" s="77"/>
     </row>
     <row r="854" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A854" s="78"/>
-      <c r="E854" s="78"/>
-      <c r="N854" s="79"/>
-      <c r="P854" s="79"/>
+      <c r="A854" s="76"/>
+      <c r="E854" s="76"/>
+      <c r="N854" s="77"/>
+      <c r="P854" s="77"/>
     </row>
     <row r="855" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A855" s="78"/>
-      <c r="E855" s="78"/>
-      <c r="N855" s="79"/>
-      <c r="P855" s="79"/>
+      <c r="A855" s="76"/>
+      <c r="E855" s="76"/>
+      <c r="N855" s="77"/>
+      <c r="P855" s="77"/>
     </row>
     <row r="856" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A856" s="78"/>
-      <c r="E856" s="78"/>
-      <c r="N856" s="79"/>
-      <c r="P856" s="79"/>
+      <c r="A856" s="76"/>
+      <c r="E856" s="76"/>
+      <c r="N856" s="77"/>
+      <c r="P856" s="77"/>
     </row>
     <row r="857" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A857" s="78"/>
-      <c r="E857" s="78"/>
-      <c r="N857" s="79"/>
-      <c r="P857" s="79"/>
+      <c r="A857" s="76"/>
+      <c r="E857" s="76"/>
+      <c r="N857" s="77"/>
+      <c r="P857" s="77"/>
     </row>
     <row r="858" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A858" s="78"/>
-      <c r="E858" s="78"/>
-      <c r="N858" s="79"/>
-      <c r="P858" s="79"/>
+      <c r="A858" s="76"/>
+      <c r="E858" s="76"/>
+      <c r="N858" s="77"/>
+      <c r="P858" s="77"/>
     </row>
     <row r="859" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A859" s="78"/>
-      <c r="E859" s="78"/>
-      <c r="N859" s="79"/>
-      <c r="P859" s="79"/>
+      <c r="A859" s="76"/>
+      <c r="E859" s="76"/>
+      <c r="N859" s="77"/>
+      <c r="P859" s="77"/>
     </row>
     <row r="860" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A860" s="78"/>
-      <c r="E860" s="78"/>
-      <c r="N860" s="79"/>
-      <c r="P860" s="79"/>
+      <c r="A860" s="76"/>
+      <c r="E860" s="76"/>
+      <c r="N860" s="77"/>
+      <c r="P860" s="77"/>
     </row>
     <row r="861" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A861" s="78"/>
-      <c r="E861" s="78"/>
-      <c r="N861" s="79"/>
-      <c r="P861" s="79"/>
+      <c r="A861" s="76"/>
+      <c r="E861" s="76"/>
+      <c r="N861" s="77"/>
+      <c r="P861" s="77"/>
     </row>
     <row r="862" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A862" s="78"/>
-      <c r="E862" s="78"/>
-      <c r="N862" s="79"/>
-      <c r="P862" s="79"/>
+      <c r="A862" s="76"/>
+      <c r="E862" s="76"/>
+      <c r="N862" s="77"/>
+      <c r="P862" s="77"/>
     </row>
     <row r="863" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A863" s="78"/>
-      <c r="E863" s="78"/>
-      <c r="N863" s="79"/>
-      <c r="P863" s="79"/>
+      <c r="A863" s="76"/>
+      <c r="E863" s="76"/>
+      <c r="N863" s="77"/>
+      <c r="P863" s="77"/>
     </row>
     <row r="864" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A864" s="78"/>
-      <c r="E864" s="78"/>
-      <c r="N864" s="79"/>
-      <c r="P864" s="79"/>
+      <c r="A864" s="76"/>
+      <c r="E864" s="76"/>
+      <c r="N864" s="77"/>
+      <c r="P864" s="77"/>
     </row>
     <row r="865" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A865" s="78"/>
-      <c r="E865" s="78"/>
-      <c r="N865" s="79"/>
-      <c r="P865" s="79"/>
+      <c r="A865" s="76"/>
+      <c r="E865" s="76"/>
+      <c r="N865" s="77"/>
+      <c r="P865" s="77"/>
     </row>
     <row r="866" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A866" s="78"/>
-      <c r="E866" s="78"/>
-      <c r="N866" s="79"/>
-      <c r="P866" s="79"/>
+      <c r="A866" s="76"/>
+      <c r="E866" s="76"/>
+      <c r="N866" s="77"/>
+      <c r="P866" s="77"/>
     </row>
     <row r="867" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A867" s="78"/>
-      <c r="E867" s="78"/>
-      <c r="N867" s="79"/>
-      <c r="P867" s="79"/>
+      <c r="A867" s="76"/>
+      <c r="E867" s="76"/>
+      <c r="N867" s="77"/>
+      <c r="P867" s="77"/>
     </row>
     <row r="868" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A868" s="78"/>
-      <c r="E868" s="78"/>
-      <c r="N868" s="79"/>
-      <c r="P868" s="79"/>
+      <c r="A868" s="76"/>
+      <c r="E868" s="76"/>
+      <c r="N868" s="77"/>
+      <c r="P868" s="77"/>
     </row>
     <row r="869" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A869" s="78"/>
-      <c r="E869" s="78"/>
-      <c r="N869" s="79"/>
-      <c r="P869" s="79"/>
+      <c r="A869" s="76"/>
+      <c r="E869" s="76"/>
+      <c r="N869" s="77"/>
+      <c r="P869" s="77"/>
     </row>
     <row r="870" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A870" s="78"/>
-      <c r="E870" s="78"/>
-      <c r="N870" s="79"/>
-      <c r="P870" s="79"/>
+      <c r="A870" s="76"/>
+      <c r="E870" s="76"/>
+      <c r="N870" s="77"/>
+      <c r="P870" s="77"/>
     </row>
     <row r="871" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A871" s="78"/>
-      <c r="E871" s="78"/>
-      <c r="N871" s="79"/>
-      <c r="P871" s="79"/>
+      <c r="A871" s="76"/>
+      <c r="E871" s="76"/>
+      <c r="N871" s="77"/>
+      <c r="P871" s="77"/>
     </row>
     <row r="872" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A872" s="78"/>
-      <c r="E872" s="78"/>
-      <c r="N872" s="79"/>
-      <c r="P872" s="79"/>
+      <c r="A872" s="76"/>
+      <c r="E872" s="76"/>
+      <c r="N872" s="77"/>
+      <c r="P872" s="77"/>
     </row>
     <row r="873" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A873" s="78"/>
-      <c r="E873" s="78"/>
-      <c r="N873" s="79"/>
-      <c r="P873" s="79"/>
+      <c r="A873" s="76"/>
+      <c r="E873" s="76"/>
+      <c r="N873" s="77"/>
+      <c r="P873" s="77"/>
     </row>
     <row r="874" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A874" s="78"/>
-      <c r="E874" s="78"/>
-      <c r="N874" s="79"/>
-      <c r="P874" s="79"/>
+      <c r="A874" s="76"/>
+      <c r="E874" s="76"/>
+      <c r="N874" s="77"/>
+      <c r="P874" s="77"/>
     </row>
     <row r="875" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A875" s="78"/>
-      <c r="E875" s="78"/>
-      <c r="N875" s="79"/>
-      <c r="P875" s="79"/>
+      <c r="A875" s="76"/>
+      <c r="E875" s="76"/>
+      <c r="N875" s="77"/>
+      <c r="P875" s="77"/>
     </row>
     <row r="876" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A876" s="78"/>
-      <c r="E876" s="78"/>
-      <c r="N876" s="79"/>
-      <c r="P876" s="79"/>
+      <c r="A876" s="76"/>
+      <c r="E876" s="76"/>
+      <c r="N876" s="77"/>
+      <c r="P876" s="77"/>
     </row>
     <row r="877" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A877" s="78"/>
-      <c r="E877" s="78"/>
-      <c r="N877" s="79"/>
-      <c r="P877" s="79"/>
+      <c r="A877" s="76"/>
+      <c r="E877" s="76"/>
+      <c r="N877" s="77"/>
+      <c r="P877" s="77"/>
     </row>
     <row r="878" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A878" s="78"/>
-      <c r="E878" s="78"/>
-      <c r="N878" s="79"/>
-      <c r="P878" s="79"/>
+      <c r="A878" s="76"/>
+      <c r="E878" s="76"/>
+      <c r="N878" s="77"/>
+      <c r="P878" s="77"/>
     </row>
     <row r="879" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A879" s="78"/>
-      <c r="E879" s="78"/>
-      <c r="N879" s="79"/>
-      <c r="P879" s="79"/>
+      <c r="A879" s="76"/>
+      <c r="E879" s="76"/>
+      <c r="N879" s="77"/>
+      <c r="P879" s="77"/>
     </row>
     <row r="880" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A880" s="78"/>
-      <c r="E880" s="78"/>
-      <c r="N880" s="79"/>
-      <c r="P880" s="79"/>
+      <c r="A880" s="76"/>
+      <c r="E880" s="76"/>
+      <c r="N880" s="77"/>
+      <c r="P880" s="77"/>
     </row>
     <row r="881" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A881" s="78"/>
-      <c r="E881" s="78"/>
-      <c r="N881" s="79"/>
-      <c r="P881" s="79"/>
+      <c r="A881" s="76"/>
+      <c r="E881" s="76"/>
+      <c r="N881" s="77"/>
+      <c r="P881" s="77"/>
     </row>
     <row r="882" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A882" s="78"/>
-      <c r="E882" s="78"/>
-      <c r="N882" s="79"/>
-      <c r="P882" s="79"/>
+      <c r="A882" s="76"/>
+      <c r="E882" s="76"/>
+      <c r="N882" s="77"/>
+      <c r="P882" s="77"/>
     </row>
     <row r="883" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A883" s="78"/>
-      <c r="E883" s="78"/>
-      <c r="N883" s="79"/>
-      <c r="P883" s="79"/>
+      <c r="A883" s="76"/>
+      <c r="E883" s="76"/>
+      <c r="N883" s="77"/>
+      <c r="P883" s="77"/>
     </row>
     <row r="884" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A884" s="78"/>
-      <c r="E884" s="78"/>
-      <c r="N884" s="79"/>
-      <c r="P884" s="79"/>
+      <c r="A884" s="76"/>
+      <c r="E884" s="76"/>
+      <c r="N884" s="77"/>
+      <c r="P884" s="77"/>
     </row>
     <row r="885" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A885" s="78"/>
-      <c r="E885" s="78"/>
-      <c r="N885" s="79"/>
-      <c r="P885" s="79"/>
+      <c r="A885" s="76"/>
+      <c r="E885" s="76"/>
+      <c r="N885" s="77"/>
+      <c r="P885" s="77"/>
     </row>
     <row r="886" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A886" s="78"/>
-      <c r="E886" s="78"/>
-      <c r="N886" s="79"/>
-      <c r="P886" s="79"/>
+      <c r="A886" s="76"/>
+      <c r="E886" s="76"/>
+      <c r="N886" s="77"/>
+      <c r="P886" s="77"/>
     </row>
     <row r="887" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A887" s="78"/>
-      <c r="E887" s="78"/>
-      <c r="N887" s="79"/>
-      <c r="P887" s="79"/>
+      <c r="A887" s="76"/>
+      <c r="E887" s="76"/>
+      <c r="N887" s="77"/>
+      <c r="P887" s="77"/>
     </row>
     <row r="888" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A888" s="78"/>
-      <c r="E888" s="78"/>
-      <c r="N888" s="79"/>
-      <c r="P888" s="79"/>
+      <c r="A888" s="76"/>
+      <c r="E888" s="76"/>
+      <c r="N888" s="77"/>
+      <c r="P888" s="77"/>
     </row>
     <row r="889" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A889" s="78"/>
-      <c r="E889" s="78"/>
-      <c r="N889" s="79"/>
-      <c r="P889" s="79"/>
+      <c r="A889" s="76"/>
+      <c r="E889" s="76"/>
+      <c r="N889" s="77"/>
+      <c r="P889" s="77"/>
     </row>
     <row r="890" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A890" s="78"/>
-      <c r="E890" s="78"/>
-      <c r="N890" s="79"/>
-      <c r="P890" s="79"/>
+      <c r="A890" s="76"/>
+      <c r="E890" s="76"/>
+      <c r="N890" s="77"/>
+      <c r="P890" s="77"/>
     </row>
     <row r="891" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A891" s="78"/>
-      <c r="E891" s="78"/>
-      <c r="N891" s="79"/>
-      <c r="P891" s="79"/>
+      <c r="A891" s="76"/>
+      <c r="E891" s="76"/>
+      <c r="N891" s="77"/>
+      <c r="P891" s="77"/>
     </row>
     <row r="892" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A892" s="78"/>
-      <c r="E892" s="78"/>
-      <c r="N892" s="79"/>
-      <c r="P892" s="79"/>
+      <c r="A892" s="76"/>
+      <c r="E892" s="76"/>
+      <c r="N892" s="77"/>
+      <c r="P892" s="77"/>
     </row>
     <row r="893" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A893" s="78"/>
-      <c r="E893" s="78"/>
-      <c r="N893" s="79"/>
-      <c r="P893" s="79"/>
+      <c r="A893" s="76"/>
+      <c r="E893" s="76"/>
+      <c r="N893" s="77"/>
+      <c r="P893" s="77"/>
     </row>
     <row r="894" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A894" s="78"/>
-      <c r="E894" s="78"/>
-      <c r="N894" s="79"/>
-      <c r="P894" s="79"/>
+      <c r="A894" s="76"/>
+      <c r="E894" s="76"/>
+      <c r="N894" s="77"/>
+      <c r="P894" s="77"/>
     </row>
     <row r="895" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A895" s="78"/>
-      <c r="E895" s="78"/>
-      <c r="N895" s="79"/>
-      <c r="P895" s="79"/>
+      <c r="A895" s="76"/>
+      <c r="E895" s="76"/>
+      <c r="N895" s="77"/>
+      <c r="P895" s="77"/>
     </row>
     <row r="896" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A896" s="78"/>
-      <c r="E896" s="78"/>
-      <c r="N896" s="79"/>
-      <c r="P896" s="79"/>
+      <c r="A896" s="76"/>
+      <c r="E896" s="76"/>
+      <c r="N896" s="77"/>
+      <c r="P896" s="77"/>
     </row>
     <row r="897" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A897" s="78"/>
-      <c r="E897" s="78"/>
-      <c r="N897" s="79"/>
-      <c r="P897" s="79"/>
+      <c r="A897" s="76"/>
+      <c r="E897" s="76"/>
+      <c r="N897" s="77"/>
+      <c r="P897" s="77"/>
     </row>
     <row r="898" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A898" s="78"/>
-      <c r="E898" s="78"/>
-      <c r="N898" s="79"/>
-      <c r="P898" s="79"/>
+      <c r="A898" s="76"/>
+      <c r="E898" s="76"/>
+      <c r="N898" s="77"/>
+      <c r="P898" s="77"/>
     </row>
     <row r="899" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A899" s="78"/>
-      <c r="E899" s="78"/>
-      <c r="N899" s="79"/>
-      <c r="P899" s="79"/>
+      <c r="A899" s="76"/>
+      <c r="E899" s="76"/>
+      <c r="N899" s="77"/>
+      <c r="P899" s="77"/>
     </row>
     <row r="900" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A900" s="78"/>
-      <c r="E900" s="78"/>
-      <c r="N900" s="79"/>
-      <c r="P900" s="79"/>
+      <c r="A900" s="76"/>
+      <c r="E900" s="76"/>
+      <c r="N900" s="77"/>
+      <c r="P900" s="77"/>
     </row>
     <row r="901" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A901" s="78"/>
-      <c r="E901" s="78"/>
-      <c r="N901" s="79"/>
-      <c r="P901" s="79"/>
+      <c r="A901" s="76"/>
+      <c r="E901" s="76"/>
+      <c r="N901" s="77"/>
+      <c r="P901" s="77"/>
     </row>
     <row r="902" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A902" s="78"/>
-      <c r="E902" s="78"/>
-      <c r="N902" s="79"/>
-      <c r="P902" s="79"/>
+      <c r="A902" s="76"/>
+      <c r="E902" s="76"/>
+      <c r="N902" s="77"/>
+      <c r="P902" s="77"/>
     </row>
     <row r="903" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A903" s="78"/>
-      <c r="E903" s="78"/>
-      <c r="N903" s="79"/>
-      <c r="P903" s="79"/>
+      <c r="A903" s="76"/>
+      <c r="E903" s="76"/>
+      <c r="N903" s="77"/>
+      <c r="P903" s="77"/>
     </row>
     <row r="904" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A904" s="78"/>
-      <c r="E904" s="78"/>
-      <c r="N904" s="79"/>
-      <c r="P904" s="79"/>
+      <c r="A904" s="76"/>
+      <c r="E904" s="76"/>
+      <c r="N904" s="77"/>
+      <c r="P904" s="77"/>
     </row>
     <row r="905" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A905" s="78"/>
-      <c r="E905" s="78"/>
-      <c r="N905" s="79"/>
-      <c r="P905" s="79"/>
+      <c r="A905" s="76"/>
+      <c r="E905" s="76"/>
+      <c r="N905" s="77"/>
+      <c r="P905" s="77"/>
     </row>
     <row r="906" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A906" s="78"/>
-      <c r="E906" s="78"/>
-      <c r="N906" s="79"/>
-      <c r="P906" s="79"/>
+      <c r="A906" s="76"/>
+      <c r="E906" s="76"/>
+      <c r="N906" s="77"/>
+      <c r="P906" s="77"/>
     </row>
     <row r="907" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A907" s="78"/>
-      <c r="E907" s="78"/>
-      <c r="N907" s="79"/>
-      <c r="P907" s="79"/>
+      <c r="A907" s="76"/>
+      <c r="E907" s="76"/>
+      <c r="N907" s="77"/>
+      <c r="P907" s="77"/>
     </row>
     <row r="908" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A908" s="78"/>
-      <c r="E908" s="78"/>
-      <c r="N908" s="79"/>
-      <c r="P908" s="79"/>
+      <c r="A908" s="76"/>
+      <c r="E908" s="76"/>
+      <c r="N908" s="77"/>
+      <c r="P908" s="77"/>
     </row>
     <row r="909" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A909" s="78"/>
-      <c r="E909" s="78"/>
-      <c r="N909" s="79"/>
-      <c r="P909" s="79"/>
+      <c r="A909" s="76"/>
+      <c r="E909" s="76"/>
+      <c r="N909" s="77"/>
+      <c r="P909" s="77"/>
     </row>
     <row r="910" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A910" s="78"/>
-      <c r="E910" s="78"/>
-      <c r="N910" s="79"/>
-      <c r="P910" s="79"/>
+      <c r="A910" s="76"/>
+      <c r="E910" s="76"/>
+      <c r="N910" s="77"/>
+      <c r="P910" s="77"/>
     </row>
     <row r="911" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A911" s="78"/>
-      <c r="E911" s="78"/>
-      <c r="N911" s="79"/>
-      <c r="P911" s="79"/>
+      <c r="A911" s="76"/>
+      <c r="E911" s="76"/>
+      <c r="N911" s="77"/>
+      <c r="P911" s="77"/>
     </row>
     <row r="912" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A912" s="78"/>
-      <c r="E912" s="78"/>
-      <c r="N912" s="79"/>
-      <c r="P912" s="79"/>
+      <c r="A912" s="76"/>
+      <c r="E912" s="76"/>
+      <c r="N912" s="77"/>
+      <c r="P912" s="77"/>
     </row>
     <row r="913" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A913" s="78"/>
-      <c r="E913" s="78"/>
-      <c r="N913" s="79"/>
-      <c r="P913" s="79"/>
+      <c r="A913" s="76"/>
+      <c r="E913" s="76"/>
+      <c r="N913" s="77"/>
+      <c r="P913" s="77"/>
     </row>
     <row r="914" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A914" s="78"/>
-      <c r="E914" s="78"/>
-      <c r="N914" s="79"/>
-      <c r="P914" s="79"/>
+      <c r="A914" s="76"/>
+      <c r="E914" s="76"/>
+      <c r="N914" s="77"/>
+      <c r="P914" s="77"/>
     </row>
     <row r="915" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A915" s="78"/>
-      <c r="E915" s="78"/>
-      <c r="N915" s="79"/>
-      <c r="P915" s="79"/>
+      <c r="A915" s="76"/>
+      <c r="E915" s="76"/>
+      <c r="N915" s="77"/>
+      <c r="P915" s="77"/>
     </row>
     <row r="916" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A916" s="78"/>
-      <c r="E916" s="78"/>
-      <c r="N916" s="79"/>
-      <c r="P916" s="79"/>
+      <c r="A916" s="76"/>
+      <c r="E916" s="76"/>
+      <c r="N916" s="77"/>
+      <c r="P916" s="77"/>
     </row>
     <row r="917" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A917" s="78"/>
-      <c r="E917" s="78"/>
-      <c r="N917" s="79"/>
-      <c r="P917" s="79"/>
+      <c r="A917" s="76"/>
+      <c r="E917" s="76"/>
+      <c r="N917" s="77"/>
+      <c r="P917" s="77"/>
     </row>
     <row r="918" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A918" s="78"/>
-      <c r="E918" s="78"/>
-      <c r="N918" s="79"/>
-      <c r="P918" s="79"/>
+      <c r="A918" s="76"/>
+      <c r="E918" s="76"/>
+      <c r="N918" s="77"/>
+      <c r="P918" s="77"/>
     </row>
     <row r="919" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A919" s="78"/>
-      <c r="E919" s="78"/>
-      <c r="N919" s="79"/>
-      <c r="P919" s="79"/>
+      <c r="A919" s="76"/>
+      <c r="E919" s="76"/>
+      <c r="N919" s="77"/>
+      <c r="P919" s="77"/>
     </row>
     <row r="920" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A920" s="78"/>
-      <c r="E920" s="78"/>
-      <c r="N920" s="79"/>
-      <c r="P920" s="79"/>
+      <c r="A920" s="76"/>
+      <c r="E920" s="76"/>
+      <c r="N920" s="77"/>
+      <c r="P920" s="77"/>
     </row>
     <row r="921" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A921" s="78"/>
-      <c r="E921" s="78"/>
-      <c r="N921" s="79"/>
-      <c r="P921" s="79"/>
+      <c r="A921" s="76"/>
+      <c r="E921" s="76"/>
+      <c r="N921" s="77"/>
+      <c r="P921" s="77"/>
     </row>
     <row r="922" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A922" s="78"/>
-      <c r="E922" s="78"/>
-      <c r="N922" s="79"/>
-      <c r="P922" s="79"/>
+      <c r="A922" s="76"/>
+      <c r="E922" s="76"/>
+      <c r="N922" s="77"/>
+      <c r="P922" s="77"/>
     </row>
     <row r="923" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A923" s="78"/>
-      <c r="E923" s="78"/>
-      <c r="N923" s="79"/>
-      <c r="P923" s="79"/>
+      <c r="A923" s="76"/>
+      <c r="E923" s="76"/>
+      <c r="N923" s="77"/>
+      <c r="P923" s="77"/>
     </row>
     <row r="924" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A924" s="78"/>
-      <c r="E924" s="78"/>
-      <c r="N924" s="79"/>
-      <c r="P924" s="79"/>
+      <c r="A924" s="76"/>
+      <c r="E924" s="76"/>
+      <c r="N924" s="77"/>
+      <c r="P924" s="77"/>
     </row>
     <row r="925" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A925" s="78"/>
-      <c r="E925" s="78"/>
-      <c r="N925" s="79"/>
-      <c r="P925" s="79"/>
+      <c r="A925" s="76"/>
+      <c r="E925" s="76"/>
+      <c r="N925" s="77"/>
+      <c r="P925" s="77"/>
     </row>
     <row r="926" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A926" s="78"/>
-      <c r="E926" s="78"/>
-      <c r="N926" s="79"/>
-      <c r="P926" s="79"/>
+      <c r="A926" s="76"/>
+      <c r="E926" s="76"/>
+      <c r="N926" s="77"/>
+      <c r="P926" s="77"/>
     </row>
     <row r="927" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A927" s="78"/>
-      <c r="E927" s="78"/>
-      <c r="N927" s="79"/>
-      <c r="P927" s="79"/>
+      <c r="A927" s="76"/>
+      <c r="E927" s="76"/>
+      <c r="N927" s="77"/>
+      <c r="P927" s="77"/>
     </row>
     <row r="928" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A928" s="78"/>
-      <c r="E928" s="78"/>
-      <c r="N928" s="79"/>
-      <c r="P928" s="79"/>
+      <c r="A928" s="76"/>
+      <c r="E928" s="76"/>
+      <c r="N928" s="77"/>
+      <c r="P928" s="77"/>
     </row>
     <row r="929" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A929" s="78"/>
-      <c r="E929" s="78"/>
-      <c r="N929" s="79"/>
-      <c r="P929" s="79"/>
+      <c r="A929" s="76"/>
+      <c r="E929" s="76"/>
+      <c r="N929" s="77"/>
+      <c r="P929" s="77"/>
     </row>
     <row r="930" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A930" s="78"/>
-      <c r="E930" s="78"/>
-      <c r="N930" s="79"/>
-      <c r="P930" s="79"/>
+      <c r="A930" s="76"/>
+      <c r="E930" s="76"/>
+      <c r="N930" s="77"/>
+      <c r="P930" s="77"/>
     </row>
     <row r="931" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A931" s="78"/>
-      <c r="E931" s="78"/>
-      <c r="N931" s="79"/>
-      <c r="P931" s="79"/>
+      <c r="A931" s="76"/>
+      <c r="E931" s="76"/>
+      <c r="N931" s="77"/>
+      <c r="P931" s="77"/>
     </row>
     <row r="932" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A932" s="78"/>
-      <c r="E932" s="78"/>
-      <c r="N932" s="79"/>
-      <c r="P932" s="79"/>
+      <c r="A932" s="76"/>
+      <c r="E932" s="76"/>
+      <c r="N932" s="77"/>
+      <c r="P932" s="77"/>
     </row>
     <row r="933" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A933" s="78"/>
-      <c r="E933" s="78"/>
-      <c r="N933" s="79"/>
-      <c r="P933" s="79"/>
+      <c r="A933" s="76"/>
+      <c r="E933" s="76"/>
+      <c r="N933" s="77"/>
+      <c r="P933" s="77"/>
     </row>
     <row r="934" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A934" s="78"/>
-      <c r="E934" s="78"/>
-      <c r="N934" s="79"/>
-      <c r="P934" s="79"/>
+      <c r="A934" s="76"/>
+      <c r="E934" s="76"/>
+      <c r="N934" s="77"/>
+      <c r="P934" s="77"/>
     </row>
     <row r="935" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A935" s="78"/>
-      <c r="E935" s="78"/>
-      <c r="N935" s="79"/>
-      <c r="P935" s="79"/>
+      <c r="A935" s="76"/>
+      <c r="E935" s="76"/>
+      <c r="N935" s="77"/>
+      <c r="P935" s="77"/>
     </row>
     <row r="936" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A936" s="78"/>
-      <c r="E936" s="78"/>
-      <c r="N936" s="79"/>
-      <c r="P936" s="79"/>
+      <c r="A936" s="76"/>
+      <c r="E936" s="76"/>
+      <c r="N936" s="77"/>
+      <c r="P936" s="77"/>
     </row>
     <row r="937" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A937" s="78"/>
-      <c r="E937" s="78"/>
-      <c r="N937" s="79"/>
-      <c r="P937" s="79"/>
+      <c r="A937" s="76"/>
+      <c r="E937" s="76"/>
+      <c r="N937" s="77"/>
+      <c r="P937" s="77"/>
     </row>
     <row r="938" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A938" s="78"/>
-      <c r="E938" s="78"/>
-      <c r="N938" s="79"/>
-      <c r="P938" s="79"/>
+      <c r="A938" s="76"/>
+      <c r="E938" s="76"/>
+      <c r="N938" s="77"/>
+      <c r="P938" s="77"/>
     </row>
     <row r="939" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A939" s="78"/>
-      <c r="E939" s="78"/>
-      <c r="N939" s="79"/>
-      <c r="P939" s="79"/>
+      <c r="A939" s="76"/>
+      <c r="E939" s="76"/>
+      <c r="N939" s="77"/>
+      <c r="P939" s="77"/>
     </row>
     <row r="940" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A940" s="78"/>
-      <c r="E940" s="78"/>
-      <c r="N940" s="79"/>
-      <c r="P940" s="79"/>
+      <c r="A940" s="76"/>
+      <c r="E940" s="76"/>
+      <c r="N940" s="77"/>
+      <c r="P940" s="77"/>
     </row>
     <row r="941" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A941" s="78"/>
-      <c r="E941" s="78"/>
-      <c r="N941" s="79"/>
-      <c r="P941" s="79"/>
+      <c r="A941" s="76"/>
+      <c r="E941" s="76"/>
+      <c r="N941" s="77"/>
+      <c r="P941" s="77"/>
     </row>
     <row r="942" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A942" s="78"/>
-      <c r="E942" s="78"/>
-      <c r="N942" s="79"/>
-      <c r="P942" s="79"/>
+      <c r="A942" s="76"/>
+      <c r="E942" s="76"/>
+      <c r="N942" s="77"/>
+      <c r="P942" s="77"/>
     </row>
     <row r="943" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A943" s="78"/>
-      <c r="E943" s="78"/>
-      <c r="N943" s="79"/>
-      <c r="P943" s="79"/>
+      <c r="A943" s="76"/>
+      <c r="E943" s="76"/>
+      <c r="N943" s="77"/>
+      <c r="P943" s="77"/>
     </row>
     <row r="944" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A944" s="78"/>
-      <c r="E944" s="78"/>
-      <c r="N944" s="79"/>
-      <c r="P944" s="79"/>
+      <c r="A944" s="76"/>
+      <c r="E944" s="76"/>
+      <c r="N944" s="77"/>
+      <c r="P944" s="77"/>
     </row>
     <row r="945" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A945" s="78"/>
-      <c r="E945" s="78"/>
-      <c r="N945" s="79"/>
-      <c r="P945" s="79"/>
+      <c r="A945" s="76"/>
+      <c r="E945" s="76"/>
+      <c r="N945" s="77"/>
+      <c r="P945" s="77"/>
     </row>
     <row r="946" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A946" s="78"/>
-      <c r="E946" s="78"/>
-      <c r="N946" s="79"/>
-      <c r="P946" s="79"/>
+      <c r="A946" s="76"/>
+      <c r="E946" s="76"/>
+      <c r="N946" s="77"/>
+      <c r="P946" s="77"/>
     </row>
     <row r="947" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A947" s="78"/>
-      <c r="E947" s="78"/>
-      <c r="N947" s="79"/>
-      <c r="P947" s="79"/>
+      <c r="A947" s="76"/>
+      <c r="E947" s="76"/>
+      <c r="N947" s="77"/>
+      <c r="P947" s="77"/>
     </row>
     <row r="948" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A948" s="78"/>
-      <c r="E948" s="78"/>
-      <c r="N948" s="79"/>
-      <c r="P948" s="79"/>
+      <c r="A948" s="76"/>
+      <c r="E948" s="76"/>
+      <c r="N948" s="77"/>
+      <c r="P948" s="77"/>
     </row>
     <row r="949" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A949" s="78"/>
-      <c r="E949" s="78"/>
-      <c r="N949" s="79"/>
-      <c r="P949" s="79"/>
+      <c r="A949" s="76"/>
+      <c r="E949" s="76"/>
+      <c r="N949" s="77"/>
+      <c r="P949" s="77"/>
     </row>
     <row r="950" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A950" s="78"/>
-      <c r="E950" s="78"/>
-      <c r="N950" s="79"/>
-      <c r="P950" s="79"/>
+      <c r="A950" s="76"/>
+      <c r="E950" s="76"/>
+      <c r="N950" s="77"/>
+      <c r="P950" s="77"/>
     </row>
     <row r="951" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A951" s="78"/>
-      <c r="E951" s="78"/>
-      <c r="N951" s="79"/>
-      <c r="P951" s="79"/>
+      <c r="A951" s="76"/>
+      <c r="E951" s="76"/>
+      <c r="N951" s="77"/>
+      <c r="P951" s="77"/>
     </row>
     <row r="952" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A952" s="78"/>
-      <c r="E952" s="78"/>
-      <c r="N952" s="79"/>
-      <c r="P952" s="79"/>
+      <c r="A952" s="76"/>
+      <c r="E952" s="76"/>
+      <c r="N952" s="77"/>
+      <c r="P952" s="77"/>
     </row>
     <row r="953" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A953" s="78"/>
-      <c r="E953" s="78"/>
-      <c r="N953" s="79"/>
-      <c r="P953" s="79"/>
+      <c r="A953" s="76"/>
+      <c r="E953" s="76"/>
+      <c r="N953" s="77"/>
+      <c r="P953" s="77"/>
     </row>
     <row r="954" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A954" s="78"/>
-      <c r="E954" s="78"/>
-      <c r="N954" s="79"/>
-      <c r="P954" s="79"/>
+      <c r="A954" s="76"/>
+      <c r="E954" s="76"/>
+      <c r="N954" s="77"/>
+      <c r="P954" s="77"/>
     </row>
     <row r="955" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A955" s="78"/>
-      <c r="E955" s="78"/>
-      <c r="N955" s="79"/>
-      <c r="P955" s="79"/>
+      <c r="A955" s="76"/>
+      <c r="E955" s="76"/>
+      <c r="N955" s="77"/>
+      <c r="P955" s="77"/>
     </row>
     <row r="956" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A956" s="78"/>
-      <c r="E956" s="78"/>
-      <c r="N956" s="79"/>
-      <c r="P956" s="79"/>
+      <c r="A956" s="76"/>
+      <c r="E956" s="76"/>
+      <c r="N956" s="77"/>
+      <c r="P956" s="77"/>
     </row>
     <row r="957" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A957" s="78"/>
-      <c r="E957" s="78"/>
-      <c r="N957" s="79"/>
-      <c r="P957" s="79"/>
+      <c r="A957" s="76"/>
+      <c r="E957" s="76"/>
+      <c r="N957" s="77"/>
+      <c r="P957" s="77"/>
     </row>
     <row r="958" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A958" s="78"/>
-      <c r="E958" s="78"/>
-      <c r="N958" s="79"/>
-      <c r="P958" s="79"/>
+      <c r="A958" s="76"/>
+      <c r="E958" s="76"/>
+      <c r="N958" s="77"/>
+      <c r="P958" s="77"/>
     </row>
     <row r="959" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A959" s="78"/>
-      <c r="E959" s="78"/>
-      <c r="N959" s="79"/>
-      <c r="P959" s="79"/>
+      <c r="A959" s="76"/>
+      <c r="E959" s="76"/>
+      <c r="N959" s="77"/>
+      <c r="P959" s="77"/>
     </row>
     <row r="960" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A960" s="78"/>
-      <c r="E960" s="78"/>
-      <c r="N960" s="79"/>
-      <c r="P960" s="79"/>
+      <c r="A960" s="76"/>
+      <c r="E960" s="76"/>
+      <c r="N960" s="77"/>
+      <c r="P960" s="77"/>
     </row>
     <row r="961" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A961" s="78"/>
-      <c r="E961" s="78"/>
-      <c r="N961" s="79"/>
-      <c r="P961" s="79"/>
+      <c r="A961" s="76"/>
+      <c r="E961" s="76"/>
+      <c r="N961" s="77"/>
+      <c r="P961" s="77"/>
     </row>
     <row r="962" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A962" s="78"/>
-      <c r="E962" s="78"/>
-      <c r="N962" s="79"/>
-      <c r="P962" s="79"/>
+      <c r="A962" s="76"/>
+      <c r="E962" s="76"/>
+      <c r="N962" s="77"/>
+      <c r="P962" s="77"/>
     </row>
     <row r="963" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A963" s="78"/>
-      <c r="E963" s="78"/>
-      <c r="N963" s="79"/>
-      <c r="P963" s="79"/>
+      <c r="A963" s="76"/>
+      <c r="E963" s="76"/>
+      <c r="N963" s="77"/>
+      <c r="P963" s="77"/>
     </row>
     <row r="964" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A964" s="78"/>
-      <c r="E964" s="78"/>
-      <c r="N964" s="79"/>
-      <c r="P964" s="79"/>
+      <c r="A964" s="76"/>
+      <c r="E964" s="76"/>
+      <c r="N964" s="77"/>
+      <c r="P964" s="77"/>
     </row>
     <row r="965" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A965" s="78"/>
-      <c r="E965" s="78"/>
-      <c r="N965" s="79"/>
-      <c r="P965" s="79"/>
+      <c r="A965" s="76"/>
+      <c r="E965" s="76"/>
+      <c r="N965" s="77"/>
+      <c r="P965" s="77"/>
     </row>
     <row r="966" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A966" s="78"/>
-      <c r="E966" s="78"/>
-      <c r="N966" s="79"/>
-      <c r="P966" s="79"/>
+      <c r="A966" s="76"/>
+      <c r="E966" s="76"/>
+      <c r="N966" s="77"/>
+      <c r="P966" s="77"/>
     </row>
     <row r="967" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A967" s="78"/>
-      <c r="E967" s="78"/>
-      <c r="N967" s="79"/>
-      <c r="P967" s="79"/>
+      <c r="A967" s="76"/>
+      <c r="E967" s="76"/>
+      <c r="N967" s="77"/>
+      <c r="P967" s="77"/>
     </row>
     <row r="968" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A968" s="78"/>
-      <c r="E968" s="78"/>
-      <c r="N968" s="79"/>
-      <c r="P968" s="79"/>
+      <c r="A968" s="76"/>
+      <c r="E968" s="76"/>
+      <c r="N968" s="77"/>
+      <c r="P968" s="77"/>
     </row>
     <row r="969" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A969" s="78"/>
-      <c r="E969" s="78"/>
-      <c r="N969" s="79"/>
-      <c r="P969" s="79"/>
+      <c r="A969" s="76"/>
+      <c r="E969" s="76"/>
+      <c r="N969" s="77"/>
+      <c r="P969" s="77"/>
     </row>
     <row r="970" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A970" s="78"/>
-      <c r="E970" s="78"/>
-      <c r="N970" s="79"/>
-      <c r="P970" s="79"/>
+      <c r="A970" s="76"/>
+      <c r="E970" s="76"/>
+      <c r="N970" s="77"/>
+      <c r="P970" s="77"/>
     </row>
     <row r="971" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A971" s="78"/>
-      <c r="E971" s="78"/>
-      <c r="N971" s="79"/>
-      <c r="P971" s="79"/>
+      <c r="A971" s="76"/>
+      <c r="E971" s="76"/>
+      <c r="N971" s="77"/>
+      <c r="P971" s="77"/>
     </row>
     <row r="972" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A972" s="78"/>
-      <c r="E972" s="78"/>
-      <c r="N972" s="79"/>
-      <c r="P972" s="79"/>
+      <c r="A972" s="76"/>
+      <c r="E972" s="76"/>
+      <c r="N972" s="77"/>
+      <c r="P972" s="77"/>
     </row>
     <row r="973" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A973" s="78"/>
-      <c r="E973" s="78"/>
-      <c r="N973" s="79"/>
-      <c r="P973" s="79"/>
+      <c r="A973" s="76"/>
+      <c r="E973" s="76"/>
+      <c r="N973" s="77"/>
+      <c r="P973" s="77"/>
     </row>
     <row r="974" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A974" s="78"/>
-      <c r="E974" s="78"/>
-      <c r="N974" s="79"/>
-      <c r="P974" s="79"/>
+      <c r="A974" s="76"/>
+      <c r="E974" s="76"/>
+      <c r="N974" s="77"/>
+      <c r="P974" s="77"/>
     </row>
     <row r="975" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A975" s="78"/>
-      <c r="E975" s="78"/>
-      <c r="N975" s="79"/>
-      <c r="P975" s="79"/>
+      <c r="A975" s="76"/>
+      <c r="E975" s="76"/>
+      <c r="N975" s="77"/>
+      <c r="P975" s="77"/>
     </row>
     <row r="976" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A976" s="78"/>
-      <c r="E976" s="78"/>
-      <c r="N976" s="79"/>
-      <c r="P976" s="79"/>
+      <c r="A976" s="76"/>
+      <c r="E976" s="76"/>
+      <c r="N976" s="77"/>
+      <c r="P976" s="77"/>
     </row>
     <row r="977" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A977" s="78"/>
-      <c r="E977" s="78"/>
-      <c r="N977" s="79"/>
-      <c r="P977" s="79"/>
+      <c r="A977" s="76"/>
+      <c r="E977" s="76"/>
+      <c r="N977" s="77"/>
+      <c r="P977" s="77"/>
     </row>
     <row r="978" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A978" s="78"/>
-      <c r="E978" s="78"/>
-      <c r="N978" s="79"/>
-      <c r="P978" s="79"/>
+      <c r="A978" s="76"/>
+      <c r="E978" s="76"/>
+      <c r="N978" s="77"/>
+      <c r="P978" s="77"/>
     </row>
     <row r="979" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A979" s="78"/>
-      <c r="E979" s="78"/>
-      <c r="N979" s="79"/>
-      <c r="P979" s="79"/>
+      <c r="A979" s="76"/>
+      <c r="E979" s="76"/>
+      <c r="N979" s="77"/>
+      <c r="P979" s="77"/>
     </row>
     <row r="980" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A980" s="78"/>
-      <c r="E980" s="78"/>
-      <c r="N980" s="79"/>
-      <c r="P980" s="79"/>
+      <c r="A980" s="76"/>
+      <c r="E980" s="76"/>
+      <c r="N980" s="77"/>
+      <c r="P980" s="77"/>
     </row>
     <row r="981" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A981" s="78"/>
-      <c r="E981" s="78"/>
-      <c r="N981" s="79"/>
-      <c r="P981" s="79"/>
+      <c r="A981" s="76"/>
+      <c r="E981" s="76"/>
+      <c r="N981" s="77"/>
+      <c r="P981" s="77"/>
     </row>
     <row r="982" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A982" s="78"/>
-      <c r="E982" s="78"/>
-      <c r="N982" s="79"/>
-      <c r="P982" s="79"/>
+      <c r="A982" s="76"/>
+      <c r="E982" s="76"/>
+      <c r="N982" s="77"/>
+      <c r="P982" s="77"/>
     </row>
     <row r="983" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A983" s="78"/>
-      <c r="E983" s="78"/>
-      <c r="N983" s="79"/>
-      <c r="P983" s="79"/>
+      <c r="A983" s="76"/>
+      <c r="E983" s="76"/>
+      <c r="N983" s="77"/>
+      <c r="P983" s="77"/>
     </row>
     <row r="984" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A984" s="78"/>
-      <c r="E984" s="78"/>
-      <c r="N984" s="79"/>
-      <c r="P984" s="79"/>
+      <c r="A984" s="76"/>
+      <c r="E984" s="76"/>
+      <c r="N984" s="77"/>
+      <c r="P984" s="77"/>
     </row>
     <row r="985" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A985" s="78"/>
-      <c r="E985" s="78"/>
-      <c r="N985" s="79"/>
-      <c r="P985" s="79"/>
+      <c r="A985" s="76"/>
+      <c r="E985" s="76"/>
+      <c r="N985" s="77"/>
+      <c r="P985" s="77"/>
     </row>
     <row r="986" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A986" s="78"/>
-      <c r="E986" s="78"/>
-      <c r="N986" s="79"/>
-      <c r="P986" s="79"/>
+      <c r="A986" s="76"/>
+      <c r="E986" s="76"/>
+      <c r="N986" s="77"/>
+      <c r="P986" s="77"/>
     </row>
     <row r="987" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A987" s="78"/>
-      <c r="E987" s="78"/>
-      <c r="N987" s="79"/>
-      <c r="P987" s="79"/>
+      <c r="A987" s="76"/>
+      <c r="E987" s="76"/>
+      <c r="N987" s="77"/>
+      <c r="P987" s="77"/>
     </row>
     <row r="988" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A988" s="78"/>
-      <c r="E988" s="78"/>
-      <c r="N988" s="79"/>
-      <c r="P988" s="79"/>
+      <c r="A988" s="76"/>
+      <c r="E988" s="76"/>
+      <c r="N988" s="77"/>
+      <c r="P988" s="77"/>
     </row>
     <row r="989" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A989" s="78"/>
-      <c r="E989" s="78"/>
-      <c r="N989" s="79"/>
-      <c r="P989" s="79"/>
+      <c r="A989" s="76"/>
+      <c r="E989" s="76"/>
+      <c r="N989" s="77"/>
+      <c r="P989" s="77"/>
     </row>
     <row r="990" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A990" s="78"/>
-      <c r="E990" s="78"/>
-      <c r="N990" s="79"/>
-      <c r="P990" s="79"/>
+      <c r="A990" s="76"/>
+      <c r="E990" s="76"/>
+      <c r="N990" s="77"/>
+      <c r="P990" s="77"/>
     </row>
     <row r="991" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A991" s="78"/>
-      <c r="E991" s="78"/>
-      <c r="N991" s="79"/>
-      <c r="P991" s="79"/>
+      <c r="A991" s="76"/>
+      <c r="E991" s="76"/>
+      <c r="N991" s="77"/>
+      <c r="P991" s="77"/>
     </row>
     <row r="992" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A992" s="78"/>
-      <c r="E992" s="78"/>
-      <c r="N992" s="79"/>
-      <c r="P992" s="79"/>
+      <c r="A992" s="76"/>
+      <c r="E992" s="76"/>
+      <c r="N992" s="77"/>
+      <c r="P992" s="77"/>
     </row>
     <row r="993" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A993" s="78"/>
-      <c r="E993" s="78"/>
-      <c r="N993" s="79"/>
-      <c r="P993" s="79"/>
+      <c r="A993" s="76"/>
+      <c r="E993" s="76"/>
+      <c r="N993" s="77"/>
+      <c r="P993" s="77"/>
     </row>
     <row r="994" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A994" s="78"/>
-      <c r="E994" s="78"/>
-      <c r="N994" s="79"/>
-      <c r="P994" s="79"/>
+      <c r="A994" s="76"/>
+      <c r="E994" s="76"/>
+      <c r="N994" s="77"/>
+      <c r="P994" s="77"/>
     </row>
     <row r="995" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A995" s="78"/>
-      <c r="E995" s="78"/>
-      <c r="N995" s="79"/>
-      <c r="P995" s="79"/>
+      <c r="A995" s="76"/>
+      <c r="E995" s="76"/>
+      <c r="N995" s="77"/>
+      <c r="P995" s="77"/>
     </row>
     <row r="996" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A996" s="78"/>
-      <c r="E996" s="78"/>
-      <c r="N996" s="79"/>
-      <c r="P996" s="79"/>
+      <c r="A996" s="76"/>
+      <c r="E996" s="76"/>
+      <c r="N996" s="77"/>
+      <c r="P996" s="77"/>
     </row>
     <row r="997" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A997" s="78"/>
-      <c r="E997" s="78"/>
-      <c r="N997" s="79"/>
-      <c r="P997" s="79"/>
+      <c r="A997" s="76"/>
+      <c r="E997" s="76"/>
+      <c r="N997" s="77"/>
+      <c r="P997" s="77"/>
     </row>
     <row r="998" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A998" s="78"/>
-      <c r="E998" s="78"/>
-      <c r="N998" s="79"/>
-      <c r="P998" s="79"/>
+      <c r="A998" s="76"/>
+      <c r="E998" s="76"/>
+      <c r="N998" s="77"/>
+      <c r="P998" s="77"/>
     </row>
     <row r="999" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A999" s="78"/>
-      <c r="E999" s="78"/>
-      <c r="N999" s="79"/>
-      <c r="P999" s="79"/>
+      <c r="A999" s="76"/>
+      <c r="E999" s="76"/>
+      <c r="N999" s="77"/>
+      <c r="P999" s="77"/>
     </row>
     <row r="1000" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1000" s="78"/>
-      <c r="E1000" s="78"/>
-      <c r="N1000" s="79"/>
-      <c r="P1000" s="79"/>
+      <c r="A1000" s="76"/>
+      <c r="E1000" s="76"/>
+      <c r="N1000" s="77"/>
+      <c r="P1000" s="77"/>
     </row>
     <row r="1001" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1001" s="78"/>
-      <c r="E1001" s="78"/>
-      <c r="N1001" s="79"/>
-      <c r="P1001" s="79"/>
+      <c r="A1001" s="76"/>
+      <c r="E1001" s="76"/>
+      <c r="N1001" s="77"/>
+      <c r="P1001" s="77"/>
     </row>
     <row r="1002" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1002" s="78"/>
-      <c r="E1002" s="78"/>
-      <c r="N1002" s="79"/>
-      <c r="P1002" s="79"/>
+      <c r="A1002" s="76"/>
+      <c r="E1002" s="76"/>
+      <c r="N1002" s="77"/>
+      <c r="P1002" s="77"/>
     </row>
     <row r="1003" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1003" s="78"/>
-      <c r="E1003" s="78"/>
-      <c r="N1003" s="79"/>
-      <c r="P1003" s="79"/>
+      <c r="A1003" s="76"/>
+      <c r="E1003" s="76"/>
+      <c r="N1003" s="77"/>
+      <c r="P1003" s="77"/>
     </row>
     <row r="1004" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1004" s="78"/>
-      <c r="E1004" s="78"/>
-      <c r="N1004" s="79"/>
-      <c r="P1004" s="79"/>
+      <c r="A1004" s="76"/>
+      <c r="E1004" s="76"/>
+      <c r="N1004" s="77"/>
+      <c r="P1004" s="77"/>
     </row>
     <row r="1005" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1005" s="78"/>
-      <c r="E1005" s="78"/>
-      <c r="N1005" s="79"/>
-      <c r="P1005" s="79"/>
+      <c r="A1005" s="76"/>
+      <c r="E1005" s="76"/>
+      <c r="N1005" s="77"/>
+      <c r="P1005" s="77"/>
     </row>
     <row r="1006" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1006" s="78"/>
-      <c r="E1006" s="78"/>
-      <c r="N1006" s="79"/>
-      <c r="P1006" s="79"/>
+      <c r="A1006" s="76"/>
+      <c r="E1006" s="76"/>
+      <c r="N1006" s="77"/>
+      <c r="P1006" s="77"/>
     </row>
     <row r="1007" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1007" s="78"/>
-      <c r="E1007" s="78"/>
-      <c r="N1007" s="79"/>
-      <c r="P1007" s="79"/>
+      <c r="A1007" s="76"/>
+      <c r="E1007" s="76"/>
+      <c r="N1007" s="77"/>
+      <c r="P1007" s="77"/>
     </row>
     <row r="1008" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1008" s="78"/>
-      <c r="E1008" s="78"/>
-      <c r="N1008" s="79"/>
-      <c r="P1008" s="79"/>
+      <c r="A1008" s="76"/>
+      <c r="E1008" s="76"/>
+      <c r="N1008" s="77"/>
+      <c r="P1008" s="77"/>
     </row>
     <row r="1009" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1009" s="78"/>
-      <c r="E1009" s="78"/>
-      <c r="N1009" s="79"/>
-      <c r="P1009" s="79"/>
+      <c r="A1009" s="76"/>
+      <c r="E1009" s="76"/>
+      <c r="N1009" s="77"/>
+      <c r="P1009" s="77"/>
     </row>
     <row r="1010" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1010" s="78"/>
-      <c r="E1010" s="78"/>
-      <c r="N1010" s="79"/>
-      <c r="P1010" s="79"/>
+      <c r="A1010" s="76"/>
+      <c r="E1010" s="76"/>
+      <c r="N1010" s="77"/>
+      <c r="P1010" s="77"/>
     </row>
     <row r="1011" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1011" s="78"/>
-      <c r="E1011" s="78"/>
-      <c r="N1011" s="79"/>
-      <c r="P1011" s="79"/>
+      <c r="A1011" s="76"/>
+      <c r="E1011" s="76"/>
+      <c r="N1011" s="77"/>
+      <c r="P1011" s="77"/>
     </row>
     <row r="1012" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1012" s="78"/>
-      <c r="E1012" s="78"/>
-      <c r="N1012" s="79"/>
-      <c r="P1012" s="79"/>
+      <c r="A1012" s="76"/>
+      <c r="E1012" s="76"/>
+      <c r="N1012" s="77"/>
+      <c r="P1012" s="77"/>
     </row>
     <row r="1013" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1013" s="78"/>
-      <c r="E1013" s="78"/>
-      <c r="N1013" s="79"/>
-      <c r="P1013" s="79"/>
+      <c r="A1013" s="76"/>
+      <c r="E1013" s="76"/>
+      <c r="N1013" s="77"/>
+      <c r="P1013" s="77"/>
     </row>
     <row r="1014" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1014" s="78"/>
-      <c r="E1014" s="78"/>
-      <c r="N1014" s="79"/>
-      <c r="P1014" s="79"/>
+      <c r="A1014" s="76"/>
+      <c r="E1014" s="76"/>
+      <c r="N1014" s="77"/>
+      <c r="P1014" s="77"/>
     </row>
     <row r="1015" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1015" s="78"/>
-      <c r="E1015" s="78"/>
-      <c r="N1015" s="79"/>
-      <c r="P1015" s="79"/>
+      <c r="A1015" s="76"/>
+      <c r="E1015" s="76"/>
+      <c r="N1015" s="77"/>
+      <c r="P1015" s="77"/>
     </row>
     <row r="1016" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1016" s="78"/>
-      <c r="E1016" s="78"/>
-      <c r="N1016" s="79"/>
-      <c r="P1016" s="79"/>
+      <c r="A1016" s="76"/>
+      <c r="E1016" s="76"/>
+      <c r="N1016" s="77"/>
+      <c r="P1016" s="77"/>
     </row>
     <row r="1017" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1017" s="78"/>
-      <c r="E1017" s="78"/>
-      <c r="N1017" s="79"/>
-      <c r="P1017" s="79"/>
+      <c r="A1017" s="76"/>
+      <c r="E1017" s="76"/>
+      <c r="N1017" s="77"/>
+      <c r="P1017" s="77"/>
     </row>
     <row r="1018" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1018" s="78"/>
-      <c r="E1018" s="78"/>
-      <c r="N1018" s="79"/>
-      <c r="P1018" s="79"/>
+      <c r="A1018" s="76"/>
+      <c r="E1018" s="76"/>
+      <c r="N1018" s="77"/>
+      <c r="P1018" s="77"/>
     </row>
     <row r="1019" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1019" s="78"/>
-      <c r="E1019" s="78"/>
-      <c r="N1019" s="79"/>
-      <c r="P1019" s="79"/>
+      <c r="A1019" s="76"/>
+      <c r="E1019" s="76"/>
+      <c r="N1019" s="77"/>
+      <c r="P1019" s="77"/>
     </row>
     <row r="1020" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1020" s="78"/>
-      <c r="E1020" s="78"/>
-      <c r="N1020" s="79"/>
-      <c r="P1020" s="79"/>
+      <c r="A1020" s="76"/>
+      <c r="E1020" s="76"/>
+      <c r="N1020" s="77"/>
+      <c r="P1020" s="77"/>
     </row>
     <row r="1021" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1021" s="78"/>
-      <c r="E1021" s="78"/>
-      <c r="N1021" s="79"/>
-      <c r="P1021" s="79"/>
+      <c r="A1021" s="76"/>
+      <c r="E1021" s="76"/>
+      <c r="N1021" s="77"/>
+      <c r="P1021" s="77"/>
     </row>
     <row r="1022" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1022" s="78"/>
-      <c r="E1022" s="78"/>
-      <c r="N1022" s="79"/>
-      <c r="P1022" s="79"/>
+      <c r="A1022" s="76"/>
+      <c r="E1022" s="76"/>
+      <c r="N1022" s="77"/>
+      <c r="P1022" s="77"/>
     </row>
     <row r="1023" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1023" s="78"/>
-      <c r="E1023" s="78"/>
-      <c r="N1023" s="79"/>
-      <c r="P1023" s="79"/>
+      <c r="A1023" s="76"/>
+      <c r="E1023" s="76"/>
+      <c r="N1023" s="77"/>
+      <c r="P1023" s="77"/>
     </row>
     <row r="1024" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1024" s="78"/>
-      <c r="E1024" s="78"/>
-      <c r="N1024" s="79"/>
-      <c r="P1024" s="79"/>
+      <c r="A1024" s="76"/>
+      <c r="E1024" s="76"/>
+      <c r="N1024" s="77"/>
+      <c r="P1024" s="77"/>
     </row>
     <row r="1025" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1025" s="78"/>
-      <c r="E1025" s="78"/>
-      <c r="N1025" s="79"/>
-      <c r="P1025" s="79"/>
+      <c r="A1025" s="76"/>
+      <c r="E1025" s="76"/>
+      <c r="N1025" s="77"/>
+      <c r="P1025" s="77"/>
     </row>
     <row r="1026" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1026" s="78"/>
-      <c r="E1026" s="78"/>
-      <c r="N1026" s="79"/>
-      <c r="P1026" s="79"/>
+      <c r="A1026" s="76"/>
+      <c r="E1026" s="76"/>
+      <c r="N1026" s="77"/>
+      <c r="P1026" s="77"/>
     </row>
     <row r="1027" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1027" s="78"/>
-      <c r="E1027" s="78"/>
-      <c r="N1027" s="79"/>
-      <c r="P1027" s="79"/>
+      <c r="A1027" s="76"/>
+      <c r="E1027" s="76"/>
+      <c r="N1027" s="77"/>
+      <c r="P1027" s="77"/>
     </row>
     <row r="1028" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1028" s="78"/>
-      <c r="E1028" s="78"/>
-      <c r="N1028" s="79"/>
-      <c r="P1028" s="79"/>
+      <c r="A1028" s="76"/>
+      <c r="E1028" s="76"/>
+      <c r="N1028" s="77"/>
+      <c r="P1028" s="77"/>
     </row>
     <row r="1029" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1029" s="78"/>
-      <c r="E1029" s="78"/>
-      <c r="N1029" s="79"/>
-      <c r="P1029" s="79"/>
+      <c r="A1029" s="76"/>
+      <c r="E1029" s="76"/>
+      <c r="N1029" s="77"/>
+      <c r="P1029" s="77"/>
     </row>
     <row r="1030" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1030" s="78"/>
-      <c r="E1030" s="78"/>
-      <c r="N1030" s="79"/>
-      <c r="P1030" s="79"/>
+      <c r="A1030" s="76"/>
+      <c r="E1030" s="76"/>
+      <c r="N1030" s="77"/>
+      <c r="P1030" s="77"/>
     </row>
     <row r="1031" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1031" s="78"/>
-      <c r="E1031" s="78"/>
-      <c r="N1031" s="79"/>
-      <c r="P1031" s="79"/>
+      <c r="A1031" s="76"/>
+      <c r="E1031" s="76"/>
+      <c r="N1031" s="77"/>
+      <c r="P1031" s="77"/>
     </row>
     <row r="1032" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1032" s="78"/>
-      <c r="E1032" s="78"/>
-      <c r="N1032" s="79"/>
-      <c r="P1032" s="79"/>
+      <c r="A1032" s="76"/>
+      <c r="E1032" s="76"/>
+      <c r="N1032" s="77"/>
+      <c r="P1032" s="77"/>
     </row>
     <row r="1033" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1033" s="78"/>
-      <c r="E1033" s="78"/>
-      <c r="N1033" s="79"/>
-      <c r="P1033" s="79"/>
+      <c r="A1033" s="76"/>
+      <c r="E1033" s="76"/>
+      <c r="N1033" s="77"/>
+      <c r="P1033" s="77"/>
     </row>
     <row r="1034" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1034" s="78"/>
-      <c r="E1034" s="78"/>
-      <c r="N1034" s="79"/>
-      <c r="P1034" s="79"/>
+      <c r="A1034" s="76"/>
+      <c r="E1034" s="76"/>
+      <c r="N1034" s="77"/>
+      <c r="P1034" s="77"/>
     </row>
     <row r="1035" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1035" s="78"/>
-      <c r="E1035" s="78"/>
-      <c r="N1035" s="79"/>
-      <c r="P1035" s="79"/>
+      <c r="A1035" s="76"/>
+      <c r="E1035" s="76"/>
+      <c r="N1035" s="77"/>
+      <c r="P1035" s="77"/>
     </row>
     <row r="1036" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1036" s="78"/>
-      <c r="E1036" s="78"/>
-      <c r="N1036" s="79"/>
-      <c r="P1036" s="79"/>
+      <c r="A1036" s="76"/>
+      <c r="E1036" s="76"/>
+      <c r="N1036" s="77"/>
+      <c r="P1036" s="77"/>
     </row>
     <row r="1037" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1037" s="78"/>
-      <c r="E1037" s="78"/>
-      <c r="N1037" s="79"/>
-      <c r="P1037" s="79"/>
+      <c r="A1037" s="76"/>
+      <c r="E1037" s="76"/>
+      <c r="N1037" s="77"/>
+      <c r="P1037" s="77"/>
     </row>
     <row r="1038" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1038" s="78"/>
-      <c r="E1038" s="78"/>
-      <c r="N1038" s="79"/>
-      <c r="P1038" s="79"/>
+      <c r="A1038" s="76"/>
+      <c r="E1038" s="76"/>
+      <c r="N1038" s="77"/>
+      <c r="P1038" s="77"/>
     </row>
     <row r="1039" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1039" s="78"/>
-      <c r="E1039" s="78"/>
-      <c r="N1039" s="79"/>
-      <c r="P1039" s="79"/>
+      <c r="A1039" s="76"/>
+      <c r="E1039" s="76"/>
+      <c r="N1039" s="77"/>
+      <c r="P1039" s="77"/>
     </row>
     <row r="1040" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1040" s="78"/>
-      <c r="E1040" s="78"/>
-      <c r="N1040" s="79"/>
-      <c r="P1040" s="79"/>
+      <c r="A1040" s="76"/>
+      <c r="E1040" s="76"/>
+      <c r="N1040" s="77"/>
+      <c r="P1040" s="77"/>
     </row>
     <row r="1041" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1041" s="78"/>
-      <c r="E1041" s="78"/>
-      <c r="N1041" s="79"/>
-      <c r="P1041" s="79"/>
+      <c r="A1041" s="76"/>
+      <c r="E1041" s="76"/>
+      <c r="N1041" s="77"/>
+      <c r="P1041" s="77"/>
     </row>
     <row r="1042" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1042" s="78"/>
-      <c r="E1042" s="78"/>
-      <c r="N1042" s="79"/>
-      <c r="P1042" s="79"/>
+      <c r="A1042" s="76"/>
+      <c r="E1042" s="76"/>
+      <c r="N1042" s="77"/>
+      <c r="P1042" s="77"/>
     </row>
     <row r="1043" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1043" s="78"/>
-      <c r="E1043" s="78"/>
-      <c r="N1043" s="79"/>
-      <c r="P1043" s="79"/>
+      <c r="A1043" s="76"/>
+      <c r="E1043" s="76"/>
+      <c r="N1043" s="77"/>
+      <c r="P1043" s="77"/>
     </row>
     <row r="1044" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1044" s="78"/>
-      <c r="E1044" s="78"/>
-      <c r="N1044" s="79"/>
-      <c r="P1044" s="79"/>
+      <c r="A1044" s="76"/>
+      <c r="E1044" s="76"/>
+      <c r="N1044" s="77"/>
+      <c r="P1044" s="77"/>
     </row>
     <row r="1045" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1045" s="78"/>
-      <c r="E1045" s="78"/>
-      <c r="N1045" s="79"/>
-      <c r="P1045" s="79"/>
+      <c r="A1045" s="76"/>
+      <c r="E1045" s="76"/>
+      <c r="N1045" s="77"/>
+      <c r="P1045" s="77"/>
     </row>
     <row r="1046" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1046" s="78"/>
-      <c r="E1046" s="78"/>
-      <c r="N1046" s="79"/>
-      <c r="P1046" s="79"/>
+      <c r="A1046" s="76"/>
+      <c r="E1046" s="76"/>
+      <c r="N1046" s="77"/>
+      <c r="P1046" s="77"/>
     </row>
     <row r="1047" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1047" s="78"/>
-      <c r="E1047" s="78"/>
-      <c r="N1047" s="79"/>
-      <c r="P1047" s="79"/>
+      <c r="A1047" s="76"/>
+      <c r="E1047" s="76"/>
+      <c r="N1047" s="77"/>
+      <c r="P1047" s="77"/>
     </row>
     <row r="1048" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1048" s="78"/>
-      <c r="E1048" s="78"/>
-      <c r="N1048" s="79"/>
-      <c r="P1048" s="79"/>
+      <c r="A1048" s="76"/>
+      <c r="E1048" s="76"/>
+      <c r="N1048" s="77"/>
+      <c r="P1048" s="77"/>
     </row>
     <row r="1049" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1049" s="78"/>
-      <c r="E1049" s="78"/>
-      <c r="N1049" s="79"/>
-      <c r="P1049" s="79"/>
+      <c r="A1049" s="76"/>
+      <c r="E1049" s="76"/>
+      <c r="N1049" s="77"/>
+      <c r="P1049" s="77"/>
     </row>
     <row r="1050" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1050" s="78"/>
-      <c r="E1050" s="78"/>
-      <c r="N1050" s="79"/>
-      <c r="P1050" s="79"/>
+      <c r="A1050" s="76"/>
+      <c r="E1050" s="76"/>
+      <c r="N1050" s="77"/>
+      <c r="P1050" s="77"/>
     </row>
     <row r="1051" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1051" s="78"/>
-      <c r="E1051" s="78"/>
-      <c r="N1051" s="79"/>
-      <c r="P1051" s="79"/>
+      <c r="A1051" s="76"/>
+      <c r="E1051" s="76"/>
+      <c r="N1051" s="77"/>
+      <c r="P1051" s="77"/>
     </row>
     <row r="1052" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1052" s="78"/>
-      <c r="E1052" s="78"/>
-      <c r="N1052" s="79"/>
-      <c r="P1052" s="79"/>
+      <c r="A1052" s="76"/>
+      <c r="E1052" s="76"/>
+      <c r="N1052" s="77"/>
+      <c r="P1052" s="77"/>
     </row>
     <row r="1053" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1053" s="78"/>
-      <c r="E1053" s="78"/>
-      <c r="N1053" s="79"/>
-      <c r="P1053" s="79"/>
+      <c r="A1053" s="76"/>
+      <c r="E1053" s="76"/>
+      <c r="N1053" s="77"/>
+      <c r="P1053" s="77"/>
     </row>
     <row r="1054" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1054" s="78"/>
-      <c r="E1054" s="78"/>
-      <c r="N1054" s="79"/>
-      <c r="P1054" s="79"/>
+      <c r="A1054" s="76"/>
+      <c r="E1054" s="76"/>
+      <c r="N1054" s="77"/>
+      <c r="P1054" s="77"/>
     </row>
     <row r="1055" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1055" s="78"/>
-      <c r="E1055" s="78"/>
-      <c r="N1055" s="79"/>
-      <c r="P1055" s="79"/>
+      <c r="A1055" s="76"/>
+      <c r="E1055" s="76"/>
+      <c r="N1055" s="77"/>
+      <c r="P1055" s="77"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:P429"/>

--- a/secretario.xlsx
+++ b/secretario.xlsx
@@ -11,7 +11,7 @@
     <sheet name="DADOS" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">DADOS!$A$1:$P$544</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">DADOS!$A$1:$P$549</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6558" uniqueCount="2241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6635" uniqueCount="2271">
   <si>
     <t xml:space="preserve">DATA</t>
   </si>
@@ -7187,7 +7187,7 @@
     <t xml:space="preserve">https://drive.google.com/file/d/1MAMMuAVjTodjDgsTjyKqtCxEi3dB-6PJ/view?usp=sharing</t>
   </si>
   <si>
-    <t xml:space="preserve">Furto de fiação elétrica no supermercado fort do bairro dos estados</t>
+    <t xml:space="preserve">Furto de fiação elétrica</t>
   </si>
   <si>
     <t xml:space="preserve">Av. Marginal Leste</t>
@@ -7748,25 +7748,7 @@
     <t xml:space="preserve">Furto de 2 retrovisores da motocicleta</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">TRIUMPH </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">SCRAMBLER</t>
-    </r>
+    <t xml:space="preserve">TRIUMPH SCRAMBLER</t>
   </si>
   <si>
     <r>
@@ -8207,7 +8189,7 @@
     <t xml:space="preserve">https://drive.google.com/file/d/1VxFpTi52WGPjfy_t_HpTxxDnkSD0tnUF/view?usp=sharing</t>
   </si>
   <si>
-    <t xml:space="preserve">2 adolescente tentaram furtar 3 garrafas de bebidas</t>
+    <t xml:space="preserve">2 adolescente tentaram furtar 3 garrafas bebidas</t>
   </si>
   <si>
     <t xml:space="preserve">Supermercado Mescke – Av. do estados</t>
@@ -8246,7 +8228,7 @@
     <t xml:space="preserve">https://drive.google.com/file/d/1pQyFyDFoMjKHQ1J7Hx74hyKGidEWg5tS/view?usp=sharing</t>
   </si>
   <si>
-    <t xml:space="preserve">Masculino furtou bicicleta da no edifício</t>
+    <t xml:space="preserve">Masculino furtou bicicleta no edifício</t>
   </si>
   <si>
     <t xml:space="preserve">Brando</t>
@@ -8264,7 +8246,7 @@
     <t xml:space="preserve">Tablet</t>
   </si>
   <si>
-    <t xml:space="preserve">Masculino furtou um tablet</t>
+    <t xml:space="preserve">Masculino furtou Tablet</t>
   </si>
   <si>
     <t xml:space="preserve">BO-00600.2026.0027512</t>
@@ -8428,7 +8410,7 @@
     <t xml:space="preserve">https://drive.google.com/file/d/1y2NbsrwzwxUbaEnbdQUhY6-5yMLbqdsh/view?usp=sharing</t>
   </si>
   <si>
-    <t xml:space="preserve">Furto de 30 metros de fiação elétrica</t>
+    <t xml:space="preserve">Furto de 30 m de fiação elétrica</t>
   </si>
   <si>
     <t xml:space="preserve">R. 990</t>
@@ -8496,9 +8478,6 @@
     <t xml:space="preserve">https://drive.google.com/file/d/1tLudBIi5hjLT4JjyQI4Breu46BvcXCdO/view?usp=sharing</t>
   </si>
   <si>
-    <t xml:space="preserve">Furto de fiação elétrica</t>
-  </si>
-  <si>
     <t xml:space="preserve">BO-00600.2026.0027705</t>
   </si>
   <si>
@@ -8566,7 +8545,7 @@
     <t xml:space="preserve">https://drive.google.com/file/d/1LZ2XtsQsVSnRWuZqWnHM-dwT1HrkYF-Z/view?usp=sharing</t>
   </si>
   <si>
-    <t xml:space="preserve">Furto de 20 metros de fiação elétrica</t>
+    <t xml:space="preserve">Furto de 20 m de fiação elétrica</t>
   </si>
   <si>
     <t xml:space="preserve">BO-00600.2026.0028065 </t>
@@ -8724,7 +8703,7 @@
     <t xml:space="preserve">https://drive.google.com/file/d/1qujZQUZdCpaHFP76BEq9GaE3dXB8a1mb/view?usp=sharing</t>
   </si>
   <si>
-    <t xml:space="preserve">Femininas furtaram 40 camisetas do brasil</t>
+    <t xml:space="preserve">Femininas furtaram 40 camisas do brasil</t>
   </si>
   <si>
     <t xml:space="preserve">BO-00600.2026.0028013</t>
@@ -8736,7 +8715,7 @@
     <t xml:space="preserve">https://drive.google.com/file/d/1n72lUmiskbk30lwDLsx4Lk3fITQ9tZTd/view?usp=sharing</t>
   </si>
   <si>
-    <t xml:space="preserve">Masculino roubou dinheiro do posto de combustível</t>
+    <t xml:space="preserve">Masculino roubou dinheiro de posto combustível</t>
   </si>
   <si>
     <t xml:space="preserve">PIT</t>
@@ -8785,7 +8764,7 @@
     <t xml:space="preserve">https://drive.google.com/file/d/1cADNjVYE8EahEruPoMNwh6pRtcZU2-i3/view?usp=sharing</t>
   </si>
   <si>
-    <t xml:space="preserve">3 masculinos furtaram uma motocicleta</t>
+    <t xml:space="preserve">3 masculinos furtaram motocicleta</t>
   </si>
   <si>
     <t xml:space="preserve">YAMAHA FZ25 FAZER </t>
@@ -8809,7 +8788,7 @@
     <t xml:space="preserve">https://drive.google.com/file/d/1txL3erVDpNSRCo_tlhMDGV93bB_WTP7y/view?usp=sharing</t>
   </si>
   <si>
-    <t xml:space="preserve">Grupo de masculinos furtou a motocicleta</t>
+    <t xml:space="preserve">Grupo de masculinos furtou motocicleta</t>
   </si>
   <si>
     <r>
@@ -8868,7 +8847,7 @@
     <t xml:space="preserve">https://drive.google.com/file/d/1OKau6JJ8yY4sMnhzHr0CJCtdS8SsGOkA/view?usp=sharing</t>
   </si>
   <si>
-    <t xml:space="preserve">Furto de 6 metros de fiação elétrica</t>
+    <t xml:space="preserve">Furto de 6 m de fiação elétrica</t>
   </si>
   <si>
     <t xml:space="preserve">Igreja </t>
@@ -8905,7 +8884,7 @@
     <t xml:space="preserve">Objetos</t>
   </si>
   <si>
-    <t xml:space="preserve">Masculino furtou computador, dinheiro e bebida</t>
+    <t xml:space="preserve">Masculino furtou computador e dinheiro</t>
   </si>
   <si>
     <t xml:space="preserve">Pastelaria da Vila</t>
@@ -8939,7 +8918,7 @@
     <t xml:space="preserve">https://drive.google.com/file/d/1S7Y40xjoD2TSfEHQSHVzxW0ZKepy6zqm/view?usp=sharing</t>
   </si>
   <si>
-    <t xml:space="preserve">Furto de 8 relógios de energia</t>
+    <t xml:space="preserve">Furto de 8 relógios de energia luz</t>
   </si>
   <si>
     <t xml:space="preserve">Edificio Itaipu</t>
@@ -8972,7 +8951,7 @@
     <t xml:space="preserve">https://drive.google.com/file/d/11Rwcff8BvPEU7q1hw9dwr1oD5R9-e8hk/view?usp=sharing</t>
   </si>
   <si>
-    <t xml:space="preserve">Furto de 956 metros de fiação elétrica</t>
+    <t xml:space="preserve">Furto de 956 m de fiação elétrica</t>
   </si>
   <si>
     <t xml:space="preserve">R. 3130</t>
@@ -9012,12 +8991,117 @@
     <t xml:space="preserve">Furto de 1 whisky e 3 picanha</t>
   </si>
   <si>
+    <t xml:space="preserve">BO-00549.2026.0006019 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://drive.google.com/file/d/1gfffrNxxl1Wu3UZTsU7b24D0S121qPbb/view?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAJAJ DOMINAR D250 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rua Israel</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rua Israel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, Balneário Camboriú, SC, Brasil</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">TPS8I64 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO-00600.2026.0028381 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://drive.google.com/file/d/1TlxiC3z1tap1CXV-MvCR8WXRuAVyq0kZ/view?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Furto de sacola de ferramentas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supermercado Munhoz</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">R. Dom Daniel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, Balneário Camboriú, SC, Brasil</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">BO-00600.2026.0028233 </t>
   </si>
   <si>
     <t xml:space="preserve">https://drive.google.com/file/d/1jBySjue8UAAIU35_3iA7BsJzjZN5y8NH/view?usp=sharing</t>
   </si>
   <si>
+    <t xml:space="preserve">BO-00600.2026.0028657 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://drive.google.com/file/d/11ayKFGhaFt_KNr0mu0HkZBlyKWqUoH3R/view?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 masculinos furtaram medidor de luz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Av. Hermógenes de Assis Feijó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Booster da EMASA </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Av. Hermógenes de Assis Feijó</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">, Balneário Camboriú, SC, Brasil</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">BO-00600.2026.0028197 </t>
   </si>
   <si>
@@ -9030,6 +9114,72 @@
     <t xml:space="preserve">https://drive.google.com/file/d/1mP4rR_hhPXP1-nfe4E-oX3M0CwP_j2Ms/view?usp=sharing</t>
   </si>
   <si>
+    <t xml:space="preserve">BO-00600.2026.0028378 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://drive.google.com/file/d/10ebLTLbC9oX_6Im1Ev9dSQH3_j75EJ1P/view?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Furto placa de motocicleta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HONDA CG TITAN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galli Center Tower </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">R. Arthur Max Doose</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, Balneário Camboriú, SC, Brasil</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">RLF4F71 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO-00600.2026.0028434 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://drive.google.com/file/d/1Oq_LjARIBqWZ9eIduWAiVIYN6zObwmNi/view?usp=sharing</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Av. Brasil</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, Balneário Camboriú, SC, Brasil</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">BOCOP-02317.2026.0002706 </t>
   </si>
   <si>
@@ -9039,7 +9189,7 @@
     <t xml:space="preserve">Tarrafa Pesca</t>
   </si>
   <si>
-    <t xml:space="preserve">Masculino roubou uma tarrafa de pesca</t>
+    <t xml:space="preserve">Masculino roubou tarrafa pesca</t>
   </si>
   <si>
     <t xml:space="preserve">R. Jacarandá</t>
@@ -9140,6 +9290,36 @@
   <si>
     <t xml:space="preserve">TQF3H23 </t>
   </si>
+  <si>
+    <t xml:space="preserve">BOCOP-02317.2026.0002712 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://drive.google.com/file/d/1HyBAwTKD0uuCf0pBmhxBJIgVqFh91RRS/view?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOTOROLA EDGE 60 NEO</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rua Concórdia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, Balneário Camboriú, SC, Brasil</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -9150,7 +9330,7 @@
     <numFmt numFmtId="165" formatCode="hh:mm:ss"/>
     <numFmt numFmtId="166" formatCode="[$R$-416]\ #,##0.00;[RED]\-[$R$-416]\ #,##0.00"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -9256,9 +9436,15 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="3">
@@ -9330,7 +9516,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="63">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -9535,8 +9721,52 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -9825,7 +10055,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD1080"/>
+  <dimension ref="A1:XFD1085"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="1" style="1" width="12.63"/>
@@ -34598,7 +34828,7 @@
         <v>116</v>
       </c>
       <c r="K510" s="11" t="s">
-        <v>2102</v>
+        <v>1811</v>
       </c>
       <c r="L510" s="4"/>
       <c r="M510" s="14" t="s">
@@ -34634,10 +34864,10 @@
         <v>219</v>
       </c>
       <c r="G511" s="11" t="s">
+        <v>2102</v>
+      </c>
+      <c r="H511" s="11" t="s">
         <v>2103</v>
-      </c>
-      <c r="H511" s="11" t="s">
-        <v>2104</v>
       </c>
       <c r="I511" s="14" t="s">
         <v>24</v>
@@ -34646,7 +34876,7 @@
         <v>501</v>
       </c>
       <c r="K511" s="4" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="L511" s="4"/>
       <c r="M511" s="14" t="s">
@@ -34656,7 +34886,7 @@
         <v>123</v>
       </c>
       <c r="O511" s="11" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="P511" s="13" t="s">
         <v>505</v>
@@ -34682,10 +34912,10 @@
         <v>219</v>
       </c>
       <c r="G512" s="11" t="s">
+        <v>2106</v>
+      </c>
+      <c r="H512" s="11" t="s">
         <v>2107</v>
-      </c>
-      <c r="H512" s="11" t="s">
-        <v>2108</v>
       </c>
       <c r="I512" s="14" t="s">
         <v>24</v>
@@ -34694,10 +34924,10 @@
         <v>25</v>
       </c>
       <c r="K512" s="11" t="s">
+        <v>2108</v>
+      </c>
+      <c r="L512" s="11" t="s">
         <v>2109</v>
-      </c>
-      <c r="L512" s="11" t="s">
-        <v>2110</v>
       </c>
       <c r="M512" s="14" t="s">
         <v>1447</v>
@@ -34709,7 +34939,7 @@
         <v>1447</v>
       </c>
       <c r="P512" s="48" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="513" s="48" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34732,10 +34962,10 @@
         <v>219</v>
       </c>
       <c r="G513" s="11" t="s">
+        <v>2106</v>
+      </c>
+      <c r="H513" s="11" t="s">
         <v>2107</v>
-      </c>
-      <c r="H513" s="11" t="s">
-        <v>2108</v>
       </c>
       <c r="I513" s="14" t="s">
         <v>24</v>
@@ -34744,10 +34974,10 @@
         <v>25</v>
       </c>
       <c r="K513" s="11" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="L513" s="11" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="M513" s="14" t="s">
         <v>1447</v>
@@ -34759,7 +34989,7 @@
         <v>1447</v>
       </c>
       <c r="P513" s="48" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="XFD513" s="14"/>
     </row>
@@ -34783,10 +35013,10 @@
         <v>253</v>
       </c>
       <c r="G514" s="11" t="s">
+        <v>2112</v>
+      </c>
+      <c r="H514" s="11" t="s">
         <v>2113</v>
-      </c>
-      <c r="H514" s="11" t="s">
-        <v>2114</v>
       </c>
       <c r="I514" s="14" t="s">
         <v>24</v>
@@ -34795,10 +35025,10 @@
         <v>25</v>
       </c>
       <c r="K514" s="11" t="s">
+        <v>2114</v>
+      </c>
+      <c r="L514" s="11" t="s">
         <v>2115</v>
-      </c>
-      <c r="L514" s="11" t="s">
-        <v>2116</v>
       </c>
       <c r="M514" s="14" t="s">
         <v>88</v>
@@ -34834,10 +35064,10 @@
         <v>253</v>
       </c>
       <c r="G515" s="11" t="s">
+        <v>2116</v>
+      </c>
+      <c r="H515" s="11" t="s">
         <v>2117</v>
-      </c>
-      <c r="H515" s="11" t="s">
-        <v>2118</v>
       </c>
       <c r="I515" s="14" t="s">
         <v>24</v>
@@ -34846,7 +35076,7 @@
         <v>116</v>
       </c>
       <c r="K515" s="11" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="L515" s="11"/>
       <c r="M515" s="9" t="s">
@@ -34883,10 +35113,10 @@
         <v>253</v>
       </c>
       <c r="G516" s="11" t="s">
+        <v>2119</v>
+      </c>
+      <c r="H516" s="11" t="s">
         <v>2120</v>
-      </c>
-      <c r="H516" s="11" t="s">
-        <v>2121</v>
       </c>
       <c r="I516" s="14" t="s">
         <v>306</v>
@@ -34895,7 +35125,7 @@
         <v>128</v>
       </c>
       <c r="K516" s="11" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="L516" s="11"/>
       <c r="M516" s="11" t="s">
@@ -34905,7 +35135,7 @@
         <v>28</v>
       </c>
       <c r="O516" s="11" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="P516" s="11" t="s">
         <v>1915</v>
@@ -34932,10 +35162,10 @@
         <v>253</v>
       </c>
       <c r="G517" s="11" t="s">
+        <v>2123</v>
+      </c>
+      <c r="H517" s="11" t="s">
         <v>2124</v>
-      </c>
-      <c r="H517" s="11" t="s">
-        <v>2125</v>
       </c>
       <c r="I517" s="14" t="s">
         <v>24</v>
@@ -34944,10 +35174,10 @@
         <v>32</v>
       </c>
       <c r="K517" s="11" t="s">
+        <v>2125</v>
+      </c>
+      <c r="L517" s="11" t="s">
         <v>2126</v>
-      </c>
-      <c r="L517" s="11" t="s">
-        <v>2127</v>
       </c>
       <c r="M517" s="14" t="s">
         <v>153</v>
@@ -34956,7 +35186,7 @@
         <v>68</v>
       </c>
       <c r="O517" s="11" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="P517" s="13" t="s">
         <v>155</v>
@@ -34985,10 +35215,10 @@
         <v>253</v>
       </c>
       <c r="G518" s="11" t="s">
+        <v>2128</v>
+      </c>
+      <c r="H518" s="11" t="s">
         <v>2129</v>
-      </c>
-      <c r="H518" s="11" t="s">
-        <v>2130</v>
       </c>
       <c r="I518" s="14" t="s">
         <v>24</v>
@@ -34997,7 +35227,7 @@
         <v>32</v>
       </c>
       <c r="K518" s="11" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="L518" s="4"/>
       <c r="M518" s="14" t="s">
@@ -35033,10 +35263,10 @@
         <v>253</v>
       </c>
       <c r="G519" s="11" t="s">
+        <v>2131</v>
+      </c>
+      <c r="H519" s="11" t="s">
         <v>2132</v>
-      </c>
-      <c r="H519" s="11" t="s">
-        <v>2133</v>
       </c>
       <c r="I519" s="14" t="s">
         <v>24</v>
@@ -35045,7 +35275,7 @@
         <v>107</v>
       </c>
       <c r="K519" s="11" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="L519" s="4"/>
       <c r="M519" s="9" t="s">
@@ -35081,10 +35311,10 @@
         <v>253</v>
       </c>
       <c r="G520" s="11" t="s">
+        <v>2134</v>
+      </c>
+      <c r="H520" s="11" t="s">
         <v>2135</v>
-      </c>
-      <c r="H520" s="11" t="s">
-        <v>2136</v>
       </c>
       <c r="I520" s="14" t="s">
         <v>24</v>
@@ -35129,10 +35359,10 @@
         <v>253</v>
       </c>
       <c r="G521" s="11" t="s">
+        <v>2136</v>
+      </c>
+      <c r="H521" s="11" t="s">
         <v>2137</v>
-      </c>
-      <c r="H521" s="11" t="s">
-        <v>2138</v>
       </c>
       <c r="I521" s="14" t="s">
         <v>24</v>
@@ -35141,7 +35371,7 @@
         <v>39</v>
       </c>
       <c r="K521" s="11" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="L521" s="4"/>
       <c r="M521" s="14" t="s">
@@ -35151,13 +35381,13 @@
         <v>68</v>
       </c>
       <c r="O521" s="11" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="P521" s="13" t="s">
         <v>505</v>
       </c>
       <c r="T521" s="14" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="522" s="48" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35180,10 +35410,10 @@
         <v>253</v>
       </c>
       <c r="G522" s="11" t="s">
+        <v>2141</v>
+      </c>
+      <c r="H522" s="11" t="s">
         <v>2142</v>
-      </c>
-      <c r="H522" s="11" t="s">
-        <v>2143</v>
       </c>
       <c r="I522" s="14" t="s">
         <v>24</v>
@@ -35192,7 +35422,7 @@
         <v>116</v>
       </c>
       <c r="K522" s="11" t="s">
-        <v>2102</v>
+        <v>1811</v>
       </c>
       <c r="L522" s="4"/>
       <c r="M522" s="14" t="s">
@@ -35205,7 +35435,7 @@
         <v>243</v>
       </c>
       <c r="P522" s="48" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="523" s="48" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35228,10 +35458,10 @@
         <v>253</v>
       </c>
       <c r="G523" s="11" t="s">
+        <v>2144</v>
+      </c>
+      <c r="H523" s="11" t="s">
         <v>2145</v>
-      </c>
-      <c r="H523" s="11" t="s">
-        <v>2146</v>
       </c>
       <c r="I523" s="14" t="s">
         <v>24</v>
@@ -35240,7 +35470,7 @@
         <v>116</v>
       </c>
       <c r="K523" s="11" t="s">
-        <v>2102</v>
+        <v>1811</v>
       </c>
       <c r="L523" s="4"/>
       <c r="M523" s="14" t="s">
@@ -35276,10 +35506,10 @@
         <v>273</v>
       </c>
       <c r="G524" s="11" t="s">
+        <v>2146</v>
+      </c>
+      <c r="H524" s="11" t="s">
         <v>2147</v>
-      </c>
-      <c r="H524" s="11" t="s">
-        <v>2148</v>
       </c>
       <c r="I524" s="14" t="s">
         <v>306</v>
@@ -35288,11 +35518,11 @@
         <v>660</v>
       </c>
       <c r="K524" s="2" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="L524" s="11"/>
       <c r="M524" s="11" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="N524" s="13" t="s">
         <v>123</v>
@@ -35301,7 +35531,7 @@
         <v>1025</v>
       </c>
       <c r="P524" s="4" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="525" s="48" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35324,10 +35554,10 @@
         <v>273</v>
       </c>
       <c r="G525" s="11" t="s">
+        <v>2151</v>
+      </c>
+      <c r="H525" s="11" t="s">
         <v>2152</v>
-      </c>
-      <c r="H525" s="11" t="s">
-        <v>2153</v>
       </c>
       <c r="I525" s="14" t="s">
         <v>414</v>
@@ -35336,10 +35566,10 @@
         <v>139</v>
       </c>
       <c r="K525" s="11" t="s">
+        <v>2153</v>
+      </c>
+      <c r="L525" s="11" t="s">
         <v>2154</v>
-      </c>
-      <c r="L525" s="11" t="s">
-        <v>2155</v>
       </c>
       <c r="M525" s="11" t="s">
         <v>309</v>
@@ -35354,7 +35584,7 @@
         <v>1836</v>
       </c>
       <c r="R525" s="11" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="526" s="14" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35377,10 +35607,10 @@
         <v>273</v>
       </c>
       <c r="G526" s="11" t="s">
+        <v>2156</v>
+      </c>
+      <c r="H526" s="11" t="s">
         <v>2157</v>
-      </c>
-      <c r="H526" s="11" t="s">
-        <v>2158</v>
       </c>
       <c r="I526" s="14" t="s">
         <v>24</v>
@@ -35389,7 +35619,7 @@
         <v>660</v>
       </c>
       <c r="K526" s="11" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="L526" s="4"/>
       <c r="M526" s="14" t="s">
@@ -35425,10 +35655,10 @@
         <v>273</v>
       </c>
       <c r="G527" s="11" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="H527" s="11" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="I527" s="14" t="s">
         <v>24</v>
@@ -35473,10 +35703,10 @@
         <v>273</v>
       </c>
       <c r="G528" s="11" t="s">
+        <v>2160</v>
+      </c>
+      <c r="H528" s="11" t="s">
         <v>2161</v>
-      </c>
-      <c r="H528" s="11" t="s">
-        <v>2162</v>
       </c>
       <c r="I528" s="14" t="s">
         <v>414</v>
@@ -35485,7 +35715,7 @@
         <v>104</v>
       </c>
       <c r="K528" s="11" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="L528" s="4"/>
       <c r="M528" s="14" t="s">
@@ -35495,7 +35725,7 @@
         <v>54</v>
       </c>
       <c r="O528" s="11" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="P528" s="13" t="s">
         <v>208</v>
@@ -35521,10 +35751,10 @@
         <v>273</v>
       </c>
       <c r="G529" s="11" t="s">
+        <v>2164</v>
+      </c>
+      <c r="H529" s="11" t="s">
         <v>2165</v>
-      </c>
-      <c r="H529" s="11" t="s">
-        <v>2166</v>
       </c>
       <c r="I529" s="14" t="s">
         <v>820</v>
@@ -35533,10 +35763,10 @@
         <v>329</v>
       </c>
       <c r="K529" s="11" t="s">
+        <v>2166</v>
+      </c>
+      <c r="L529" s="11" t="s">
         <v>2167</v>
-      </c>
-      <c r="L529" s="11" t="s">
-        <v>2168</v>
       </c>
       <c r="M529" s="14" t="s">
         <v>367</v>
@@ -35548,10 +35778,10 @@
         <v>367</v>
       </c>
       <c r="P529" s="48" t="s">
+        <v>2168</v>
+      </c>
+      <c r="R529" s="11" t="s">
         <v>2169</v>
-      </c>
-      <c r="R529" s="11" t="s">
-        <v>2170</v>
       </c>
     </row>
     <row r="530" s="48" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35574,10 +35804,10 @@
         <v>22</v>
       </c>
       <c r="G530" s="11" t="s">
+        <v>2170</v>
+      </c>
+      <c r="H530" s="11" t="s">
         <v>2171</v>
-      </c>
-      <c r="H530" s="11" t="s">
-        <v>2172</v>
       </c>
       <c r="I530" s="14" t="s">
         <v>24</v>
@@ -35586,25 +35816,25 @@
         <v>329</v>
       </c>
       <c r="K530" s="11" t="s">
+        <v>2172</v>
+      </c>
+      <c r="L530" s="11" t="s">
         <v>2173</v>
       </c>
-      <c r="L530" s="11" t="s">
+      <c r="M530" s="14" t="s">
         <v>2174</v>
-      </c>
-      <c r="M530" s="14" t="s">
-        <v>2175</v>
       </c>
       <c r="N530" s="13" t="s">
         <v>35</v>
       </c>
       <c r="O530" s="11" t="s">
+        <v>2175</v>
+      </c>
+      <c r="P530" s="8" t="s">
         <v>2176</v>
       </c>
-      <c r="P530" s="8" t="s">
+      <c r="R530" s="11" t="s">
         <v>2177</v>
-      </c>
-      <c r="R530" s="11" t="s">
-        <v>2178</v>
       </c>
     </row>
     <row r="531" s="48" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35627,10 +35857,10 @@
         <v>22</v>
       </c>
       <c r="G531" s="11" t="s">
+        <v>2178</v>
+      </c>
+      <c r="H531" s="11" t="s">
         <v>2179</v>
-      </c>
-      <c r="H531" s="11" t="s">
-        <v>2180</v>
       </c>
       <c r="I531" s="14" t="s">
         <v>24</v>
@@ -35639,10 +35869,10 @@
         <v>329</v>
       </c>
       <c r="K531" s="11" t="s">
+        <v>2180</v>
+      </c>
+      <c r="L531" s="4" t="s">
         <v>2181</v>
-      </c>
-      <c r="L531" s="4" t="s">
-        <v>2182</v>
       </c>
       <c r="M531" s="11" t="s">
         <v>1706</v>
@@ -35651,13 +35881,13 @@
         <v>276</v>
       </c>
       <c r="O531" s="11" t="s">
+        <v>2182</v>
+      </c>
+      <c r="P531" s="4" t="s">
         <v>2183</v>
       </c>
-      <c r="P531" s="4" t="s">
+      <c r="R531" s="11" t="s">
         <v>2184</v>
-      </c>
-      <c r="R531" s="11" t="s">
-        <v>2185</v>
       </c>
     </row>
     <row r="532" s="48" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35680,10 +35910,10 @@
         <v>22</v>
       </c>
       <c r="G532" s="11" t="s">
+        <v>2185</v>
+      </c>
+      <c r="H532" s="11" t="s">
         <v>2186</v>
-      </c>
-      <c r="H532" s="11" t="s">
-        <v>2187</v>
       </c>
       <c r="I532" s="14" t="s">
         <v>24</v>
@@ -35692,7 +35922,7 @@
         <v>116</v>
       </c>
       <c r="K532" s="11" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="L532" s="11"/>
       <c r="M532" s="11" t="s">
@@ -35702,10 +35932,10 @@
         <v>68</v>
       </c>
       <c r="O532" s="11" t="s">
+        <v>2188</v>
+      </c>
+      <c r="P532" s="4" t="s">
         <v>2189</v>
-      </c>
-      <c r="P532" s="4" t="s">
-        <v>2190</v>
       </c>
     </row>
     <row r="533" s="48" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35728,19 +35958,19 @@
         <v>22</v>
       </c>
       <c r="G533" s="11" t="s">
+        <v>2190</v>
+      </c>
+      <c r="H533" s="11" t="s">
         <v>2191</v>
       </c>
-      <c r="H533" s="11" t="s">
+      <c r="I533" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="J533" s="14" t="s">
         <v>2192</v>
       </c>
-      <c r="I533" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="J533" s="14" t="s">
+      <c r="K533" s="11" t="s">
         <v>2193</v>
-      </c>
-      <c r="K533" s="11" t="s">
-        <v>2194</v>
       </c>
       <c r="L533" s="11"/>
       <c r="M533" s="11" t="s">
@@ -35750,10 +35980,10 @@
         <v>226</v>
       </c>
       <c r="O533" s="11" t="s">
+        <v>2194</v>
+      </c>
+      <c r="P533" s="4" t="s">
         <v>2195</v>
-      </c>
-      <c r="P533" s="4" t="s">
-        <v>2196</v>
       </c>
       <c r="T533" s="14" t="s">
         <v>2005</v>
@@ -35779,10 +36009,10 @@
         <v>22</v>
       </c>
       <c r="G534" s="11" t="s">
+        <v>2196</v>
+      </c>
+      <c r="H534" s="11" t="s">
         <v>2197</v>
-      </c>
-      <c r="H534" s="11" t="s">
-        <v>2198</v>
       </c>
       <c r="I534" s="14" t="s">
         <v>24</v>
@@ -35791,7 +36021,7 @@
         <v>1092</v>
       </c>
       <c r="K534" s="11" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
       <c r="L534" s="11"/>
       <c r="M534" s="11" t="s">
@@ -35801,10 +36031,10 @@
         <v>28</v>
       </c>
       <c r="O534" s="11" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
       <c r="P534" s="48" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="535" s="48" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35827,22 +36057,22 @@
         <v>22</v>
       </c>
       <c r="G535" s="4" t="s">
+        <v>2200</v>
+      </c>
+      <c r="H535" s="11" t="s">
         <v>2201</v>
       </c>
-      <c r="H535" s="11" t="s">
+      <c r="I535" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="J535" s="14" t="s">
         <v>2202</v>
       </c>
-      <c r="I535" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="J535" s="14" t="s">
+      <c r="K535" s="11" t="s">
         <v>2203</v>
       </c>
-      <c r="K535" s="11" t="s">
+      <c r="L535" s="4" t="s">
         <v>2204</v>
-      </c>
-      <c r="L535" s="4" t="s">
-        <v>2205</v>
       </c>
       <c r="M535" s="14" t="s">
         <v>53</v>
@@ -35877,10 +36107,10 @@
         <v>22</v>
       </c>
       <c r="G536" s="11" t="s">
+        <v>2205</v>
+      </c>
+      <c r="H536" s="11" t="s">
         <v>2206</v>
-      </c>
-      <c r="H536" s="11" t="s">
-        <v>2207</v>
       </c>
       <c r="I536" s="14" t="s">
         <v>24</v>
@@ -35889,7 +36119,7 @@
         <v>116</v>
       </c>
       <c r="K536" s="11" t="s">
-        <v>2102</v>
+        <v>1811</v>
       </c>
       <c r="L536" s="11"/>
       <c r="M536" s="14" t="s">
@@ -35925,10 +36155,10 @@
         <v>22</v>
       </c>
       <c r="G537" s="14" t="s">
+        <v>2207</v>
+      </c>
+      <c r="H537" s="11" t="s">
         <v>2208</v>
-      </c>
-      <c r="H537" s="11" t="s">
-        <v>2209</v>
       </c>
       <c r="I537" s="14" t="s">
         <v>24</v>
@@ -35937,23 +36167,23 @@
         <v>116</v>
       </c>
       <c r="K537" s="11" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="L537" s="11"/>
       <c r="M537" s="11" t="s">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="N537" s="13" t="s">
         <v>28</v>
       </c>
       <c r="O537" s="11" t="s">
+        <v>2211</v>
+      </c>
+      <c r="P537" s="4" t="s">
         <v>2212</v>
       </c>
-      <c r="P537" s="4" t="s">
-        <v>2213</v>
-      </c>
       <c r="T537" s="14" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="538" s="48" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35976,10 +36206,10 @@
         <v>22</v>
       </c>
       <c r="G538" s="11" t="s">
+        <v>2213</v>
+      </c>
+      <c r="H538" s="11" t="s">
         <v>2214</v>
-      </c>
-      <c r="H538" s="11" t="s">
-        <v>2215</v>
       </c>
       <c r="I538" s="14" t="s">
         <v>24</v>
@@ -35988,7 +36218,7 @@
         <v>32</v>
       </c>
       <c r="K538" s="11" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="L538" s="11"/>
       <c r="M538" s="14" t="s">
@@ -36004,3511 +36234,3812 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="539" s="48" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="539" s="51" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A539" s="50" t="n">
         <v>18</v>
       </c>
-      <c r="B539" s="48" t="s">
+      <c r="B539" s="51" t="s">
         <v>1471</v>
       </c>
-      <c r="C539" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D539" s="49" t="n">
-        <v>0.138888888888889</v>
-      </c>
-      <c r="E539" s="50" t="s">
+      <c r="C539" s="51" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D539" s="52" t="n">
+        <v>0.117361111111111</v>
+      </c>
+      <c r="E539" s="51" t="s">
         <v>71</v>
       </c>
-      <c r="F539" s="48" t="s">
+      <c r="F539" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="G539" s="4" t="s">
+      <c r="G539" s="53" t="s">
+        <v>2216</v>
+      </c>
+      <c r="H539" s="51" t="s">
         <v>2217</v>
       </c>
-      <c r="H539" s="4" t="s">
+      <c r="I539" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="J539" s="51" t="s">
+        <v>329</v>
+      </c>
+      <c r="K539" s="51" t="s">
+        <v>330</v>
+      </c>
+      <c r="L539" s="53" t="s">
         <v>2218</v>
       </c>
-      <c r="I539" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="J539" s="48" t="s">
-        <v>501</v>
-      </c>
-      <c r="K539" s="4" t="s">
-        <v>2105</v>
-      </c>
-      <c r="L539" s="4"/>
-      <c r="M539" s="48" t="s">
-        <v>503</v>
-      </c>
-      <c r="N539" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="O539" s="4" t="s">
-        <v>504</v>
-      </c>
-      <c r="P539" s="8" t="s">
-        <v>505</v>
-      </c>
-      <c r="XFD539" s="51"/>
-    </row>
-    <row r="540" s="48" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M539" s="53" t="s">
+        <v>1351</v>
+      </c>
+      <c r="N539" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="O539" s="53" t="s">
+        <v>2219</v>
+      </c>
+      <c r="P539" s="53" t="s">
+        <v>2220</v>
+      </c>
+      <c r="R539" s="53" t="s">
+        <v>2221</v>
+      </c>
+      <c r="XFD539" s="54"/>
+    </row>
+    <row r="540" s="51" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A540" s="50" t="n">
         <v>18</v>
       </c>
-      <c r="B540" s="48" t="s">
+      <c r="B540" s="51" t="s">
         <v>1471</v>
       </c>
-      <c r="C540" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D540" s="49" t="n">
-        <v>0.305555555555556</v>
-      </c>
-      <c r="E540" s="50" t="s">
-        <v>126</v>
-      </c>
-      <c r="F540" s="48" t="s">
+      <c r="C540" s="51" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D540" s="52" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="E540" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="F540" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="G540" s="4" t="s">
-        <v>2219</v>
-      </c>
-      <c r="H540" s="4" t="s">
-        <v>2220</v>
-      </c>
-      <c r="I540" s="48" t="s">
-        <v>306</v>
-      </c>
-      <c r="J540" s="48" t="s">
-        <v>468</v>
-      </c>
-      <c r="K540" s="4" t="s">
-        <v>2149</v>
-      </c>
-      <c r="L540" s="4"/>
-      <c r="M540" s="48" t="s">
-        <v>503</v>
-      </c>
-      <c r="N540" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="O540" s="4" t="s">
-        <v>1025</v>
-      </c>
-      <c r="P540" s="8" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="541" s="48" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G540" s="53" t="s">
+        <v>2222</v>
+      </c>
+      <c r="H540" s="51" t="s">
+        <v>2223</v>
+      </c>
+      <c r="I540" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="J540" s="51" t="s">
+        <v>722</v>
+      </c>
+      <c r="K540" s="51" t="s">
+        <v>2224</v>
+      </c>
+      <c r="L540" s="53"/>
+      <c r="M540" s="53" t="s">
+        <v>782</v>
+      </c>
+      <c r="N540" s="51" t="s">
+        <v>226</v>
+      </c>
+      <c r="O540" s="53" t="s">
+        <v>2225</v>
+      </c>
+      <c r="P540" s="53" t="s">
+        <v>2226</v>
+      </c>
+      <c r="R540" s="53"/>
+      <c r="XFD540" s="55"/>
+    </row>
+    <row r="541" s="51" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A541" s="50" t="n">
         <v>18</v>
       </c>
-      <c r="B541" s="48" t="s">
+      <c r="B541" s="51" t="s">
         <v>1471</v>
       </c>
-      <c r="C541" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D541" s="49" t="n">
-        <v>0.458333333333333</v>
+      <c r="C541" s="51" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D541" s="56" t="n">
+        <v>0.138888888888889</v>
       </c>
       <c r="E541" s="50" t="s">
-        <v>126</v>
-      </c>
-      <c r="F541" s="48" t="s">
+        <v>71</v>
+      </c>
+      <c r="F541" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="G541" s="4" t="s">
-        <v>2221</v>
-      </c>
-      <c r="H541" s="4" t="s">
-        <v>2222</v>
-      </c>
-      <c r="I541" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="J541" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="K541" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="L541" s="4"/>
-      <c r="M541" s="48" t="s">
-        <v>206</v>
-      </c>
-      <c r="N541" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="O541" s="48" t="s">
-        <v>206</v>
-      </c>
-      <c r="P541" s="13" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="542" s="48" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G541" s="57" t="s">
+        <v>2227</v>
+      </c>
+      <c r="H541" s="57" t="s">
+        <v>2228</v>
+      </c>
+      <c r="I541" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="J541" s="51" t="s">
+        <v>501</v>
+      </c>
+      <c r="K541" s="57" t="s">
+        <v>2104</v>
+      </c>
+      <c r="L541" s="57"/>
+      <c r="M541" s="51" t="s">
+        <v>503</v>
+      </c>
+      <c r="N541" s="58" t="s">
+        <v>123</v>
+      </c>
+      <c r="O541" s="57" t="s">
+        <v>504</v>
+      </c>
+      <c r="P541" s="58" t="s">
+        <v>505</v>
+      </c>
+      <c r="XFD541" s="59"/>
+    </row>
+    <row r="542" s="51" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A542" s="50" t="n">
         <v>18</v>
       </c>
-      <c r="B542" s="48" t="s">
+      <c r="B542" s="51" t="s">
         <v>1471</v>
       </c>
-      <c r="C542" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D542" s="49" t="n">
-        <v>0.760416666666667</v>
+      <c r="C542" s="51" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D542" s="52" t="n">
+        <v>0.166666666666667</v>
       </c>
       <c r="E542" s="50" t="s">
-        <v>45</v>
-      </c>
-      <c r="F542" s="48" t="s">
+        <v>71</v>
+      </c>
+      <c r="F542" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="G542" s="4" t="s">
-        <v>2223</v>
-      </c>
-      <c r="H542" s="4" t="s">
-        <v>2224</v>
-      </c>
-      <c r="I542" s="48" t="s">
-        <v>414</v>
-      </c>
-      <c r="J542" s="48" t="s">
-        <v>2225</v>
-      </c>
-      <c r="K542" s="4" t="s">
-        <v>2226</v>
-      </c>
-      <c r="L542" s="4"/>
-      <c r="M542" s="4" t="s">
-        <v>2227</v>
-      </c>
-      <c r="N542" s="8" t="s">
-        <v>2228</v>
-      </c>
-      <c r="O542" s="4" t="s">
+      <c r="G542" s="53" t="s">
         <v>2229</v>
       </c>
-      <c r="P542" s="4" t="s">
+      <c r="H542" s="57" t="s">
         <v>2230</v>
       </c>
-    </row>
-    <row r="543" s="48" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I542" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="J542" s="51" t="s">
+        <v>1092</v>
+      </c>
+      <c r="K542" s="57" t="s">
+        <v>2231</v>
+      </c>
+      <c r="L542" s="57"/>
+      <c r="M542" s="53" t="s">
+        <v>2232</v>
+      </c>
+      <c r="N542" s="58" t="s">
+        <v>195</v>
+      </c>
+      <c r="O542" s="53" t="s">
+        <v>2233</v>
+      </c>
+      <c r="P542" s="53" t="s">
+        <v>2234</v>
+      </c>
+    </row>
+    <row r="543" s="51" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A543" s="50" t="n">
         <v>18</v>
       </c>
-      <c r="B543" s="48" t="s">
+      <c r="B543" s="51" t="s">
         <v>1471</v>
       </c>
-      <c r="C543" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D543" s="49" t="n">
-        <v>0.822222222222222</v>
-      </c>
-      <c r="E543" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="F543" s="48" t="s">
+      <c r="C543" s="51" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D543" s="56" t="n">
+        <v>0.305555555555556</v>
+      </c>
+      <c r="E543" s="50" t="s">
+        <v>126</v>
+      </c>
+      <c r="F543" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="G543" s="4" t="s">
-        <v>2231</v>
-      </c>
-      <c r="H543" s="48" t="s">
-        <v>2232</v>
-      </c>
-      <c r="I543" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="J543" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="K543" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="M543" s="48" t="s">
-        <v>2233</v>
-      </c>
-      <c r="N543" s="48" t="s">
-        <v>28</v>
-      </c>
-      <c r="O543" s="48" t="s">
-        <v>2234</v>
-      </c>
-      <c r="P543" s="48" t="s">
+      <c r="G543" s="57" t="s">
         <v>2235</v>
       </c>
-    </row>
-    <row r="544" s="48" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H543" s="57" t="s">
+        <v>2236</v>
+      </c>
+      <c r="I543" s="51" t="s">
+        <v>306</v>
+      </c>
+      <c r="J543" s="51" t="s">
+        <v>468</v>
+      </c>
+      <c r="K543" s="57" t="s">
+        <v>2148</v>
+      </c>
+      <c r="L543" s="57"/>
+      <c r="M543" s="51" t="s">
+        <v>503</v>
+      </c>
+      <c r="N543" s="58" t="s">
+        <v>123</v>
+      </c>
+      <c r="O543" s="57" t="s">
+        <v>1025</v>
+      </c>
+      <c r="P543" s="58" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="544" s="51" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A544" s="50" t="n">
         <v>18</v>
       </c>
-      <c r="B544" s="48" t="s">
+      <c r="B544" s="51" t="s">
         <v>1471</v>
       </c>
-      <c r="C544" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D544" s="49" t="n">
+      <c r="C544" s="51" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D544" s="56" t="n">
+        <v>0.458333333333333</v>
+      </c>
+      <c r="E544" s="50" t="s">
+        <v>126</v>
+      </c>
+      <c r="F544" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="G544" s="57" t="s">
+        <v>2237</v>
+      </c>
+      <c r="H544" s="57" t="s">
+        <v>2238</v>
+      </c>
+      <c r="I544" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="J544" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="K544" s="57" t="s">
+        <v>160</v>
+      </c>
+      <c r="L544" s="57"/>
+      <c r="M544" s="51" t="s">
+        <v>206</v>
+      </c>
+      <c r="N544" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="O544" s="51" t="s">
+        <v>206</v>
+      </c>
+      <c r="P544" s="60" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="545" s="51" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A545" s="50" t="n">
+        <v>18</v>
+      </c>
+      <c r="B545" s="51" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C545" s="51" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D545" s="52" t="n">
+        <v>0.541666666666667</v>
+      </c>
+      <c r="E545" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="F545" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="G545" s="53" t="s">
+        <v>2239</v>
+      </c>
+      <c r="H545" s="57" t="s">
+        <v>2240</v>
+      </c>
+      <c r="I545" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="J545" s="51" t="s">
+        <v>836</v>
+      </c>
+      <c r="K545" s="57" t="s">
+        <v>2241</v>
+      </c>
+      <c r="L545" s="53" t="s">
+        <v>2242</v>
+      </c>
+      <c r="M545" s="53" t="s">
+        <v>302</v>
+      </c>
+      <c r="N545" s="58" t="s">
+        <v>131</v>
+      </c>
+      <c r="O545" s="53" t="s">
+        <v>2243</v>
+      </c>
+      <c r="P545" s="53" t="s">
+        <v>2244</v>
+      </c>
+      <c r="R545" s="53" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="546" s="51" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A546" s="50" t="n">
+        <v>18</v>
+      </c>
+      <c r="B546" s="51" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C546" s="51" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D546" s="52" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E546" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="F546" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="G546" s="53" t="s">
+        <v>2246</v>
+      </c>
+      <c r="H546" s="57" t="s">
+        <v>2247</v>
+      </c>
+      <c r="I546" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="J546" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="K546" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="L546" s="57"/>
+      <c r="M546" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="N546" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="O546" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="P546" s="51" t="s">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="547" s="51" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A547" s="50" t="n">
+        <v>18</v>
+      </c>
+      <c r="B547" s="51" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C547" s="51" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D547" s="56" t="n">
+        <v>0.760416666666667</v>
+      </c>
+      <c r="E547" s="50" t="s">
+        <v>45</v>
+      </c>
+      <c r="F547" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="G547" s="57" t="s">
+        <v>2249</v>
+      </c>
+      <c r="H547" s="57" t="s">
+        <v>2250</v>
+      </c>
+      <c r="I547" s="51" t="s">
+        <v>414</v>
+      </c>
+      <c r="J547" s="51" t="s">
+        <v>2251</v>
+      </c>
+      <c r="K547" s="57" t="s">
+        <v>2252</v>
+      </c>
+      <c r="L547" s="57"/>
+      <c r="M547" s="57" t="s">
+        <v>2253</v>
+      </c>
+      <c r="N547" s="58" t="s">
+        <v>2254</v>
+      </c>
+      <c r="O547" s="57" t="s">
+        <v>2255</v>
+      </c>
+      <c r="P547" s="57" t="s">
+        <v>2256</v>
+      </c>
+    </row>
+    <row r="548" s="51" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A548" s="50" t="n">
+        <v>18</v>
+      </c>
+      <c r="B548" s="51" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C548" s="51" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D548" s="56" t="n">
+        <v>0.822222222222222</v>
+      </c>
+      <c r="E548" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="F548" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="G548" s="57" t="s">
+        <v>2257</v>
+      </c>
+      <c r="H548" s="51" t="s">
+        <v>2258</v>
+      </c>
+      <c r="I548" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="J548" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="K548" s="51" t="s">
+        <v>179</v>
+      </c>
+      <c r="M548" s="51" t="s">
+        <v>2259</v>
+      </c>
+      <c r="N548" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="O548" s="51" t="s">
+        <v>2260</v>
+      </c>
+      <c r="P548" s="51" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="549" s="51" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A549" s="50" t="n">
+        <v>18</v>
+      </c>
+      <c r="B549" s="51" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C549" s="51" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D549" s="56" t="n">
         <v>0.875</v>
       </c>
-      <c r="E544" s="48" t="s">
+      <c r="E549" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="F544" s="48" t="s">
+      <c r="F549" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="G544" s="4" t="s">
-        <v>2236</v>
-      </c>
-      <c r="H544" s="48" t="s">
-        <v>2237</v>
-      </c>
-      <c r="I544" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="J544" s="48" t="s">
+      <c r="G549" s="57" t="s">
+        <v>2262</v>
+      </c>
+      <c r="H549" s="51" t="s">
+        <v>2263</v>
+      </c>
+      <c r="I549" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="J549" s="51" t="s">
         <v>329</v>
       </c>
-      <c r="K544" s="48" t="s">
+      <c r="K549" s="51" t="s">
         <v>330</v>
       </c>
-      <c r="L544" s="4" t="s">
-        <v>2238</v>
-      </c>
-      <c r="M544" s="48" t="s">
+      <c r="L549" s="57" t="s">
+        <v>2264</v>
+      </c>
+      <c r="M549" s="51" t="s">
         <v>332</v>
       </c>
-      <c r="N544" s="48" t="s">
+      <c r="N549" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="O544" s="48" t="s">
+      <c r="O549" s="51" t="s">
         <v>332</v>
       </c>
-      <c r="P544" s="48" t="s">
-        <v>2239</v>
-      </c>
-      <c r="R544" s="4" t="s">
-        <v>2240</v>
-      </c>
-    </row>
-    <row r="545" s="51" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="L545" s="1"/>
-    </row>
-    <row r="546" s="51" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L546" s="1"/>
-    </row>
-    <row r="547" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A547" s="50"/>
-      <c r="E547" s="50"/>
-      <c r="N547" s="8"/>
-      <c r="P547" s="8"/>
-    </row>
-    <row r="548" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A548" s="50"/>
-      <c r="E548" s="50"/>
-      <c r="N548" s="8"/>
-      <c r="P548" s="8"/>
-    </row>
-    <row r="549" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A549" s="50"/>
-      <c r="E549" s="50"/>
-      <c r="N549" s="8"/>
-      <c r="P549" s="8"/>
-    </row>
-    <row r="550" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A550" s="50"/>
-      <c r="E550" s="50"/>
-      <c r="N550" s="8"/>
-      <c r="P550" s="8"/>
-    </row>
-    <row r="551" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A551" s="50"/>
-      <c r="E551" s="50"/>
-      <c r="N551" s="8"/>
-      <c r="P551" s="8"/>
+      <c r="P549" s="51" t="s">
+        <v>2265</v>
+      </c>
+      <c r="R549" s="57" t="s">
+        <v>2266</v>
+      </c>
+    </row>
+    <row r="550" s="55" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A550" s="50" t="n">
+        <v>18</v>
+      </c>
+      <c r="B550" s="51" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C550" s="51" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D550" s="52" t="n">
+        <v>0.916666666666667</v>
+      </c>
+      <c r="E550" s="55" t="s">
+        <v>45</v>
+      </c>
+      <c r="F550" s="55" t="s">
+        <v>72</v>
+      </c>
+      <c r="G550" s="53" t="s">
+        <v>2267</v>
+      </c>
+      <c r="H550" s="55" t="s">
+        <v>2268</v>
+      </c>
+      <c r="I550" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="J550" s="55" t="s">
+        <v>57</v>
+      </c>
+      <c r="K550" s="55" t="s">
+        <v>58</v>
+      </c>
+      <c r="L550" s="53" t="s">
+        <v>2269</v>
+      </c>
+      <c r="M550" s="53" t="s">
+        <v>1384</v>
+      </c>
+      <c r="N550" s="55" t="s">
+        <v>68</v>
+      </c>
+      <c r="O550" s="53" t="s">
+        <v>1385</v>
+      </c>
+      <c r="P550" s="53" t="s">
+        <v>2270</v>
+      </c>
+      <c r="XFD550" s="51"/>
+    </row>
+    <row r="551" s="61" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L551" s="1"/>
     </row>
     <row r="552" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A552" s="50"/>
-      <c r="E552" s="50"/>
+      <c r="A552" s="62"/>
+      <c r="E552" s="62"/>
       <c r="N552" s="8"/>
       <c r="P552" s="8"/>
     </row>
     <row r="553" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A553" s="50"/>
-      <c r="E553" s="50"/>
+      <c r="A553" s="62"/>
+      <c r="E553" s="62"/>
       <c r="N553" s="8"/>
       <c r="P553" s="8"/>
     </row>
     <row r="554" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A554" s="50"/>
-      <c r="E554" s="50"/>
+      <c r="A554" s="62"/>
+      <c r="E554" s="62"/>
       <c r="N554" s="8"/>
       <c r="P554" s="8"/>
     </row>
     <row r="555" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A555" s="50"/>
-      <c r="E555" s="50"/>
+      <c r="A555" s="62"/>
+      <c r="E555" s="62"/>
       <c r="N555" s="8"/>
       <c r="P555" s="8"/>
     </row>
     <row r="556" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A556" s="50"/>
-      <c r="E556" s="50"/>
+      <c r="A556" s="62"/>
+      <c r="E556" s="62"/>
       <c r="N556" s="8"/>
       <c r="P556" s="8"/>
     </row>
     <row r="557" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A557" s="50"/>
-      <c r="E557" s="50"/>
+      <c r="A557" s="62"/>
+      <c r="E557" s="62"/>
       <c r="N557" s="8"/>
       <c r="P557" s="8"/>
     </row>
     <row r="558" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A558" s="50"/>
-      <c r="E558" s="50"/>
+      <c r="A558" s="62"/>
+      <c r="E558" s="62"/>
       <c r="N558" s="8"/>
       <c r="P558" s="8"/>
     </row>
     <row r="559" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A559" s="50"/>
-      <c r="E559" s="50"/>
+      <c r="A559" s="62"/>
+      <c r="E559" s="62"/>
       <c r="N559" s="8"/>
       <c r="P559" s="8"/>
     </row>
     <row r="560" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A560" s="50"/>
-      <c r="E560" s="50"/>
+      <c r="A560" s="62"/>
+      <c r="E560" s="62"/>
       <c r="N560" s="8"/>
       <c r="P560" s="8"/>
     </row>
     <row r="561" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A561" s="50"/>
-      <c r="E561" s="50"/>
+      <c r="A561" s="62"/>
+      <c r="E561" s="62"/>
       <c r="N561" s="8"/>
       <c r="P561" s="8"/>
     </row>
     <row r="562" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A562" s="50"/>
-      <c r="E562" s="50"/>
+      <c r="A562" s="62"/>
+      <c r="E562" s="62"/>
       <c r="N562" s="8"/>
       <c r="P562" s="8"/>
     </row>
     <row r="563" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A563" s="50"/>
-      <c r="E563" s="50"/>
+      <c r="A563" s="62"/>
+      <c r="E563" s="62"/>
       <c r="N563" s="8"/>
       <c r="P563" s="8"/>
     </row>
     <row r="564" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A564" s="50"/>
-      <c r="E564" s="50"/>
+      <c r="A564" s="62"/>
+      <c r="E564" s="62"/>
       <c r="N564" s="8"/>
       <c r="P564" s="8"/>
     </row>
     <row r="565" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A565" s="50"/>
-      <c r="E565" s="50"/>
+      <c r="A565" s="62"/>
+      <c r="E565" s="62"/>
       <c r="N565" s="8"/>
       <c r="P565" s="8"/>
     </row>
     <row r="566" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A566" s="50"/>
-      <c r="E566" s="50"/>
+      <c r="A566" s="62"/>
+      <c r="E566" s="62"/>
       <c r="N566" s="8"/>
       <c r="P566" s="8"/>
     </row>
     <row r="567" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A567" s="50"/>
-      <c r="E567" s="50"/>
+      <c r="A567" s="62"/>
+      <c r="E567" s="62"/>
       <c r="N567" s="8"/>
       <c r="P567" s="8"/>
     </row>
     <row r="568" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A568" s="50"/>
-      <c r="E568" s="50"/>
+      <c r="A568" s="62"/>
+      <c r="E568" s="62"/>
       <c r="N568" s="8"/>
       <c r="P568" s="8"/>
     </row>
     <row r="569" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A569" s="50"/>
-      <c r="E569" s="50"/>
+      <c r="A569" s="62"/>
+      <c r="E569" s="62"/>
       <c r="N569" s="8"/>
       <c r="P569" s="8"/>
     </row>
     <row r="570" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A570" s="50"/>
-      <c r="E570" s="50"/>
+      <c r="A570" s="62"/>
+      <c r="E570" s="62"/>
       <c r="N570" s="8"/>
       <c r="P570" s="8"/>
     </row>
     <row r="571" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A571" s="50"/>
-      <c r="E571" s="50"/>
+      <c r="A571" s="62"/>
+      <c r="E571" s="62"/>
       <c r="N571" s="8"/>
       <c r="P571" s="8"/>
     </row>
     <row r="572" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A572" s="50"/>
-      <c r="E572" s="50"/>
+      <c r="A572" s="62"/>
+      <c r="E572" s="62"/>
       <c r="N572" s="8"/>
       <c r="P572" s="8"/>
     </row>
     <row r="573" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A573" s="50"/>
-      <c r="E573" s="50"/>
+      <c r="A573" s="62"/>
+      <c r="E573" s="62"/>
       <c r="N573" s="8"/>
       <c r="P573" s="8"/>
     </row>
     <row r="574" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A574" s="50"/>
-      <c r="E574" s="50"/>
+      <c r="A574" s="62"/>
+      <c r="E574" s="62"/>
       <c r="N574" s="8"/>
       <c r="P574" s="8"/>
     </row>
     <row r="575" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A575" s="50"/>
-      <c r="E575" s="50"/>
+      <c r="A575" s="62"/>
+      <c r="E575" s="62"/>
       <c r="N575" s="8"/>
       <c r="P575" s="8"/>
     </row>
     <row r="576" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A576" s="50"/>
-      <c r="E576" s="50"/>
+      <c r="A576" s="62"/>
+      <c r="E576" s="62"/>
       <c r="N576" s="8"/>
       <c r="P576" s="8"/>
     </row>
     <row r="577" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A577" s="50"/>
-      <c r="E577" s="50"/>
+      <c r="A577" s="62"/>
+      <c r="E577" s="62"/>
       <c r="N577" s="8"/>
       <c r="P577" s="8"/>
     </row>
     <row r="578" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A578" s="50"/>
-      <c r="E578" s="50"/>
+      <c r="A578" s="62"/>
+      <c r="E578" s="62"/>
       <c r="N578" s="8"/>
       <c r="P578" s="8"/>
     </row>
     <row r="579" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A579" s="50"/>
-      <c r="E579" s="50"/>
+      <c r="A579" s="62"/>
+      <c r="E579" s="62"/>
       <c r="N579" s="8"/>
       <c r="P579" s="8"/>
     </row>
     <row r="580" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A580" s="50"/>
-      <c r="E580" s="50"/>
+      <c r="A580" s="62"/>
+      <c r="E580" s="62"/>
       <c r="N580" s="8"/>
       <c r="P580" s="8"/>
     </row>
     <row r="581" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A581" s="50"/>
-      <c r="E581" s="50"/>
+      <c r="A581" s="62"/>
+      <c r="E581" s="62"/>
       <c r="N581" s="8"/>
       <c r="P581" s="8"/>
     </row>
     <row r="582" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A582" s="50"/>
-      <c r="E582" s="50"/>
+      <c r="A582" s="62"/>
+      <c r="E582" s="62"/>
       <c r="N582" s="8"/>
       <c r="P582" s="8"/>
     </row>
     <row r="583" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A583" s="50"/>
-      <c r="E583" s="50"/>
+      <c r="A583" s="62"/>
+      <c r="E583" s="62"/>
       <c r="N583" s="8"/>
       <c r="P583" s="8"/>
     </row>
     <row r="584" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A584" s="50"/>
-      <c r="E584" s="50"/>
+      <c r="A584" s="62"/>
+      <c r="E584" s="62"/>
       <c r="N584" s="8"/>
       <c r="P584" s="8"/>
     </row>
     <row r="585" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A585" s="50"/>
-      <c r="E585" s="50"/>
+      <c r="A585" s="62"/>
+      <c r="E585" s="62"/>
       <c r="N585" s="8"/>
       <c r="P585" s="8"/>
     </row>
     <row r="586" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A586" s="50"/>
-      <c r="E586" s="50"/>
+      <c r="A586" s="62"/>
+      <c r="E586" s="62"/>
       <c r="N586" s="8"/>
       <c r="P586" s="8"/>
     </row>
     <row r="587" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A587" s="50"/>
-      <c r="E587" s="50"/>
+      <c r="A587" s="62"/>
+      <c r="E587" s="62"/>
       <c r="N587" s="8"/>
       <c r="P587" s="8"/>
     </row>
     <row r="588" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A588" s="50"/>
-      <c r="E588" s="50"/>
+      <c r="A588" s="62"/>
+      <c r="E588" s="62"/>
       <c r="N588" s="8"/>
       <c r="P588" s="8"/>
     </row>
     <row r="589" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A589" s="50"/>
-      <c r="E589" s="50"/>
+      <c r="A589" s="62"/>
+      <c r="E589" s="62"/>
       <c r="N589" s="8"/>
       <c r="P589" s="8"/>
     </row>
     <row r="590" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A590" s="50"/>
-      <c r="E590" s="50"/>
+      <c r="A590" s="62"/>
+      <c r="E590" s="62"/>
       <c r="N590" s="8"/>
       <c r="P590" s="8"/>
     </row>
     <row r="591" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A591" s="50"/>
-      <c r="E591" s="50"/>
+      <c r="A591" s="62"/>
+      <c r="E591" s="62"/>
       <c r="N591" s="8"/>
       <c r="P591" s="8"/>
     </row>
     <row r="592" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A592" s="50"/>
-      <c r="E592" s="50"/>
+      <c r="A592" s="62"/>
+      <c r="E592" s="62"/>
       <c r="N592" s="8"/>
       <c r="P592" s="8"/>
     </row>
     <row r="593" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A593" s="50"/>
-      <c r="E593" s="50"/>
+      <c r="A593" s="62"/>
+      <c r="E593" s="62"/>
       <c r="N593" s="8"/>
       <c r="P593" s="8"/>
     </row>
     <row r="594" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A594" s="50"/>
-      <c r="E594" s="50"/>
+      <c r="A594" s="62"/>
+      <c r="E594" s="62"/>
       <c r="N594" s="8"/>
       <c r="P594" s="8"/>
     </row>
     <row r="595" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A595" s="50"/>
-      <c r="E595" s="50"/>
+      <c r="A595" s="62"/>
+      <c r="E595" s="62"/>
       <c r="N595" s="8"/>
       <c r="P595" s="8"/>
     </row>
     <row r="596" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A596" s="50"/>
-      <c r="E596" s="50"/>
+      <c r="A596" s="62"/>
+      <c r="E596" s="62"/>
       <c r="N596" s="8"/>
       <c r="P596" s="8"/>
     </row>
     <row r="597" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A597" s="50"/>
-      <c r="E597" s="50"/>
+      <c r="A597" s="62"/>
+      <c r="E597" s="62"/>
       <c r="N597" s="8"/>
       <c r="P597" s="8"/>
     </row>
     <row r="598" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A598" s="50"/>
-      <c r="E598" s="50"/>
+      <c r="A598" s="62"/>
+      <c r="E598" s="62"/>
       <c r="N598" s="8"/>
       <c r="P598" s="8"/>
     </row>
     <row r="599" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A599" s="50"/>
-      <c r="E599" s="50"/>
+      <c r="A599" s="62"/>
+      <c r="E599" s="62"/>
       <c r="N599" s="8"/>
       <c r="P599" s="8"/>
     </row>
     <row r="600" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A600" s="50"/>
-      <c r="E600" s="50"/>
+      <c r="A600" s="62"/>
+      <c r="E600" s="62"/>
       <c r="N600" s="8"/>
       <c r="P600" s="8"/>
     </row>
     <row r="601" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A601" s="50"/>
-      <c r="E601" s="50"/>
+      <c r="A601" s="62"/>
+      <c r="E601" s="62"/>
       <c r="N601" s="8"/>
       <c r="P601" s="8"/>
     </row>
     <row r="602" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A602" s="50"/>
-      <c r="E602" s="50"/>
+      <c r="A602" s="62"/>
+      <c r="E602" s="62"/>
       <c r="N602" s="8"/>
       <c r="P602" s="8"/>
     </row>
     <row r="603" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A603" s="50"/>
-      <c r="E603" s="50"/>
+      <c r="A603" s="62"/>
+      <c r="E603" s="62"/>
       <c r="N603" s="8"/>
       <c r="P603" s="8"/>
     </row>
     <row r="604" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A604" s="50"/>
-      <c r="E604" s="50"/>
+      <c r="A604" s="62"/>
+      <c r="E604" s="62"/>
       <c r="N604" s="8"/>
       <c r="P604" s="8"/>
     </row>
     <row r="605" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A605" s="50"/>
-      <c r="E605" s="50"/>
+      <c r="A605" s="62"/>
+      <c r="E605" s="62"/>
       <c r="N605" s="8"/>
       <c r="P605" s="8"/>
     </row>
     <row r="606" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A606" s="50"/>
-      <c r="E606" s="50"/>
+      <c r="A606" s="62"/>
+      <c r="E606" s="62"/>
       <c r="N606" s="8"/>
       <c r="P606" s="8"/>
     </row>
     <row r="607" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A607" s="50"/>
-      <c r="E607" s="50"/>
+      <c r="A607" s="62"/>
+      <c r="E607" s="62"/>
       <c r="N607" s="8"/>
       <c r="P607" s="8"/>
     </row>
     <row r="608" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A608" s="50"/>
-      <c r="E608" s="50"/>
+      <c r="A608" s="62"/>
+      <c r="E608" s="62"/>
       <c r="N608" s="8"/>
       <c r="P608" s="8"/>
     </row>
     <row r="609" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A609" s="50"/>
-      <c r="E609" s="50"/>
+      <c r="A609" s="62"/>
+      <c r="E609" s="62"/>
       <c r="N609" s="8"/>
       <c r="P609" s="8"/>
     </row>
     <row r="610" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A610" s="50"/>
-      <c r="E610" s="50"/>
+      <c r="A610" s="62"/>
+      <c r="E610" s="62"/>
       <c r="N610" s="8"/>
       <c r="P610" s="8"/>
     </row>
     <row r="611" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A611" s="50"/>
-      <c r="E611" s="50"/>
+      <c r="A611" s="62"/>
+      <c r="E611" s="62"/>
       <c r="N611" s="8"/>
       <c r="P611" s="8"/>
     </row>
     <row r="612" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A612" s="50"/>
-      <c r="E612" s="50"/>
+      <c r="A612" s="62"/>
+      <c r="E612" s="62"/>
       <c r="N612" s="8"/>
       <c r="P612" s="8"/>
     </row>
     <row r="613" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A613" s="50"/>
-      <c r="E613" s="50"/>
+      <c r="A613" s="62"/>
+      <c r="E613" s="62"/>
       <c r="N613" s="8"/>
       <c r="P613" s="8"/>
     </row>
     <row r="614" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A614" s="50"/>
-      <c r="E614" s="50"/>
+      <c r="A614" s="62"/>
+      <c r="E614" s="62"/>
       <c r="N614" s="8"/>
       <c r="P614" s="8"/>
     </row>
     <row r="615" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A615" s="50"/>
-      <c r="E615" s="50"/>
+      <c r="A615" s="62"/>
+      <c r="E615" s="62"/>
       <c r="N615" s="8"/>
       <c r="P615" s="8"/>
     </row>
     <row r="616" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A616" s="50"/>
-      <c r="E616" s="50"/>
+      <c r="A616" s="62"/>
+      <c r="E616" s="62"/>
       <c r="N616" s="8"/>
       <c r="P616" s="8"/>
     </row>
     <row r="617" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A617" s="50"/>
-      <c r="E617" s="50"/>
+      <c r="A617" s="62"/>
+      <c r="E617" s="62"/>
       <c r="N617" s="8"/>
       <c r="P617" s="8"/>
     </row>
     <row r="618" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A618" s="50"/>
-      <c r="E618" s="50"/>
+      <c r="A618" s="62"/>
+      <c r="E618" s="62"/>
       <c r="N618" s="8"/>
       <c r="P618" s="8"/>
     </row>
     <row r="619" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A619" s="50"/>
-      <c r="E619" s="50"/>
+      <c r="A619" s="62"/>
+      <c r="E619" s="62"/>
       <c r="N619" s="8"/>
       <c r="P619" s="8"/>
     </row>
     <row r="620" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A620" s="50"/>
-      <c r="E620" s="50"/>
+      <c r="A620" s="62"/>
+      <c r="E620" s="62"/>
       <c r="N620" s="8"/>
       <c r="P620" s="8"/>
     </row>
     <row r="621" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A621" s="50"/>
-      <c r="E621" s="50"/>
+      <c r="A621" s="62"/>
+      <c r="E621" s="62"/>
       <c r="N621" s="8"/>
       <c r="P621" s="8"/>
     </row>
     <row r="622" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A622" s="50"/>
-      <c r="E622" s="50"/>
+      <c r="A622" s="62"/>
+      <c r="E622" s="62"/>
       <c r="N622" s="8"/>
       <c r="P622" s="8"/>
     </row>
     <row r="623" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A623" s="50"/>
-      <c r="E623" s="50"/>
+      <c r="A623" s="62"/>
+      <c r="E623" s="62"/>
       <c r="N623" s="8"/>
       <c r="P623" s="8"/>
     </row>
     <row r="624" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A624" s="50"/>
-      <c r="E624" s="50"/>
+      <c r="A624" s="62"/>
+      <c r="E624" s="62"/>
       <c r="N624" s="8"/>
       <c r="P624" s="8"/>
     </row>
     <row r="625" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A625" s="50"/>
-      <c r="E625" s="50"/>
+      <c r="A625" s="62"/>
+      <c r="E625" s="62"/>
       <c r="N625" s="8"/>
       <c r="P625" s="8"/>
     </row>
     <row r="626" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A626" s="50"/>
-      <c r="E626" s="50"/>
+      <c r="A626" s="62"/>
+      <c r="E626" s="62"/>
       <c r="N626" s="8"/>
       <c r="P626" s="8"/>
     </row>
     <row r="627" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A627" s="50"/>
-      <c r="E627" s="50"/>
+      <c r="A627" s="62"/>
+      <c r="E627" s="62"/>
       <c r="N627" s="8"/>
       <c r="P627" s="8"/>
     </row>
     <row r="628" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A628" s="50"/>
-      <c r="E628" s="50"/>
+      <c r="A628" s="62"/>
+      <c r="E628" s="62"/>
       <c r="N628" s="8"/>
       <c r="P628" s="8"/>
     </row>
     <row r="629" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A629" s="50"/>
-      <c r="E629" s="50"/>
+      <c r="A629" s="62"/>
+      <c r="E629" s="62"/>
       <c r="N629" s="8"/>
       <c r="P629" s="8"/>
     </row>
     <row r="630" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A630" s="50"/>
-      <c r="E630" s="50"/>
+      <c r="A630" s="62"/>
+      <c r="E630" s="62"/>
       <c r="N630" s="8"/>
       <c r="P630" s="8"/>
     </row>
     <row r="631" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A631" s="50"/>
-      <c r="E631" s="50"/>
+      <c r="A631" s="62"/>
+      <c r="E631" s="62"/>
       <c r="N631" s="8"/>
       <c r="P631" s="8"/>
     </row>
     <row r="632" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A632" s="50"/>
-      <c r="E632" s="50"/>
+      <c r="A632" s="62"/>
+      <c r="E632" s="62"/>
       <c r="N632" s="8"/>
       <c r="P632" s="8"/>
     </row>
     <row r="633" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A633" s="50"/>
-      <c r="E633" s="50"/>
+      <c r="A633" s="62"/>
+      <c r="E633" s="62"/>
       <c r="N633" s="8"/>
       <c r="P633" s="8"/>
     </row>
     <row r="634" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A634" s="50"/>
-      <c r="E634" s="50"/>
+      <c r="A634" s="62"/>
+      <c r="E634" s="62"/>
       <c r="N634" s="8"/>
       <c r="P634" s="8"/>
     </row>
     <row r="635" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A635" s="50"/>
-      <c r="E635" s="50"/>
+      <c r="A635" s="62"/>
+      <c r="E635" s="62"/>
       <c r="N635" s="8"/>
       <c r="P635" s="8"/>
     </row>
     <row r="636" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A636" s="50"/>
-      <c r="E636" s="50"/>
+      <c r="A636" s="62"/>
+      <c r="E636" s="62"/>
       <c r="N636" s="8"/>
       <c r="P636" s="8"/>
     </row>
     <row r="637" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A637" s="50"/>
-      <c r="E637" s="50"/>
+      <c r="A637" s="62"/>
+      <c r="E637" s="62"/>
       <c r="N637" s="8"/>
       <c r="P637" s="8"/>
     </row>
     <row r="638" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A638" s="50"/>
-      <c r="E638" s="50"/>
+      <c r="A638" s="62"/>
+      <c r="E638" s="62"/>
       <c r="N638" s="8"/>
       <c r="P638" s="8"/>
     </row>
     <row r="639" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A639" s="50"/>
-      <c r="E639" s="50"/>
+      <c r="A639" s="62"/>
+      <c r="E639" s="62"/>
       <c r="N639" s="8"/>
       <c r="P639" s="8"/>
     </row>
     <row r="640" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A640" s="50"/>
-      <c r="E640" s="50"/>
+      <c r="A640" s="62"/>
+      <c r="E640" s="62"/>
       <c r="N640" s="8"/>
       <c r="P640" s="8"/>
     </row>
     <row r="641" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A641" s="50"/>
-      <c r="E641" s="50"/>
+      <c r="A641" s="62"/>
+      <c r="E641" s="62"/>
       <c r="N641" s="8"/>
       <c r="P641" s="8"/>
     </row>
     <row r="642" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A642" s="50"/>
-      <c r="E642" s="50"/>
+      <c r="A642" s="62"/>
+      <c r="E642" s="62"/>
       <c r="N642" s="8"/>
       <c r="P642" s="8"/>
     </row>
     <row r="643" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A643" s="50"/>
-      <c r="E643" s="50"/>
+      <c r="A643" s="62"/>
+      <c r="E643" s="62"/>
       <c r="N643" s="8"/>
       <c r="P643" s="8"/>
     </row>
     <row r="644" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A644" s="50"/>
-      <c r="E644" s="50"/>
+      <c r="A644" s="62"/>
+      <c r="E644" s="62"/>
       <c r="N644" s="8"/>
       <c r="P644" s="8"/>
     </row>
     <row r="645" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A645" s="50"/>
-      <c r="E645" s="50"/>
+      <c r="A645" s="62"/>
+      <c r="E645" s="62"/>
       <c r="N645" s="8"/>
       <c r="P645" s="8"/>
     </row>
     <row r="646" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A646" s="50"/>
-      <c r="E646" s="50"/>
+      <c r="A646" s="62"/>
+      <c r="E646" s="62"/>
       <c r="N646" s="8"/>
       <c r="P646" s="8"/>
     </row>
     <row r="647" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A647" s="50"/>
-      <c r="E647" s="50"/>
+      <c r="A647" s="62"/>
+      <c r="E647" s="62"/>
       <c r="N647" s="8"/>
       <c r="P647" s="8"/>
     </row>
     <row r="648" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A648" s="50"/>
-      <c r="E648" s="50"/>
+      <c r="A648" s="62"/>
+      <c r="E648" s="62"/>
       <c r="N648" s="8"/>
       <c r="P648" s="8"/>
     </row>
     <row r="649" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A649" s="50"/>
-      <c r="E649" s="50"/>
+      <c r="A649" s="62"/>
+      <c r="E649" s="62"/>
       <c r="N649" s="8"/>
       <c r="P649" s="8"/>
     </row>
     <row r="650" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A650" s="50"/>
-      <c r="E650" s="50"/>
+      <c r="A650" s="62"/>
+      <c r="E650" s="62"/>
       <c r="N650" s="8"/>
       <c r="P650" s="8"/>
     </row>
     <row r="651" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A651" s="50"/>
-      <c r="E651" s="50"/>
+      <c r="A651" s="62"/>
+      <c r="E651" s="62"/>
       <c r="N651" s="8"/>
       <c r="P651" s="8"/>
     </row>
     <row r="652" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A652" s="50"/>
-      <c r="E652" s="50"/>
+      <c r="A652" s="62"/>
+      <c r="E652" s="62"/>
       <c r="N652" s="8"/>
       <c r="P652" s="8"/>
     </row>
     <row r="653" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A653" s="50"/>
-      <c r="E653" s="50"/>
+      <c r="A653" s="62"/>
+      <c r="E653" s="62"/>
       <c r="N653" s="8"/>
       <c r="P653" s="8"/>
     </row>
     <row r="654" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A654" s="50"/>
-      <c r="E654" s="50"/>
+      <c r="A654" s="62"/>
+      <c r="E654" s="62"/>
       <c r="N654" s="8"/>
       <c r="P654" s="8"/>
     </row>
     <row r="655" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A655" s="50"/>
-      <c r="E655" s="50"/>
+      <c r="A655" s="62"/>
+      <c r="E655" s="62"/>
       <c r="N655" s="8"/>
       <c r="P655" s="8"/>
     </row>
     <row r="656" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A656" s="50"/>
-      <c r="E656" s="50"/>
+      <c r="A656" s="62"/>
+      <c r="E656" s="62"/>
       <c r="N656" s="8"/>
       <c r="P656" s="8"/>
     </row>
     <row r="657" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A657" s="50"/>
-      <c r="E657" s="50"/>
+      <c r="A657" s="62"/>
+      <c r="E657" s="62"/>
       <c r="N657" s="8"/>
       <c r="P657" s="8"/>
     </row>
     <row r="658" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A658" s="50"/>
-      <c r="E658" s="50"/>
+      <c r="A658" s="62"/>
+      <c r="E658" s="62"/>
       <c r="N658" s="8"/>
       <c r="P658" s="8"/>
     </row>
     <row r="659" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A659" s="50"/>
-      <c r="E659" s="50"/>
+      <c r="A659" s="62"/>
+      <c r="E659" s="62"/>
       <c r="N659" s="8"/>
       <c r="P659" s="8"/>
     </row>
     <row r="660" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A660" s="50"/>
-      <c r="E660" s="50"/>
+      <c r="A660" s="62"/>
+      <c r="E660" s="62"/>
       <c r="N660" s="8"/>
       <c r="P660" s="8"/>
     </row>
     <row r="661" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A661" s="50"/>
-      <c r="E661" s="50"/>
+      <c r="A661" s="62"/>
+      <c r="E661" s="62"/>
       <c r="N661" s="8"/>
       <c r="P661" s="8"/>
     </row>
     <row r="662" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A662" s="50"/>
-      <c r="E662" s="50"/>
+      <c r="A662" s="62"/>
+      <c r="E662" s="62"/>
       <c r="N662" s="8"/>
       <c r="P662" s="8"/>
     </row>
     <row r="663" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A663" s="50"/>
-      <c r="E663" s="50"/>
+      <c r="A663" s="62"/>
+      <c r="E663" s="62"/>
       <c r="N663" s="8"/>
       <c r="P663" s="8"/>
     </row>
     <row r="664" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A664" s="50"/>
-      <c r="E664" s="50"/>
+      <c r="A664" s="62"/>
+      <c r="E664" s="62"/>
       <c r="N664" s="8"/>
       <c r="P664" s="8"/>
     </row>
     <row r="665" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A665" s="50"/>
-      <c r="E665" s="50"/>
+      <c r="A665" s="62"/>
+      <c r="E665" s="62"/>
       <c r="N665" s="8"/>
       <c r="P665" s="8"/>
     </row>
     <row r="666" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A666" s="50"/>
-      <c r="E666" s="50"/>
+      <c r="A666" s="62"/>
+      <c r="E666" s="62"/>
       <c r="N666" s="8"/>
       <c r="P666" s="8"/>
     </row>
     <row r="667" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A667" s="50"/>
-      <c r="E667" s="50"/>
+      <c r="A667" s="62"/>
+      <c r="E667" s="62"/>
       <c r="N667" s="8"/>
       <c r="P667" s="8"/>
     </row>
     <row r="668" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A668" s="50"/>
-      <c r="E668" s="50"/>
+      <c r="A668" s="62"/>
+      <c r="E668" s="62"/>
       <c r="N668" s="8"/>
       <c r="P668" s="8"/>
     </row>
     <row r="669" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A669" s="50"/>
-      <c r="E669" s="50"/>
+      <c r="A669" s="62"/>
+      <c r="E669" s="62"/>
       <c r="N669" s="8"/>
       <c r="P669" s="8"/>
     </row>
     <row r="670" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A670" s="50"/>
-      <c r="E670" s="50"/>
+      <c r="A670" s="62"/>
+      <c r="E670" s="62"/>
       <c r="N670" s="8"/>
       <c r="P670" s="8"/>
     </row>
     <row r="671" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A671" s="50"/>
-      <c r="E671" s="50"/>
+      <c r="A671" s="62"/>
+      <c r="E671" s="62"/>
       <c r="N671" s="8"/>
       <c r="P671" s="8"/>
     </row>
     <row r="672" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A672" s="50"/>
-      <c r="E672" s="50"/>
+      <c r="A672" s="62"/>
+      <c r="E672" s="62"/>
       <c r="N672" s="8"/>
       <c r="P672" s="8"/>
     </row>
     <row r="673" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A673" s="50"/>
-      <c r="E673" s="50"/>
+      <c r="A673" s="62"/>
+      <c r="E673" s="62"/>
       <c r="N673" s="8"/>
       <c r="P673" s="8"/>
     </row>
     <row r="674" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A674" s="50"/>
-      <c r="E674" s="50"/>
+      <c r="A674" s="62"/>
+      <c r="E674" s="62"/>
       <c r="N674" s="8"/>
       <c r="P674" s="8"/>
     </row>
     <row r="675" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A675" s="50"/>
-      <c r="E675" s="50"/>
+      <c r="A675" s="62"/>
+      <c r="E675" s="62"/>
       <c r="N675" s="8"/>
       <c r="P675" s="8"/>
     </row>
     <row r="676" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A676" s="50"/>
-      <c r="E676" s="50"/>
+      <c r="A676" s="62"/>
+      <c r="E676" s="62"/>
       <c r="N676" s="8"/>
       <c r="P676" s="8"/>
     </row>
     <row r="677" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A677" s="50"/>
-      <c r="E677" s="50"/>
+      <c r="A677" s="62"/>
+      <c r="E677" s="62"/>
       <c r="N677" s="8"/>
       <c r="P677" s="8"/>
     </row>
     <row r="678" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A678" s="50"/>
-      <c r="E678" s="50"/>
+      <c r="A678" s="62"/>
+      <c r="E678" s="62"/>
       <c r="N678" s="8"/>
       <c r="P678" s="8"/>
     </row>
     <row r="679" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A679" s="50"/>
-      <c r="E679" s="50"/>
+      <c r="A679" s="62"/>
+      <c r="E679" s="62"/>
       <c r="N679" s="8"/>
       <c r="P679" s="8"/>
     </row>
     <row r="680" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A680" s="50"/>
-      <c r="E680" s="50"/>
+      <c r="A680" s="62"/>
+      <c r="E680" s="62"/>
       <c r="N680" s="8"/>
       <c r="P680" s="8"/>
     </row>
     <row r="681" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A681" s="50"/>
-      <c r="E681" s="50"/>
+      <c r="A681" s="62"/>
+      <c r="E681" s="62"/>
       <c r="N681" s="8"/>
       <c r="P681" s="8"/>
     </row>
     <row r="682" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A682" s="50"/>
-      <c r="E682" s="50"/>
+      <c r="A682" s="62"/>
+      <c r="E682" s="62"/>
       <c r="N682" s="8"/>
       <c r="P682" s="8"/>
     </row>
     <row r="683" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A683" s="50"/>
-      <c r="E683" s="50"/>
+      <c r="A683" s="62"/>
+      <c r="E683" s="62"/>
       <c r="N683" s="8"/>
       <c r="P683" s="8"/>
     </row>
     <row r="684" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A684" s="50"/>
-      <c r="E684" s="50"/>
+      <c r="A684" s="62"/>
+      <c r="E684" s="62"/>
       <c r="N684" s="8"/>
       <c r="P684" s="8"/>
     </row>
     <row r="685" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A685" s="50"/>
-      <c r="E685" s="50"/>
+      <c r="A685" s="62"/>
+      <c r="E685" s="62"/>
       <c r="N685" s="8"/>
       <c r="P685" s="8"/>
     </row>
     <row r="686" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A686" s="50"/>
-      <c r="E686" s="50"/>
+      <c r="A686" s="62"/>
+      <c r="E686" s="62"/>
       <c r="N686" s="8"/>
       <c r="P686" s="8"/>
     </row>
     <row r="687" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A687" s="50"/>
-      <c r="E687" s="50"/>
+      <c r="A687" s="62"/>
+      <c r="E687" s="62"/>
       <c r="N687" s="8"/>
       <c r="P687" s="8"/>
     </row>
     <row r="688" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A688" s="50"/>
-      <c r="E688" s="50"/>
+      <c r="A688" s="62"/>
+      <c r="E688" s="62"/>
       <c r="N688" s="8"/>
       <c r="P688" s="8"/>
     </row>
     <row r="689" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A689" s="50"/>
-      <c r="E689" s="50"/>
+      <c r="A689" s="62"/>
+      <c r="E689" s="62"/>
       <c r="N689" s="8"/>
       <c r="P689" s="8"/>
     </row>
     <row r="690" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A690" s="50"/>
-      <c r="E690" s="50"/>
+      <c r="A690" s="62"/>
+      <c r="E690" s="62"/>
       <c r="N690" s="8"/>
       <c r="P690" s="8"/>
     </row>
     <row r="691" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A691" s="50"/>
-      <c r="E691" s="50"/>
+      <c r="A691" s="62"/>
+      <c r="E691" s="62"/>
       <c r="N691" s="8"/>
       <c r="P691" s="8"/>
     </row>
     <row r="692" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A692" s="50"/>
-      <c r="E692" s="50"/>
+      <c r="A692" s="62"/>
+      <c r="E692" s="62"/>
       <c r="N692" s="8"/>
       <c r="P692" s="8"/>
     </row>
     <row r="693" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A693" s="50"/>
-      <c r="E693" s="50"/>
+      <c r="A693" s="62"/>
+      <c r="E693" s="62"/>
       <c r="N693" s="8"/>
       <c r="P693" s="8"/>
     </row>
     <row r="694" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A694" s="50"/>
-      <c r="E694" s="50"/>
+      <c r="A694" s="62"/>
+      <c r="E694" s="62"/>
       <c r="N694" s="8"/>
       <c r="P694" s="8"/>
     </row>
     <row r="695" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A695" s="50"/>
-      <c r="E695" s="50"/>
+      <c r="A695" s="62"/>
+      <c r="E695" s="62"/>
       <c r="N695" s="8"/>
       <c r="P695" s="8"/>
     </row>
     <row r="696" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A696" s="50"/>
-      <c r="E696" s="50"/>
+      <c r="A696" s="62"/>
+      <c r="E696" s="62"/>
       <c r="N696" s="8"/>
       <c r="P696" s="8"/>
     </row>
     <row r="697" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A697" s="50"/>
-      <c r="E697" s="50"/>
+      <c r="A697" s="62"/>
+      <c r="E697" s="62"/>
       <c r="N697" s="8"/>
       <c r="P697" s="8"/>
     </row>
     <row r="698" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A698" s="50"/>
-      <c r="E698" s="50"/>
+      <c r="A698" s="62"/>
+      <c r="E698" s="62"/>
       <c r="N698" s="8"/>
       <c r="P698" s="8"/>
     </row>
     <row r="699" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A699" s="50"/>
-      <c r="E699" s="50"/>
+      <c r="A699" s="62"/>
+      <c r="E699" s="62"/>
       <c r="N699" s="8"/>
       <c r="P699" s="8"/>
     </row>
     <row r="700" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A700" s="50"/>
-      <c r="E700" s="50"/>
+      <c r="A700" s="62"/>
+      <c r="E700" s="62"/>
       <c r="N700" s="8"/>
       <c r="P700" s="8"/>
     </row>
     <row r="701" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A701" s="50"/>
-      <c r="E701" s="50"/>
+      <c r="A701" s="62"/>
+      <c r="E701" s="62"/>
       <c r="N701" s="8"/>
       <c r="P701" s="8"/>
     </row>
     <row r="702" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A702" s="50"/>
-      <c r="E702" s="50"/>
+      <c r="A702" s="62"/>
+      <c r="E702" s="62"/>
       <c r="N702" s="8"/>
       <c r="P702" s="8"/>
     </row>
     <row r="703" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A703" s="50"/>
-      <c r="E703" s="50"/>
+      <c r="A703" s="62"/>
+      <c r="E703" s="62"/>
       <c r="N703" s="8"/>
       <c r="P703" s="8"/>
     </row>
     <row r="704" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A704" s="50"/>
-      <c r="E704" s="50"/>
+      <c r="A704" s="62"/>
+      <c r="E704" s="62"/>
       <c r="N704" s="8"/>
       <c r="P704" s="8"/>
     </row>
     <row r="705" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A705" s="50"/>
-      <c r="E705" s="50"/>
+      <c r="A705" s="62"/>
+      <c r="E705" s="62"/>
       <c r="N705" s="8"/>
       <c r="P705" s="8"/>
     </row>
     <row r="706" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A706" s="50"/>
-      <c r="E706" s="50"/>
+      <c r="A706" s="62"/>
+      <c r="E706" s="62"/>
       <c r="N706" s="8"/>
       <c r="P706" s="8"/>
     </row>
     <row r="707" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A707" s="50"/>
-      <c r="E707" s="50"/>
+      <c r="A707" s="62"/>
+      <c r="E707" s="62"/>
       <c r="N707" s="8"/>
       <c r="P707" s="8"/>
     </row>
     <row r="708" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A708" s="50"/>
-      <c r="E708" s="50"/>
+      <c r="A708" s="62"/>
+      <c r="E708" s="62"/>
       <c r="N708" s="8"/>
       <c r="P708" s="8"/>
     </row>
     <row r="709" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A709" s="50"/>
-      <c r="E709" s="50"/>
+      <c r="A709" s="62"/>
+      <c r="E709" s="62"/>
       <c r="N709" s="8"/>
       <c r="P709" s="8"/>
     </row>
     <row r="710" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A710" s="50"/>
-      <c r="E710" s="50"/>
+      <c r="A710" s="62"/>
+      <c r="E710" s="62"/>
       <c r="N710" s="8"/>
       <c r="P710" s="8"/>
     </row>
     <row r="711" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A711" s="50"/>
-      <c r="E711" s="50"/>
+      <c r="A711" s="62"/>
+      <c r="E711" s="62"/>
       <c r="N711" s="8"/>
       <c r="P711" s="8"/>
     </row>
     <row r="712" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A712" s="50"/>
-      <c r="E712" s="50"/>
+      <c r="A712" s="62"/>
+      <c r="E712" s="62"/>
       <c r="N712" s="8"/>
       <c r="P712" s="8"/>
     </row>
     <row r="713" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A713" s="50"/>
-      <c r="E713" s="50"/>
+      <c r="A713" s="62"/>
+      <c r="E713" s="62"/>
       <c r="N713" s="8"/>
       <c r="P713" s="8"/>
     </row>
     <row r="714" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A714" s="50"/>
-      <c r="E714" s="50"/>
+      <c r="A714" s="62"/>
+      <c r="E714" s="62"/>
       <c r="N714" s="8"/>
       <c r="P714" s="8"/>
     </row>
     <row r="715" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A715" s="50"/>
-      <c r="E715" s="50"/>
+      <c r="A715" s="62"/>
+      <c r="E715" s="62"/>
       <c r="N715" s="8"/>
       <c r="P715" s="8"/>
     </row>
     <row r="716" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A716" s="50"/>
-      <c r="E716" s="50"/>
+      <c r="A716" s="62"/>
+      <c r="E716" s="62"/>
       <c r="N716" s="8"/>
       <c r="P716" s="8"/>
     </row>
     <row r="717" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A717" s="50"/>
-      <c r="E717" s="50"/>
+      <c r="A717" s="62"/>
+      <c r="E717" s="62"/>
       <c r="N717" s="8"/>
       <c r="P717" s="8"/>
     </row>
     <row r="718" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A718" s="50"/>
-      <c r="E718" s="50"/>
+      <c r="A718" s="62"/>
+      <c r="E718" s="62"/>
       <c r="N718" s="8"/>
       <c r="P718" s="8"/>
     </row>
     <row r="719" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A719" s="50"/>
-      <c r="E719" s="50"/>
+      <c r="A719" s="62"/>
+      <c r="E719" s="62"/>
       <c r="N719" s="8"/>
       <c r="P719" s="8"/>
     </row>
     <row r="720" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A720" s="50"/>
-      <c r="E720" s="50"/>
+      <c r="A720" s="62"/>
+      <c r="E720" s="62"/>
       <c r="N720" s="8"/>
       <c r="P720" s="8"/>
     </row>
     <row r="721" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A721" s="50"/>
-      <c r="E721" s="50"/>
+      <c r="A721" s="62"/>
+      <c r="E721" s="62"/>
       <c r="N721" s="8"/>
       <c r="P721" s="8"/>
     </row>
     <row r="722" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A722" s="50"/>
-      <c r="E722" s="50"/>
+      <c r="A722" s="62"/>
+      <c r="E722" s="62"/>
       <c r="N722" s="8"/>
       <c r="P722" s="8"/>
     </row>
     <row r="723" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A723" s="50"/>
-      <c r="E723" s="50"/>
+      <c r="A723" s="62"/>
+      <c r="E723" s="62"/>
       <c r="N723" s="8"/>
       <c r="P723" s="8"/>
     </row>
     <row r="724" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A724" s="50"/>
-      <c r="E724" s="50"/>
+      <c r="A724" s="62"/>
+      <c r="E724" s="62"/>
       <c r="N724" s="8"/>
       <c r="P724" s="8"/>
     </row>
     <row r="725" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A725" s="50"/>
-      <c r="E725" s="50"/>
+      <c r="A725" s="62"/>
+      <c r="E725" s="62"/>
       <c r="N725" s="8"/>
       <c r="P725" s="8"/>
     </row>
     <row r="726" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A726" s="50"/>
-      <c r="E726" s="50"/>
+      <c r="A726" s="62"/>
+      <c r="E726" s="62"/>
       <c r="N726" s="8"/>
       <c r="P726" s="8"/>
     </row>
     <row r="727" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A727" s="50"/>
-      <c r="E727" s="50"/>
+      <c r="A727" s="62"/>
+      <c r="E727" s="62"/>
       <c r="N727" s="8"/>
       <c r="P727" s="8"/>
     </row>
     <row r="728" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A728" s="50"/>
-      <c r="E728" s="50"/>
+      <c r="A728" s="62"/>
+      <c r="E728" s="62"/>
       <c r="N728" s="8"/>
       <c r="P728" s="8"/>
     </row>
     <row r="729" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A729" s="50"/>
-      <c r="E729" s="50"/>
+      <c r="A729" s="62"/>
+      <c r="E729" s="62"/>
       <c r="N729" s="8"/>
       <c r="P729" s="8"/>
     </row>
     <row r="730" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A730" s="50"/>
-      <c r="E730" s="50"/>
+      <c r="A730" s="62"/>
+      <c r="E730" s="62"/>
       <c r="N730" s="8"/>
       <c r="P730" s="8"/>
     </row>
     <row r="731" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A731" s="50"/>
-      <c r="E731" s="50"/>
+      <c r="A731" s="62"/>
+      <c r="E731" s="62"/>
       <c r="N731" s="8"/>
       <c r="P731" s="8"/>
     </row>
     <row r="732" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A732" s="50"/>
-      <c r="E732" s="50"/>
+      <c r="A732" s="62"/>
+      <c r="E732" s="62"/>
       <c r="N732" s="8"/>
       <c r="P732" s="8"/>
     </row>
     <row r="733" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A733" s="50"/>
-      <c r="E733" s="50"/>
+      <c r="A733" s="62"/>
+      <c r="E733" s="62"/>
       <c r="N733" s="8"/>
       <c r="P733" s="8"/>
     </row>
     <row r="734" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A734" s="50"/>
-      <c r="E734" s="50"/>
+      <c r="A734" s="62"/>
+      <c r="E734" s="62"/>
       <c r="N734" s="8"/>
       <c r="P734" s="8"/>
     </row>
     <row r="735" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A735" s="50"/>
-      <c r="E735" s="50"/>
+      <c r="A735" s="62"/>
+      <c r="E735" s="62"/>
       <c r="N735" s="8"/>
       <c r="P735" s="8"/>
     </row>
     <row r="736" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A736" s="50"/>
-      <c r="E736" s="50"/>
+      <c r="A736" s="62"/>
+      <c r="E736" s="62"/>
       <c r="N736" s="8"/>
       <c r="P736" s="8"/>
     </row>
     <row r="737" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A737" s="50"/>
-      <c r="E737" s="50"/>
+      <c r="A737" s="62"/>
+      <c r="E737" s="62"/>
       <c r="N737" s="8"/>
       <c r="P737" s="8"/>
     </row>
     <row r="738" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A738" s="50"/>
-      <c r="E738" s="50"/>
+      <c r="A738" s="62"/>
+      <c r="E738" s="62"/>
       <c r="N738" s="8"/>
       <c r="P738" s="8"/>
     </row>
     <row r="739" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A739" s="50"/>
-      <c r="E739" s="50"/>
+      <c r="A739" s="62"/>
+      <c r="E739" s="62"/>
       <c r="N739" s="8"/>
       <c r="P739" s="8"/>
     </row>
     <row r="740" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A740" s="50"/>
-      <c r="E740" s="50"/>
+      <c r="A740" s="62"/>
+      <c r="E740" s="62"/>
       <c r="N740" s="8"/>
       <c r="P740" s="8"/>
     </row>
     <row r="741" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A741" s="50"/>
-      <c r="E741" s="50"/>
+      <c r="A741" s="62"/>
+      <c r="E741" s="62"/>
       <c r="N741" s="8"/>
       <c r="P741" s="8"/>
     </row>
     <row r="742" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A742" s="50"/>
-      <c r="E742" s="50"/>
+      <c r="A742" s="62"/>
+      <c r="E742" s="62"/>
       <c r="N742" s="8"/>
       <c r="P742" s="8"/>
     </row>
     <row r="743" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A743" s="50"/>
-      <c r="E743" s="50"/>
+      <c r="A743" s="62"/>
+      <c r="E743" s="62"/>
       <c r="N743" s="8"/>
       <c r="P743" s="8"/>
     </row>
     <row r="744" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A744" s="50"/>
-      <c r="E744" s="50"/>
+      <c r="A744" s="62"/>
+      <c r="E744" s="62"/>
       <c r="N744" s="8"/>
       <c r="P744" s="8"/>
     </row>
     <row r="745" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A745" s="50"/>
-      <c r="E745" s="50"/>
+      <c r="A745" s="62"/>
+      <c r="E745" s="62"/>
       <c r="N745" s="8"/>
       <c r="P745" s="8"/>
     </row>
     <row r="746" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A746" s="50"/>
-      <c r="E746" s="50"/>
+      <c r="A746" s="62"/>
+      <c r="E746" s="62"/>
       <c r="N746" s="8"/>
       <c r="P746" s="8"/>
     </row>
     <row r="747" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A747" s="50"/>
-      <c r="E747" s="50"/>
+      <c r="A747" s="62"/>
+      <c r="E747" s="62"/>
       <c r="N747" s="8"/>
       <c r="P747" s="8"/>
     </row>
     <row r="748" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A748" s="50"/>
-      <c r="E748" s="50"/>
+      <c r="A748" s="62"/>
+      <c r="E748" s="62"/>
       <c r="N748" s="8"/>
       <c r="P748" s="8"/>
     </row>
     <row r="749" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A749" s="50"/>
-      <c r="E749" s="50"/>
+      <c r="A749" s="62"/>
+      <c r="E749" s="62"/>
       <c r="N749" s="8"/>
       <c r="P749" s="8"/>
     </row>
     <row r="750" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A750" s="50"/>
-      <c r="E750" s="50"/>
+      <c r="A750" s="62"/>
+      <c r="E750" s="62"/>
       <c r="N750" s="8"/>
       <c r="P750" s="8"/>
     </row>
     <row r="751" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A751" s="50"/>
-      <c r="E751" s="50"/>
+      <c r="A751" s="62"/>
+      <c r="E751" s="62"/>
       <c r="N751" s="8"/>
       <c r="P751" s="8"/>
     </row>
     <row r="752" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A752" s="50"/>
-      <c r="E752" s="50"/>
+      <c r="A752" s="62"/>
+      <c r="E752" s="62"/>
       <c r="N752" s="8"/>
       <c r="P752" s="8"/>
     </row>
     <row r="753" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A753" s="50"/>
-      <c r="E753" s="50"/>
+      <c r="A753" s="62"/>
+      <c r="E753" s="62"/>
       <c r="N753" s="8"/>
       <c r="P753" s="8"/>
     </row>
     <row r="754" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A754" s="50"/>
-      <c r="E754" s="50"/>
+      <c r="A754" s="62"/>
+      <c r="E754" s="62"/>
       <c r="N754" s="8"/>
       <c r="P754" s="8"/>
     </row>
     <row r="755" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A755" s="50"/>
-      <c r="E755" s="50"/>
+      <c r="A755" s="62"/>
+      <c r="E755" s="62"/>
       <c r="N755" s="8"/>
       <c r="P755" s="8"/>
     </row>
     <row r="756" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A756" s="50"/>
-      <c r="E756" s="50"/>
+      <c r="A756" s="62"/>
+      <c r="E756" s="62"/>
       <c r="N756" s="8"/>
       <c r="P756" s="8"/>
     </row>
     <row r="757" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A757" s="50"/>
-      <c r="E757" s="50"/>
+      <c r="A757" s="62"/>
+      <c r="E757" s="62"/>
       <c r="N757" s="8"/>
       <c r="P757" s="8"/>
     </row>
     <row r="758" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A758" s="50"/>
-      <c r="E758" s="50"/>
+      <c r="A758" s="62"/>
+      <c r="E758" s="62"/>
       <c r="N758" s="8"/>
       <c r="P758" s="8"/>
     </row>
     <row r="759" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A759" s="50"/>
-      <c r="E759" s="50"/>
+      <c r="A759" s="62"/>
+      <c r="E759" s="62"/>
       <c r="N759" s="8"/>
       <c r="P759" s="8"/>
     </row>
     <row r="760" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A760" s="50"/>
-      <c r="E760" s="50"/>
+      <c r="A760" s="62"/>
+      <c r="E760" s="62"/>
       <c r="N760" s="8"/>
       <c r="P760" s="8"/>
     </row>
     <row r="761" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A761" s="50"/>
-      <c r="E761" s="50"/>
+      <c r="A761" s="62"/>
+      <c r="E761" s="62"/>
       <c r="N761" s="8"/>
       <c r="P761" s="8"/>
     </row>
     <row r="762" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A762" s="50"/>
-      <c r="E762" s="50"/>
+      <c r="A762" s="62"/>
+      <c r="E762" s="62"/>
       <c r="N762" s="8"/>
       <c r="P762" s="8"/>
     </row>
     <row r="763" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A763" s="50"/>
-      <c r="E763" s="50"/>
+      <c r="A763" s="62"/>
+      <c r="E763" s="62"/>
       <c r="N763" s="8"/>
       <c r="P763" s="8"/>
     </row>
     <row r="764" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A764" s="50"/>
-      <c r="E764" s="50"/>
+      <c r="A764" s="62"/>
+      <c r="E764" s="62"/>
       <c r="N764" s="8"/>
       <c r="P764" s="8"/>
     </row>
     <row r="765" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A765" s="50"/>
-      <c r="E765" s="50"/>
+      <c r="A765" s="62"/>
+      <c r="E765" s="62"/>
       <c r="N765" s="8"/>
       <c r="P765" s="8"/>
     </row>
     <row r="766" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A766" s="50"/>
-      <c r="E766" s="50"/>
+      <c r="A766" s="62"/>
+      <c r="E766" s="62"/>
       <c r="N766" s="8"/>
       <c r="P766" s="8"/>
     </row>
     <row r="767" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A767" s="50"/>
-      <c r="E767" s="50"/>
+      <c r="A767" s="62"/>
+      <c r="E767" s="62"/>
       <c r="N767" s="8"/>
       <c r="P767" s="8"/>
     </row>
     <row r="768" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A768" s="50"/>
-      <c r="E768" s="50"/>
+      <c r="A768" s="62"/>
+      <c r="E768" s="62"/>
       <c r="N768" s="8"/>
       <c r="P768" s="8"/>
     </row>
     <row r="769" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A769" s="50"/>
-      <c r="E769" s="50"/>
+      <c r="A769" s="62"/>
+      <c r="E769" s="62"/>
       <c r="N769" s="8"/>
       <c r="P769" s="8"/>
     </row>
     <row r="770" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A770" s="50"/>
-      <c r="E770" s="50"/>
+      <c r="A770" s="62"/>
+      <c r="E770" s="62"/>
       <c r="N770" s="8"/>
       <c r="P770" s="8"/>
     </row>
     <row r="771" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A771" s="50"/>
-      <c r="E771" s="50"/>
+      <c r="A771" s="62"/>
+      <c r="E771" s="62"/>
       <c r="N771" s="8"/>
       <c r="P771" s="8"/>
     </row>
     <row r="772" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A772" s="50"/>
-      <c r="E772" s="50"/>
+      <c r="A772" s="62"/>
+      <c r="E772" s="62"/>
       <c r="N772" s="8"/>
       <c r="P772" s="8"/>
     </row>
     <row r="773" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A773" s="50"/>
-      <c r="E773" s="50"/>
+      <c r="A773" s="62"/>
+      <c r="E773" s="62"/>
       <c r="N773" s="8"/>
       <c r="P773" s="8"/>
     </row>
     <row r="774" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A774" s="50"/>
-      <c r="E774" s="50"/>
+      <c r="A774" s="62"/>
+      <c r="E774" s="62"/>
       <c r="N774" s="8"/>
       <c r="P774" s="8"/>
     </row>
     <row r="775" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A775" s="50"/>
-      <c r="E775" s="50"/>
+      <c r="A775" s="62"/>
+      <c r="E775" s="62"/>
       <c r="N775" s="8"/>
       <c r="P775" s="8"/>
     </row>
     <row r="776" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A776" s="50"/>
-      <c r="E776" s="50"/>
+      <c r="A776" s="62"/>
+      <c r="E776" s="62"/>
       <c r="N776" s="8"/>
       <c r="P776" s="8"/>
     </row>
     <row r="777" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A777" s="50"/>
-      <c r="E777" s="50"/>
+      <c r="A777" s="62"/>
+      <c r="E777" s="62"/>
       <c r="N777" s="8"/>
       <c r="P777" s="8"/>
     </row>
     <row r="778" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A778" s="50"/>
-      <c r="E778" s="50"/>
+      <c r="A778" s="62"/>
+      <c r="E778" s="62"/>
       <c r="N778" s="8"/>
       <c r="P778" s="8"/>
     </row>
     <row r="779" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A779" s="50"/>
-      <c r="E779" s="50"/>
+      <c r="A779" s="62"/>
+      <c r="E779" s="62"/>
       <c r="N779" s="8"/>
       <c r="P779" s="8"/>
     </row>
     <row r="780" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A780" s="50"/>
-      <c r="E780" s="50"/>
+      <c r="A780" s="62"/>
+      <c r="E780" s="62"/>
       <c r="N780" s="8"/>
       <c r="P780" s="8"/>
     </row>
     <row r="781" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A781" s="50"/>
-      <c r="E781" s="50"/>
+      <c r="A781" s="62"/>
+      <c r="E781" s="62"/>
       <c r="N781" s="8"/>
       <c r="P781" s="8"/>
     </row>
     <row r="782" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A782" s="50"/>
-      <c r="E782" s="50"/>
+      <c r="A782" s="62"/>
+      <c r="E782" s="62"/>
       <c r="N782" s="8"/>
       <c r="P782" s="8"/>
     </row>
     <row r="783" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A783" s="50"/>
-      <c r="E783" s="50"/>
+      <c r="A783" s="62"/>
+      <c r="E783" s="62"/>
       <c r="N783" s="8"/>
       <c r="P783" s="8"/>
     </row>
     <row r="784" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A784" s="50"/>
-      <c r="E784" s="50"/>
+      <c r="A784" s="62"/>
+      <c r="E784" s="62"/>
       <c r="N784" s="8"/>
       <c r="P784" s="8"/>
     </row>
     <row r="785" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A785" s="50"/>
-      <c r="E785" s="50"/>
+      <c r="A785" s="62"/>
+      <c r="E785" s="62"/>
       <c r="N785" s="8"/>
       <c r="P785" s="8"/>
     </row>
     <row r="786" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A786" s="50"/>
-      <c r="E786" s="50"/>
+      <c r="A786" s="62"/>
+      <c r="E786" s="62"/>
       <c r="N786" s="8"/>
       <c r="P786" s="8"/>
     </row>
     <row r="787" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A787" s="50"/>
-      <c r="E787" s="50"/>
+      <c r="A787" s="62"/>
+      <c r="E787" s="62"/>
       <c r="N787" s="8"/>
       <c r="P787" s="8"/>
     </row>
     <row r="788" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A788" s="50"/>
-      <c r="E788" s="50"/>
+      <c r="A788" s="62"/>
+      <c r="E788" s="62"/>
       <c r="N788" s="8"/>
       <c r="P788" s="8"/>
     </row>
     <row r="789" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A789" s="50"/>
-      <c r="E789" s="50"/>
+      <c r="A789" s="62"/>
+      <c r="E789" s="62"/>
       <c r="N789" s="8"/>
       <c r="P789" s="8"/>
     </row>
     <row r="790" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A790" s="50"/>
-      <c r="E790" s="50"/>
+      <c r="A790" s="62"/>
+      <c r="E790" s="62"/>
       <c r="N790" s="8"/>
       <c r="P790" s="8"/>
     </row>
     <row r="791" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A791" s="50"/>
-      <c r="E791" s="50"/>
+      <c r="A791" s="62"/>
+      <c r="E791" s="62"/>
       <c r="N791" s="8"/>
       <c r="P791" s="8"/>
     </row>
     <row r="792" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A792" s="50"/>
-      <c r="E792" s="50"/>
+      <c r="A792" s="62"/>
+      <c r="E792" s="62"/>
       <c r="N792" s="8"/>
       <c r="P792" s="8"/>
     </row>
     <row r="793" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A793" s="50"/>
-      <c r="E793" s="50"/>
+      <c r="A793" s="62"/>
+      <c r="E793" s="62"/>
       <c r="N793" s="8"/>
       <c r="P793" s="8"/>
     </row>
     <row r="794" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A794" s="50"/>
-      <c r="E794" s="50"/>
+      <c r="A794" s="62"/>
+      <c r="E794" s="62"/>
       <c r="N794" s="8"/>
       <c r="P794" s="8"/>
     </row>
     <row r="795" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A795" s="50"/>
-      <c r="E795" s="50"/>
+      <c r="A795" s="62"/>
+      <c r="E795" s="62"/>
       <c r="N795" s="8"/>
       <c r="P795" s="8"/>
     </row>
     <row r="796" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A796" s="50"/>
-      <c r="E796" s="50"/>
+      <c r="A796" s="62"/>
+      <c r="E796" s="62"/>
       <c r="N796" s="8"/>
       <c r="P796" s="8"/>
     </row>
     <row r="797" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A797" s="50"/>
-      <c r="E797" s="50"/>
+      <c r="A797" s="62"/>
+      <c r="E797" s="62"/>
       <c r="N797" s="8"/>
       <c r="P797" s="8"/>
     </row>
     <row r="798" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A798" s="50"/>
-      <c r="E798" s="50"/>
+      <c r="A798" s="62"/>
+      <c r="E798" s="62"/>
       <c r="N798" s="8"/>
       <c r="P798" s="8"/>
     </row>
     <row r="799" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A799" s="50"/>
-      <c r="E799" s="50"/>
+      <c r="A799" s="62"/>
+      <c r="E799" s="62"/>
       <c r="N799" s="8"/>
       <c r="P799" s="8"/>
     </row>
     <row r="800" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A800" s="50"/>
-      <c r="E800" s="50"/>
+      <c r="A800" s="62"/>
+      <c r="E800" s="62"/>
       <c r="N800" s="8"/>
       <c r="P800" s="8"/>
     </row>
     <row r="801" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A801" s="50"/>
-      <c r="E801" s="50"/>
+      <c r="A801" s="62"/>
+      <c r="E801" s="62"/>
       <c r="N801" s="8"/>
       <c r="P801" s="8"/>
     </row>
     <row r="802" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A802" s="50"/>
-      <c r="E802" s="50"/>
+      <c r="A802" s="62"/>
+      <c r="E802" s="62"/>
       <c r="N802" s="8"/>
       <c r="P802" s="8"/>
     </row>
     <row r="803" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A803" s="50"/>
-      <c r="E803" s="50"/>
+      <c r="A803" s="62"/>
+      <c r="E803" s="62"/>
       <c r="N803" s="8"/>
       <c r="P803" s="8"/>
     </row>
     <row r="804" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A804" s="50"/>
-      <c r="E804" s="50"/>
+      <c r="A804" s="62"/>
+      <c r="E804" s="62"/>
       <c r="N804" s="8"/>
       <c r="P804" s="8"/>
     </row>
     <row r="805" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A805" s="50"/>
-      <c r="E805" s="50"/>
+      <c r="A805" s="62"/>
+      <c r="E805" s="62"/>
       <c r="N805" s="8"/>
       <c r="P805" s="8"/>
     </row>
     <row r="806" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A806" s="50"/>
-      <c r="E806" s="50"/>
+      <c r="A806" s="62"/>
+      <c r="E806" s="62"/>
       <c r="N806" s="8"/>
       <c r="P806" s="8"/>
     </row>
     <row r="807" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A807" s="50"/>
-      <c r="E807" s="50"/>
+      <c r="A807" s="62"/>
+      <c r="E807" s="62"/>
       <c r="N807" s="8"/>
       <c r="P807" s="8"/>
     </row>
     <row r="808" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A808" s="50"/>
-      <c r="E808" s="50"/>
+      <c r="A808" s="62"/>
+      <c r="E808" s="62"/>
       <c r="N808" s="8"/>
       <c r="P808" s="8"/>
     </row>
     <row r="809" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A809" s="50"/>
-      <c r="E809" s="50"/>
+      <c r="A809" s="62"/>
+      <c r="E809" s="62"/>
       <c r="N809" s="8"/>
       <c r="P809" s="8"/>
     </row>
     <row r="810" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A810" s="50"/>
-      <c r="E810" s="50"/>
+      <c r="A810" s="62"/>
+      <c r="E810" s="62"/>
       <c r="N810" s="8"/>
       <c r="P810" s="8"/>
     </row>
     <row r="811" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A811" s="50"/>
-      <c r="E811" s="50"/>
+      <c r="A811" s="62"/>
+      <c r="E811" s="62"/>
       <c r="N811" s="8"/>
       <c r="P811" s="8"/>
     </row>
     <row r="812" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A812" s="50"/>
-      <c r="E812" s="50"/>
+      <c r="A812" s="62"/>
+      <c r="E812" s="62"/>
       <c r="N812" s="8"/>
       <c r="P812" s="8"/>
     </row>
     <row r="813" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A813" s="50"/>
-      <c r="E813" s="50"/>
+      <c r="A813" s="62"/>
+      <c r="E813" s="62"/>
       <c r="N813" s="8"/>
       <c r="P813" s="8"/>
     </row>
     <row r="814" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A814" s="50"/>
-      <c r="E814" s="50"/>
+      <c r="A814" s="62"/>
+      <c r="E814" s="62"/>
       <c r="N814" s="8"/>
       <c r="P814" s="8"/>
     </row>
     <row r="815" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A815" s="50"/>
-      <c r="E815" s="50"/>
+      <c r="A815" s="62"/>
+      <c r="E815" s="62"/>
       <c r="N815" s="8"/>
       <c r="P815" s="8"/>
     </row>
     <row r="816" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A816" s="50"/>
-      <c r="E816" s="50"/>
+      <c r="A816" s="62"/>
+      <c r="E816" s="62"/>
       <c r="N816" s="8"/>
       <c r="P816" s="8"/>
     </row>
     <row r="817" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A817" s="50"/>
-      <c r="E817" s="50"/>
+      <c r="A817" s="62"/>
+      <c r="E817" s="62"/>
       <c r="N817" s="8"/>
       <c r="P817" s="8"/>
     </row>
     <row r="818" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A818" s="50"/>
-      <c r="E818" s="50"/>
+      <c r="A818" s="62"/>
+      <c r="E818" s="62"/>
       <c r="N818" s="8"/>
       <c r="P818" s="8"/>
     </row>
     <row r="819" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A819" s="50"/>
-      <c r="E819" s="50"/>
+      <c r="A819" s="62"/>
+      <c r="E819" s="62"/>
       <c r="N819" s="8"/>
       <c r="P819" s="8"/>
     </row>
     <row r="820" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A820" s="50"/>
-      <c r="E820" s="50"/>
+      <c r="A820" s="62"/>
+      <c r="E820" s="62"/>
       <c r="N820" s="8"/>
       <c r="P820" s="8"/>
     </row>
     <row r="821" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A821" s="50"/>
-      <c r="E821" s="50"/>
+      <c r="A821" s="62"/>
+      <c r="E821" s="62"/>
       <c r="N821" s="8"/>
       <c r="P821" s="8"/>
     </row>
     <row r="822" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A822" s="50"/>
-      <c r="E822" s="50"/>
+      <c r="A822" s="62"/>
+      <c r="E822" s="62"/>
       <c r="N822" s="8"/>
       <c r="P822" s="8"/>
     </row>
     <row r="823" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A823" s="50"/>
-      <c r="E823" s="50"/>
+      <c r="A823" s="62"/>
+      <c r="E823" s="62"/>
       <c r="N823" s="8"/>
       <c r="P823" s="8"/>
     </row>
     <row r="824" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A824" s="50"/>
-      <c r="E824" s="50"/>
+      <c r="A824" s="62"/>
+      <c r="E824" s="62"/>
       <c r="N824" s="8"/>
       <c r="P824" s="8"/>
     </row>
     <row r="825" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A825" s="50"/>
-      <c r="E825" s="50"/>
+      <c r="A825" s="62"/>
+      <c r="E825" s="62"/>
       <c r="N825" s="8"/>
       <c r="P825" s="8"/>
     </row>
     <row r="826" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A826" s="50"/>
-      <c r="E826" s="50"/>
+      <c r="A826" s="62"/>
+      <c r="E826" s="62"/>
       <c r="N826" s="8"/>
       <c r="P826" s="8"/>
     </row>
     <row r="827" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A827" s="50"/>
-      <c r="E827" s="50"/>
+      <c r="A827" s="62"/>
+      <c r="E827" s="62"/>
       <c r="N827" s="8"/>
       <c r="P827" s="8"/>
     </row>
     <row r="828" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A828" s="50"/>
-      <c r="E828" s="50"/>
+      <c r="A828" s="62"/>
+      <c r="E828" s="62"/>
       <c r="N828" s="8"/>
       <c r="P828" s="8"/>
     </row>
     <row r="829" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A829" s="50"/>
-      <c r="E829" s="50"/>
+      <c r="A829" s="62"/>
+      <c r="E829" s="62"/>
       <c r="N829" s="8"/>
       <c r="P829" s="8"/>
     </row>
     <row r="830" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A830" s="50"/>
-      <c r="E830" s="50"/>
+      <c r="A830" s="62"/>
+      <c r="E830" s="62"/>
       <c r="N830" s="8"/>
       <c r="P830" s="8"/>
     </row>
     <row r="831" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A831" s="50"/>
-      <c r="E831" s="50"/>
+      <c r="A831" s="62"/>
+      <c r="E831" s="62"/>
       <c r="N831" s="8"/>
       <c r="P831" s="8"/>
     </row>
     <row r="832" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A832" s="50"/>
-      <c r="E832" s="50"/>
+      <c r="A832" s="62"/>
+      <c r="E832" s="62"/>
       <c r="N832" s="8"/>
       <c r="P832" s="8"/>
     </row>
     <row r="833" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A833" s="50"/>
-      <c r="E833" s="50"/>
+      <c r="A833" s="62"/>
+      <c r="E833" s="62"/>
       <c r="N833" s="8"/>
       <c r="P833" s="8"/>
     </row>
     <row r="834" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A834" s="50"/>
-      <c r="E834" s="50"/>
+      <c r="A834" s="62"/>
+      <c r="E834" s="62"/>
       <c r="N834" s="8"/>
       <c r="P834" s="8"/>
     </row>
     <row r="835" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A835" s="50"/>
-      <c r="E835" s="50"/>
+      <c r="A835" s="62"/>
+      <c r="E835" s="62"/>
       <c r="N835" s="8"/>
       <c r="P835" s="8"/>
     </row>
     <row r="836" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A836" s="50"/>
-      <c r="E836" s="50"/>
+      <c r="A836" s="62"/>
+      <c r="E836" s="62"/>
       <c r="N836" s="8"/>
       <c r="P836" s="8"/>
     </row>
     <row r="837" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A837" s="50"/>
-      <c r="E837" s="50"/>
+      <c r="A837" s="62"/>
+      <c r="E837" s="62"/>
       <c r="N837" s="8"/>
       <c r="P837" s="8"/>
     </row>
     <row r="838" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A838" s="50"/>
-      <c r="E838" s="50"/>
+      <c r="A838" s="62"/>
+      <c r="E838" s="62"/>
       <c r="N838" s="8"/>
       <c r="P838" s="8"/>
     </row>
     <row r="839" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A839" s="50"/>
-      <c r="E839" s="50"/>
+      <c r="A839" s="62"/>
+      <c r="E839" s="62"/>
       <c r="N839" s="8"/>
       <c r="P839" s="8"/>
     </row>
     <row r="840" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A840" s="50"/>
-      <c r="E840" s="50"/>
+      <c r="A840" s="62"/>
+      <c r="E840" s="62"/>
       <c r="N840" s="8"/>
       <c r="P840" s="8"/>
     </row>
     <row r="841" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A841" s="50"/>
-      <c r="E841" s="50"/>
+      <c r="A841" s="62"/>
+      <c r="E841" s="62"/>
       <c r="N841" s="8"/>
       <c r="P841" s="8"/>
     </row>
     <row r="842" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A842" s="50"/>
-      <c r="E842" s="50"/>
+      <c r="A842" s="62"/>
+      <c r="E842" s="62"/>
       <c r="N842" s="8"/>
       <c r="P842" s="8"/>
     </row>
     <row r="843" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A843" s="50"/>
-      <c r="E843" s="50"/>
+      <c r="A843" s="62"/>
+      <c r="E843" s="62"/>
       <c r="N843" s="8"/>
       <c r="P843" s="8"/>
     </row>
     <row r="844" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A844" s="50"/>
-      <c r="E844" s="50"/>
+      <c r="A844" s="62"/>
+      <c r="E844" s="62"/>
       <c r="N844" s="8"/>
       <c r="P844" s="8"/>
     </row>
     <row r="845" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A845" s="50"/>
-      <c r="E845" s="50"/>
+      <c r="A845" s="62"/>
+      <c r="E845" s="62"/>
       <c r="N845" s="8"/>
       <c r="P845" s="8"/>
     </row>
     <row r="846" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A846" s="50"/>
-      <c r="E846" s="50"/>
+      <c r="A846" s="62"/>
+      <c r="E846" s="62"/>
       <c r="N846" s="8"/>
       <c r="P846" s="8"/>
     </row>
     <row r="847" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A847" s="50"/>
-      <c r="E847" s="50"/>
+      <c r="A847" s="62"/>
+      <c r="E847" s="62"/>
       <c r="N847" s="8"/>
       <c r="P847" s="8"/>
     </row>
     <row r="848" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A848" s="50"/>
-      <c r="E848" s="50"/>
+      <c r="A848" s="62"/>
+      <c r="E848" s="62"/>
       <c r="N848" s="8"/>
       <c r="P848" s="8"/>
     </row>
     <row r="849" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A849" s="50"/>
-      <c r="E849" s="50"/>
+      <c r="A849" s="62"/>
+      <c r="E849" s="62"/>
       <c r="N849" s="8"/>
       <c r="P849" s="8"/>
     </row>
     <row r="850" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A850" s="50"/>
-      <c r="E850" s="50"/>
+      <c r="A850" s="62"/>
+      <c r="E850" s="62"/>
       <c r="N850" s="8"/>
       <c r="P850" s="8"/>
     </row>
     <row r="851" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A851" s="50"/>
-      <c r="E851" s="50"/>
+      <c r="A851" s="62"/>
+      <c r="E851" s="62"/>
       <c r="N851" s="8"/>
       <c r="P851" s="8"/>
     </row>
     <row r="852" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A852" s="50"/>
-      <c r="E852" s="50"/>
+      <c r="A852" s="62"/>
+      <c r="E852" s="62"/>
       <c r="N852" s="8"/>
       <c r="P852" s="8"/>
     </row>
     <row r="853" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A853" s="50"/>
-      <c r="E853" s="50"/>
+      <c r="A853" s="62"/>
+      <c r="E853" s="62"/>
       <c r="N853" s="8"/>
       <c r="P853" s="8"/>
     </row>
     <row r="854" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A854" s="50"/>
-      <c r="E854" s="50"/>
+      <c r="A854" s="62"/>
+      <c r="E854" s="62"/>
       <c r="N854" s="8"/>
       <c r="P854" s="8"/>
     </row>
     <row r="855" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A855" s="50"/>
-      <c r="E855" s="50"/>
+      <c r="A855" s="62"/>
+      <c r="E855" s="62"/>
       <c r="N855" s="8"/>
       <c r="P855" s="8"/>
     </row>
     <row r="856" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A856" s="50"/>
-      <c r="E856" s="50"/>
+      <c r="A856" s="62"/>
+      <c r="E856" s="62"/>
       <c r="N856" s="8"/>
       <c r="P856" s="8"/>
     </row>
     <row r="857" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A857" s="50"/>
-      <c r="E857" s="50"/>
+      <c r="A857" s="62"/>
+      <c r="E857" s="62"/>
       <c r="N857" s="8"/>
       <c r="P857" s="8"/>
     </row>
     <row r="858" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A858" s="50"/>
-      <c r="E858" s="50"/>
+      <c r="A858" s="62"/>
+      <c r="E858" s="62"/>
       <c r="N858" s="8"/>
       <c r="P858" s="8"/>
     </row>
     <row r="859" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A859" s="50"/>
-      <c r="E859" s="50"/>
+      <c r="A859" s="62"/>
+      <c r="E859" s="62"/>
       <c r="N859" s="8"/>
       <c r="P859" s="8"/>
     </row>
     <row r="860" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A860" s="50"/>
-      <c r="E860" s="50"/>
+      <c r="A860" s="62"/>
+      <c r="E860" s="62"/>
       <c r="N860" s="8"/>
       <c r="P860" s="8"/>
     </row>
     <row r="861" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A861" s="50"/>
-      <c r="E861" s="50"/>
+      <c r="A861" s="62"/>
+      <c r="E861" s="62"/>
       <c r="N861" s="8"/>
       <c r="P861" s="8"/>
     </row>
     <row r="862" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A862" s="50"/>
-      <c r="E862" s="50"/>
+      <c r="A862" s="62"/>
+      <c r="E862" s="62"/>
       <c r="N862" s="8"/>
       <c r="P862" s="8"/>
     </row>
     <row r="863" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A863" s="50"/>
-      <c r="E863" s="50"/>
+      <c r="A863" s="62"/>
+      <c r="E863" s="62"/>
       <c r="N863" s="8"/>
       <c r="P863" s="8"/>
     </row>
     <row r="864" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A864" s="50"/>
-      <c r="E864" s="50"/>
+      <c r="A864" s="62"/>
+      <c r="E864" s="62"/>
       <c r="N864" s="8"/>
       <c r="P864" s="8"/>
     </row>
     <row r="865" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A865" s="50"/>
-      <c r="E865" s="50"/>
+      <c r="A865" s="62"/>
+      <c r="E865" s="62"/>
       <c r="N865" s="8"/>
       <c r="P865" s="8"/>
     </row>
     <row r="866" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A866" s="50"/>
-      <c r="E866" s="50"/>
+      <c r="A866" s="62"/>
+      <c r="E866" s="62"/>
       <c r="N866" s="8"/>
       <c r="P866" s="8"/>
     </row>
     <row r="867" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A867" s="50"/>
-      <c r="E867" s="50"/>
+      <c r="A867" s="62"/>
+      <c r="E867" s="62"/>
       <c r="N867" s="8"/>
       <c r="P867" s="8"/>
     </row>
     <row r="868" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A868" s="50"/>
-      <c r="E868" s="50"/>
+      <c r="A868" s="62"/>
+      <c r="E868" s="62"/>
       <c r="N868" s="8"/>
       <c r="P868" s="8"/>
     </row>
     <row r="869" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A869" s="50"/>
-      <c r="E869" s="50"/>
+      <c r="A869" s="62"/>
+      <c r="E869" s="62"/>
       <c r="N869" s="8"/>
       <c r="P869" s="8"/>
     </row>
     <row r="870" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A870" s="50"/>
-      <c r="E870" s="50"/>
+      <c r="A870" s="62"/>
+      <c r="E870" s="62"/>
       <c r="N870" s="8"/>
       <c r="P870" s="8"/>
     </row>
     <row r="871" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A871" s="50"/>
-      <c r="E871" s="50"/>
+      <c r="A871" s="62"/>
+      <c r="E871" s="62"/>
       <c r="N871" s="8"/>
       <c r="P871" s="8"/>
     </row>
     <row r="872" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A872" s="50"/>
-      <c r="E872" s="50"/>
+      <c r="A872" s="62"/>
+      <c r="E872" s="62"/>
       <c r="N872" s="8"/>
       <c r="P872" s="8"/>
     </row>
     <row r="873" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A873" s="50"/>
-      <c r="E873" s="50"/>
+      <c r="A873" s="62"/>
+      <c r="E873" s="62"/>
       <c r="N873" s="8"/>
       <c r="P873" s="8"/>
     </row>
     <row r="874" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A874" s="50"/>
-      <c r="E874" s="50"/>
+      <c r="A874" s="62"/>
+      <c r="E874" s="62"/>
       <c r="N874" s="8"/>
       <c r="P874" s="8"/>
     </row>
     <row r="875" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A875" s="50"/>
-      <c r="E875" s="50"/>
+      <c r="A875" s="62"/>
+      <c r="E875" s="62"/>
       <c r="N875" s="8"/>
       <c r="P875" s="8"/>
     </row>
     <row r="876" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A876" s="50"/>
-      <c r="E876" s="50"/>
+      <c r="A876" s="62"/>
+      <c r="E876" s="62"/>
       <c r="N876" s="8"/>
       <c r="P876" s="8"/>
     </row>
     <row r="877" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A877" s="50"/>
-      <c r="E877" s="50"/>
+      <c r="A877" s="62"/>
+      <c r="E877" s="62"/>
       <c r="N877" s="8"/>
       <c r="P877" s="8"/>
     </row>
     <row r="878" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A878" s="50"/>
-      <c r="E878" s="50"/>
+      <c r="A878" s="62"/>
+      <c r="E878" s="62"/>
       <c r="N878" s="8"/>
       <c r="P878" s="8"/>
     </row>
     <row r="879" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A879" s="50"/>
-      <c r="E879" s="50"/>
+      <c r="A879" s="62"/>
+      <c r="E879" s="62"/>
       <c r="N879" s="8"/>
       <c r="P879" s="8"/>
     </row>
     <row r="880" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A880" s="50"/>
-      <c r="E880" s="50"/>
+      <c r="A880" s="62"/>
+      <c r="E880" s="62"/>
       <c r="N880" s="8"/>
       <c r="P880" s="8"/>
     </row>
     <row r="881" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A881" s="50"/>
-      <c r="E881" s="50"/>
+      <c r="A881" s="62"/>
+      <c r="E881" s="62"/>
       <c r="N881" s="8"/>
       <c r="P881" s="8"/>
     </row>
     <row r="882" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A882" s="50"/>
-      <c r="E882" s="50"/>
+      <c r="A882" s="62"/>
+      <c r="E882" s="62"/>
       <c r="N882" s="8"/>
       <c r="P882" s="8"/>
     </row>
     <row r="883" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A883" s="50"/>
-      <c r="E883" s="50"/>
+      <c r="A883" s="62"/>
+      <c r="E883" s="62"/>
       <c r="N883" s="8"/>
       <c r="P883" s="8"/>
     </row>
     <row r="884" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A884" s="50"/>
-      <c r="E884" s="50"/>
+      <c r="A884" s="62"/>
+      <c r="E884" s="62"/>
       <c r="N884" s="8"/>
       <c r="P884" s="8"/>
     </row>
     <row r="885" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A885" s="50"/>
-      <c r="E885" s="50"/>
+      <c r="A885" s="62"/>
+      <c r="E885" s="62"/>
       <c r="N885" s="8"/>
       <c r="P885" s="8"/>
     </row>
     <row r="886" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A886" s="50"/>
-      <c r="E886" s="50"/>
+      <c r="A886" s="62"/>
+      <c r="E886" s="62"/>
       <c r="N886" s="8"/>
       <c r="P886" s="8"/>
     </row>
     <row r="887" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A887" s="50"/>
-      <c r="E887" s="50"/>
+      <c r="A887" s="62"/>
+      <c r="E887" s="62"/>
       <c r="N887" s="8"/>
       <c r="P887" s="8"/>
     </row>
     <row r="888" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A888" s="50"/>
-      <c r="E888" s="50"/>
+      <c r="A888" s="62"/>
+      <c r="E888" s="62"/>
       <c r="N888" s="8"/>
       <c r="P888" s="8"/>
     </row>
     <row r="889" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A889" s="50"/>
-      <c r="E889" s="50"/>
+      <c r="A889" s="62"/>
+      <c r="E889" s="62"/>
       <c r="N889" s="8"/>
       <c r="P889" s="8"/>
     </row>
     <row r="890" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A890" s="50"/>
-      <c r="E890" s="50"/>
+      <c r="A890" s="62"/>
+      <c r="E890" s="62"/>
       <c r="N890" s="8"/>
       <c r="P890" s="8"/>
     </row>
     <row r="891" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A891" s="50"/>
-      <c r="E891" s="50"/>
+      <c r="A891" s="62"/>
+      <c r="E891" s="62"/>
       <c r="N891" s="8"/>
       <c r="P891" s="8"/>
     </row>
     <row r="892" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A892" s="50"/>
-      <c r="E892" s="50"/>
+      <c r="A892" s="62"/>
+      <c r="E892" s="62"/>
       <c r="N892" s="8"/>
       <c r="P892" s="8"/>
     </row>
     <row r="893" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A893" s="50"/>
-      <c r="E893" s="50"/>
+      <c r="A893" s="62"/>
+      <c r="E893" s="62"/>
       <c r="N893" s="8"/>
       <c r="P893" s="8"/>
     </row>
     <row r="894" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A894" s="50"/>
-      <c r="E894" s="50"/>
+      <c r="A894" s="62"/>
+      <c r="E894" s="62"/>
       <c r="N894" s="8"/>
       <c r="P894" s="8"/>
     </row>
     <row r="895" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A895" s="50"/>
-      <c r="E895" s="50"/>
+      <c r="A895" s="62"/>
+      <c r="E895" s="62"/>
       <c r="N895" s="8"/>
       <c r="P895" s="8"/>
     </row>
     <row r="896" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A896" s="50"/>
-      <c r="E896" s="50"/>
+      <c r="A896" s="62"/>
+      <c r="E896" s="62"/>
       <c r="N896" s="8"/>
       <c r="P896" s="8"/>
     </row>
     <row r="897" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A897" s="50"/>
-      <c r="E897" s="50"/>
+      <c r="A897" s="62"/>
+      <c r="E897" s="62"/>
       <c r="N897" s="8"/>
       <c r="P897" s="8"/>
     </row>
     <row r="898" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A898" s="50"/>
-      <c r="E898" s="50"/>
+      <c r="A898" s="62"/>
+      <c r="E898" s="62"/>
       <c r="N898" s="8"/>
       <c r="P898" s="8"/>
     </row>
     <row r="899" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A899" s="50"/>
-      <c r="E899" s="50"/>
+      <c r="A899" s="62"/>
+      <c r="E899" s="62"/>
       <c r="N899" s="8"/>
       <c r="P899" s="8"/>
     </row>
     <row r="900" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A900" s="50"/>
-      <c r="E900" s="50"/>
+      <c r="A900" s="62"/>
+      <c r="E900" s="62"/>
       <c r="N900" s="8"/>
       <c r="P900" s="8"/>
     </row>
     <row r="901" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A901" s="50"/>
-      <c r="E901" s="50"/>
+      <c r="A901" s="62"/>
+      <c r="E901" s="62"/>
       <c r="N901" s="8"/>
       <c r="P901" s="8"/>
     </row>
     <row r="902" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A902" s="50"/>
-      <c r="E902" s="50"/>
+      <c r="A902" s="62"/>
+      <c r="E902" s="62"/>
       <c r="N902" s="8"/>
       <c r="P902" s="8"/>
     </row>
     <row r="903" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A903" s="50"/>
-      <c r="E903" s="50"/>
+      <c r="A903" s="62"/>
+      <c r="E903" s="62"/>
       <c r="N903" s="8"/>
       <c r="P903" s="8"/>
     </row>
     <row r="904" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A904" s="50"/>
-      <c r="E904" s="50"/>
+      <c r="A904" s="62"/>
+      <c r="E904" s="62"/>
       <c r="N904" s="8"/>
       <c r="P904" s="8"/>
     </row>
     <row r="905" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A905" s="50"/>
-      <c r="E905" s="50"/>
+      <c r="A905" s="62"/>
+      <c r="E905" s="62"/>
       <c r="N905" s="8"/>
       <c r="P905" s="8"/>
     </row>
     <row r="906" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A906" s="50"/>
-      <c r="E906" s="50"/>
+      <c r="A906" s="62"/>
+      <c r="E906" s="62"/>
       <c r="N906" s="8"/>
       <c r="P906" s="8"/>
     </row>
     <row r="907" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A907" s="50"/>
-      <c r="E907" s="50"/>
+      <c r="A907" s="62"/>
+      <c r="E907" s="62"/>
       <c r="N907" s="8"/>
       <c r="P907" s="8"/>
     </row>
     <row r="908" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A908" s="50"/>
-      <c r="E908" s="50"/>
+      <c r="A908" s="62"/>
+      <c r="E908" s="62"/>
       <c r="N908" s="8"/>
       <c r="P908" s="8"/>
     </row>
     <row r="909" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A909" s="50"/>
-      <c r="E909" s="50"/>
+      <c r="A909" s="62"/>
+      <c r="E909" s="62"/>
       <c r="N909" s="8"/>
       <c r="P909" s="8"/>
     </row>
     <row r="910" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A910" s="50"/>
-      <c r="E910" s="50"/>
+      <c r="A910" s="62"/>
+      <c r="E910" s="62"/>
       <c r="N910" s="8"/>
       <c r="P910" s="8"/>
     </row>
     <row r="911" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A911" s="50"/>
-      <c r="E911" s="50"/>
+      <c r="A911" s="62"/>
+      <c r="E911" s="62"/>
       <c r="N911" s="8"/>
       <c r="P911" s="8"/>
     </row>
     <row r="912" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A912" s="50"/>
-      <c r="E912" s="50"/>
+      <c r="A912" s="62"/>
+      <c r="E912" s="62"/>
       <c r="N912" s="8"/>
       <c r="P912" s="8"/>
     </row>
     <row r="913" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A913" s="50"/>
-      <c r="E913" s="50"/>
+      <c r="A913" s="62"/>
+      <c r="E913" s="62"/>
       <c r="N913" s="8"/>
       <c r="P913" s="8"/>
     </row>
     <row r="914" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A914" s="50"/>
-      <c r="E914" s="50"/>
+      <c r="A914" s="62"/>
+      <c r="E914" s="62"/>
       <c r="N914" s="8"/>
       <c r="P914" s="8"/>
     </row>
     <row r="915" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A915" s="50"/>
-      <c r="E915" s="50"/>
+      <c r="A915" s="62"/>
+      <c r="E915" s="62"/>
       <c r="N915" s="8"/>
       <c r="P915" s="8"/>
     </row>
     <row r="916" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A916" s="50"/>
-      <c r="E916" s="50"/>
+      <c r="A916" s="62"/>
+      <c r="E916" s="62"/>
       <c r="N916" s="8"/>
       <c r="P916" s="8"/>
     </row>
     <row r="917" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A917" s="50"/>
-      <c r="E917" s="50"/>
+      <c r="A917" s="62"/>
+      <c r="E917" s="62"/>
       <c r="N917" s="8"/>
       <c r="P917" s="8"/>
     </row>
     <row r="918" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A918" s="50"/>
-      <c r="E918" s="50"/>
+      <c r="A918" s="62"/>
+      <c r="E918" s="62"/>
       <c r="N918" s="8"/>
       <c r="P918" s="8"/>
     </row>
     <row r="919" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A919" s="50"/>
-      <c r="E919" s="50"/>
+      <c r="A919" s="62"/>
+      <c r="E919" s="62"/>
       <c r="N919" s="8"/>
       <c r="P919" s="8"/>
     </row>
     <row r="920" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A920" s="50"/>
-      <c r="E920" s="50"/>
+      <c r="A920" s="62"/>
+      <c r="E920" s="62"/>
       <c r="N920" s="8"/>
       <c r="P920" s="8"/>
     </row>
     <row r="921" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A921" s="50"/>
-      <c r="E921" s="50"/>
+      <c r="A921" s="62"/>
+      <c r="E921" s="62"/>
       <c r="N921" s="8"/>
       <c r="P921" s="8"/>
     </row>
     <row r="922" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A922" s="50"/>
-      <c r="E922" s="50"/>
+      <c r="A922" s="62"/>
+      <c r="E922" s="62"/>
       <c r="N922" s="8"/>
       <c r="P922" s="8"/>
     </row>
     <row r="923" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A923" s="50"/>
-      <c r="E923" s="50"/>
+      <c r="A923" s="62"/>
+      <c r="E923" s="62"/>
       <c r="N923" s="8"/>
       <c r="P923" s="8"/>
     </row>
     <row r="924" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A924" s="50"/>
-      <c r="E924" s="50"/>
+      <c r="A924" s="62"/>
+      <c r="E924" s="62"/>
       <c r="N924" s="8"/>
       <c r="P924" s="8"/>
     </row>
     <row r="925" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A925" s="50"/>
-      <c r="E925" s="50"/>
+      <c r="A925" s="62"/>
+      <c r="E925" s="62"/>
       <c r="N925" s="8"/>
       <c r="P925" s="8"/>
     </row>
     <row r="926" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A926" s="50"/>
-      <c r="E926" s="50"/>
+      <c r="A926" s="62"/>
+      <c r="E926" s="62"/>
       <c r="N926" s="8"/>
       <c r="P926" s="8"/>
     </row>
     <row r="927" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A927" s="50"/>
-      <c r="E927" s="50"/>
+      <c r="A927" s="62"/>
+      <c r="E927" s="62"/>
       <c r="N927" s="8"/>
       <c r="P927" s="8"/>
     </row>
     <row r="928" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A928" s="50"/>
-      <c r="E928" s="50"/>
+      <c r="A928" s="62"/>
+      <c r="E928" s="62"/>
       <c r="N928" s="8"/>
       <c r="P928" s="8"/>
     </row>
     <row r="929" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A929" s="50"/>
-      <c r="E929" s="50"/>
+      <c r="A929" s="62"/>
+      <c r="E929" s="62"/>
       <c r="N929" s="8"/>
       <c r="P929" s="8"/>
     </row>
     <row r="930" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A930" s="50"/>
-      <c r="E930" s="50"/>
+      <c r="A930" s="62"/>
+      <c r="E930" s="62"/>
       <c r="N930" s="8"/>
       <c r="P930" s="8"/>
     </row>
     <row r="931" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A931" s="50"/>
-      <c r="E931" s="50"/>
+      <c r="A931" s="62"/>
+      <c r="E931" s="62"/>
       <c r="N931" s="8"/>
       <c r="P931" s="8"/>
     </row>
     <row r="932" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A932" s="50"/>
-      <c r="E932" s="50"/>
+      <c r="A932" s="62"/>
+      <c r="E932" s="62"/>
       <c r="N932" s="8"/>
       <c r="P932" s="8"/>
     </row>
     <row r="933" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A933" s="50"/>
-      <c r="E933" s="50"/>
+      <c r="A933" s="62"/>
+      <c r="E933" s="62"/>
       <c r="N933" s="8"/>
       <c r="P933" s="8"/>
     </row>
     <row r="934" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A934" s="50"/>
-      <c r="E934" s="50"/>
+      <c r="A934" s="62"/>
+      <c r="E934" s="62"/>
       <c r="N934" s="8"/>
       <c r="P934" s="8"/>
     </row>
     <row r="935" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A935" s="50"/>
-      <c r="E935" s="50"/>
+      <c r="A935" s="62"/>
+      <c r="E935" s="62"/>
       <c r="N935" s="8"/>
       <c r="P935" s="8"/>
     </row>
     <row r="936" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A936" s="50"/>
-      <c r="E936" s="50"/>
+      <c r="A936" s="62"/>
+      <c r="E936" s="62"/>
       <c r="N936" s="8"/>
       <c r="P936" s="8"/>
     </row>
     <row r="937" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A937" s="50"/>
-      <c r="E937" s="50"/>
+      <c r="A937" s="62"/>
+      <c r="E937" s="62"/>
       <c r="N937" s="8"/>
       <c r="P937" s="8"/>
     </row>
     <row r="938" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A938" s="50"/>
-      <c r="E938" s="50"/>
+      <c r="A938" s="62"/>
+      <c r="E938" s="62"/>
       <c r="N938" s="8"/>
       <c r="P938" s="8"/>
     </row>
     <row r="939" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A939" s="50"/>
-      <c r="E939" s="50"/>
+      <c r="A939" s="62"/>
+      <c r="E939" s="62"/>
       <c r="N939" s="8"/>
       <c r="P939" s="8"/>
     </row>
     <row r="940" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A940" s="50"/>
-      <c r="E940" s="50"/>
+      <c r="A940" s="62"/>
+      <c r="E940" s="62"/>
       <c r="N940" s="8"/>
       <c r="P940" s="8"/>
     </row>
     <row r="941" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A941" s="50"/>
-      <c r="E941" s="50"/>
+      <c r="A941" s="62"/>
+      <c r="E941" s="62"/>
       <c r="N941" s="8"/>
       <c r="P941" s="8"/>
     </row>
     <row r="942" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A942" s="50"/>
-      <c r="E942" s="50"/>
+      <c r="A942" s="62"/>
+      <c r="E942" s="62"/>
       <c r="N942" s="8"/>
       <c r="P942" s="8"/>
     </row>
     <row r="943" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A943" s="50"/>
-      <c r="E943" s="50"/>
+      <c r="A943" s="62"/>
+      <c r="E943" s="62"/>
       <c r="N943" s="8"/>
       <c r="P943" s="8"/>
     </row>
     <row r="944" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A944" s="50"/>
-      <c r="E944" s="50"/>
+      <c r="A944" s="62"/>
+      <c r="E944" s="62"/>
       <c r="N944" s="8"/>
       <c r="P944" s="8"/>
     </row>
     <row r="945" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A945" s="50"/>
-      <c r="E945" s="50"/>
+      <c r="A945" s="62"/>
+      <c r="E945" s="62"/>
       <c r="N945" s="8"/>
       <c r="P945" s="8"/>
     </row>
     <row r="946" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A946" s="50"/>
-      <c r="E946" s="50"/>
+      <c r="A946" s="62"/>
+      <c r="E946" s="62"/>
       <c r="N946" s="8"/>
       <c r="P946" s="8"/>
     </row>
     <row r="947" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A947" s="50"/>
-      <c r="E947" s="50"/>
+      <c r="A947" s="62"/>
+      <c r="E947" s="62"/>
       <c r="N947" s="8"/>
       <c r="P947" s="8"/>
     </row>
     <row r="948" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A948" s="50"/>
-      <c r="E948" s="50"/>
+      <c r="A948" s="62"/>
+      <c r="E948" s="62"/>
       <c r="N948" s="8"/>
       <c r="P948" s="8"/>
     </row>
     <row r="949" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A949" s="50"/>
-      <c r="E949" s="50"/>
+      <c r="A949" s="62"/>
+      <c r="E949" s="62"/>
       <c r="N949" s="8"/>
       <c r="P949" s="8"/>
     </row>
     <row r="950" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A950" s="50"/>
-      <c r="E950" s="50"/>
+      <c r="A950" s="62"/>
+      <c r="E950" s="62"/>
       <c r="N950" s="8"/>
       <c r="P950" s="8"/>
     </row>
     <row r="951" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A951" s="50"/>
-      <c r="E951" s="50"/>
+      <c r="A951" s="62"/>
+      <c r="E951" s="62"/>
       <c r="N951" s="8"/>
       <c r="P951" s="8"/>
     </row>
     <row r="952" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A952" s="50"/>
-      <c r="E952" s="50"/>
+      <c r="A952" s="62"/>
+      <c r="E952" s="62"/>
       <c r="N952" s="8"/>
       <c r="P952" s="8"/>
     </row>
     <row r="953" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A953" s="50"/>
-      <c r="E953" s="50"/>
+      <c r="A953" s="62"/>
+      <c r="E953" s="62"/>
       <c r="N953" s="8"/>
       <c r="P953" s="8"/>
     </row>
     <row r="954" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A954" s="50"/>
-      <c r="E954" s="50"/>
+      <c r="A954" s="62"/>
+      <c r="E954" s="62"/>
       <c r="N954" s="8"/>
       <c r="P954" s="8"/>
     </row>
     <row r="955" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A955" s="50"/>
-      <c r="E955" s="50"/>
+      <c r="A955" s="62"/>
+      <c r="E955" s="62"/>
       <c r="N955" s="8"/>
       <c r="P955" s="8"/>
     </row>
     <row r="956" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A956" s="50"/>
-      <c r="E956" s="50"/>
+      <c r="A956" s="62"/>
+      <c r="E956" s="62"/>
       <c r="N956" s="8"/>
       <c r="P956" s="8"/>
     </row>
     <row r="957" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A957" s="50"/>
-      <c r="E957" s="50"/>
+      <c r="A957" s="62"/>
+      <c r="E957" s="62"/>
       <c r="N957" s="8"/>
       <c r="P957" s="8"/>
     </row>
     <row r="958" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A958" s="50"/>
-      <c r="E958" s="50"/>
+      <c r="A958" s="62"/>
+      <c r="E958" s="62"/>
       <c r="N958" s="8"/>
       <c r="P958" s="8"/>
     </row>
     <row r="959" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A959" s="50"/>
-      <c r="E959" s="50"/>
+      <c r="A959" s="62"/>
+      <c r="E959" s="62"/>
       <c r="N959" s="8"/>
       <c r="P959" s="8"/>
     </row>
     <row r="960" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A960" s="50"/>
-      <c r="E960" s="50"/>
+      <c r="A960" s="62"/>
+      <c r="E960" s="62"/>
       <c r="N960" s="8"/>
       <c r="P960" s="8"/>
     </row>
     <row r="961" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A961" s="50"/>
-      <c r="E961" s="50"/>
+      <c r="A961" s="62"/>
+      <c r="E961" s="62"/>
       <c r="N961" s="8"/>
       <c r="P961" s="8"/>
     </row>
     <row r="962" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A962" s="50"/>
-      <c r="E962" s="50"/>
+      <c r="A962" s="62"/>
+      <c r="E962" s="62"/>
       <c r="N962" s="8"/>
       <c r="P962" s="8"/>
     </row>
     <row r="963" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A963" s="50"/>
-      <c r="E963" s="50"/>
+      <c r="A963" s="62"/>
+      <c r="E963" s="62"/>
       <c r="N963" s="8"/>
       <c r="P963" s="8"/>
     </row>
     <row r="964" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A964" s="50"/>
-      <c r="E964" s="50"/>
+      <c r="A964" s="62"/>
+      <c r="E964" s="62"/>
       <c r="N964" s="8"/>
       <c r="P964" s="8"/>
     </row>
     <row r="965" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A965" s="50"/>
-      <c r="E965" s="50"/>
+      <c r="A965" s="62"/>
+      <c r="E965" s="62"/>
       <c r="N965" s="8"/>
       <c r="P965" s="8"/>
     </row>
     <row r="966" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A966" s="50"/>
-      <c r="E966" s="50"/>
+      <c r="A966" s="62"/>
+      <c r="E966" s="62"/>
       <c r="N966" s="8"/>
       <c r="P966" s="8"/>
     </row>
     <row r="967" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A967" s="50"/>
-      <c r="E967" s="50"/>
+      <c r="A967" s="62"/>
+      <c r="E967" s="62"/>
       <c r="N967" s="8"/>
       <c r="P967" s="8"/>
     </row>
     <row r="968" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A968" s="50"/>
-      <c r="E968" s="50"/>
+      <c r="A968" s="62"/>
+      <c r="E968" s="62"/>
       <c r="N968" s="8"/>
       <c r="P968" s="8"/>
     </row>
     <row r="969" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A969" s="50"/>
-      <c r="E969" s="50"/>
+      <c r="A969" s="62"/>
+      <c r="E969" s="62"/>
       <c r="N969" s="8"/>
       <c r="P969" s="8"/>
     </row>
     <row r="970" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A970" s="50"/>
-      <c r="E970" s="50"/>
+      <c r="A970" s="62"/>
+      <c r="E970" s="62"/>
       <c r="N970" s="8"/>
       <c r="P970" s="8"/>
     </row>
     <row r="971" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A971" s="50"/>
-      <c r="E971" s="50"/>
+      <c r="A971" s="62"/>
+      <c r="E971" s="62"/>
       <c r="N971" s="8"/>
       <c r="P971" s="8"/>
     </row>
     <row r="972" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A972" s="50"/>
-      <c r="E972" s="50"/>
+      <c r="A972" s="62"/>
+      <c r="E972" s="62"/>
       <c r="N972" s="8"/>
       <c r="P972" s="8"/>
     </row>
     <row r="973" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A973" s="50"/>
-      <c r="E973" s="50"/>
+      <c r="A973" s="62"/>
+      <c r="E973" s="62"/>
       <c r="N973" s="8"/>
       <c r="P973" s="8"/>
     </row>
     <row r="974" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A974" s="50"/>
-      <c r="E974" s="50"/>
+      <c r="A974" s="62"/>
+      <c r="E974" s="62"/>
       <c r="N974" s="8"/>
       <c r="P974" s="8"/>
     </row>
     <row r="975" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A975" s="50"/>
-      <c r="E975" s="50"/>
+      <c r="A975" s="62"/>
+      <c r="E975" s="62"/>
       <c r="N975" s="8"/>
       <c r="P975" s="8"/>
     </row>
     <row r="976" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A976" s="50"/>
-      <c r="E976" s="50"/>
+      <c r="A976" s="62"/>
+      <c r="E976" s="62"/>
       <c r="N976" s="8"/>
       <c r="P976" s="8"/>
     </row>
     <row r="977" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A977" s="50"/>
-      <c r="E977" s="50"/>
+      <c r="A977" s="62"/>
+      <c r="E977" s="62"/>
       <c r="N977" s="8"/>
       <c r="P977" s="8"/>
     </row>
     <row r="978" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A978" s="50"/>
-      <c r="E978" s="50"/>
+      <c r="A978" s="62"/>
+      <c r="E978" s="62"/>
       <c r="N978" s="8"/>
       <c r="P978" s="8"/>
     </row>
     <row r="979" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A979" s="50"/>
-      <c r="E979" s="50"/>
+      <c r="A979" s="62"/>
+      <c r="E979" s="62"/>
       <c r="N979" s="8"/>
       <c r="P979" s="8"/>
     </row>
     <row r="980" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A980" s="50"/>
-      <c r="E980" s="50"/>
+      <c r="A980" s="62"/>
+      <c r="E980" s="62"/>
       <c r="N980" s="8"/>
       <c r="P980" s="8"/>
     </row>
     <row r="981" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A981" s="50"/>
-      <c r="E981" s="50"/>
+      <c r="A981" s="62"/>
+      <c r="E981" s="62"/>
       <c r="N981" s="8"/>
       <c r="P981" s="8"/>
     </row>
     <row r="982" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A982" s="50"/>
-      <c r="E982" s="50"/>
+      <c r="A982" s="62"/>
+      <c r="E982" s="62"/>
       <c r="N982" s="8"/>
       <c r="P982" s="8"/>
     </row>
     <row r="983" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A983" s="50"/>
-      <c r="E983" s="50"/>
+      <c r="A983" s="62"/>
+      <c r="E983" s="62"/>
       <c r="N983" s="8"/>
       <c r="P983" s="8"/>
     </row>
     <row r="984" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A984" s="50"/>
-      <c r="E984" s="50"/>
+      <c r="A984" s="62"/>
+      <c r="E984" s="62"/>
       <c r="N984" s="8"/>
       <c r="P984" s="8"/>
     </row>
     <row r="985" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A985" s="50"/>
-      <c r="E985" s="50"/>
+      <c r="A985" s="62"/>
+      <c r="E985" s="62"/>
       <c r="N985" s="8"/>
       <c r="P985" s="8"/>
     </row>
     <row r="986" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A986" s="50"/>
-      <c r="E986" s="50"/>
+      <c r="A986" s="62"/>
+      <c r="E986" s="62"/>
       <c r="N986" s="8"/>
       <c r="P986" s="8"/>
     </row>
     <row r="987" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A987" s="50"/>
-      <c r="E987" s="50"/>
+      <c r="A987" s="62"/>
+      <c r="E987" s="62"/>
       <c r="N987" s="8"/>
       <c r="P987" s="8"/>
     </row>
     <row r="988" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A988" s="50"/>
-      <c r="E988" s="50"/>
+      <c r="A988" s="62"/>
+      <c r="E988" s="62"/>
       <c r="N988" s="8"/>
       <c r="P988" s="8"/>
     </row>
     <row r="989" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A989" s="50"/>
-      <c r="E989" s="50"/>
+      <c r="A989" s="62"/>
+      <c r="E989" s="62"/>
       <c r="N989" s="8"/>
       <c r="P989" s="8"/>
     </row>
     <row r="990" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A990" s="50"/>
-      <c r="E990" s="50"/>
+      <c r="A990" s="62"/>
+      <c r="E990" s="62"/>
       <c r="N990" s="8"/>
       <c r="P990" s="8"/>
     </row>
     <row r="991" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A991" s="50"/>
-      <c r="E991" s="50"/>
+      <c r="A991" s="62"/>
+      <c r="E991" s="62"/>
       <c r="N991" s="8"/>
       <c r="P991" s="8"/>
     </row>
     <row r="992" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A992" s="50"/>
-      <c r="E992" s="50"/>
+      <c r="A992" s="62"/>
+      <c r="E992" s="62"/>
       <c r="N992" s="8"/>
       <c r="P992" s="8"/>
     </row>
     <row r="993" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A993" s="50"/>
-      <c r="E993" s="50"/>
+      <c r="A993" s="62"/>
+      <c r="E993" s="62"/>
       <c r="N993" s="8"/>
       <c r="P993" s="8"/>
     </row>
     <row r="994" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A994" s="50"/>
-      <c r="E994" s="50"/>
+      <c r="A994" s="62"/>
+      <c r="E994" s="62"/>
       <c r="N994" s="8"/>
       <c r="P994" s="8"/>
     </row>
     <row r="995" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A995" s="50"/>
-      <c r="E995" s="50"/>
+      <c r="A995" s="62"/>
+      <c r="E995" s="62"/>
       <c r="N995" s="8"/>
       <c r="P995" s="8"/>
     </row>
     <row r="996" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A996" s="50"/>
-      <c r="E996" s="50"/>
+      <c r="A996" s="62"/>
+      <c r="E996" s="62"/>
       <c r="N996" s="8"/>
       <c r="P996" s="8"/>
     </row>
     <row r="997" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A997" s="50"/>
-      <c r="E997" s="50"/>
+      <c r="A997" s="62"/>
+      <c r="E997" s="62"/>
       <c r="N997" s="8"/>
       <c r="P997" s="8"/>
     </row>
     <row r="998" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A998" s="50"/>
-      <c r="E998" s="50"/>
+      <c r="A998" s="62"/>
+      <c r="E998" s="62"/>
       <c r="N998" s="8"/>
       <c r="P998" s="8"/>
     </row>
     <row r="999" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A999" s="50"/>
-      <c r="E999" s="50"/>
+      <c r="A999" s="62"/>
+      <c r="E999" s="62"/>
       <c r="N999" s="8"/>
       <c r="P999" s="8"/>
     </row>
     <row r="1000" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1000" s="50"/>
-      <c r="E1000" s="50"/>
+      <c r="A1000" s="62"/>
+      <c r="E1000" s="62"/>
       <c r="N1000" s="8"/>
       <c r="P1000" s="8"/>
     </row>
     <row r="1001" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1001" s="50"/>
-      <c r="E1001" s="50"/>
+      <c r="A1001" s="62"/>
+      <c r="E1001" s="62"/>
       <c r="N1001" s="8"/>
       <c r="P1001" s="8"/>
     </row>
     <row r="1002" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1002" s="50"/>
-      <c r="E1002" s="50"/>
+      <c r="A1002" s="62"/>
+      <c r="E1002" s="62"/>
       <c r="N1002" s="8"/>
       <c r="P1002" s="8"/>
     </row>
     <row r="1003" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1003" s="50"/>
-      <c r="E1003" s="50"/>
+      <c r="A1003" s="62"/>
+      <c r="E1003" s="62"/>
       <c r="N1003" s="8"/>
       <c r="P1003" s="8"/>
     </row>
     <row r="1004" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1004" s="50"/>
-      <c r="E1004" s="50"/>
+      <c r="A1004" s="62"/>
+      <c r="E1004" s="62"/>
       <c r="N1004" s="8"/>
       <c r="P1004" s="8"/>
     </row>
     <row r="1005" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1005" s="50"/>
-      <c r="E1005" s="50"/>
+      <c r="A1005" s="62"/>
+      <c r="E1005" s="62"/>
       <c r="N1005" s="8"/>
       <c r="P1005" s="8"/>
     </row>
     <row r="1006" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1006" s="50"/>
-      <c r="E1006" s="50"/>
+      <c r="A1006" s="62"/>
+      <c r="E1006" s="62"/>
       <c r="N1006" s="8"/>
       <c r="P1006" s="8"/>
     </row>
     <row r="1007" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1007" s="50"/>
-      <c r="E1007" s="50"/>
+      <c r="A1007" s="62"/>
+      <c r="E1007" s="62"/>
       <c r="N1007" s="8"/>
       <c r="P1007" s="8"/>
     </row>
     <row r="1008" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1008" s="50"/>
-      <c r="E1008" s="50"/>
+      <c r="A1008" s="62"/>
+      <c r="E1008" s="62"/>
       <c r="N1008" s="8"/>
       <c r="P1008" s="8"/>
     </row>
     <row r="1009" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1009" s="50"/>
-      <c r="E1009" s="50"/>
+      <c r="A1009" s="62"/>
+      <c r="E1009" s="62"/>
       <c r="N1009" s="8"/>
       <c r="P1009" s="8"/>
     </row>
     <row r="1010" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1010" s="50"/>
-      <c r="E1010" s="50"/>
+      <c r="A1010" s="62"/>
+      <c r="E1010" s="62"/>
       <c r="N1010" s="8"/>
       <c r="P1010" s="8"/>
     </row>
     <row r="1011" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1011" s="50"/>
-      <c r="E1011" s="50"/>
+      <c r="A1011" s="62"/>
+      <c r="E1011" s="62"/>
       <c r="N1011" s="8"/>
       <c r="P1011" s="8"/>
     </row>
     <row r="1012" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1012" s="50"/>
-      <c r="E1012" s="50"/>
+      <c r="A1012" s="62"/>
+      <c r="E1012" s="62"/>
       <c r="N1012" s="8"/>
       <c r="P1012" s="8"/>
     </row>
     <row r="1013" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1013" s="50"/>
-      <c r="E1013" s="50"/>
+      <c r="A1013" s="62"/>
+      <c r="E1013" s="62"/>
       <c r="N1013" s="8"/>
       <c r="P1013" s="8"/>
     </row>
     <row r="1014" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1014" s="50"/>
-      <c r="E1014" s="50"/>
+      <c r="A1014" s="62"/>
+      <c r="E1014" s="62"/>
       <c r="N1014" s="8"/>
       <c r="P1014" s="8"/>
     </row>
     <row r="1015" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1015" s="50"/>
-      <c r="E1015" s="50"/>
+      <c r="A1015" s="62"/>
+      <c r="E1015" s="62"/>
       <c r="N1015" s="8"/>
       <c r="P1015" s="8"/>
     </row>
     <row r="1016" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1016" s="50"/>
-      <c r="E1016" s="50"/>
+      <c r="A1016" s="62"/>
+      <c r="E1016" s="62"/>
       <c r="N1016" s="8"/>
       <c r="P1016" s="8"/>
     </row>
     <row r="1017" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1017" s="50"/>
-      <c r="E1017" s="50"/>
+      <c r="A1017" s="62"/>
+      <c r="E1017" s="62"/>
       <c r="N1017" s="8"/>
       <c r="P1017" s="8"/>
     </row>
     <row r="1018" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1018" s="50"/>
-      <c r="E1018" s="50"/>
+      <c r="A1018" s="62"/>
+      <c r="E1018" s="62"/>
       <c r="N1018" s="8"/>
       <c r="P1018" s="8"/>
     </row>
     <row r="1019" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1019" s="50"/>
-      <c r="E1019" s="50"/>
+      <c r="A1019" s="62"/>
+      <c r="E1019" s="62"/>
       <c r="N1019" s="8"/>
       <c r="P1019" s="8"/>
     </row>
     <row r="1020" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1020" s="50"/>
-      <c r="E1020" s="50"/>
+      <c r="A1020" s="62"/>
+      <c r="E1020" s="62"/>
       <c r="N1020" s="8"/>
       <c r="P1020" s="8"/>
     </row>
     <row r="1021" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1021" s="50"/>
-      <c r="E1021" s="50"/>
+      <c r="A1021" s="62"/>
+      <c r="E1021" s="62"/>
       <c r="N1021" s="8"/>
       <c r="P1021" s="8"/>
     </row>
     <row r="1022" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1022" s="50"/>
-      <c r="E1022" s="50"/>
+      <c r="A1022" s="62"/>
+      <c r="E1022" s="62"/>
       <c r="N1022" s="8"/>
       <c r="P1022" s="8"/>
     </row>
     <row r="1023" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1023" s="50"/>
-      <c r="E1023" s="50"/>
+      <c r="A1023" s="62"/>
+      <c r="E1023" s="62"/>
       <c r="N1023" s="8"/>
       <c r="P1023" s="8"/>
     </row>
     <row r="1024" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1024" s="50"/>
-      <c r="E1024" s="50"/>
+      <c r="A1024" s="62"/>
+      <c r="E1024" s="62"/>
       <c r="N1024" s="8"/>
       <c r="P1024" s="8"/>
     </row>
     <row r="1025" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1025" s="50"/>
-      <c r="E1025" s="50"/>
+      <c r="A1025" s="62"/>
+      <c r="E1025" s="62"/>
       <c r="N1025" s="8"/>
       <c r="P1025" s="8"/>
     </row>
     <row r="1026" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1026" s="50"/>
-      <c r="E1026" s="50"/>
+      <c r="A1026" s="62"/>
+      <c r="E1026" s="62"/>
       <c r="N1026" s="8"/>
       <c r="P1026" s="8"/>
     </row>
     <row r="1027" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1027" s="50"/>
-      <c r="E1027" s="50"/>
+      <c r="A1027" s="62"/>
+      <c r="E1027" s="62"/>
       <c r="N1027" s="8"/>
       <c r="P1027" s="8"/>
     </row>
     <row r="1028" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1028" s="50"/>
-      <c r="E1028" s="50"/>
+      <c r="A1028" s="62"/>
+      <c r="E1028" s="62"/>
       <c r="N1028" s="8"/>
       <c r="P1028" s="8"/>
     </row>
     <row r="1029" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1029" s="50"/>
-      <c r="E1029" s="50"/>
+      <c r="A1029" s="62"/>
+      <c r="E1029" s="62"/>
       <c r="N1029" s="8"/>
       <c r="P1029" s="8"/>
     </row>
     <row r="1030" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1030" s="50"/>
-      <c r="E1030" s="50"/>
+      <c r="A1030" s="62"/>
+      <c r="E1030" s="62"/>
       <c r="N1030" s="8"/>
       <c r="P1030" s="8"/>
     </row>
     <row r="1031" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1031" s="50"/>
-      <c r="E1031" s="50"/>
+      <c r="A1031" s="62"/>
+      <c r="E1031" s="62"/>
       <c r="N1031" s="8"/>
       <c r="P1031" s="8"/>
     </row>
     <row r="1032" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1032" s="50"/>
-      <c r="E1032" s="50"/>
+      <c r="A1032" s="62"/>
+      <c r="E1032" s="62"/>
       <c r="N1032" s="8"/>
       <c r="P1032" s="8"/>
     </row>
     <row r="1033" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1033" s="50"/>
-      <c r="E1033" s="50"/>
+      <c r="A1033" s="62"/>
+      <c r="E1033" s="62"/>
       <c r="N1033" s="8"/>
       <c r="P1033" s="8"/>
     </row>
     <row r="1034" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1034" s="50"/>
-      <c r="E1034" s="50"/>
+      <c r="A1034" s="62"/>
+      <c r="E1034" s="62"/>
       <c r="N1034" s="8"/>
       <c r="P1034" s="8"/>
     </row>
     <row r="1035" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1035" s="50"/>
-      <c r="E1035" s="50"/>
+      <c r="A1035" s="62"/>
+      <c r="E1035" s="62"/>
       <c r="N1035" s="8"/>
       <c r="P1035" s="8"/>
     </row>
     <row r="1036" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1036" s="50"/>
-      <c r="E1036" s="50"/>
+      <c r="A1036" s="62"/>
+      <c r="E1036" s="62"/>
       <c r="N1036" s="8"/>
       <c r="P1036" s="8"/>
     </row>
     <row r="1037" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1037" s="50"/>
-      <c r="E1037" s="50"/>
+      <c r="A1037" s="62"/>
+      <c r="E1037" s="62"/>
       <c r="N1037" s="8"/>
       <c r="P1037" s="8"/>
     </row>
     <row r="1038" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1038" s="50"/>
-      <c r="E1038" s="50"/>
+      <c r="A1038" s="62"/>
+      <c r="E1038" s="62"/>
       <c r="N1038" s="8"/>
       <c r="P1038" s="8"/>
     </row>
     <row r="1039" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1039" s="50"/>
-      <c r="E1039" s="50"/>
+      <c r="A1039" s="62"/>
+      <c r="E1039" s="62"/>
       <c r="N1039" s="8"/>
       <c r="P1039" s="8"/>
     </row>
     <row r="1040" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1040" s="50"/>
-      <c r="E1040" s="50"/>
+      <c r="A1040" s="62"/>
+      <c r="E1040" s="62"/>
       <c r="N1040" s="8"/>
       <c r="P1040" s="8"/>
     </row>
     <row r="1041" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1041" s="50"/>
-      <c r="E1041" s="50"/>
+      <c r="A1041" s="62"/>
+      <c r="E1041" s="62"/>
       <c r="N1041" s="8"/>
       <c r="P1041" s="8"/>
     </row>
     <row r="1042" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1042" s="50"/>
-      <c r="E1042" s="50"/>
+      <c r="A1042" s="62"/>
+      <c r="E1042" s="62"/>
       <c r="N1042" s="8"/>
       <c r="P1042" s="8"/>
     </row>
     <row r="1043" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1043" s="50"/>
-      <c r="E1043" s="50"/>
+      <c r="A1043" s="62"/>
+      <c r="E1043" s="62"/>
       <c r="N1043" s="8"/>
       <c r="P1043" s="8"/>
     </row>
     <row r="1044" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1044" s="50"/>
-      <c r="E1044" s="50"/>
+      <c r="A1044" s="62"/>
+      <c r="E1044" s="62"/>
       <c r="N1044" s="8"/>
       <c r="P1044" s="8"/>
     </row>
     <row r="1045" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1045" s="50"/>
-      <c r="E1045" s="50"/>
+      <c r="A1045" s="62"/>
+      <c r="E1045" s="62"/>
       <c r="N1045" s="8"/>
       <c r="P1045" s="8"/>
     </row>
     <row r="1046" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1046" s="50"/>
-      <c r="E1046" s="50"/>
+      <c r="A1046" s="62"/>
+      <c r="E1046" s="62"/>
       <c r="N1046" s="8"/>
       <c r="P1046" s="8"/>
     </row>
     <row r="1047" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1047" s="50"/>
-      <c r="E1047" s="50"/>
+      <c r="A1047" s="62"/>
+      <c r="E1047" s="62"/>
       <c r="N1047" s="8"/>
       <c r="P1047" s="8"/>
     </row>
     <row r="1048" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1048" s="50"/>
-      <c r="E1048" s="50"/>
+      <c r="A1048" s="62"/>
+      <c r="E1048" s="62"/>
       <c r="N1048" s="8"/>
       <c r="P1048" s="8"/>
     </row>
     <row r="1049" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1049" s="50"/>
-      <c r="E1049" s="50"/>
+      <c r="A1049" s="62"/>
+      <c r="E1049" s="62"/>
       <c r="N1049" s="8"/>
       <c r="P1049" s="8"/>
     </row>
     <row r="1050" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1050" s="50"/>
-      <c r="E1050" s="50"/>
+      <c r="A1050" s="62"/>
+      <c r="E1050" s="62"/>
       <c r="N1050" s="8"/>
       <c r="P1050" s="8"/>
     </row>
     <row r="1051" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1051" s="50"/>
-      <c r="E1051" s="50"/>
+      <c r="A1051" s="62"/>
+      <c r="E1051" s="62"/>
       <c r="N1051" s="8"/>
       <c r="P1051" s="8"/>
     </row>
     <row r="1052" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1052" s="50"/>
-      <c r="E1052" s="50"/>
+      <c r="A1052" s="62"/>
+      <c r="E1052" s="62"/>
       <c r="N1052" s="8"/>
       <c r="P1052" s="8"/>
     </row>
     <row r="1053" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1053" s="50"/>
-      <c r="E1053" s="50"/>
+      <c r="A1053" s="62"/>
+      <c r="E1053" s="62"/>
       <c r="N1053" s="8"/>
       <c r="P1053" s="8"/>
     </row>
     <row r="1054" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1054" s="50"/>
-      <c r="E1054" s="50"/>
+      <c r="A1054" s="62"/>
+      <c r="E1054" s="62"/>
       <c r="N1054" s="8"/>
       <c r="P1054" s="8"/>
     </row>
     <row r="1055" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1055" s="50"/>
-      <c r="E1055" s="50"/>
+      <c r="A1055" s="62"/>
+      <c r="E1055" s="62"/>
       <c r="N1055" s="8"/>
       <c r="P1055" s="8"/>
     </row>
     <row r="1056" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1056" s="50"/>
-      <c r="E1056" s="50"/>
+      <c r="A1056" s="62"/>
+      <c r="E1056" s="62"/>
       <c r="N1056" s="8"/>
       <c r="P1056" s="8"/>
     </row>
     <row r="1057" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1057" s="50"/>
-      <c r="E1057" s="50"/>
+      <c r="A1057" s="62"/>
+      <c r="E1057" s="62"/>
       <c r="N1057" s="8"/>
       <c r="P1057" s="8"/>
     </row>
     <row r="1058" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1058" s="50"/>
-      <c r="E1058" s="50"/>
+      <c r="A1058" s="62"/>
+      <c r="E1058" s="62"/>
       <c r="N1058" s="8"/>
       <c r="P1058" s="8"/>
     </row>
     <row r="1059" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1059" s="50"/>
-      <c r="E1059" s="50"/>
+      <c r="A1059" s="62"/>
+      <c r="E1059" s="62"/>
       <c r="N1059" s="8"/>
       <c r="P1059" s="8"/>
     </row>
     <row r="1060" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1060" s="50"/>
-      <c r="E1060" s="50"/>
+      <c r="A1060" s="62"/>
+      <c r="E1060" s="62"/>
       <c r="N1060" s="8"/>
       <c r="P1060" s="8"/>
     </row>
     <row r="1061" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1061" s="50"/>
-      <c r="E1061" s="50"/>
+      <c r="A1061" s="62"/>
+      <c r="E1061" s="62"/>
       <c r="N1061" s="8"/>
       <c r="P1061" s="8"/>
     </row>
     <row r="1062" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1062" s="50"/>
-      <c r="E1062" s="50"/>
+      <c r="A1062" s="62"/>
+      <c r="E1062" s="62"/>
       <c r="N1062" s="8"/>
       <c r="P1062" s="8"/>
     </row>
     <row r="1063" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1063" s="50"/>
-      <c r="E1063" s="50"/>
+      <c r="A1063" s="62"/>
+      <c r="E1063" s="62"/>
       <c r="N1063" s="8"/>
       <c r="P1063" s="8"/>
     </row>
     <row r="1064" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1064" s="50"/>
-      <c r="E1064" s="50"/>
+      <c r="A1064" s="62"/>
+      <c r="E1064" s="62"/>
       <c r="N1064" s="8"/>
       <c r="P1064" s="8"/>
     </row>
     <row r="1065" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1065" s="50"/>
-      <c r="E1065" s="50"/>
+      <c r="A1065" s="62"/>
+      <c r="E1065" s="62"/>
       <c r="N1065" s="8"/>
       <c r="P1065" s="8"/>
     </row>
     <row r="1066" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1066" s="50"/>
-      <c r="E1066" s="50"/>
+      <c r="A1066" s="62"/>
+      <c r="E1066" s="62"/>
       <c r="N1066" s="8"/>
       <c r="P1066" s="8"/>
     </row>
     <row r="1067" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1067" s="50"/>
-      <c r="E1067" s="50"/>
+      <c r="A1067" s="62"/>
+      <c r="E1067" s="62"/>
       <c r="N1067" s="8"/>
       <c r="P1067" s="8"/>
     </row>
     <row r="1068" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1068" s="50"/>
-      <c r="E1068" s="50"/>
+      <c r="A1068" s="62"/>
+      <c r="E1068" s="62"/>
       <c r="N1068" s="8"/>
       <c r="P1068" s="8"/>
     </row>
     <row r="1069" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1069" s="50"/>
-      <c r="E1069" s="50"/>
+      <c r="A1069" s="62"/>
+      <c r="E1069" s="62"/>
       <c r="N1069" s="8"/>
       <c r="P1069" s="8"/>
     </row>
     <row r="1070" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1070" s="50"/>
-      <c r="E1070" s="50"/>
+      <c r="A1070" s="62"/>
+      <c r="E1070" s="62"/>
       <c r="N1070" s="8"/>
       <c r="P1070" s="8"/>
     </row>
     <row r="1071" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1071" s="50"/>
-      <c r="E1071" s="50"/>
+      <c r="A1071" s="62"/>
+      <c r="E1071" s="62"/>
       <c r="N1071" s="8"/>
       <c r="P1071" s="8"/>
     </row>
     <row r="1072" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1072" s="50"/>
-      <c r="E1072" s="50"/>
+      <c r="A1072" s="62"/>
+      <c r="E1072" s="62"/>
       <c r="N1072" s="8"/>
       <c r="P1072" s="8"/>
     </row>
     <row r="1073" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1073" s="50"/>
-      <c r="E1073" s="50"/>
+      <c r="A1073" s="62"/>
+      <c r="E1073" s="62"/>
       <c r="N1073" s="8"/>
       <c r="P1073" s="8"/>
     </row>
     <row r="1074" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1074" s="50"/>
-      <c r="E1074" s="50"/>
+      <c r="A1074" s="62"/>
+      <c r="E1074" s="62"/>
       <c r="N1074" s="8"/>
       <c r="P1074" s="8"/>
     </row>
     <row r="1075" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1075" s="50"/>
-      <c r="E1075" s="50"/>
+      <c r="A1075" s="62"/>
+      <c r="E1075" s="62"/>
       <c r="N1075" s="8"/>
       <c r="P1075" s="8"/>
     </row>
     <row r="1076" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1076" s="50"/>
-      <c r="E1076" s="50"/>
+      <c r="A1076" s="62"/>
+      <c r="E1076" s="62"/>
       <c r="N1076" s="8"/>
       <c r="P1076" s="8"/>
     </row>
     <row r="1077" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1077" s="50"/>
-      <c r="E1077" s="50"/>
+      <c r="A1077" s="62"/>
+      <c r="E1077" s="62"/>
       <c r="N1077" s="8"/>
       <c r="P1077" s="8"/>
     </row>
     <row r="1078" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1078" s="50"/>
-      <c r="E1078" s="50"/>
+      <c r="A1078" s="62"/>
+      <c r="E1078" s="62"/>
       <c r="N1078" s="8"/>
       <c r="P1078" s="8"/>
     </row>
     <row r="1079" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1079" s="50"/>
-      <c r="E1079" s="50"/>
+      <c r="A1079" s="62"/>
+      <c r="E1079" s="62"/>
       <c r="N1079" s="8"/>
       <c r="P1079" s="8"/>
     </row>
     <row r="1080" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1080" s="50"/>
-      <c r="E1080" s="50"/>
+      <c r="A1080" s="62"/>
+      <c r="E1080" s="62"/>
       <c r="N1080" s="8"/>
       <c r="P1080" s="8"/>
     </row>
+    <row r="1081" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1081" s="62"/>
+      <c r="E1081" s="62"/>
+      <c r="N1081" s="8"/>
+      <c r="P1081" s="8"/>
+    </row>
+    <row r="1082" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1082" s="62"/>
+      <c r="E1082" s="62"/>
+      <c r="N1082" s="8"/>
+      <c r="P1082" s="8"/>
+    </row>
+    <row r="1083" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1083" s="62"/>
+      <c r="E1083" s="62"/>
+      <c r="N1083" s="8"/>
+      <c r="P1083" s="8"/>
+    </row>
+    <row r="1084" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1084" s="62"/>
+      <c r="E1084" s="62"/>
+      <c r="N1084" s="8"/>
+      <c r="P1084" s="8"/>
+    </row>
+    <row r="1085" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1085" s="62"/>
+      <c r="E1085" s="62"/>
+      <c r="N1085" s="8"/>
+      <c r="P1085" s="8"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P544"/>
+  <autoFilter ref="A1:P549"/>
   <dataValidations count="5">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="N2 N4:N5 N10:N11 N13:N15 N18:N23 N25 N28:N29 N31:N34 N36 N39:N50 N52:N58 N60:N66 N68 N71 N73 N75:N76 N78:N83 N87 N91:N94 N96 N98:N99 N101:N110 N113:N114 N116:N117 N119:N121 N124:N125 N127 N129:N131 N133:N141 N143:N144 N148:N151 N153 N159 N161:N162 N170 N173:N174 N177:N180 N183:N185 N191:N192 N195 N208 N216 N229:N230 N232 N235:N236 N248 N253:N254 N256:N258 N263:N265 N273 N276 N279 N284:N285 N296 N315:N317 N326 N328 N330 N333:N335 N359 N369 N376 N380:N381 N394:N395 N415 N428 N434 N478 N499:N500" type="list">
       <formula1>"CENTRO,NAÇÕES,ESTADOS,MUNICIPIOS,N. ESPERANÇA,PIONEIROS,PONTAL NORTE,ARIRIBA,BARRA,VILA REAL,Barra Sul,São J. Tadeu"</formula1>

--- a/secretario.xlsx
+++ b/secretario.xlsx
@@ -11,7 +11,7 @@
     <sheet name="DADOS" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">DADOS!$A$1:$P$549</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">DADOS!$A$1:$P$557</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6635" uniqueCount="2271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6727" uniqueCount="2303">
   <si>
     <t xml:space="preserve">DATA</t>
   </si>
@@ -9003,27 +9003,6 @@
     <t xml:space="preserve">Rua Israel</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Rua Israel</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, Balneário Camboriú, SC, Brasil</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">TPS8I64 </t>
   </si>
   <si>
@@ -9055,6 +9034,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">, Balneário Camboriú, SC, Brasil</t>
     </r>
@@ -9097,6 +9077,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">, Balneário Camboriú, SC, Brasil</t>
     </r>
@@ -9145,6 +9126,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">, Balneário Camboriú, SC, Brasil</t>
     </r>
@@ -9175,6 +9157,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">, Balneário Camboriú, SC, Brasil</t>
     </r>
@@ -9316,9 +9299,163 @@
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">, Balneário Camboriú, SC, Brasil</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">BO-00549.2026.0006020 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://drive.google.com/file/d/1uVaV7uKqxxaA-cBaKpV8FS9bmhO_Qx0A/view?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Furto de camionete </t>
+  </si>
+  <si>
+    <t xml:space="preserve">I TOYOTA HILUX SWSRXA4FD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casas da Água </t>
+  </si>
+  <si>
+    <t xml:space="preserve">QIU5F44 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO-00012.2026.0001043 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://drive.google.com/file/d/1g4zY5X6cmdg5WTQIotWpQipfq7df7prk/view?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Furto de 2 ar condicionado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOCOP-02317.2026.0002715 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://drive.google.com/file/d/1H9NKaa9q8pD_sjGWvY_leXKdidwmm-Vv/view?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Furto de 20 m de canos de cobre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R. José Francisco Vítor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casa Linhares </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">R. José Francisco Vítor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, Balneário Camboriú, SC, Brasil</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">BOCOP-02317.2026.0002721 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://drive.google.com/file/d/1yQxAqCr_JfIw0CVnxMFHRtDIx-vAcQSC/view?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOTOROLA MOTO G05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pizzaria Herois da Pizza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOCOP-02317.2026.0002725 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://drive.google.com/file/d/1rEwQSvbtKU-VQbh7yoJMSew4sSwJyVjw/view?usp=sharing</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">R. 2400</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, Balneário Camboriú, SC, Brasil</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">SXR1G40 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO-00549.2026.0006050 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://drive.google.com/file/d/1E-Rm0TwzTPj-UHQzKQvjMUPfr_SWk03a/view?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HONDA CBX 200 STRADA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rua Dom Francisco </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rua Dom Francisco</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, Balneário Camboriú, SC, Brasil</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">LZJ1G81 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO-00600.2026.0028537 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://drive.google.com/file/d/1yAgmsJmNJCf0FMLc6xguVd28Qom1qmZP/view?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC X1 1000 W </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Av. Central, Balneário Camboriú, SC, Brasil</t>
   </si>
 </sst>
 </file>
@@ -9441,8 +9578,8 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
     </font>
@@ -9721,6 +9858,14 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -9733,6 +9878,22 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -9741,31 +9902,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10055,7 +10192,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD1085"/>
+  <dimension ref="A1:XFD1090"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="1" style="1" width="12.63"/>
@@ -36234,3812 +36371,4166 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="539" s="51" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="539" s="48" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A539" s="50" t="n">
         <v>18</v>
       </c>
-      <c r="B539" s="51" t="s">
+      <c r="B539" s="48" t="s">
         <v>1471</v>
       </c>
-      <c r="C539" s="51" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D539" s="52" t="n">
+      <c r="C539" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D539" s="49" t="n">
         <v>0.117361111111111</v>
       </c>
-      <c r="E539" s="51" t="s">
+      <c r="E539" s="48" t="s">
         <v>71</v>
       </c>
-      <c r="F539" s="51" t="s">
+      <c r="F539" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="G539" s="53" t="s">
+      <c r="G539" s="4" t="s">
         <v>2216</v>
       </c>
-      <c r="H539" s="51" t="s">
+      <c r="H539" s="48" t="s">
         <v>2217</v>
       </c>
-      <c r="I539" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="J539" s="51" t="s">
+      <c r="I539" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="J539" s="48" t="s">
         <v>329</v>
       </c>
-      <c r="K539" s="51" t="s">
+      <c r="K539" s="48" t="s">
         <v>330</v>
       </c>
-      <c r="L539" s="53" t="s">
+      <c r="L539" s="4" t="s">
         <v>2218</v>
       </c>
-      <c r="M539" s="53" t="s">
+      <c r="M539" s="4" t="s">
         <v>1351</v>
       </c>
-      <c r="N539" s="51" t="s">
+      <c r="N539" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="O539" s="53" t="s">
+      <c r="O539" s="4" t="s">
         <v>2219</v>
       </c>
-      <c r="P539" s="53" t="s">
+      <c r="P539" s="4" t="s">
+        <v>1353</v>
+      </c>
+      <c r="R539" s="4" t="s">
         <v>2220</v>
       </c>
-      <c r="R539" s="53" t="s">
-        <v>2221</v>
-      </c>
-      <c r="XFD539" s="54"/>
-    </row>
-    <row r="540" s="51" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="XFD539" s="51"/>
+    </row>
+    <row r="540" s="48" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A540" s="50" t="n">
         <v>18</v>
       </c>
-      <c r="B540" s="51" t="s">
+      <c r="B540" s="48" t="s">
         <v>1471</v>
       </c>
-      <c r="C540" s="51" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D540" s="52" t="n">
+      <c r="C540" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D540" s="49" t="n">
         <v>0.125</v>
       </c>
-      <c r="E540" s="51" t="s">
+      <c r="E540" s="48" t="s">
         <v>71</v>
       </c>
-      <c r="F540" s="51" t="s">
+      <c r="F540" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="G540" s="53" t="s">
+      <c r="G540" s="4" t="s">
+        <v>2221</v>
+      </c>
+      <c r="H540" s="48" t="s">
         <v>2222</v>
       </c>
-      <c r="H540" s="51" t="s">
+      <c r="I540" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="J540" s="48" t="s">
+        <v>722</v>
+      </c>
+      <c r="K540" s="48" t="s">
         <v>2223</v>
       </c>
-      <c r="I540" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="J540" s="51" t="s">
-        <v>722</v>
-      </c>
-      <c r="K540" s="51" t="s">
+      <c r="L540" s="4"/>
+      <c r="M540" s="4" t="s">
+        <v>782</v>
+      </c>
+      <c r="N540" s="48" t="s">
+        <v>226</v>
+      </c>
+      <c r="O540" s="4" t="s">
         <v>2224</v>
       </c>
-      <c r="L540" s="53"/>
-      <c r="M540" s="53" t="s">
-        <v>782</v>
-      </c>
-      <c r="N540" s="51" t="s">
-        <v>226</v>
-      </c>
-      <c r="O540" s="53" t="s">
+      <c r="P540" s="4" t="s">
         <v>2225</v>
       </c>
-      <c r="P540" s="53" t="s">
-        <v>2226</v>
-      </c>
-      <c r="R540" s="53"/>
-      <c r="XFD540" s="55"/>
-    </row>
-    <row r="541" s="51" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="R540" s="4"/>
+      <c r="XFD540" s="1"/>
+    </row>
+    <row r="541" s="48" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A541" s="50" t="n">
         <v>18</v>
       </c>
-      <c r="B541" s="51" t="s">
+      <c r="B541" s="48" t="s">
         <v>1471</v>
       </c>
-      <c r="C541" s="51" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D541" s="56" t="n">
+      <c r="C541" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D541" s="49" t="n">
         <v>0.138888888888889</v>
       </c>
       <c r="E541" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="F541" s="51" t="s">
+      <c r="F541" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="G541" s="57" t="s">
+      <c r="G541" s="4" t="s">
+        <v>2226</v>
+      </c>
+      <c r="H541" s="4" t="s">
         <v>2227</v>
       </c>
-      <c r="H541" s="57" t="s">
-        <v>2228</v>
-      </c>
-      <c r="I541" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="J541" s="51" t="s">
+      <c r="I541" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="J541" s="48" t="s">
         <v>501</v>
       </c>
-      <c r="K541" s="57" t="s">
+      <c r="K541" s="4" t="s">
         <v>2104</v>
       </c>
-      <c r="L541" s="57"/>
-      <c r="M541" s="51" t="s">
+      <c r="L541" s="4"/>
+      <c r="M541" s="48" t="s">
         <v>503</v>
       </c>
-      <c r="N541" s="58" t="s">
+      <c r="N541" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="O541" s="57" t="s">
+      <c r="O541" s="4" t="s">
         <v>504</v>
       </c>
-      <c r="P541" s="58" t="s">
+      <c r="P541" s="8" t="s">
         <v>505</v>
       </c>
-      <c r="XFD541" s="59"/>
-    </row>
-    <row r="542" s="51" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="XFD541" s="51"/>
+    </row>
+    <row r="542" s="48" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A542" s="50" t="n">
         <v>18</v>
       </c>
-      <c r="B542" s="51" t="s">
+      <c r="B542" s="48" t="s">
         <v>1471</v>
       </c>
-      <c r="C542" s="51" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D542" s="52" t="n">
+      <c r="C542" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D542" s="49" t="n">
         <v>0.166666666666667</v>
       </c>
       <c r="E542" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="F542" s="51" t="s">
+      <c r="F542" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="G542" s="53" t="s">
+      <c r="G542" s="4" t="s">
+        <v>2228</v>
+      </c>
+      <c r="H542" s="4" t="s">
         <v>2229</v>
       </c>
-      <c r="H542" s="57" t="s">
+      <c r="I542" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="J542" s="48" t="s">
+        <v>1092</v>
+      </c>
+      <c r="K542" s="4" t="s">
         <v>2230</v>
       </c>
-      <c r="I542" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="J542" s="51" t="s">
-        <v>1092</v>
-      </c>
-      <c r="K542" s="57" t="s">
+      <c r="L542" s="4"/>
+      <c r="M542" s="4" t="s">
         <v>2231</v>
       </c>
-      <c r="L542" s="57"/>
-      <c r="M542" s="53" t="s">
+      <c r="N542" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="O542" s="4" t="s">
         <v>2232</v>
       </c>
-      <c r="N542" s="58" t="s">
-        <v>195</v>
-      </c>
-      <c r="O542" s="53" t="s">
+      <c r="P542" s="4" t="s">
         <v>2233</v>
       </c>
-      <c r="P542" s="53" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="543" s="51" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="543" s="48" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A543" s="50" t="n">
         <v>18</v>
       </c>
-      <c r="B543" s="51" t="s">
+      <c r="B543" s="48" t="s">
         <v>1471</v>
       </c>
-      <c r="C543" s="51" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D543" s="56" t="n">
+      <c r="C543" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D543" s="49" t="n">
         <v>0.305555555555556</v>
       </c>
       <c r="E543" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="F543" s="51" t="s">
+      <c r="F543" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="G543" s="57" t="s">
+      <c r="G543" s="4" t="s">
+        <v>2234</v>
+      </c>
+      <c r="H543" s="4" t="s">
         <v>2235</v>
       </c>
-      <c r="H543" s="57" t="s">
-        <v>2236</v>
-      </c>
-      <c r="I543" s="51" t="s">
+      <c r="I543" s="48" t="s">
         <v>306</v>
       </c>
-      <c r="J543" s="51" t="s">
+      <c r="J543" s="48" t="s">
         <v>468</v>
       </c>
-      <c r="K543" s="57" t="s">
+      <c r="K543" s="4" t="s">
         <v>2148</v>
       </c>
-      <c r="L543" s="57"/>
-      <c r="M543" s="51" t="s">
+      <c r="L543" s="4"/>
+      <c r="M543" s="48" t="s">
         <v>503</v>
       </c>
-      <c r="N543" s="58" t="s">
+      <c r="N543" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="O543" s="57" t="s">
+      <c r="O543" s="4" t="s">
         <v>1025</v>
       </c>
-      <c r="P543" s="58" t="s">
+      <c r="P543" s="8" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="544" s="51" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="544" s="48" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A544" s="50" t="n">
         <v>18</v>
       </c>
-      <c r="B544" s="51" t="s">
+      <c r="B544" s="48" t="s">
         <v>1471</v>
       </c>
-      <c r="C544" s="51" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D544" s="56" t="n">
+      <c r="C544" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D544" s="49" t="n">
         <v>0.458333333333333</v>
       </c>
       <c r="E544" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="F544" s="51" t="s">
+      <c r="F544" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="G544" s="57" t="s">
+      <c r="G544" s="4" t="s">
+        <v>2236</v>
+      </c>
+      <c r="H544" s="4" t="s">
         <v>2237</v>
       </c>
-      <c r="H544" s="57" t="s">
-        <v>2238</v>
-      </c>
-      <c r="I544" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="J544" s="51" t="s">
+      <c r="I544" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="J544" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="K544" s="57" t="s">
+      <c r="K544" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="L544" s="57"/>
-      <c r="M544" s="51" t="s">
+      <c r="L544" s="4"/>
+      <c r="M544" s="48" t="s">
         <v>206</v>
       </c>
-      <c r="N544" s="58" t="s">
+      <c r="N544" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="O544" s="51" t="s">
+      <c r="O544" s="48" t="s">
         <v>206</v>
       </c>
-      <c r="P544" s="60" t="s">
+      <c r="P544" s="13" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="545" s="51" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="545" s="48" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A545" s="50" t="n">
         <v>18</v>
       </c>
-      <c r="B545" s="51" t="s">
+      <c r="B545" s="48" t="s">
         <v>1471</v>
       </c>
-      <c r="C545" s="51" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D545" s="52" t="n">
+      <c r="C545" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D545" s="49" t="n">
         <v>0.541666666666667</v>
       </c>
       <c r="E545" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="F545" s="51" t="s">
+      <c r="F545" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="G545" s="53" t="s">
+      <c r="G545" s="4" t="s">
+        <v>2238</v>
+      </c>
+      <c r="H545" s="4" t="s">
         <v>2239</v>
       </c>
-      <c r="H545" s="57" t="s">
+      <c r="I545" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="J545" s="48" t="s">
+        <v>836</v>
+      </c>
+      <c r="K545" s="4" t="s">
         <v>2240</v>
       </c>
-      <c r="I545" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="J545" s="51" t="s">
-        <v>836</v>
-      </c>
-      <c r="K545" s="57" t="s">
+      <c r="L545" s="4" t="s">
         <v>2241</v>
       </c>
-      <c r="L545" s="53" t="s">
+      <c r="M545" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="N545" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="O545" s="4" t="s">
         <v>2242</v>
       </c>
-      <c r="M545" s="53" t="s">
-        <v>302</v>
-      </c>
-      <c r="N545" s="58" t="s">
-        <v>131</v>
-      </c>
-      <c r="O545" s="53" t="s">
+      <c r="P545" s="4" t="s">
         <v>2243</v>
       </c>
-      <c r="P545" s="53" t="s">
+      <c r="R545" s="4" t="s">
         <v>2244</v>
       </c>
-      <c r="R545" s="53" t="s">
-        <v>2245</v>
-      </c>
-    </row>
-    <row r="546" s="51" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="546" s="48" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A546" s="50" t="n">
         <v>18</v>
       </c>
-      <c r="B546" s="51" t="s">
+      <c r="B546" s="48" t="s">
         <v>1471</v>
       </c>
-      <c r="C546" s="51" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D546" s="52" t="n">
+      <c r="C546" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D546" s="49" t="n">
         <v>0.625</v>
       </c>
       <c r="E546" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="F546" s="51" t="s">
+      <c r="F546" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="G546" s="53" t="s">
+      <c r="G546" s="4" t="s">
+        <v>2245</v>
+      </c>
+      <c r="H546" s="4" t="s">
         <v>2246</v>
       </c>
-      <c r="H546" s="57" t="s">
+      <c r="I546" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="J546" s="48" t="s">
+        <v>39</v>
+      </c>
+      <c r="K546" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="L546" s="4"/>
+      <c r="M546" s="48" t="s">
+        <v>88</v>
+      </c>
+      <c r="N546" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="O546" s="48" t="s">
+        <v>88</v>
+      </c>
+      <c r="P546" s="48" t="s">
         <v>2247</v>
       </c>
-      <c r="I546" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="J546" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="K546" s="57" t="s">
-        <v>179</v>
-      </c>
-      <c r="L546" s="57"/>
-      <c r="M546" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="N546" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="O546" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="P546" s="51" t="s">
-        <v>2248</v>
-      </c>
-    </row>
-    <row r="547" s="51" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="547" s="48" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A547" s="50" t="n">
         <v>18</v>
       </c>
-      <c r="B547" s="51" t="s">
+      <c r="B547" s="48" t="s">
         <v>1471</v>
       </c>
-      <c r="C547" s="51" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D547" s="56" t="n">
+      <c r="C547" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D547" s="49" t="n">
         <v>0.760416666666667</v>
       </c>
       <c r="E547" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="F547" s="51" t="s">
+      <c r="F547" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="G547" s="57" t="s">
+      <c r="G547" s="4" t="s">
+        <v>2248</v>
+      </c>
+      <c r="H547" s="4" t="s">
         <v>2249</v>
       </c>
-      <c r="H547" s="57" t="s">
+      <c r="I547" s="48" t="s">
+        <v>414</v>
+      </c>
+      <c r="J547" s="48" t="s">
         <v>2250</v>
       </c>
-      <c r="I547" s="51" t="s">
-        <v>414</v>
-      </c>
-      <c r="J547" s="51" t="s">
+      <c r="K547" s="4" t="s">
         <v>2251</v>
       </c>
-      <c r="K547" s="57" t="s">
+      <c r="L547" s="4"/>
+      <c r="M547" s="4" t="s">
         <v>2252</v>
       </c>
-      <c r="L547" s="57"/>
-      <c r="M547" s="57" t="s">
+      <c r="N547" s="8" t="s">
         <v>2253</v>
       </c>
-      <c r="N547" s="58" t="s">
+      <c r="O547" s="4" t="s">
         <v>2254</v>
       </c>
-      <c r="O547" s="57" t="s">
+      <c r="P547" s="4" t="s">
         <v>2255</v>
       </c>
-      <c r="P547" s="57" t="s">
-        <v>2256</v>
-      </c>
-    </row>
-    <row r="548" s="51" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="548" s="48" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A548" s="50" t="n">
         <v>18</v>
       </c>
-      <c r="B548" s="51" t="s">
+      <c r="B548" s="48" t="s">
         <v>1471</v>
       </c>
-      <c r="C548" s="51" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D548" s="56" t="n">
+      <c r="C548" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D548" s="49" t="n">
         <v>0.822222222222222</v>
       </c>
-      <c r="E548" s="51" t="s">
+      <c r="E548" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="F548" s="51" t="s">
+      <c r="F548" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="G548" s="57" t="s">
+      <c r="G548" s="4" t="s">
+        <v>2256</v>
+      </c>
+      <c r="H548" s="48" t="s">
         <v>2257</v>
       </c>
-      <c r="H548" s="51" t="s">
+      <c r="I548" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="J548" s="48" t="s">
+        <v>39</v>
+      </c>
+      <c r="K548" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="M548" s="48" t="s">
         <v>2258</v>
       </c>
-      <c r="I548" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="J548" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="K548" s="51" t="s">
-        <v>179</v>
-      </c>
-      <c r="M548" s="51" t="s">
+      <c r="N548" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="O548" s="48" t="s">
         <v>2259</v>
       </c>
-      <c r="N548" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="O548" s="51" t="s">
+      <c r="P548" s="48" t="s">
         <v>2260</v>
       </c>
-      <c r="P548" s="51" t="s">
-        <v>2261</v>
-      </c>
-    </row>
-    <row r="549" s="51" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="549" s="48" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A549" s="50" t="n">
         <v>18</v>
       </c>
-      <c r="B549" s="51" t="s">
+      <c r="B549" s="48" t="s">
         <v>1471</v>
       </c>
-      <c r="C549" s="51" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D549" s="56" t="n">
+      <c r="C549" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D549" s="49" t="n">
         <v>0.875</v>
       </c>
-      <c r="E549" s="51" t="s">
+      <c r="E549" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="F549" s="51" t="s">
+      <c r="F549" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="G549" s="57" t="s">
+      <c r="G549" s="4" t="s">
+        <v>2261</v>
+      </c>
+      <c r="H549" s="48" t="s">
         <v>2262</v>
       </c>
-      <c r="H549" s="51" t="s">
+      <c r="I549" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="J549" s="48" t="s">
+        <v>329</v>
+      </c>
+      <c r="K549" s="48" t="s">
+        <v>330</v>
+      </c>
+      <c r="L549" s="4" t="s">
         <v>2263</v>
       </c>
-      <c r="I549" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="J549" s="51" t="s">
-        <v>329</v>
-      </c>
-      <c r="K549" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="L549" s="57" t="s">
+      <c r="M549" s="48" t="s">
+        <v>332</v>
+      </c>
+      <c r="N549" s="48" t="s">
+        <v>68</v>
+      </c>
+      <c r="O549" s="48" t="s">
+        <v>332</v>
+      </c>
+      <c r="P549" s="48" t="s">
         <v>2264</v>
       </c>
-      <c r="M549" s="51" t="s">
-        <v>332</v>
-      </c>
-      <c r="N549" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="O549" s="51" t="s">
-        <v>332</v>
-      </c>
-      <c r="P549" s="51" t="s">
+      <c r="R549" s="4" t="s">
         <v>2265</v>
       </c>
-      <c r="R549" s="57" t="s">
-        <v>2266</v>
-      </c>
-    </row>
-    <row r="550" s="55" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="550" customFormat="false" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A550" s="50" t="n">
         <v>18</v>
       </c>
-      <c r="B550" s="51" t="s">
+      <c r="B550" s="48" t="s">
         <v>1471</v>
       </c>
-      <c r="C550" s="51" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D550" s="52" t="n">
+      <c r="C550" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D550" s="49" t="n">
         <v>0.916666666666667</v>
       </c>
-      <c r="E550" s="55" t="s">
+      <c r="E550" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F550" s="55" t="s">
+      <c r="F550" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G550" s="53" t="s">
+      <c r="G550" s="4" t="s">
+        <v>2266</v>
+      </c>
+      <c r="H550" s="1" t="s">
         <v>2267</v>
       </c>
-      <c r="H550" s="55" t="s">
+      <c r="I550" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J550" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K550" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L550" s="4" t="s">
         <v>2268</v>
       </c>
-      <c r="I550" s="55" t="s">
-        <v>24</v>
-      </c>
-      <c r="J550" s="55" t="s">
+      <c r="M550" s="4" t="s">
+        <v>1384</v>
+      </c>
+      <c r="N550" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="O550" s="4" t="s">
+        <v>1385</v>
+      </c>
+      <c r="P550" s="4" t="s">
+        <v>2269</v>
+      </c>
+      <c r="XFD550" s="48"/>
+    </row>
+    <row r="551" s="53" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A551" s="52" t="n">
+        <v>19</v>
+      </c>
+      <c r="B551" s="53" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C551" s="53" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D551" s="54" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="E551" s="52" t="s">
+        <v>71</v>
+      </c>
+      <c r="F551" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="G551" s="55" t="s">
+        <v>2270</v>
+      </c>
+      <c r="H551" s="56" t="s">
+        <v>2271</v>
+      </c>
+      <c r="I551" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="J551" s="57" t="s">
+        <v>139</v>
+      </c>
+      <c r="K551" s="56" t="s">
+        <v>2272</v>
+      </c>
+      <c r="L551" s="55" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M551" s="53" t="s">
+        <v>206</v>
+      </c>
+      <c r="N551" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="O551" s="55" t="s">
+        <v>2274</v>
+      </c>
+      <c r="P551" s="59" t="s">
+        <v>208</v>
+      </c>
+      <c r="R551" s="55" t="s">
+        <v>2275</v>
+      </c>
+      <c r="XFD551" s="60"/>
+    </row>
+    <row r="552" s="53" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A552" s="52" t="n">
+        <v>19</v>
+      </c>
+      <c r="B552" s="53" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C552" s="53" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D552" s="54" t="n">
+        <v>0.179861111111111</v>
+      </c>
+      <c r="E552" s="52" t="s">
+        <v>71</v>
+      </c>
+      <c r="F552" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="G552" s="55" t="s">
+        <v>2276</v>
+      </c>
+      <c r="H552" s="56" t="s">
+        <v>2277</v>
+      </c>
+      <c r="I552" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="J552" s="57" t="s">
+        <v>1318</v>
+      </c>
+      <c r="K552" s="56" t="s">
+        <v>2278</v>
+      </c>
+      <c r="L552" s="55"/>
+      <c r="M552" s="53" t="s">
+        <v>664</v>
+      </c>
+      <c r="N552" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="O552" s="55" t="s">
+        <v>665</v>
+      </c>
+      <c r="P552" s="59" t="s">
+        <v>666</v>
+      </c>
+      <c r="R552" s="55"/>
+      <c r="XFD552" s="61"/>
+    </row>
+    <row r="553" s="53" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A553" s="52" t="n">
+        <v>19</v>
+      </c>
+      <c r="B553" s="53" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C553" s="53" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D553" s="54" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E553" s="52" t="s">
+        <v>126</v>
+      </c>
+      <c r="F553" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="G553" s="55" t="s">
+        <v>2279</v>
+      </c>
+      <c r="H553" s="56" t="s">
+        <v>2280</v>
+      </c>
+      <c r="I553" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="J553" s="57" t="s">
+        <v>1982</v>
+      </c>
+      <c r="K553" s="56" t="s">
+        <v>2281</v>
+      </c>
+      <c r="L553" s="55"/>
+      <c r="M553" s="55" t="s">
+        <v>2282</v>
+      </c>
+      <c r="N553" s="58" t="s">
+        <v>195</v>
+      </c>
+      <c r="O553" s="55" t="s">
+        <v>2283</v>
+      </c>
+      <c r="P553" s="55" t="s">
+        <v>2284</v>
+      </c>
+      <c r="R553" s="55"/>
+      <c r="XFD553" s="61"/>
+    </row>
+    <row r="554" s="53" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A554" s="52" t="n">
+        <v>19</v>
+      </c>
+      <c r="B554" s="53" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C554" s="53" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D554" s="54" t="n">
+        <v>0.688888888888889</v>
+      </c>
+      <c r="E554" s="52" t="s">
+        <v>21</v>
+      </c>
+      <c r="F554" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="G554" s="55" t="s">
+        <v>2285</v>
+      </c>
+      <c r="H554" s="56" t="s">
+        <v>2286</v>
+      </c>
+      <c r="I554" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="J554" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="K550" s="55" t="s">
+      <c r="K554" s="56" t="s">
         <v>58</v>
       </c>
-      <c r="L550" s="53" t="s">
-        <v>2269</v>
-      </c>
-      <c r="M550" s="53" t="s">
-        <v>1384</v>
-      </c>
-      <c r="N550" s="55" t="s">
-        <v>68</v>
-      </c>
-      <c r="O550" s="53" t="s">
-        <v>1385</v>
-      </c>
-      <c r="P550" s="53" t="s">
-        <v>2270</v>
-      </c>
-      <c r="XFD550" s="51"/>
-    </row>
-    <row r="551" s="61" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L551" s="1"/>
-    </row>
-    <row r="552" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A552" s="62"/>
-      <c r="E552" s="62"/>
-      <c r="N552" s="8"/>
-      <c r="P552" s="8"/>
-    </row>
-    <row r="553" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A553" s="62"/>
-      <c r="E553" s="62"/>
-      <c r="N553" s="8"/>
-      <c r="P553" s="8"/>
-    </row>
-    <row r="554" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A554" s="62"/>
-      <c r="E554" s="62"/>
-      <c r="N554" s="8"/>
-      <c r="P554" s="8"/>
-    </row>
-    <row r="555" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A555" s="62"/>
-      <c r="E555" s="62"/>
-      <c r="N555" s="8"/>
-      <c r="P555" s="8"/>
-    </row>
-    <row r="556" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A556" s="62"/>
-      <c r="E556" s="62"/>
-      <c r="N556" s="8"/>
-      <c r="P556" s="8"/>
-    </row>
-    <row r="557" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A557" s="62"/>
-      <c r="E557" s="62"/>
-      <c r="N557" s="8"/>
-      <c r="P557" s="8"/>
+      <c r="L554" s="55" t="s">
+        <v>2287</v>
+      </c>
+      <c r="M554" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N554" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="O554" s="55" t="s">
+        <v>2288</v>
+      </c>
+      <c r="P554" s="59" t="s">
+        <v>94</v>
+      </c>
+      <c r="R554" s="55"/>
+      <c r="XFD554" s="61"/>
+    </row>
+    <row r="555" s="53" customFormat="true" ht="22.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A555" s="52" t="n">
+        <v>19</v>
+      </c>
+      <c r="B555" s="53" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C555" s="53" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D555" s="54" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="E555" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="F555" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="G555" s="55" t="s">
+        <v>2289</v>
+      </c>
+      <c r="H555" s="53" t="s">
+        <v>2290</v>
+      </c>
+      <c r="I555" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="J555" s="53" t="s">
+        <v>329</v>
+      </c>
+      <c r="K555" s="53" t="s">
+        <v>330</v>
+      </c>
+      <c r="L555" s="55" t="s">
+        <v>2218</v>
+      </c>
+      <c r="M555" s="55" t="s">
+        <v>922</v>
+      </c>
+      <c r="N555" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="O555" s="55" t="s">
+        <v>922</v>
+      </c>
+      <c r="P555" s="55" t="s">
+        <v>2291</v>
+      </c>
+      <c r="R555" s="55" t="s">
+        <v>2292</v>
+      </c>
+    </row>
+    <row r="556" s="53" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A556" s="52" t="n">
+        <v>19</v>
+      </c>
+      <c r="B556" s="53" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C556" s="53" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D556" s="54" t="n">
+        <v>0.892361111111111</v>
+      </c>
+      <c r="E556" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="F556" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="G556" s="55" t="s">
+        <v>2293</v>
+      </c>
+      <c r="H556" s="53" t="s">
+        <v>2294</v>
+      </c>
+      <c r="I556" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="J556" s="53" t="s">
+        <v>329</v>
+      </c>
+      <c r="K556" s="53" t="s">
+        <v>330</v>
+      </c>
+      <c r="L556" s="55" t="s">
+        <v>2295</v>
+      </c>
+      <c r="M556" s="55" t="s">
+        <v>864</v>
+      </c>
+      <c r="N556" s="53" t="s">
+        <v>226</v>
+      </c>
+      <c r="O556" s="62" t="s">
+        <v>2296</v>
+      </c>
+      <c r="P556" s="55" t="s">
+        <v>2297</v>
+      </c>
+      <c r="R556" s="55" t="s">
+        <v>2298</v>
+      </c>
+    </row>
+    <row r="557" s="61" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A557" s="52" t="n">
+        <v>19</v>
+      </c>
+      <c r="B557" s="53" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C557" s="53" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D557" s="54" t="n">
+        <v>0.977083333333333</v>
+      </c>
+      <c r="E557" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="F557" s="61" t="s">
+        <v>102</v>
+      </c>
+      <c r="G557" s="55" t="s">
+        <v>2299</v>
+      </c>
+      <c r="H557" s="61" t="s">
+        <v>2300</v>
+      </c>
+      <c r="I557" s="61" t="s">
+        <v>24</v>
+      </c>
+      <c r="J557" s="61" t="s">
+        <v>39</v>
+      </c>
+      <c r="K557" s="61" t="s">
+        <v>179</v>
+      </c>
+      <c r="L557" s="55" t="s">
+        <v>2301</v>
+      </c>
+      <c r="M557" s="61" t="s">
+        <v>191</v>
+      </c>
+      <c r="N557" s="61" t="s">
+        <v>28</v>
+      </c>
+      <c r="O557" s="61" t="s">
+        <v>893</v>
+      </c>
+      <c r="P557" s="61" t="s">
+        <v>2302</v>
+      </c>
+      <c r="XFD557" s="53"/>
     </row>
     <row r="558" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A558" s="62"/>
-      <c r="E558" s="62"/>
+      <c r="A558" s="50"/>
+      <c r="E558" s="50"/>
       <c r="N558" s="8"/>
       <c r="P558" s="8"/>
     </row>
     <row r="559" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A559" s="62"/>
-      <c r="E559" s="62"/>
+      <c r="A559" s="50"/>
+      <c r="E559" s="50"/>
       <c r="N559" s="8"/>
       <c r="P559" s="8"/>
     </row>
     <row r="560" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A560" s="62"/>
-      <c r="E560" s="62"/>
+      <c r="A560" s="50"/>
+      <c r="E560" s="50"/>
       <c r="N560" s="8"/>
       <c r="P560" s="8"/>
     </row>
     <row r="561" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A561" s="62"/>
-      <c r="E561" s="62"/>
+      <c r="A561" s="50"/>
+      <c r="E561" s="50"/>
       <c r="N561" s="8"/>
       <c r="P561" s="8"/>
     </row>
     <row r="562" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A562" s="62"/>
-      <c r="E562" s="62"/>
+      <c r="A562" s="50"/>
+      <c r="E562" s="50"/>
       <c r="N562" s="8"/>
       <c r="P562" s="8"/>
     </row>
     <row r="563" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A563" s="62"/>
-      <c r="E563" s="62"/>
+      <c r="A563" s="50"/>
+      <c r="E563" s="50"/>
       <c r="N563" s="8"/>
       <c r="P563" s="8"/>
     </row>
     <row r="564" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A564" s="62"/>
-      <c r="E564" s="62"/>
+      <c r="A564" s="50"/>
+      <c r="E564" s="50"/>
       <c r="N564" s="8"/>
       <c r="P564" s="8"/>
     </row>
     <row r="565" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A565" s="62"/>
-      <c r="E565" s="62"/>
+      <c r="A565" s="50"/>
+      <c r="E565" s="50"/>
       <c r="N565" s="8"/>
       <c r="P565" s="8"/>
     </row>
     <row r="566" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A566" s="62"/>
-      <c r="E566" s="62"/>
+      <c r="A566" s="50"/>
+      <c r="E566" s="50"/>
       <c r="N566" s="8"/>
       <c r="P566" s="8"/>
     </row>
     <row r="567" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A567" s="62"/>
-      <c r="E567" s="62"/>
+      <c r="A567" s="50"/>
+      <c r="E567" s="50"/>
       <c r="N567" s="8"/>
       <c r="P567" s="8"/>
     </row>
     <row r="568" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A568" s="62"/>
-      <c r="E568" s="62"/>
+      <c r="A568" s="50"/>
+      <c r="E568" s="50"/>
       <c r="N568" s="8"/>
       <c r="P568" s="8"/>
     </row>
     <row r="569" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A569" s="62"/>
-      <c r="E569" s="62"/>
+      <c r="A569" s="50"/>
+      <c r="E569" s="50"/>
       <c r="N569" s="8"/>
       <c r="P569" s="8"/>
     </row>
     <row r="570" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A570" s="62"/>
-      <c r="E570" s="62"/>
+      <c r="A570" s="50"/>
+      <c r="E570" s="50"/>
       <c r="N570" s="8"/>
       <c r="P570" s="8"/>
     </row>
     <row r="571" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A571" s="62"/>
-      <c r="E571" s="62"/>
+      <c r="A571" s="50"/>
+      <c r="E571" s="50"/>
       <c r="N571" s="8"/>
       <c r="P571" s="8"/>
     </row>
     <row r="572" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A572" s="62"/>
-      <c r="E572" s="62"/>
+      <c r="A572" s="50"/>
+      <c r="E572" s="50"/>
       <c r="N572" s="8"/>
       <c r="P572" s="8"/>
     </row>
     <row r="573" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A573" s="62"/>
-      <c r="E573" s="62"/>
+      <c r="A573" s="50"/>
+      <c r="E573" s="50"/>
       <c r="N573" s="8"/>
       <c r="P573" s="8"/>
     </row>
     <row r="574" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A574" s="62"/>
-      <c r="E574" s="62"/>
+      <c r="A574" s="50"/>
+      <c r="E574" s="50"/>
       <c r="N574" s="8"/>
       <c r="P574" s="8"/>
     </row>
     <row r="575" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A575" s="62"/>
-      <c r="E575" s="62"/>
+      <c r="A575" s="50"/>
+      <c r="E575" s="50"/>
       <c r="N575" s="8"/>
       <c r="P575" s="8"/>
     </row>
     <row r="576" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A576" s="62"/>
-      <c r="E576" s="62"/>
+      <c r="A576" s="50"/>
+      <c r="E576" s="50"/>
       <c r="N576" s="8"/>
       <c r="P576" s="8"/>
     </row>
     <row r="577" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A577" s="62"/>
-      <c r="E577" s="62"/>
+      <c r="A577" s="50"/>
+      <c r="E577" s="50"/>
       <c r="N577" s="8"/>
       <c r="P577" s="8"/>
     </row>
     <row r="578" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A578" s="62"/>
-      <c r="E578" s="62"/>
+      <c r="A578" s="50"/>
+      <c r="E578" s="50"/>
       <c r="N578" s="8"/>
       <c r="P578" s="8"/>
     </row>
     <row r="579" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A579" s="62"/>
-      <c r="E579" s="62"/>
+      <c r="A579" s="50"/>
+      <c r="E579" s="50"/>
       <c r="N579" s="8"/>
       <c r="P579" s="8"/>
     </row>
     <row r="580" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A580" s="62"/>
-      <c r="E580" s="62"/>
+      <c r="A580" s="50"/>
+      <c r="E580" s="50"/>
       <c r="N580" s="8"/>
       <c r="P580" s="8"/>
     </row>
     <row r="581" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A581" s="62"/>
-      <c r="E581" s="62"/>
+      <c r="A581" s="50"/>
+      <c r="E581" s="50"/>
       <c r="N581" s="8"/>
       <c r="P581" s="8"/>
     </row>
     <row r="582" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A582" s="62"/>
-      <c r="E582" s="62"/>
+      <c r="A582" s="50"/>
+      <c r="E582" s="50"/>
       <c r="N582" s="8"/>
       <c r="P582" s="8"/>
     </row>
     <row r="583" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A583" s="62"/>
-      <c r="E583" s="62"/>
+      <c r="A583" s="50"/>
+      <c r="E583" s="50"/>
       <c r="N583" s="8"/>
       <c r="P583" s="8"/>
     </row>
     <row r="584" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A584" s="62"/>
-      <c r="E584" s="62"/>
+      <c r="A584" s="50"/>
+      <c r="E584" s="50"/>
       <c r="N584" s="8"/>
       <c r="P584" s="8"/>
     </row>
     <row r="585" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A585" s="62"/>
-      <c r="E585" s="62"/>
+      <c r="A585" s="50"/>
+      <c r="E585" s="50"/>
       <c r="N585" s="8"/>
       <c r="P585" s="8"/>
     </row>
     <row r="586" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A586" s="62"/>
-      <c r="E586" s="62"/>
+      <c r="A586" s="50"/>
+      <c r="E586" s="50"/>
       <c r="N586" s="8"/>
       <c r="P586" s="8"/>
     </row>
     <row r="587" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A587" s="62"/>
-      <c r="E587" s="62"/>
+      <c r="A587" s="50"/>
+      <c r="E587" s="50"/>
       <c r="N587" s="8"/>
       <c r="P587" s="8"/>
     </row>
     <row r="588" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A588" s="62"/>
-      <c r="E588" s="62"/>
+      <c r="A588" s="50"/>
+      <c r="E588" s="50"/>
       <c r="N588" s="8"/>
       <c r="P588" s="8"/>
     </row>
     <row r="589" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A589" s="62"/>
-      <c r="E589" s="62"/>
+      <c r="A589" s="50"/>
+      <c r="E589" s="50"/>
       <c r="N589" s="8"/>
       <c r="P589" s="8"/>
     </row>
     <row r="590" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A590" s="62"/>
-      <c r="E590" s="62"/>
+      <c r="A590" s="50"/>
+      <c r="E590" s="50"/>
       <c r="N590" s="8"/>
       <c r="P590" s="8"/>
     </row>
     <row r="591" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A591" s="62"/>
-      <c r="E591" s="62"/>
+      <c r="A591" s="50"/>
+      <c r="E591" s="50"/>
       <c r="N591" s="8"/>
       <c r="P591" s="8"/>
     </row>
     <row r="592" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A592" s="62"/>
-      <c r="E592" s="62"/>
+      <c r="A592" s="50"/>
+      <c r="E592" s="50"/>
       <c r="N592" s="8"/>
       <c r="P592" s="8"/>
     </row>
     <row r="593" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A593" s="62"/>
-      <c r="E593" s="62"/>
+      <c r="A593" s="50"/>
+      <c r="E593" s="50"/>
       <c r="N593" s="8"/>
       <c r="P593" s="8"/>
     </row>
     <row r="594" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A594" s="62"/>
-      <c r="E594" s="62"/>
+      <c r="A594" s="50"/>
+      <c r="E594" s="50"/>
       <c r="N594" s="8"/>
       <c r="P594" s="8"/>
     </row>
     <row r="595" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A595" s="62"/>
-      <c r="E595" s="62"/>
+      <c r="A595" s="50"/>
+      <c r="E595" s="50"/>
       <c r="N595" s="8"/>
       <c r="P595" s="8"/>
     </row>
     <row r="596" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A596" s="62"/>
-      <c r="E596" s="62"/>
+      <c r="A596" s="50"/>
+      <c r="E596" s="50"/>
       <c r="N596" s="8"/>
       <c r="P596" s="8"/>
     </row>
     <row r="597" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A597" s="62"/>
-      <c r="E597" s="62"/>
+      <c r="A597" s="50"/>
+      <c r="E597" s="50"/>
       <c r="N597" s="8"/>
       <c r="P597" s="8"/>
     </row>
     <row r="598" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A598" s="62"/>
-      <c r="E598" s="62"/>
+      <c r="A598" s="50"/>
+      <c r="E598" s="50"/>
       <c r="N598" s="8"/>
       <c r="P598" s="8"/>
     </row>
     <row r="599" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A599" s="62"/>
-      <c r="E599" s="62"/>
+      <c r="A599" s="50"/>
+      <c r="E599" s="50"/>
       <c r="N599" s="8"/>
       <c r="P599" s="8"/>
     </row>
     <row r="600" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A600" s="62"/>
-      <c r="E600" s="62"/>
+      <c r="A600" s="50"/>
+      <c r="E600" s="50"/>
       <c r="N600" s="8"/>
       <c r="P600" s="8"/>
     </row>
     <row r="601" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A601" s="62"/>
-      <c r="E601" s="62"/>
+      <c r="A601" s="50"/>
+      <c r="E601" s="50"/>
       <c r="N601" s="8"/>
       <c r="P601" s="8"/>
     </row>
     <row r="602" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A602" s="62"/>
-      <c r="E602" s="62"/>
+      <c r="A602" s="50"/>
+      <c r="E602" s="50"/>
       <c r="N602" s="8"/>
       <c r="P602" s="8"/>
     </row>
     <row r="603" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A603" s="62"/>
-      <c r="E603" s="62"/>
+      <c r="A603" s="50"/>
+      <c r="E603" s="50"/>
       <c r="N603" s="8"/>
       <c r="P603" s="8"/>
     </row>
     <row r="604" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A604" s="62"/>
-      <c r="E604" s="62"/>
+      <c r="A604" s="50"/>
+      <c r="E604" s="50"/>
       <c r="N604" s="8"/>
       <c r="P604" s="8"/>
     </row>
     <row r="605" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A605" s="62"/>
-      <c r="E605" s="62"/>
+      <c r="A605" s="50"/>
+      <c r="E605" s="50"/>
       <c r="N605" s="8"/>
       <c r="P605" s="8"/>
     </row>
     <row r="606" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A606" s="62"/>
-      <c r="E606" s="62"/>
+      <c r="A606" s="50"/>
+      <c r="E606" s="50"/>
       <c r="N606" s="8"/>
       <c r="P606" s="8"/>
     </row>
     <row r="607" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A607" s="62"/>
-      <c r="E607" s="62"/>
+      <c r="A607" s="50"/>
+      <c r="E607" s="50"/>
       <c r="N607" s="8"/>
       <c r="P607" s="8"/>
     </row>
     <row r="608" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A608" s="62"/>
-      <c r="E608" s="62"/>
+      <c r="A608" s="50"/>
+      <c r="E608" s="50"/>
       <c r="N608" s="8"/>
       <c r="P608" s="8"/>
     </row>
     <row r="609" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A609" s="62"/>
-      <c r="E609" s="62"/>
+      <c r="A609" s="50"/>
+      <c r="E609" s="50"/>
       <c r="N609" s="8"/>
       <c r="P609" s="8"/>
     </row>
     <row r="610" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A610" s="62"/>
-      <c r="E610" s="62"/>
+      <c r="A610" s="50"/>
+      <c r="E610" s="50"/>
       <c r="N610" s="8"/>
       <c r="P610" s="8"/>
     </row>
     <row r="611" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A611" s="62"/>
-      <c r="E611" s="62"/>
+      <c r="A611" s="50"/>
+      <c r="E611" s="50"/>
       <c r="N611" s="8"/>
       <c r="P611" s="8"/>
     </row>
     <row r="612" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A612" s="62"/>
-      <c r="E612" s="62"/>
+      <c r="A612" s="50"/>
+      <c r="E612" s="50"/>
       <c r="N612" s="8"/>
       <c r="P612" s="8"/>
     </row>
     <row r="613" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A613" s="62"/>
-      <c r="E613" s="62"/>
+      <c r="A613" s="50"/>
+      <c r="E613" s="50"/>
       <c r="N613" s="8"/>
       <c r="P613" s="8"/>
     </row>
     <row r="614" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A614" s="62"/>
-      <c r="E614" s="62"/>
+      <c r="A614" s="50"/>
+      <c r="E614" s="50"/>
       <c r="N614" s="8"/>
       <c r="P614" s="8"/>
     </row>
     <row r="615" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A615" s="62"/>
-      <c r="E615" s="62"/>
+      <c r="A615" s="50"/>
+      <c r="E615" s="50"/>
       <c r="N615" s="8"/>
       <c r="P615" s="8"/>
     </row>
     <row r="616" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A616" s="62"/>
-      <c r="E616" s="62"/>
+      <c r="A616" s="50"/>
+      <c r="E616" s="50"/>
       <c r="N616" s="8"/>
       <c r="P616" s="8"/>
     </row>
     <row r="617" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A617" s="62"/>
-      <c r="E617" s="62"/>
+      <c r="A617" s="50"/>
+      <c r="E617" s="50"/>
       <c r="N617" s="8"/>
       <c r="P617" s="8"/>
     </row>
     <row r="618" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A618" s="62"/>
-      <c r="E618" s="62"/>
+      <c r="A618" s="50"/>
+      <c r="E618" s="50"/>
       <c r="N618" s="8"/>
       <c r="P618" s="8"/>
     </row>
     <row r="619" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A619" s="62"/>
-      <c r="E619" s="62"/>
+      <c r="A619" s="50"/>
+      <c r="E619" s="50"/>
       <c r="N619" s="8"/>
       <c r="P619" s="8"/>
     </row>
     <row r="620" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A620" s="62"/>
-      <c r="E620" s="62"/>
+      <c r="A620" s="50"/>
+      <c r="E620" s="50"/>
       <c r="N620" s="8"/>
       <c r="P620" s="8"/>
     </row>
     <row r="621" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A621" s="62"/>
-      <c r="E621" s="62"/>
+      <c r="A621" s="50"/>
+      <c r="E621" s="50"/>
       <c r="N621" s="8"/>
       <c r="P621" s="8"/>
     </row>
     <row r="622" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A622" s="62"/>
-      <c r="E622" s="62"/>
+      <c r="A622" s="50"/>
+      <c r="E622" s="50"/>
       <c r="N622" s="8"/>
       <c r="P622" s="8"/>
     </row>
     <row r="623" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A623" s="62"/>
-      <c r="E623" s="62"/>
+      <c r="A623" s="50"/>
+      <c r="E623" s="50"/>
       <c r="N623" s="8"/>
       <c r="P623" s="8"/>
     </row>
     <row r="624" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A624" s="62"/>
-      <c r="E624" s="62"/>
+      <c r="A624" s="50"/>
+      <c r="E624" s="50"/>
       <c r="N624" s="8"/>
       <c r="P624" s="8"/>
     </row>
     <row r="625" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A625" s="62"/>
-      <c r="E625" s="62"/>
+      <c r="A625" s="50"/>
+      <c r="E625" s="50"/>
       <c r="N625" s="8"/>
       <c r="P625" s="8"/>
     </row>
     <row r="626" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A626" s="62"/>
-      <c r="E626" s="62"/>
+      <c r="A626" s="50"/>
+      <c r="E626" s="50"/>
       <c r="N626" s="8"/>
       <c r="P626" s="8"/>
     </row>
     <row r="627" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A627" s="62"/>
-      <c r="E627" s="62"/>
+      <c r="A627" s="50"/>
+      <c r="E627" s="50"/>
       <c r="N627" s="8"/>
       <c r="P627" s="8"/>
     </row>
     <row r="628" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A628" s="62"/>
-      <c r="E628" s="62"/>
+      <c r="A628" s="50"/>
+      <c r="E628" s="50"/>
       <c r="N628" s="8"/>
       <c r="P628" s="8"/>
     </row>
     <row r="629" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A629" s="62"/>
-      <c r="E629" s="62"/>
+      <c r="A629" s="50"/>
+      <c r="E629" s="50"/>
       <c r="N629" s="8"/>
       <c r="P629" s="8"/>
     </row>
     <row r="630" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A630" s="62"/>
-      <c r="E630" s="62"/>
+      <c r="A630" s="50"/>
+      <c r="E630" s="50"/>
       <c r="N630" s="8"/>
       <c r="P630" s="8"/>
     </row>
     <row r="631" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A631" s="62"/>
-      <c r="E631" s="62"/>
+      <c r="A631" s="50"/>
+      <c r="E631" s="50"/>
       <c r="N631" s="8"/>
       <c r="P631" s="8"/>
     </row>
     <row r="632" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A632" s="62"/>
-      <c r="E632" s="62"/>
+      <c r="A632" s="50"/>
+      <c r="E632" s="50"/>
       <c r="N632" s="8"/>
       <c r="P632" s="8"/>
     </row>
     <row r="633" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A633" s="62"/>
-      <c r="E633" s="62"/>
+      <c r="A633" s="50"/>
+      <c r="E633" s="50"/>
       <c r="N633" s="8"/>
       <c r="P633" s="8"/>
     </row>
     <row r="634" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A634" s="62"/>
-      <c r="E634" s="62"/>
+      <c r="A634" s="50"/>
+      <c r="E634" s="50"/>
       <c r="N634" s="8"/>
       <c r="P634" s="8"/>
     </row>
     <row r="635" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A635" s="62"/>
-      <c r="E635" s="62"/>
+      <c r="A635" s="50"/>
+      <c r="E635" s="50"/>
       <c r="N635" s="8"/>
       <c r="P635" s="8"/>
     </row>
     <row r="636" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A636" s="62"/>
-      <c r="E636" s="62"/>
+      <c r="A636" s="50"/>
+      <c r="E636" s="50"/>
       <c r="N636" s="8"/>
       <c r="P636" s="8"/>
     </row>
     <row r="637" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A637" s="62"/>
-      <c r="E637" s="62"/>
+      <c r="A637" s="50"/>
+      <c r="E637" s="50"/>
       <c r="N637" s="8"/>
       <c r="P637" s="8"/>
     </row>
     <row r="638" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A638" s="62"/>
-      <c r="E638" s="62"/>
+      <c r="A638" s="50"/>
+      <c r="E638" s="50"/>
       <c r="N638" s="8"/>
       <c r="P638" s="8"/>
     </row>
     <row r="639" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A639" s="62"/>
-      <c r="E639" s="62"/>
+      <c r="A639" s="50"/>
+      <c r="E639" s="50"/>
       <c r="N639" s="8"/>
       <c r="P639" s="8"/>
     </row>
     <row r="640" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A640" s="62"/>
-      <c r="E640" s="62"/>
+      <c r="A640" s="50"/>
+      <c r="E640" s="50"/>
       <c r="N640" s="8"/>
       <c r="P640" s="8"/>
     </row>
     <row r="641" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A641" s="62"/>
-      <c r="E641" s="62"/>
+      <c r="A641" s="50"/>
+      <c r="E641" s="50"/>
       <c r="N641" s="8"/>
       <c r="P641" s="8"/>
     </row>
     <row r="642" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A642" s="62"/>
-      <c r="E642" s="62"/>
+      <c r="A642" s="50"/>
+      <c r="E642" s="50"/>
       <c r="N642" s="8"/>
       <c r="P642" s="8"/>
     </row>
     <row r="643" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A643" s="62"/>
-      <c r="E643" s="62"/>
+      <c r="A643" s="50"/>
+      <c r="E643" s="50"/>
       <c r="N643" s="8"/>
       <c r="P643" s="8"/>
     </row>
     <row r="644" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A644" s="62"/>
-      <c r="E644" s="62"/>
+      <c r="A644" s="50"/>
+      <c r="E644" s="50"/>
       <c r="N644" s="8"/>
       <c r="P644" s="8"/>
     </row>
     <row r="645" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A645" s="62"/>
-      <c r="E645" s="62"/>
+      <c r="A645" s="50"/>
+      <c r="E645" s="50"/>
       <c r="N645" s="8"/>
       <c r="P645" s="8"/>
     </row>
     <row r="646" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A646" s="62"/>
-      <c r="E646" s="62"/>
+      <c r="A646" s="50"/>
+      <c r="E646" s="50"/>
       <c r="N646" s="8"/>
       <c r="P646" s="8"/>
     </row>
     <row r="647" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A647" s="62"/>
-      <c r="E647" s="62"/>
+      <c r="A647" s="50"/>
+      <c r="E647" s="50"/>
       <c r="N647" s="8"/>
       <c r="P647" s="8"/>
     </row>
     <row r="648" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A648" s="62"/>
-      <c r="E648" s="62"/>
+      <c r="A648" s="50"/>
+      <c r="E648" s="50"/>
       <c r="N648" s="8"/>
       <c r="P648" s="8"/>
     </row>
     <row r="649" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A649" s="62"/>
-      <c r="E649" s="62"/>
+      <c r="A649" s="50"/>
+      <c r="E649" s="50"/>
       <c r="N649" s="8"/>
       <c r="P649" s="8"/>
     </row>
     <row r="650" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A650" s="62"/>
-      <c r="E650" s="62"/>
+      <c r="A650" s="50"/>
+      <c r="E650" s="50"/>
       <c r="N650" s="8"/>
       <c r="P650" s="8"/>
     </row>
     <row r="651" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A651" s="62"/>
-      <c r="E651" s="62"/>
+      <c r="A651" s="50"/>
+      <c r="E651" s="50"/>
       <c r="N651" s="8"/>
       <c r="P651" s="8"/>
     </row>
     <row r="652" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A652" s="62"/>
-      <c r="E652" s="62"/>
+      <c r="A652" s="50"/>
+      <c r="E652" s="50"/>
       <c r="N652" s="8"/>
       <c r="P652" s="8"/>
     </row>
     <row r="653" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A653" s="62"/>
-      <c r="E653" s="62"/>
+      <c r="A653" s="50"/>
+      <c r="E653" s="50"/>
       <c r="N653" s="8"/>
       <c r="P653" s="8"/>
     </row>
     <row r="654" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A654" s="62"/>
-      <c r="E654" s="62"/>
+      <c r="A654" s="50"/>
+      <c r="E654" s="50"/>
       <c r="N654" s="8"/>
       <c r="P654" s="8"/>
     </row>
     <row r="655" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A655" s="62"/>
-      <c r="E655" s="62"/>
+      <c r="A655" s="50"/>
+      <c r="E655" s="50"/>
       <c r="N655" s="8"/>
       <c r="P655" s="8"/>
     </row>
     <row r="656" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A656" s="62"/>
-      <c r="E656" s="62"/>
+      <c r="A656" s="50"/>
+      <c r="E656" s="50"/>
       <c r="N656" s="8"/>
       <c r="P656" s="8"/>
     </row>
     <row r="657" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A657" s="62"/>
-      <c r="E657" s="62"/>
+      <c r="A657" s="50"/>
+      <c r="E657" s="50"/>
       <c r="N657" s="8"/>
       <c r="P657" s="8"/>
     </row>
     <row r="658" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A658" s="62"/>
-      <c r="E658" s="62"/>
+      <c r="A658" s="50"/>
+      <c r="E658" s="50"/>
       <c r="N658" s="8"/>
       <c r="P658" s="8"/>
     </row>
     <row r="659" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A659" s="62"/>
-      <c r="E659" s="62"/>
+      <c r="A659" s="50"/>
+      <c r="E659" s="50"/>
       <c r="N659" s="8"/>
       <c r="P659" s="8"/>
     </row>
     <row r="660" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A660" s="62"/>
-      <c r="E660" s="62"/>
+      <c r="A660" s="50"/>
+      <c r="E660" s="50"/>
       <c r="N660" s="8"/>
       <c r="P660" s="8"/>
     </row>
     <row r="661" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A661" s="62"/>
-      <c r="E661" s="62"/>
+      <c r="A661" s="50"/>
+      <c r="E661" s="50"/>
       <c r="N661" s="8"/>
       <c r="P661" s="8"/>
     </row>
     <row r="662" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A662" s="62"/>
-      <c r="E662" s="62"/>
+      <c r="A662" s="50"/>
+      <c r="E662" s="50"/>
       <c r="N662" s="8"/>
       <c r="P662" s="8"/>
     </row>
     <row r="663" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A663" s="62"/>
-      <c r="E663" s="62"/>
+      <c r="A663" s="50"/>
+      <c r="E663" s="50"/>
       <c r="N663" s="8"/>
       <c r="P663" s="8"/>
     </row>
     <row r="664" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A664" s="62"/>
-      <c r="E664" s="62"/>
+      <c r="A664" s="50"/>
+      <c r="E664" s="50"/>
       <c r="N664" s="8"/>
       <c r="P664" s="8"/>
     </row>
     <row r="665" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A665" s="62"/>
-      <c r="E665" s="62"/>
+      <c r="A665" s="50"/>
+      <c r="E665" s="50"/>
       <c r="N665" s="8"/>
       <c r="P665" s="8"/>
     </row>
     <row r="666" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A666" s="62"/>
-      <c r="E666" s="62"/>
+      <c r="A666" s="50"/>
+      <c r="E666" s="50"/>
       <c r="N666" s="8"/>
       <c r="P666" s="8"/>
     </row>
     <row r="667" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A667" s="62"/>
-      <c r="E667" s="62"/>
+      <c r="A667" s="50"/>
+      <c r="E667" s="50"/>
       <c r="N667" s="8"/>
       <c r="P667" s="8"/>
     </row>
     <row r="668" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A668" s="62"/>
-      <c r="E668" s="62"/>
+      <c r="A668" s="50"/>
+      <c r="E668" s="50"/>
       <c r="N668" s="8"/>
       <c r="P668" s="8"/>
     </row>
     <row r="669" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A669" s="62"/>
-      <c r="E669" s="62"/>
+      <c r="A669" s="50"/>
+      <c r="E669" s="50"/>
       <c r="N669" s="8"/>
       <c r="P669" s="8"/>
     </row>
     <row r="670" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A670" s="62"/>
-      <c r="E670" s="62"/>
+      <c r="A670" s="50"/>
+      <c r="E670" s="50"/>
       <c r="N670" s="8"/>
       <c r="P670" s="8"/>
     </row>
     <row r="671" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A671" s="62"/>
-      <c r="E671" s="62"/>
+      <c r="A671" s="50"/>
+      <c r="E671" s="50"/>
       <c r="N671" s="8"/>
       <c r="P671" s="8"/>
     </row>
     <row r="672" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A672" s="62"/>
-      <c r="E672" s="62"/>
+      <c r="A672" s="50"/>
+      <c r="E672" s="50"/>
       <c r="N672" s="8"/>
       <c r="P672" s="8"/>
     </row>
     <row r="673" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A673" s="62"/>
-      <c r="E673" s="62"/>
+      <c r="A673" s="50"/>
+      <c r="E673" s="50"/>
       <c r="N673" s="8"/>
       <c r="P673" s="8"/>
     </row>
     <row r="674" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A674" s="62"/>
-      <c r="E674" s="62"/>
+      <c r="A674" s="50"/>
+      <c r="E674" s="50"/>
       <c r="N674" s="8"/>
       <c r="P674" s="8"/>
     </row>
     <row r="675" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A675" s="62"/>
-      <c r="E675" s="62"/>
+      <c r="A675" s="50"/>
+      <c r="E675" s="50"/>
       <c r="N675" s="8"/>
       <c r="P675" s="8"/>
     </row>
     <row r="676" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A676" s="62"/>
-      <c r="E676" s="62"/>
+      <c r="A676" s="50"/>
+      <c r="E676" s="50"/>
       <c r="N676" s="8"/>
       <c r="P676" s="8"/>
     </row>
     <row r="677" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A677" s="62"/>
-      <c r="E677" s="62"/>
+      <c r="A677" s="50"/>
+      <c r="E677" s="50"/>
       <c r="N677" s="8"/>
       <c r="P677" s="8"/>
     </row>
     <row r="678" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A678" s="62"/>
-      <c r="E678" s="62"/>
+      <c r="A678" s="50"/>
+      <c r="E678" s="50"/>
       <c r="N678" s="8"/>
       <c r="P678" s="8"/>
     </row>
     <row r="679" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A679" s="62"/>
-      <c r="E679" s="62"/>
+      <c r="A679" s="50"/>
+      <c r="E679" s="50"/>
       <c r="N679" s="8"/>
       <c r="P679" s="8"/>
     </row>
     <row r="680" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A680" s="62"/>
-      <c r="E680" s="62"/>
+      <c r="A680" s="50"/>
+      <c r="E680" s="50"/>
       <c r="N680" s="8"/>
       <c r="P680" s="8"/>
     </row>
     <row r="681" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A681" s="62"/>
-      <c r="E681" s="62"/>
+      <c r="A681" s="50"/>
+      <c r="E681" s="50"/>
       <c r="N681" s="8"/>
       <c r="P681" s="8"/>
     </row>
     <row r="682" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A682" s="62"/>
-      <c r="E682" s="62"/>
+      <c r="A682" s="50"/>
+      <c r="E682" s="50"/>
       <c r="N682" s="8"/>
       <c r="P682" s="8"/>
     </row>
     <row r="683" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A683" s="62"/>
-      <c r="E683" s="62"/>
+      <c r="A683" s="50"/>
+      <c r="E683" s="50"/>
       <c r="N683" s="8"/>
       <c r="P683" s="8"/>
     </row>
     <row r="684" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A684" s="62"/>
-      <c r="E684" s="62"/>
+      <c r="A684" s="50"/>
+      <c r="E684" s="50"/>
       <c r="N684" s="8"/>
       <c r="P684" s="8"/>
     </row>
     <row r="685" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A685" s="62"/>
-      <c r="E685" s="62"/>
+      <c r="A685" s="50"/>
+      <c r="E685" s="50"/>
       <c r="N685" s="8"/>
       <c r="P685" s="8"/>
     </row>
     <row r="686" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A686" s="62"/>
-      <c r="E686" s="62"/>
+      <c r="A686" s="50"/>
+      <c r="E686" s="50"/>
       <c r="N686" s="8"/>
       <c r="P686" s="8"/>
     </row>
     <row r="687" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A687" s="62"/>
-      <c r="E687" s="62"/>
+      <c r="A687" s="50"/>
+      <c r="E687" s="50"/>
       <c r="N687" s="8"/>
       <c r="P687" s="8"/>
     </row>
     <row r="688" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A688" s="62"/>
-      <c r="E688" s="62"/>
+      <c r="A688" s="50"/>
+      <c r="E688" s="50"/>
       <c r="N688" s="8"/>
       <c r="P688" s="8"/>
     </row>
     <row r="689" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A689" s="62"/>
-      <c r="E689" s="62"/>
+      <c r="A689" s="50"/>
+      <c r="E689" s="50"/>
       <c r="N689" s="8"/>
       <c r="P689" s="8"/>
     </row>
     <row r="690" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A690" s="62"/>
-      <c r="E690" s="62"/>
+      <c r="A690" s="50"/>
+      <c r="E690" s="50"/>
       <c r="N690" s="8"/>
       <c r="P690" s="8"/>
     </row>
     <row r="691" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A691" s="62"/>
-      <c r="E691" s="62"/>
+      <c r="A691" s="50"/>
+      <c r="E691" s="50"/>
       <c r="N691" s="8"/>
       <c r="P691" s="8"/>
     </row>
     <row r="692" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A692" s="62"/>
-      <c r="E692" s="62"/>
+      <c r="A692" s="50"/>
+      <c r="E692" s="50"/>
       <c r="N692" s="8"/>
       <c r="P692" s="8"/>
     </row>
     <row r="693" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A693" s="62"/>
-      <c r="E693" s="62"/>
+      <c r="A693" s="50"/>
+      <c r="E693" s="50"/>
       <c r="N693" s="8"/>
       <c r="P693" s="8"/>
     </row>
     <row r="694" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A694" s="62"/>
-      <c r="E694" s="62"/>
+      <c r="A694" s="50"/>
+      <c r="E694" s="50"/>
       <c r="N694" s="8"/>
       <c r="P694" s="8"/>
     </row>
     <row r="695" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A695" s="62"/>
-      <c r="E695" s="62"/>
+      <c r="A695" s="50"/>
+      <c r="E695" s="50"/>
       <c r="N695" s="8"/>
       <c r="P695" s="8"/>
     </row>
     <row r="696" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A696" s="62"/>
-      <c r="E696" s="62"/>
+      <c r="A696" s="50"/>
+      <c r="E696" s="50"/>
       <c r="N696" s="8"/>
       <c r="P696" s="8"/>
     </row>
     <row r="697" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A697" s="62"/>
-      <c r="E697" s="62"/>
+      <c r="A697" s="50"/>
+      <c r="E697" s="50"/>
       <c r="N697" s="8"/>
       <c r="P697" s="8"/>
     </row>
     <row r="698" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A698" s="62"/>
-      <c r="E698" s="62"/>
+      <c r="A698" s="50"/>
+      <c r="E698" s="50"/>
       <c r="N698" s="8"/>
       <c r="P698" s="8"/>
     </row>
     <row r="699" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A699" s="62"/>
-      <c r="E699" s="62"/>
+      <c r="A699" s="50"/>
+      <c r="E699" s="50"/>
       <c r="N699" s="8"/>
       <c r="P699" s="8"/>
     </row>
     <row r="700" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A700" s="62"/>
-      <c r="E700" s="62"/>
+      <c r="A700" s="50"/>
+      <c r="E700" s="50"/>
       <c r="N700" s="8"/>
       <c r="P700" s="8"/>
     </row>
     <row r="701" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A701" s="62"/>
-      <c r="E701" s="62"/>
+      <c r="A701" s="50"/>
+      <c r="E701" s="50"/>
       <c r="N701" s="8"/>
       <c r="P701" s="8"/>
     </row>
     <row r="702" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A702" s="62"/>
-      <c r="E702" s="62"/>
+      <c r="A702" s="50"/>
+      <c r="E702" s="50"/>
       <c r="N702" s="8"/>
       <c r="P702" s="8"/>
     </row>
     <row r="703" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A703" s="62"/>
-      <c r="E703" s="62"/>
+      <c r="A703" s="50"/>
+      <c r="E703" s="50"/>
       <c r="N703" s="8"/>
       <c r="P703" s="8"/>
     </row>
     <row r="704" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A704" s="62"/>
-      <c r="E704" s="62"/>
+      <c r="A704" s="50"/>
+      <c r="E704" s="50"/>
       <c r="N704" s="8"/>
       <c r="P704" s="8"/>
     </row>
     <row r="705" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A705" s="62"/>
-      <c r="E705" s="62"/>
+      <c r="A705" s="50"/>
+      <c r="E705" s="50"/>
       <c r="N705" s="8"/>
       <c r="P705" s="8"/>
     </row>
     <row r="706" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A706" s="62"/>
-      <c r="E706" s="62"/>
+      <c r="A706" s="50"/>
+      <c r="E706" s="50"/>
       <c r="N706" s="8"/>
       <c r="P706" s="8"/>
     </row>
     <row r="707" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A707" s="62"/>
-      <c r="E707" s="62"/>
+      <c r="A707" s="50"/>
+      <c r="E707" s="50"/>
       <c r="N707" s="8"/>
       <c r="P707" s="8"/>
     </row>
     <row r="708" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A708" s="62"/>
-      <c r="E708" s="62"/>
+      <c r="A708" s="50"/>
+      <c r="E708" s="50"/>
       <c r="N708" s="8"/>
       <c r="P708" s="8"/>
     </row>
     <row r="709" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A709" s="62"/>
-      <c r="E709" s="62"/>
+      <c r="A709" s="50"/>
+      <c r="E709" s="50"/>
       <c r="N709" s="8"/>
       <c r="P709" s="8"/>
     </row>
     <row r="710" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A710" s="62"/>
-      <c r="E710" s="62"/>
+      <c r="A710" s="50"/>
+      <c r="E710" s="50"/>
       <c r="N710" s="8"/>
       <c r="P710" s="8"/>
     </row>
     <row r="711" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A711" s="62"/>
-      <c r="E711" s="62"/>
+      <c r="A711" s="50"/>
+      <c r="E711" s="50"/>
       <c r="N711" s="8"/>
       <c r="P711" s="8"/>
     </row>
     <row r="712" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A712" s="62"/>
-      <c r="E712" s="62"/>
+      <c r="A712" s="50"/>
+      <c r="E712" s="50"/>
       <c r="N712" s="8"/>
       <c r="P712" s="8"/>
     </row>
     <row r="713" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A713" s="62"/>
-      <c r="E713" s="62"/>
+      <c r="A713" s="50"/>
+      <c r="E713" s="50"/>
       <c r="N713" s="8"/>
       <c r="P713" s="8"/>
     </row>
     <row r="714" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A714" s="62"/>
-      <c r="E714" s="62"/>
+      <c r="A714" s="50"/>
+      <c r="E714" s="50"/>
       <c r="N714" s="8"/>
       <c r="P714" s="8"/>
     </row>
     <row r="715" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A715" s="62"/>
-      <c r="E715" s="62"/>
+      <c r="A715" s="50"/>
+      <c r="E715" s="50"/>
       <c r="N715" s="8"/>
       <c r="P715" s="8"/>
     </row>
     <row r="716" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A716" s="62"/>
-      <c r="E716" s="62"/>
+      <c r="A716" s="50"/>
+      <c r="E716" s="50"/>
       <c r="N716" s="8"/>
       <c r="P716" s="8"/>
     </row>
     <row r="717" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A717" s="62"/>
-      <c r="E717" s="62"/>
+      <c r="A717" s="50"/>
+      <c r="E717" s="50"/>
       <c r="N717" s="8"/>
       <c r="P717" s="8"/>
     </row>
     <row r="718" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A718" s="62"/>
-      <c r="E718" s="62"/>
+      <c r="A718" s="50"/>
+      <c r="E718" s="50"/>
       <c r="N718" s="8"/>
       <c r="P718" s="8"/>
     </row>
     <row r="719" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A719" s="62"/>
-      <c r="E719" s="62"/>
+      <c r="A719" s="50"/>
+      <c r="E719" s="50"/>
       <c r="N719" s="8"/>
       <c r="P719" s="8"/>
     </row>
     <row r="720" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A720" s="62"/>
-      <c r="E720" s="62"/>
+      <c r="A720" s="50"/>
+      <c r="E720" s="50"/>
       <c r="N720" s="8"/>
       <c r="P720" s="8"/>
     </row>
     <row r="721" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A721" s="62"/>
-      <c r="E721" s="62"/>
+      <c r="A721" s="50"/>
+      <c r="E721" s="50"/>
       <c r="N721" s="8"/>
       <c r="P721" s="8"/>
     </row>
     <row r="722" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A722" s="62"/>
-      <c r="E722" s="62"/>
+      <c r="A722" s="50"/>
+      <c r="E722" s="50"/>
       <c r="N722" s="8"/>
       <c r="P722" s="8"/>
     </row>
     <row r="723" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A723" s="62"/>
-      <c r="E723" s="62"/>
+      <c r="A723" s="50"/>
+      <c r="E723" s="50"/>
       <c r="N723" s="8"/>
       <c r="P723" s="8"/>
     </row>
     <row r="724" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A724" s="62"/>
-      <c r="E724" s="62"/>
+      <c r="A724" s="50"/>
+      <c r="E724" s="50"/>
       <c r="N724" s="8"/>
       <c r="P724" s="8"/>
     </row>
     <row r="725" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A725" s="62"/>
-      <c r="E725" s="62"/>
+      <c r="A725" s="50"/>
+      <c r="E725" s="50"/>
       <c r="N725" s="8"/>
       <c r="P725" s="8"/>
     </row>
     <row r="726" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A726" s="62"/>
-      <c r="E726" s="62"/>
+      <c r="A726" s="50"/>
+      <c r="E726" s="50"/>
       <c r="N726" s="8"/>
       <c r="P726" s="8"/>
     </row>
     <row r="727" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A727" s="62"/>
-      <c r="E727" s="62"/>
+      <c r="A727" s="50"/>
+      <c r="E727" s="50"/>
       <c r="N727" s="8"/>
       <c r="P727" s="8"/>
     </row>
     <row r="728" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A728" s="62"/>
-      <c r="E728" s="62"/>
+      <c r="A728" s="50"/>
+      <c r="E728" s="50"/>
       <c r="N728" s="8"/>
       <c r="P728" s="8"/>
     </row>
     <row r="729" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A729" s="62"/>
-      <c r="E729" s="62"/>
+      <c r="A729" s="50"/>
+      <c r="E729" s="50"/>
       <c r="N729" s="8"/>
       <c r="P729" s="8"/>
     </row>
     <row r="730" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A730" s="62"/>
-      <c r="E730" s="62"/>
+      <c r="A730" s="50"/>
+      <c r="E730" s="50"/>
       <c r="N730" s="8"/>
       <c r="P730" s="8"/>
     </row>
     <row r="731" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A731" s="62"/>
-      <c r="E731" s="62"/>
+      <c r="A731" s="50"/>
+      <c r="E731" s="50"/>
       <c r="N731" s="8"/>
       <c r="P731" s="8"/>
     </row>
     <row r="732" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A732" s="62"/>
-      <c r="E732" s="62"/>
+      <c r="A732" s="50"/>
+      <c r="E732" s="50"/>
       <c r="N732" s="8"/>
       <c r="P732" s="8"/>
     </row>
     <row r="733" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A733" s="62"/>
-      <c r="E733" s="62"/>
+      <c r="A733" s="50"/>
+      <c r="E733" s="50"/>
       <c r="N733" s="8"/>
       <c r="P733" s="8"/>
     </row>
     <row r="734" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A734" s="62"/>
-      <c r="E734" s="62"/>
+      <c r="A734" s="50"/>
+      <c r="E734" s="50"/>
       <c r="N734" s="8"/>
       <c r="P734" s="8"/>
     </row>
     <row r="735" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A735" s="62"/>
-      <c r="E735" s="62"/>
+      <c r="A735" s="50"/>
+      <c r="E735" s="50"/>
       <c r="N735" s="8"/>
       <c r="P735" s="8"/>
     </row>
     <row r="736" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A736" s="62"/>
-      <c r="E736" s="62"/>
+      <c r="A736" s="50"/>
+      <c r="E736" s="50"/>
       <c r="N736" s="8"/>
       <c r="P736" s="8"/>
     </row>
     <row r="737" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A737" s="62"/>
-      <c r="E737" s="62"/>
+      <c r="A737" s="50"/>
+      <c r="E737" s="50"/>
       <c r="N737" s="8"/>
       <c r="P737" s="8"/>
     </row>
     <row r="738" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A738" s="62"/>
-      <c r="E738" s="62"/>
+      <c r="A738" s="50"/>
+      <c r="E738" s="50"/>
       <c r="N738" s="8"/>
       <c r="P738" s="8"/>
     </row>
     <row r="739" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A739" s="62"/>
-      <c r="E739" s="62"/>
+      <c r="A739" s="50"/>
+      <c r="E739" s="50"/>
       <c r="N739" s="8"/>
       <c r="P739" s="8"/>
     </row>
     <row r="740" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A740" s="62"/>
-      <c r="E740" s="62"/>
+      <c r="A740" s="50"/>
+      <c r="E740" s="50"/>
       <c r="N740" s="8"/>
       <c r="P740" s="8"/>
     </row>
     <row r="741" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A741" s="62"/>
-      <c r="E741" s="62"/>
+      <c r="A741" s="50"/>
+      <c r="E741" s="50"/>
       <c r="N741" s="8"/>
       <c r="P741" s="8"/>
     </row>
     <row r="742" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A742" s="62"/>
-      <c r="E742" s="62"/>
+      <c r="A742" s="50"/>
+      <c r="E742" s="50"/>
       <c r="N742" s="8"/>
       <c r="P742" s="8"/>
     </row>
     <row r="743" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A743" s="62"/>
-      <c r="E743" s="62"/>
+      <c r="A743" s="50"/>
+      <c r="E743" s="50"/>
       <c r="N743" s="8"/>
       <c r="P743" s="8"/>
     </row>
     <row r="744" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A744" s="62"/>
-      <c r="E744" s="62"/>
+      <c r="A744" s="50"/>
+      <c r="E744" s="50"/>
       <c r="N744" s="8"/>
       <c r="P744" s="8"/>
     </row>
     <row r="745" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A745" s="62"/>
-      <c r="E745" s="62"/>
+      <c r="A745" s="50"/>
+      <c r="E745" s="50"/>
       <c r="N745" s="8"/>
       <c r="P745" s="8"/>
     </row>
     <row r="746" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A746" s="62"/>
-      <c r="E746" s="62"/>
+      <c r="A746" s="50"/>
+      <c r="E746" s="50"/>
       <c r="N746" s="8"/>
       <c r="P746" s="8"/>
     </row>
     <row r="747" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A747" s="62"/>
-      <c r="E747" s="62"/>
+      <c r="A747" s="50"/>
+      <c r="E747" s="50"/>
       <c r="N747" s="8"/>
       <c r="P747" s="8"/>
     </row>
     <row r="748" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A748" s="62"/>
-      <c r="E748" s="62"/>
+      <c r="A748" s="50"/>
+      <c r="E748" s="50"/>
       <c r="N748" s="8"/>
       <c r="P748" s="8"/>
     </row>
     <row r="749" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A749" s="62"/>
-      <c r="E749" s="62"/>
+      <c r="A749" s="50"/>
+      <c r="E749" s="50"/>
       <c r="N749" s="8"/>
       <c r="P749" s="8"/>
     </row>
     <row r="750" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A750" s="62"/>
-      <c r="E750" s="62"/>
+      <c r="A750" s="50"/>
+      <c r="E750" s="50"/>
       <c r="N750" s="8"/>
       <c r="P750" s="8"/>
     </row>
     <row r="751" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A751" s="62"/>
-      <c r="E751" s="62"/>
+      <c r="A751" s="50"/>
+      <c r="E751" s="50"/>
       <c r="N751" s="8"/>
       <c r="P751" s="8"/>
     </row>
     <row r="752" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A752" s="62"/>
-      <c r="E752" s="62"/>
+      <c r="A752" s="50"/>
+      <c r="E752" s="50"/>
       <c r="N752" s="8"/>
       <c r="P752" s="8"/>
     </row>
     <row r="753" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A753" s="62"/>
-      <c r="E753" s="62"/>
+      <c r="A753" s="50"/>
+      <c r="E753" s="50"/>
       <c r="N753" s="8"/>
       <c r="P753" s="8"/>
     </row>
     <row r="754" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A754" s="62"/>
-      <c r="E754" s="62"/>
+      <c r="A754" s="50"/>
+      <c r="E754" s="50"/>
       <c r="N754" s="8"/>
       <c r="P754" s="8"/>
     </row>
     <row r="755" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A755" s="62"/>
-      <c r="E755" s="62"/>
+      <c r="A755" s="50"/>
+      <c r="E755" s="50"/>
       <c r="N755" s="8"/>
       <c r="P755" s="8"/>
     </row>
     <row r="756" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A756" s="62"/>
-      <c r="E756" s="62"/>
+      <c r="A756" s="50"/>
+      <c r="E756" s="50"/>
       <c r="N756" s="8"/>
       <c r="P756" s="8"/>
     </row>
     <row r="757" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A757" s="62"/>
-      <c r="E757" s="62"/>
+      <c r="A757" s="50"/>
+      <c r="E757" s="50"/>
       <c r="N757" s="8"/>
       <c r="P757" s="8"/>
     </row>
     <row r="758" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A758" s="62"/>
-      <c r="E758" s="62"/>
+      <c r="A758" s="50"/>
+      <c r="E758" s="50"/>
       <c r="N758" s="8"/>
       <c r="P758" s="8"/>
     </row>
     <row r="759" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A759" s="62"/>
-      <c r="E759" s="62"/>
+      <c r="A759" s="50"/>
+      <c r="E759" s="50"/>
       <c r="N759" s="8"/>
       <c r="P759" s="8"/>
     </row>
     <row r="760" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A760" s="62"/>
-      <c r="E760" s="62"/>
+      <c r="A760" s="50"/>
+      <c r="E760" s="50"/>
       <c r="N760" s="8"/>
       <c r="P760" s="8"/>
     </row>
     <row r="761" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A761" s="62"/>
-      <c r="E761" s="62"/>
+      <c r="A761" s="50"/>
+      <c r="E761" s="50"/>
       <c r="N761" s="8"/>
       <c r="P761" s="8"/>
     </row>
     <row r="762" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A762" s="62"/>
-      <c r="E762" s="62"/>
+      <c r="A762" s="50"/>
+      <c r="E762" s="50"/>
       <c r="N762" s="8"/>
       <c r="P762" s="8"/>
     </row>
     <row r="763" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A763" s="62"/>
-      <c r="E763" s="62"/>
+      <c r="A763" s="50"/>
+      <c r="E763" s="50"/>
       <c r="N763" s="8"/>
       <c r="P763" s="8"/>
     </row>
     <row r="764" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A764" s="62"/>
-      <c r="E764" s="62"/>
+      <c r="A764" s="50"/>
+      <c r="E764" s="50"/>
       <c r="N764" s="8"/>
       <c r="P764" s="8"/>
     </row>
     <row r="765" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A765" s="62"/>
-      <c r="E765" s="62"/>
+      <c r="A765" s="50"/>
+      <c r="E765" s="50"/>
       <c r="N765" s="8"/>
       <c r="P765" s="8"/>
     </row>
     <row r="766" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A766" s="62"/>
-      <c r="E766" s="62"/>
+      <c r="A766" s="50"/>
+      <c r="E766" s="50"/>
       <c r="N766" s="8"/>
       <c r="P766" s="8"/>
     </row>
     <row r="767" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A767" s="62"/>
-      <c r="E767" s="62"/>
+      <c r="A767" s="50"/>
+      <c r="E767" s="50"/>
       <c r="N767" s="8"/>
       <c r="P767" s="8"/>
     </row>
     <row r="768" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A768" s="62"/>
-      <c r="E768" s="62"/>
+      <c r="A768" s="50"/>
+      <c r="E768" s="50"/>
       <c r="N768" s="8"/>
       <c r="P768" s="8"/>
     </row>
     <row r="769" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A769" s="62"/>
-      <c r="E769" s="62"/>
+      <c r="A769" s="50"/>
+      <c r="E769" s="50"/>
       <c r="N769" s="8"/>
       <c r="P769" s="8"/>
     </row>
     <row r="770" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A770" s="62"/>
-      <c r="E770" s="62"/>
+      <c r="A770" s="50"/>
+      <c r="E770" s="50"/>
       <c r="N770" s="8"/>
       <c r="P770" s="8"/>
     </row>
     <row r="771" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A771" s="62"/>
-      <c r="E771" s="62"/>
+      <c r="A771" s="50"/>
+      <c r="E771" s="50"/>
       <c r="N771" s="8"/>
       <c r="P771" s="8"/>
     </row>
     <row r="772" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A772" s="62"/>
-      <c r="E772" s="62"/>
+      <c r="A772" s="50"/>
+      <c r="E772" s="50"/>
       <c r="N772" s="8"/>
       <c r="P772" s="8"/>
     </row>
     <row r="773" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A773" s="62"/>
-      <c r="E773" s="62"/>
+      <c r="A773" s="50"/>
+      <c r="E773" s="50"/>
       <c r="N773" s="8"/>
       <c r="P773" s="8"/>
     </row>
     <row r="774" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A774" s="62"/>
-      <c r="E774" s="62"/>
+      <c r="A774" s="50"/>
+      <c r="E774" s="50"/>
       <c r="N774" s="8"/>
       <c r="P774" s="8"/>
     </row>
     <row r="775" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A775" s="62"/>
-      <c r="E775" s="62"/>
+      <c r="A775" s="50"/>
+      <c r="E775" s="50"/>
       <c r="N775" s="8"/>
       <c r="P775" s="8"/>
     </row>
     <row r="776" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A776" s="62"/>
-      <c r="E776" s="62"/>
+      <c r="A776" s="50"/>
+      <c r="E776" s="50"/>
       <c r="N776" s="8"/>
       <c r="P776" s="8"/>
     </row>
     <row r="777" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A777" s="62"/>
-      <c r="E777" s="62"/>
+      <c r="A777" s="50"/>
+      <c r="E777" s="50"/>
       <c r="N777" s="8"/>
       <c r="P777" s="8"/>
     </row>
     <row r="778" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A778" s="62"/>
-      <c r="E778" s="62"/>
+      <c r="A778" s="50"/>
+      <c r="E778" s="50"/>
       <c r="N778" s="8"/>
       <c r="P778" s="8"/>
     </row>
     <row r="779" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A779" s="62"/>
-      <c r="E779" s="62"/>
+      <c r="A779" s="50"/>
+      <c r="E779" s="50"/>
       <c r="N779" s="8"/>
       <c r="P779" s="8"/>
     </row>
     <row r="780" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A780" s="62"/>
-      <c r="E780" s="62"/>
+      <c r="A780" s="50"/>
+      <c r="E780" s="50"/>
       <c r="N780" s="8"/>
       <c r="P780" s="8"/>
     </row>
     <row r="781" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A781" s="62"/>
-      <c r="E781" s="62"/>
+      <c r="A781" s="50"/>
+      <c r="E781" s="50"/>
       <c r="N781" s="8"/>
       <c r="P781" s="8"/>
     </row>
     <row r="782" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A782" s="62"/>
-      <c r="E782" s="62"/>
+      <c r="A782" s="50"/>
+      <c r="E782" s="50"/>
       <c r="N782" s="8"/>
       <c r="P782" s="8"/>
     </row>
     <row r="783" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A783" s="62"/>
-      <c r="E783" s="62"/>
+      <c r="A783" s="50"/>
+      <c r="E783" s="50"/>
       <c r="N783" s="8"/>
       <c r="P783" s="8"/>
     </row>
     <row r="784" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A784" s="62"/>
-      <c r="E784" s="62"/>
+      <c r="A784" s="50"/>
+      <c r="E784" s="50"/>
       <c r="N784" s="8"/>
       <c r="P784" s="8"/>
     </row>
     <row r="785" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A785" s="62"/>
-      <c r="E785" s="62"/>
+      <c r="A785" s="50"/>
+      <c r="E785" s="50"/>
       <c r="N785" s="8"/>
       <c r="P785" s="8"/>
     </row>
     <row r="786" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A786" s="62"/>
-      <c r="E786" s="62"/>
+      <c r="A786" s="50"/>
+      <c r="E786" s="50"/>
       <c r="N786" s="8"/>
       <c r="P786" s="8"/>
     </row>
     <row r="787" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A787" s="62"/>
-      <c r="E787" s="62"/>
+      <c r="A787" s="50"/>
+      <c r="E787" s="50"/>
       <c r="N787" s="8"/>
       <c r="P787" s="8"/>
     </row>
     <row r="788" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A788" s="62"/>
-      <c r="E788" s="62"/>
+      <c r="A788" s="50"/>
+      <c r="E788" s="50"/>
       <c r="N788" s="8"/>
       <c r="P788" s="8"/>
     </row>
     <row r="789" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A789" s="62"/>
-      <c r="E789" s="62"/>
+      <c r="A789" s="50"/>
+      <c r="E789" s="50"/>
       <c r="N789" s="8"/>
       <c r="P789" s="8"/>
     </row>
     <row r="790" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A790" s="62"/>
-      <c r="E790" s="62"/>
+      <c r="A790" s="50"/>
+      <c r="E790" s="50"/>
       <c r="N790" s="8"/>
       <c r="P790" s="8"/>
     </row>
     <row r="791" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A791" s="62"/>
-      <c r="E791" s="62"/>
+      <c r="A791" s="50"/>
+      <c r="E791" s="50"/>
       <c r="N791" s="8"/>
       <c r="P791" s="8"/>
     </row>
     <row r="792" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A792" s="62"/>
-      <c r="E792" s="62"/>
+      <c r="A792" s="50"/>
+      <c r="E792" s="50"/>
       <c r="N792" s="8"/>
       <c r="P792" s="8"/>
     </row>
     <row r="793" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A793" s="62"/>
-      <c r="E793" s="62"/>
+      <c r="A793" s="50"/>
+      <c r="E793" s="50"/>
       <c r="N793" s="8"/>
       <c r="P793" s="8"/>
     </row>
     <row r="794" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A794" s="62"/>
-      <c r="E794" s="62"/>
+      <c r="A794" s="50"/>
+      <c r="E794" s="50"/>
       <c r="N794" s="8"/>
       <c r="P794" s="8"/>
     </row>
     <row r="795" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A795" s="62"/>
-      <c r="E795" s="62"/>
+      <c r="A795" s="50"/>
+      <c r="E795" s="50"/>
       <c r="N795" s="8"/>
       <c r="P795" s="8"/>
     </row>
     <row r="796" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A796" s="62"/>
-      <c r="E796" s="62"/>
+      <c r="A796" s="50"/>
+      <c r="E796" s="50"/>
       <c r="N796" s="8"/>
       <c r="P796" s="8"/>
     </row>
     <row r="797" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A797" s="62"/>
-      <c r="E797" s="62"/>
+      <c r="A797" s="50"/>
+      <c r="E797" s="50"/>
       <c r="N797" s="8"/>
       <c r="P797" s="8"/>
     </row>
     <row r="798" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A798" s="62"/>
-      <c r="E798" s="62"/>
+      <c r="A798" s="50"/>
+      <c r="E798" s="50"/>
       <c r="N798" s="8"/>
       <c r="P798" s="8"/>
     </row>
     <row r="799" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A799" s="62"/>
-      <c r="E799" s="62"/>
+      <c r="A799" s="50"/>
+      <c r="E799" s="50"/>
       <c r="N799" s="8"/>
       <c r="P799" s="8"/>
     </row>
     <row r="800" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A800" s="62"/>
-      <c r="E800" s="62"/>
+      <c r="A800" s="50"/>
+      <c r="E800" s="50"/>
       <c r="N800" s="8"/>
       <c r="P800" s="8"/>
     </row>
     <row r="801" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A801" s="62"/>
-      <c r="E801" s="62"/>
+      <c r="A801" s="50"/>
+      <c r="E801" s="50"/>
       <c r="N801" s="8"/>
       <c r="P801" s="8"/>
     </row>
     <row r="802" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A802" s="62"/>
-      <c r="E802" s="62"/>
+      <c r="A802" s="50"/>
+      <c r="E802" s="50"/>
       <c r="N802" s="8"/>
       <c r="P802" s="8"/>
     </row>
     <row r="803" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A803" s="62"/>
-      <c r="E803" s="62"/>
+      <c r="A803" s="50"/>
+      <c r="E803" s="50"/>
       <c r="N803" s="8"/>
       <c r="P803" s="8"/>
     </row>
     <row r="804" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A804" s="62"/>
-      <c r="E804" s="62"/>
+      <c r="A804" s="50"/>
+      <c r="E804" s="50"/>
       <c r="N804" s="8"/>
       <c r="P804" s="8"/>
     </row>
     <row r="805" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A805" s="62"/>
-      <c r="E805" s="62"/>
+      <c r="A805" s="50"/>
+      <c r="E805" s="50"/>
       <c r="N805" s="8"/>
       <c r="P805" s="8"/>
     </row>
     <row r="806" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A806" s="62"/>
-      <c r="E806" s="62"/>
+      <c r="A806" s="50"/>
+      <c r="E806" s="50"/>
       <c r="N806" s="8"/>
       <c r="P806" s="8"/>
     </row>
     <row r="807" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A807" s="62"/>
-      <c r="E807" s="62"/>
+      <c r="A807" s="50"/>
+      <c r="E807" s="50"/>
       <c r="N807" s="8"/>
       <c r="P807" s="8"/>
     </row>
     <row r="808" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A808" s="62"/>
-      <c r="E808" s="62"/>
+      <c r="A808" s="50"/>
+      <c r="E808" s="50"/>
       <c r="N808" s="8"/>
       <c r="P808" s="8"/>
     </row>
     <row r="809" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A809" s="62"/>
-      <c r="E809" s="62"/>
+      <c r="A809" s="50"/>
+      <c r="E809" s="50"/>
       <c r="N809" s="8"/>
       <c r="P809" s="8"/>
     </row>
     <row r="810" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A810" s="62"/>
-      <c r="E810" s="62"/>
+      <c r="A810" s="50"/>
+      <c r="E810" s="50"/>
       <c r="N810" s="8"/>
       <c r="P810" s="8"/>
     </row>
     <row r="811" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A811" s="62"/>
-      <c r="E811" s="62"/>
+      <c r="A811" s="50"/>
+      <c r="E811" s="50"/>
       <c r="N811" s="8"/>
       <c r="P811" s="8"/>
     </row>
     <row r="812" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A812" s="62"/>
-      <c r="E812" s="62"/>
+      <c r="A812" s="50"/>
+      <c r="E812" s="50"/>
       <c r="N812" s="8"/>
       <c r="P812" s="8"/>
     </row>
     <row r="813" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A813" s="62"/>
-      <c r="E813" s="62"/>
+      <c r="A813" s="50"/>
+      <c r="E813" s="50"/>
       <c r="N813" s="8"/>
       <c r="P813" s="8"/>
     </row>
     <row r="814" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A814" s="62"/>
-      <c r="E814" s="62"/>
+      <c r="A814" s="50"/>
+      <c r="E814" s="50"/>
       <c r="N814" s="8"/>
       <c r="P814" s="8"/>
     </row>
     <row r="815" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A815" s="62"/>
-      <c r="E815" s="62"/>
+      <c r="A815" s="50"/>
+      <c r="E815" s="50"/>
       <c r="N815" s="8"/>
       <c r="P815" s="8"/>
     </row>
     <row r="816" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A816" s="62"/>
-      <c r="E816" s="62"/>
+      <c r="A816" s="50"/>
+      <c r="E816" s="50"/>
       <c r="N816" s="8"/>
       <c r="P816" s="8"/>
     </row>
     <row r="817" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A817" s="62"/>
-      <c r="E817" s="62"/>
+      <c r="A817" s="50"/>
+      <c r="E817" s="50"/>
       <c r="N817" s="8"/>
       <c r="P817" s="8"/>
     </row>
     <row r="818" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A818" s="62"/>
-      <c r="E818" s="62"/>
+      <c r="A818" s="50"/>
+      <c r="E818" s="50"/>
       <c r="N818" s="8"/>
       <c r="P818" s="8"/>
     </row>
     <row r="819" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A819" s="62"/>
-      <c r="E819" s="62"/>
+      <c r="A819" s="50"/>
+      <c r="E819" s="50"/>
       <c r="N819" s="8"/>
       <c r="P819" s="8"/>
     </row>
     <row r="820" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A820" s="62"/>
-      <c r="E820" s="62"/>
+      <c r="A820" s="50"/>
+      <c r="E820" s="50"/>
       <c r="N820" s="8"/>
       <c r="P820" s="8"/>
     </row>
     <row r="821" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A821" s="62"/>
-      <c r="E821" s="62"/>
+      <c r="A821" s="50"/>
+      <c r="E821" s="50"/>
       <c r="N821" s="8"/>
       <c r="P821" s="8"/>
     </row>
     <row r="822" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A822" s="62"/>
-      <c r="E822" s="62"/>
+      <c r="A822" s="50"/>
+      <c r="E822" s="50"/>
       <c r="N822" s="8"/>
       <c r="P822" s="8"/>
     </row>
     <row r="823" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A823" s="62"/>
-      <c r="E823" s="62"/>
+      <c r="A823" s="50"/>
+      <c r="E823" s="50"/>
       <c r="N823" s="8"/>
       <c r="P823" s="8"/>
     </row>
     <row r="824" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A824" s="62"/>
-      <c r="E824" s="62"/>
+      <c r="A824" s="50"/>
+      <c r="E824" s="50"/>
       <c r="N824" s="8"/>
       <c r="P824" s="8"/>
     </row>
     <row r="825" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A825" s="62"/>
-      <c r="E825" s="62"/>
+      <c r="A825" s="50"/>
+      <c r="E825" s="50"/>
       <c r="N825" s="8"/>
       <c r="P825" s="8"/>
     </row>
     <row r="826" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A826" s="62"/>
-      <c r="E826" s="62"/>
+      <c r="A826" s="50"/>
+      <c r="E826" s="50"/>
       <c r="N826" s="8"/>
       <c r="P826" s="8"/>
     </row>
     <row r="827" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A827" s="62"/>
-      <c r="E827" s="62"/>
+      <c r="A827" s="50"/>
+      <c r="E827" s="50"/>
       <c r="N827" s="8"/>
       <c r="P827" s="8"/>
     </row>
     <row r="828" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A828" s="62"/>
-      <c r="E828" s="62"/>
+      <c r="A828" s="50"/>
+      <c r="E828" s="50"/>
       <c r="N828" s="8"/>
       <c r="P828" s="8"/>
     </row>
     <row r="829" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A829" s="62"/>
-      <c r="E829" s="62"/>
+      <c r="A829" s="50"/>
+      <c r="E829" s="50"/>
       <c r="N829" s="8"/>
       <c r="P829" s="8"/>
     </row>
     <row r="830" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A830" s="62"/>
-      <c r="E830" s="62"/>
+      <c r="A830" s="50"/>
+      <c r="E830" s="50"/>
       <c r="N830" s="8"/>
       <c r="P830" s="8"/>
     </row>
     <row r="831" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A831" s="62"/>
-      <c r="E831" s="62"/>
+      <c r="A831" s="50"/>
+      <c r="E831" s="50"/>
       <c r="N831" s="8"/>
       <c r="P831" s="8"/>
     </row>
     <row r="832" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A832" s="62"/>
-      <c r="E832" s="62"/>
+      <c r="A832" s="50"/>
+      <c r="E832" s="50"/>
       <c r="N832" s="8"/>
       <c r="P832" s="8"/>
     </row>
     <row r="833" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A833" s="62"/>
-      <c r="E833" s="62"/>
+      <c r="A833" s="50"/>
+      <c r="E833" s="50"/>
       <c r="N833" s="8"/>
       <c r="P833" s="8"/>
     </row>
     <row r="834" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A834" s="62"/>
-      <c r="E834" s="62"/>
+      <c r="A834" s="50"/>
+      <c r="E834" s="50"/>
       <c r="N834" s="8"/>
       <c r="P834" s="8"/>
     </row>
     <row r="835" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A835" s="62"/>
-      <c r="E835" s="62"/>
+      <c r="A835" s="50"/>
+      <c r="E835" s="50"/>
       <c r="N835" s="8"/>
       <c r="P835" s="8"/>
     </row>
     <row r="836" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A836" s="62"/>
-      <c r="E836" s="62"/>
+      <c r="A836" s="50"/>
+      <c r="E836" s="50"/>
       <c r="N836" s="8"/>
       <c r="P836" s="8"/>
     </row>
     <row r="837" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A837" s="62"/>
-      <c r="E837" s="62"/>
+      <c r="A837" s="50"/>
+      <c r="E837" s="50"/>
       <c r="N837" s="8"/>
       <c r="P837" s="8"/>
     </row>
     <row r="838" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A838" s="62"/>
-      <c r="E838" s="62"/>
+      <c r="A838" s="50"/>
+      <c r="E838" s="50"/>
       <c r="N838" s="8"/>
       <c r="P838" s="8"/>
     </row>
     <row r="839" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A839" s="62"/>
-      <c r="E839" s="62"/>
+      <c r="A839" s="50"/>
+      <c r="E839" s="50"/>
       <c r="N839" s="8"/>
       <c r="P839" s="8"/>
     </row>
     <row r="840" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A840" s="62"/>
-      <c r="E840" s="62"/>
+      <c r="A840" s="50"/>
+      <c r="E840" s="50"/>
       <c r="N840" s="8"/>
       <c r="P840" s="8"/>
     </row>
     <row r="841" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A841" s="62"/>
-      <c r="E841" s="62"/>
+      <c r="A841" s="50"/>
+      <c r="E841" s="50"/>
       <c r="N841" s="8"/>
       <c r="P841" s="8"/>
     </row>
     <row r="842" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A842" s="62"/>
-      <c r="E842" s="62"/>
+      <c r="A842" s="50"/>
+      <c r="E842" s="50"/>
       <c r="N842" s="8"/>
       <c r="P842" s="8"/>
     </row>
     <row r="843" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A843" s="62"/>
-      <c r="E843" s="62"/>
+      <c r="A843" s="50"/>
+      <c r="E843" s="50"/>
       <c r="N843" s="8"/>
       <c r="P843" s="8"/>
     </row>
     <row r="844" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A844" s="62"/>
-      <c r="E844" s="62"/>
+      <c r="A844" s="50"/>
+      <c r="E844" s="50"/>
       <c r="N844" s="8"/>
       <c r="P844" s="8"/>
     </row>
     <row r="845" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A845" s="62"/>
-      <c r="E845" s="62"/>
+      <c r="A845" s="50"/>
+      <c r="E845" s="50"/>
       <c r="N845" s="8"/>
       <c r="P845" s="8"/>
     </row>
     <row r="846" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A846" s="62"/>
-      <c r="E846" s="62"/>
+      <c r="A846" s="50"/>
+      <c r="E846" s="50"/>
       <c r="N846" s="8"/>
       <c r="P846" s="8"/>
     </row>
     <row r="847" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A847" s="62"/>
-      <c r="E847" s="62"/>
+      <c r="A847" s="50"/>
+      <c r="E847" s="50"/>
       <c r="N847" s="8"/>
       <c r="P847" s="8"/>
     </row>
     <row r="848" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A848" s="62"/>
-      <c r="E848" s="62"/>
+      <c r="A848" s="50"/>
+      <c r="E848" s="50"/>
       <c r="N848" s="8"/>
       <c r="P848" s="8"/>
     </row>
     <row r="849" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A849" s="62"/>
-      <c r="E849" s="62"/>
+      <c r="A849" s="50"/>
+      <c r="E849" s="50"/>
       <c r="N849" s="8"/>
       <c r="P849" s="8"/>
     </row>
     <row r="850" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A850" s="62"/>
-      <c r="E850" s="62"/>
+      <c r="A850" s="50"/>
+      <c r="E850" s="50"/>
       <c r="N850" s="8"/>
       <c r="P850" s="8"/>
     </row>
     <row r="851" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A851" s="62"/>
-      <c r="E851" s="62"/>
+      <c r="A851" s="50"/>
+      <c r="E851" s="50"/>
       <c r="N851" s="8"/>
       <c r="P851" s="8"/>
     </row>
     <row r="852" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A852" s="62"/>
-      <c r="E852" s="62"/>
+      <c r="A852" s="50"/>
+      <c r="E852" s="50"/>
       <c r="N852" s="8"/>
       <c r="P852" s="8"/>
     </row>
     <row r="853" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A853" s="62"/>
-      <c r="E853" s="62"/>
+      <c r="A853" s="50"/>
+      <c r="E853" s="50"/>
       <c r="N853" s="8"/>
       <c r="P853" s="8"/>
     </row>
     <row r="854" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A854" s="62"/>
-      <c r="E854" s="62"/>
+      <c r="A854" s="50"/>
+      <c r="E854" s="50"/>
       <c r="N854" s="8"/>
       <c r="P854" s="8"/>
     </row>
     <row r="855" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A855" s="62"/>
-      <c r="E855" s="62"/>
+      <c r="A855" s="50"/>
+      <c r="E855" s="50"/>
       <c r="N855" s="8"/>
       <c r="P855" s="8"/>
     </row>
     <row r="856" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A856" s="62"/>
-      <c r="E856" s="62"/>
+      <c r="A856" s="50"/>
+      <c r="E856" s="50"/>
       <c r="N856" s="8"/>
       <c r="P856" s="8"/>
     </row>
     <row r="857" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A857" s="62"/>
-      <c r="E857" s="62"/>
+      <c r="A857" s="50"/>
+      <c r="E857" s="50"/>
       <c r="N857" s="8"/>
       <c r="P857" s="8"/>
     </row>
     <row r="858" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A858" s="62"/>
-      <c r="E858" s="62"/>
+      <c r="A858" s="50"/>
+      <c r="E858" s="50"/>
       <c r="N858" s="8"/>
       <c r="P858" s="8"/>
     </row>
     <row r="859" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A859" s="62"/>
-      <c r="E859" s="62"/>
+      <c r="A859" s="50"/>
+      <c r="E859" s="50"/>
       <c r="N859" s="8"/>
       <c r="P859" s="8"/>
     </row>
     <row r="860" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A860" s="62"/>
-      <c r="E860" s="62"/>
+      <c r="A860" s="50"/>
+      <c r="E860" s="50"/>
       <c r="N860" s="8"/>
       <c r="P860" s="8"/>
     </row>
     <row r="861" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A861" s="62"/>
-      <c r="E861" s="62"/>
+      <c r="A861" s="50"/>
+      <c r="E861" s="50"/>
       <c r="N861" s="8"/>
       <c r="P861" s="8"/>
     </row>
     <row r="862" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A862" s="62"/>
-      <c r="E862" s="62"/>
+      <c r="A862" s="50"/>
+      <c r="E862" s="50"/>
       <c r="N862" s="8"/>
       <c r="P862" s="8"/>
     </row>
     <row r="863" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A863" s="62"/>
-      <c r="E863" s="62"/>
+      <c r="A863" s="50"/>
+      <c r="E863" s="50"/>
       <c r="N863" s="8"/>
       <c r="P863" s="8"/>
     </row>
     <row r="864" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A864" s="62"/>
-      <c r="E864" s="62"/>
+      <c r="A864" s="50"/>
+      <c r="E864" s="50"/>
       <c r="N864" s="8"/>
       <c r="P864" s="8"/>
     </row>
     <row r="865" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A865" s="62"/>
-      <c r="E865" s="62"/>
+      <c r="A865" s="50"/>
+      <c r="E865" s="50"/>
       <c r="N865" s="8"/>
       <c r="P865" s="8"/>
     </row>
     <row r="866" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A866" s="62"/>
-      <c r="E866" s="62"/>
+      <c r="A866" s="50"/>
+      <c r="E866" s="50"/>
       <c r="N866" s="8"/>
       <c r="P866" s="8"/>
     </row>
     <row r="867" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A867" s="62"/>
-      <c r="E867" s="62"/>
+      <c r="A867" s="50"/>
+      <c r="E867" s="50"/>
       <c r="N867" s="8"/>
       <c r="P867" s="8"/>
     </row>
     <row r="868" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A868" s="62"/>
-      <c r="E868" s="62"/>
+      <c r="A868" s="50"/>
+      <c r="E868" s="50"/>
       <c r="N868" s="8"/>
       <c r="P868" s="8"/>
     </row>
     <row r="869" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A869" s="62"/>
-      <c r="E869" s="62"/>
+      <c r="A869" s="50"/>
+      <c r="E869" s="50"/>
       <c r="N869" s="8"/>
       <c r="P869" s="8"/>
     </row>
     <row r="870" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A870" s="62"/>
-      <c r="E870" s="62"/>
+      <c r="A870" s="50"/>
+      <c r="E870" s="50"/>
       <c r="N870" s="8"/>
       <c r="P870" s="8"/>
     </row>
     <row r="871" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A871" s="62"/>
-      <c r="E871" s="62"/>
+      <c r="A871" s="50"/>
+      <c r="E871" s="50"/>
       <c r="N871" s="8"/>
       <c r="P871" s="8"/>
     </row>
     <row r="872" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A872" s="62"/>
-      <c r="E872" s="62"/>
+      <c r="A872" s="50"/>
+      <c r="E872" s="50"/>
       <c r="N872" s="8"/>
       <c r="P872" s="8"/>
     </row>
     <row r="873" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A873" s="62"/>
-      <c r="E873" s="62"/>
+      <c r="A873" s="50"/>
+      <c r="E873" s="50"/>
       <c r="N873" s="8"/>
       <c r="P873" s="8"/>
     </row>
     <row r="874" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A874" s="62"/>
-      <c r="E874" s="62"/>
+      <c r="A874" s="50"/>
+      <c r="E874" s="50"/>
       <c r="N874" s="8"/>
       <c r="P874" s="8"/>
     </row>
     <row r="875" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A875" s="62"/>
-      <c r="E875" s="62"/>
+      <c r="A875" s="50"/>
+      <c r="E875" s="50"/>
       <c r="N875" s="8"/>
       <c r="P875" s="8"/>
     </row>
     <row r="876" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A876" s="62"/>
-      <c r="E876" s="62"/>
+      <c r="A876" s="50"/>
+      <c r="E876" s="50"/>
       <c r="N876" s="8"/>
       <c r="P876" s="8"/>
     </row>
     <row r="877" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A877" s="62"/>
-      <c r="E877" s="62"/>
+      <c r="A877" s="50"/>
+      <c r="E877" s="50"/>
       <c r="N877" s="8"/>
       <c r="P877" s="8"/>
     </row>
     <row r="878" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A878" s="62"/>
-      <c r="E878" s="62"/>
+      <c r="A878" s="50"/>
+      <c r="E878" s="50"/>
       <c r="N878" s="8"/>
       <c r="P878" s="8"/>
     </row>
     <row r="879" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A879" s="62"/>
-      <c r="E879" s="62"/>
+      <c r="A879" s="50"/>
+      <c r="E879" s="50"/>
       <c r="N879" s="8"/>
       <c r="P879" s="8"/>
     </row>
     <row r="880" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A880" s="62"/>
-      <c r="E880" s="62"/>
+      <c r="A880" s="50"/>
+      <c r="E880" s="50"/>
       <c r="N880" s="8"/>
       <c r="P880" s="8"/>
     </row>
     <row r="881" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A881" s="62"/>
-      <c r="E881" s="62"/>
+      <c r="A881" s="50"/>
+      <c r="E881" s="50"/>
       <c r="N881" s="8"/>
       <c r="P881" s="8"/>
     </row>
     <row r="882" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A882" s="62"/>
-      <c r="E882" s="62"/>
+      <c r="A882" s="50"/>
+      <c r="E882" s="50"/>
       <c r="N882" s="8"/>
       <c r="P882" s="8"/>
     </row>
     <row r="883" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A883" s="62"/>
-      <c r="E883" s="62"/>
+      <c r="A883" s="50"/>
+      <c r="E883" s="50"/>
       <c r="N883" s="8"/>
       <c r="P883" s="8"/>
     </row>
     <row r="884" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A884" s="62"/>
-      <c r="E884" s="62"/>
+      <c r="A884" s="50"/>
+      <c r="E884" s="50"/>
       <c r="N884" s="8"/>
       <c r="P884" s="8"/>
     </row>
     <row r="885" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A885" s="62"/>
-      <c r="E885" s="62"/>
+      <c r="A885" s="50"/>
+      <c r="E885" s="50"/>
       <c r="N885" s="8"/>
       <c r="P885" s="8"/>
     </row>
     <row r="886" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A886" s="62"/>
-      <c r="E886" s="62"/>
+      <c r="A886" s="50"/>
+      <c r="E886" s="50"/>
       <c r="N886" s="8"/>
       <c r="P886" s="8"/>
     </row>
     <row r="887" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A887" s="62"/>
-      <c r="E887" s="62"/>
+      <c r="A887" s="50"/>
+      <c r="E887" s="50"/>
       <c r="N887" s="8"/>
       <c r="P887" s="8"/>
     </row>
     <row r="888" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A888" s="62"/>
-      <c r="E888" s="62"/>
+      <c r="A888" s="50"/>
+      <c r="E888" s="50"/>
       <c r="N888" s="8"/>
       <c r="P888" s="8"/>
     </row>
     <row r="889" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A889" s="62"/>
-      <c r="E889" s="62"/>
+      <c r="A889" s="50"/>
+      <c r="E889" s="50"/>
       <c r="N889" s="8"/>
       <c r="P889" s="8"/>
     </row>
     <row r="890" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A890" s="62"/>
-      <c r="E890" s="62"/>
+      <c r="A890" s="50"/>
+      <c r="E890" s="50"/>
       <c r="N890" s="8"/>
       <c r="P890" s="8"/>
     </row>
     <row r="891" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A891" s="62"/>
-      <c r="E891" s="62"/>
+      <c r="A891" s="50"/>
+      <c r="E891" s="50"/>
       <c r="N891" s="8"/>
       <c r="P891" s="8"/>
     </row>
     <row r="892" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A892" s="62"/>
-      <c r="E892" s="62"/>
+      <c r="A892" s="50"/>
+      <c r="E892" s="50"/>
       <c r="N892" s="8"/>
       <c r="P892" s="8"/>
     </row>
     <row r="893" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A893" s="62"/>
-      <c r="E893" s="62"/>
+      <c r="A893" s="50"/>
+      <c r="E893" s="50"/>
       <c r="N893" s="8"/>
       <c r="P893" s="8"/>
     </row>
     <row r="894" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A894" s="62"/>
-      <c r="E894" s="62"/>
+      <c r="A894" s="50"/>
+      <c r="E894" s="50"/>
       <c r="N894" s="8"/>
       <c r="P894" s="8"/>
     </row>
     <row r="895" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A895" s="62"/>
-      <c r="E895" s="62"/>
+      <c r="A895" s="50"/>
+      <c r="E895" s="50"/>
       <c r="N895" s="8"/>
       <c r="P895" s="8"/>
     </row>
     <row r="896" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A896" s="62"/>
-      <c r="E896" s="62"/>
+      <c r="A896" s="50"/>
+      <c r="E896" s="50"/>
       <c r="N896" s="8"/>
       <c r="P896" s="8"/>
     </row>
     <row r="897" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A897" s="62"/>
-      <c r="E897" s="62"/>
+      <c r="A897" s="50"/>
+      <c r="E897" s="50"/>
       <c r="N897" s="8"/>
       <c r="P897" s="8"/>
     </row>
     <row r="898" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A898" s="62"/>
-      <c r="E898" s="62"/>
+      <c r="A898" s="50"/>
+      <c r="E898" s="50"/>
       <c r="N898" s="8"/>
       <c r="P898" s="8"/>
     </row>
     <row r="899" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A899" s="62"/>
-      <c r="E899" s="62"/>
+      <c r="A899" s="50"/>
+      <c r="E899" s="50"/>
       <c r="N899" s="8"/>
       <c r="P899" s="8"/>
     </row>
     <row r="900" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A900" s="62"/>
-      <c r="E900" s="62"/>
+      <c r="A900" s="50"/>
+      <c r="E900" s="50"/>
       <c r="N900" s="8"/>
       <c r="P900" s="8"/>
     </row>
     <row r="901" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A901" s="62"/>
-      <c r="E901" s="62"/>
+      <c r="A901" s="50"/>
+      <c r="E901" s="50"/>
       <c r="N901" s="8"/>
       <c r="P901" s="8"/>
     </row>
     <row r="902" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A902" s="62"/>
-      <c r="E902" s="62"/>
+      <c r="A902" s="50"/>
+      <c r="E902" s="50"/>
       <c r="N902" s="8"/>
       <c r="P902" s="8"/>
     </row>
     <row r="903" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A903" s="62"/>
-      <c r="E903" s="62"/>
+      <c r="A903" s="50"/>
+      <c r="E903" s="50"/>
       <c r="N903" s="8"/>
       <c r="P903" s="8"/>
     </row>
     <row r="904" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A904" s="62"/>
-      <c r="E904" s="62"/>
+      <c r="A904" s="50"/>
+      <c r="E904" s="50"/>
       <c r="N904" s="8"/>
       <c r="P904" s="8"/>
     </row>
     <row r="905" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A905" s="62"/>
-      <c r="E905" s="62"/>
+      <c r="A905" s="50"/>
+      <c r="E905" s="50"/>
       <c r="N905" s="8"/>
       <c r="P905" s="8"/>
     </row>
     <row r="906" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A906" s="62"/>
-      <c r="E906" s="62"/>
+      <c r="A906" s="50"/>
+      <c r="E906" s="50"/>
       <c r="N906" s="8"/>
       <c r="P906" s="8"/>
     </row>
     <row r="907" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A907" s="62"/>
-      <c r="E907" s="62"/>
+      <c r="A907" s="50"/>
+      <c r="E907" s="50"/>
       <c r="N907" s="8"/>
       <c r="P907" s="8"/>
     </row>
     <row r="908" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A908" s="62"/>
-      <c r="E908" s="62"/>
+      <c r="A908" s="50"/>
+      <c r="E908" s="50"/>
       <c r="N908" s="8"/>
       <c r="P908" s="8"/>
     </row>
     <row r="909" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A909" s="62"/>
-      <c r="E909" s="62"/>
+      <c r="A909" s="50"/>
+      <c r="E909" s="50"/>
       <c r="N909" s="8"/>
       <c r="P909" s="8"/>
     </row>
     <row r="910" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A910" s="62"/>
-      <c r="E910" s="62"/>
+      <c r="A910" s="50"/>
+      <c r="E910" s="50"/>
       <c r="N910" s="8"/>
       <c r="P910" s="8"/>
     </row>
     <row r="911" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A911" s="62"/>
-      <c r="E911" s="62"/>
+      <c r="A911" s="50"/>
+      <c r="E911" s="50"/>
       <c r="N911" s="8"/>
       <c r="P911" s="8"/>
     </row>
     <row r="912" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A912" s="62"/>
-      <c r="E912" s="62"/>
+      <c r="A912" s="50"/>
+      <c r="E912" s="50"/>
       <c r="N912" s="8"/>
       <c r="P912" s="8"/>
     </row>
     <row r="913" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A913" s="62"/>
-      <c r="E913" s="62"/>
+      <c r="A913" s="50"/>
+      <c r="E913" s="50"/>
       <c r="N913" s="8"/>
       <c r="P913" s="8"/>
     </row>
     <row r="914" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A914" s="62"/>
-      <c r="E914" s="62"/>
+      <c r="A914" s="50"/>
+      <c r="E914" s="50"/>
       <c r="N914" s="8"/>
       <c r="P914" s="8"/>
     </row>
     <row r="915" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A915" s="62"/>
-      <c r="E915" s="62"/>
+      <c r="A915" s="50"/>
+      <c r="E915" s="50"/>
       <c r="N915" s="8"/>
       <c r="P915" s="8"/>
     </row>
     <row r="916" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A916" s="62"/>
-      <c r="E916" s="62"/>
+      <c r="A916" s="50"/>
+      <c r="E916" s="50"/>
       <c r="N916" s="8"/>
       <c r="P916" s="8"/>
     </row>
     <row r="917" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A917" s="62"/>
-      <c r="E917" s="62"/>
+      <c r="A917" s="50"/>
+      <c r="E917" s="50"/>
       <c r="N917" s="8"/>
       <c r="P917" s="8"/>
     </row>
     <row r="918" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A918" s="62"/>
-      <c r="E918" s="62"/>
+      <c r="A918" s="50"/>
+      <c r="E918" s="50"/>
       <c r="N918" s="8"/>
       <c r="P918" s="8"/>
     </row>
     <row r="919" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A919" s="62"/>
-      <c r="E919" s="62"/>
+      <c r="A919" s="50"/>
+      <c r="E919" s="50"/>
       <c r="N919" s="8"/>
       <c r="P919" s="8"/>
     </row>
     <row r="920" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A920" s="62"/>
-      <c r="E920" s="62"/>
+      <c r="A920" s="50"/>
+      <c r="E920" s="50"/>
       <c r="N920" s="8"/>
       <c r="P920" s="8"/>
     </row>
     <row r="921" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A921" s="62"/>
-      <c r="E921" s="62"/>
+      <c r="A921" s="50"/>
+      <c r="E921" s="50"/>
       <c r="N921" s="8"/>
       <c r="P921" s="8"/>
     </row>
     <row r="922" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A922" s="62"/>
-      <c r="E922" s="62"/>
+      <c r="A922" s="50"/>
+      <c r="E922" s="50"/>
       <c r="N922" s="8"/>
       <c r="P922" s="8"/>
     </row>
     <row r="923" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A923" s="62"/>
-      <c r="E923" s="62"/>
+      <c r="A923" s="50"/>
+      <c r="E923" s="50"/>
       <c r="N923" s="8"/>
       <c r="P923" s="8"/>
     </row>
     <row r="924" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A924" s="62"/>
-      <c r="E924" s="62"/>
+      <c r="A924" s="50"/>
+      <c r="E924" s="50"/>
       <c r="N924" s="8"/>
       <c r="P924" s="8"/>
     </row>
     <row r="925" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A925" s="62"/>
-      <c r="E925" s="62"/>
+      <c r="A925" s="50"/>
+      <c r="E925" s="50"/>
       <c r="N925" s="8"/>
       <c r="P925" s="8"/>
     </row>
     <row r="926" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A926" s="62"/>
-      <c r="E926" s="62"/>
+      <c r="A926" s="50"/>
+      <c r="E926" s="50"/>
       <c r="N926" s="8"/>
       <c r="P926" s="8"/>
     </row>
     <row r="927" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A927" s="62"/>
-      <c r="E927" s="62"/>
+      <c r="A927" s="50"/>
+      <c r="E927" s="50"/>
       <c r="N927" s="8"/>
       <c r="P927" s="8"/>
     </row>
     <row r="928" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A928" s="62"/>
-      <c r="E928" s="62"/>
+      <c r="A928" s="50"/>
+      <c r="E928" s="50"/>
       <c r="N928" s="8"/>
       <c r="P928" s="8"/>
     </row>
     <row r="929" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A929" s="62"/>
-      <c r="E929" s="62"/>
+      <c r="A929" s="50"/>
+      <c r="E929" s="50"/>
       <c r="N929" s="8"/>
       <c r="P929" s="8"/>
     </row>
     <row r="930" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A930" s="62"/>
-      <c r="E930" s="62"/>
+      <c r="A930" s="50"/>
+      <c r="E930" s="50"/>
       <c r="N930" s="8"/>
       <c r="P930" s="8"/>
     </row>
     <row r="931" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A931" s="62"/>
-      <c r="E931" s="62"/>
+      <c r="A931" s="50"/>
+      <c r="E931" s="50"/>
       <c r="N931" s="8"/>
       <c r="P931" s="8"/>
     </row>
     <row r="932" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A932" s="62"/>
-      <c r="E932" s="62"/>
+      <c r="A932" s="50"/>
+      <c r="E932" s="50"/>
       <c r="N932" s="8"/>
       <c r="P932" s="8"/>
     </row>
     <row r="933" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A933" s="62"/>
-      <c r="E933" s="62"/>
+      <c r="A933" s="50"/>
+      <c r="E933" s="50"/>
       <c r="N933" s="8"/>
       <c r="P933" s="8"/>
     </row>
     <row r="934" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A934" s="62"/>
-      <c r="E934" s="62"/>
+      <c r="A934" s="50"/>
+      <c r="E934" s="50"/>
       <c r="N934" s="8"/>
       <c r="P934" s="8"/>
     </row>
     <row r="935" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A935" s="62"/>
-      <c r="E935" s="62"/>
+      <c r="A935" s="50"/>
+      <c r="E935" s="50"/>
       <c r="N935" s="8"/>
       <c r="P935" s="8"/>
     </row>
     <row r="936" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A936" s="62"/>
-      <c r="E936" s="62"/>
+      <c r="A936" s="50"/>
+      <c r="E936" s="50"/>
       <c r="N936" s="8"/>
       <c r="P936" s="8"/>
     </row>
     <row r="937" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A937" s="62"/>
-      <c r="E937" s="62"/>
+      <c r="A937" s="50"/>
+      <c r="E937" s="50"/>
       <c r="N937" s="8"/>
       <c r="P937" s="8"/>
     </row>
     <row r="938" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A938" s="62"/>
-      <c r="E938" s="62"/>
+      <c r="A938" s="50"/>
+      <c r="E938" s="50"/>
       <c r="N938" s="8"/>
       <c r="P938" s="8"/>
     </row>
     <row r="939" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A939" s="62"/>
-      <c r="E939" s="62"/>
+      <c r="A939" s="50"/>
+      <c r="E939" s="50"/>
       <c r="N939" s="8"/>
       <c r="P939" s="8"/>
     </row>
     <row r="940" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A940" s="62"/>
-      <c r="E940" s="62"/>
+      <c r="A940" s="50"/>
+      <c r="E940" s="50"/>
       <c r="N940" s="8"/>
       <c r="P940" s="8"/>
     </row>
     <row r="941" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A941" s="62"/>
-      <c r="E941" s="62"/>
+      <c r="A941" s="50"/>
+      <c r="E941" s="50"/>
       <c r="N941" s="8"/>
       <c r="P941" s="8"/>
     </row>
     <row r="942" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A942" s="62"/>
-      <c r="E942" s="62"/>
+      <c r="A942" s="50"/>
+      <c r="E942" s="50"/>
       <c r="N942" s="8"/>
       <c r="P942" s="8"/>
     </row>
     <row r="943" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A943" s="62"/>
-      <c r="E943" s="62"/>
+      <c r="A943" s="50"/>
+      <c r="E943" s="50"/>
       <c r="N943" s="8"/>
       <c r="P943" s="8"/>
     </row>
     <row r="944" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A944" s="62"/>
-      <c r="E944" s="62"/>
+      <c r="A944" s="50"/>
+      <c r="E944" s="50"/>
       <c r="N944" s="8"/>
       <c r="P944" s="8"/>
     </row>
     <row r="945" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A945" s="62"/>
-      <c r="E945" s="62"/>
+      <c r="A945" s="50"/>
+      <c r="E945" s="50"/>
       <c r="N945" s="8"/>
       <c r="P945" s="8"/>
     </row>
     <row r="946" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A946" s="62"/>
-      <c r="E946" s="62"/>
+      <c r="A946" s="50"/>
+      <c r="E946" s="50"/>
       <c r="N946" s="8"/>
       <c r="P946" s="8"/>
     </row>
     <row r="947" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A947" s="62"/>
-      <c r="E947" s="62"/>
+      <c r="A947" s="50"/>
+      <c r="E947" s="50"/>
       <c r="N947" s="8"/>
       <c r="P947" s="8"/>
     </row>
     <row r="948" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A948" s="62"/>
-      <c r="E948" s="62"/>
+      <c r="A948" s="50"/>
+      <c r="E948" s="50"/>
       <c r="N948" s="8"/>
       <c r="P948" s="8"/>
     </row>
     <row r="949" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A949" s="62"/>
-      <c r="E949" s="62"/>
+      <c r="A949" s="50"/>
+      <c r="E949" s="50"/>
       <c r="N949" s="8"/>
       <c r="P949" s="8"/>
     </row>
     <row r="950" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A950" s="62"/>
-      <c r="E950" s="62"/>
+      <c r="A950" s="50"/>
+      <c r="E950" s="50"/>
       <c r="N950" s="8"/>
       <c r="P950" s="8"/>
     </row>
     <row r="951" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A951" s="62"/>
-      <c r="E951" s="62"/>
+      <c r="A951" s="50"/>
+      <c r="E951" s="50"/>
       <c r="N951" s="8"/>
       <c r="P951" s="8"/>
     </row>
     <row r="952" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A952" s="62"/>
-      <c r="E952" s="62"/>
+      <c r="A952" s="50"/>
+      <c r="E952" s="50"/>
       <c r="N952" s="8"/>
       <c r="P952" s="8"/>
     </row>
     <row r="953" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A953" s="62"/>
-      <c r="E953" s="62"/>
+      <c r="A953" s="50"/>
+      <c r="E953" s="50"/>
       <c r="N953" s="8"/>
       <c r="P953" s="8"/>
     </row>
     <row r="954" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A954" s="62"/>
-      <c r="E954" s="62"/>
+      <c r="A954" s="50"/>
+      <c r="E954" s="50"/>
       <c r="N954" s="8"/>
       <c r="P954" s="8"/>
     </row>
     <row r="955" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A955" s="62"/>
-      <c r="E955" s="62"/>
+      <c r="A955" s="50"/>
+      <c r="E955" s="50"/>
       <c r="N955" s="8"/>
       <c r="P955" s="8"/>
     </row>
     <row r="956" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A956" s="62"/>
-      <c r="E956" s="62"/>
+      <c r="A956" s="50"/>
+      <c r="E956" s="50"/>
       <c r="N956" s="8"/>
       <c r="P956" s="8"/>
     </row>
     <row r="957" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A957" s="62"/>
-      <c r="E957" s="62"/>
+      <c r="A957" s="50"/>
+      <c r="E957" s="50"/>
       <c r="N957" s="8"/>
       <c r="P957" s="8"/>
     </row>
     <row r="958" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A958" s="62"/>
-      <c r="E958" s="62"/>
+      <c r="A958" s="50"/>
+      <c r="E958" s="50"/>
       <c r="N958" s="8"/>
       <c r="P958" s="8"/>
     </row>
     <row r="959" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A959" s="62"/>
-      <c r="E959" s="62"/>
+      <c r="A959" s="50"/>
+      <c r="E959" s="50"/>
       <c r="N959" s="8"/>
       <c r="P959" s="8"/>
     </row>
     <row r="960" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A960" s="62"/>
-      <c r="E960" s="62"/>
+      <c r="A960" s="50"/>
+      <c r="E960" s="50"/>
       <c r="N960" s="8"/>
       <c r="P960" s="8"/>
     </row>
     <row r="961" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A961" s="62"/>
-      <c r="E961" s="62"/>
+      <c r="A961" s="50"/>
+      <c r="E961" s="50"/>
       <c r="N961" s="8"/>
       <c r="P961" s="8"/>
     </row>
     <row r="962" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A962" s="62"/>
-      <c r="E962" s="62"/>
+      <c r="A962" s="50"/>
+      <c r="E962" s="50"/>
       <c r="N962" s="8"/>
       <c r="P962" s="8"/>
     </row>
     <row r="963" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A963" s="62"/>
-      <c r="E963" s="62"/>
+      <c r="A963" s="50"/>
+      <c r="E963" s="50"/>
       <c r="N963" s="8"/>
       <c r="P963" s="8"/>
     </row>
     <row r="964" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A964" s="62"/>
-      <c r="E964" s="62"/>
+      <c r="A964" s="50"/>
+      <c r="E964" s="50"/>
       <c r="N964" s="8"/>
       <c r="P964" s="8"/>
     </row>
     <row r="965" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A965" s="62"/>
-      <c r="E965" s="62"/>
+      <c r="A965" s="50"/>
+      <c r="E965" s="50"/>
       <c r="N965" s="8"/>
       <c r="P965" s="8"/>
     </row>
     <row r="966" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A966" s="62"/>
-      <c r="E966" s="62"/>
+      <c r="A966" s="50"/>
+      <c r="E966" s="50"/>
       <c r="N966" s="8"/>
       <c r="P966" s="8"/>
     </row>
     <row r="967" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A967" s="62"/>
-      <c r="E967" s="62"/>
+      <c r="A967" s="50"/>
+      <c r="E967" s="50"/>
       <c r="N967" s="8"/>
       <c r="P967" s="8"/>
     </row>
     <row r="968" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A968" s="62"/>
-      <c r="E968" s="62"/>
+      <c r="A968" s="50"/>
+      <c r="E968" s="50"/>
       <c r="N968" s="8"/>
       <c r="P968" s="8"/>
     </row>
     <row r="969" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A969" s="62"/>
-      <c r="E969" s="62"/>
+      <c r="A969" s="50"/>
+      <c r="E969" s="50"/>
       <c r="N969" s="8"/>
       <c r="P969" s="8"/>
     </row>
     <row r="970" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A970" s="62"/>
-      <c r="E970" s="62"/>
+      <c r="A970" s="50"/>
+      <c r="E970" s="50"/>
       <c r="N970" s="8"/>
       <c r="P970" s="8"/>
     </row>
     <row r="971" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A971" s="62"/>
-      <c r="E971" s="62"/>
+      <c r="A971" s="50"/>
+      <c r="E971" s="50"/>
       <c r="N971" s="8"/>
       <c r="P971" s="8"/>
     </row>
     <row r="972" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A972" s="62"/>
-      <c r="E972" s="62"/>
+      <c r="A972" s="50"/>
+      <c r="E972" s="50"/>
       <c r="N972" s="8"/>
       <c r="P972" s="8"/>
     </row>
     <row r="973" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A973" s="62"/>
-      <c r="E973" s="62"/>
+      <c r="A973" s="50"/>
+      <c r="E973" s="50"/>
       <c r="N973" s="8"/>
       <c r="P973" s="8"/>
     </row>
     <row r="974" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A974" s="62"/>
-      <c r="E974" s="62"/>
+      <c r="A974" s="50"/>
+      <c r="E974" s="50"/>
       <c r="N974" s="8"/>
       <c r="P974" s="8"/>
     </row>
     <row r="975" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A975" s="62"/>
-      <c r="E975" s="62"/>
+      <c r="A975" s="50"/>
+      <c r="E975" s="50"/>
       <c r="N975" s="8"/>
       <c r="P975" s="8"/>
     </row>
     <row r="976" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A976" s="62"/>
-      <c r="E976" s="62"/>
+      <c r="A976" s="50"/>
+      <c r="E976" s="50"/>
       <c r="N976" s="8"/>
       <c r="P976" s="8"/>
     </row>
     <row r="977" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A977" s="62"/>
-      <c r="E977" s="62"/>
+      <c r="A977" s="50"/>
+      <c r="E977" s="50"/>
       <c r="N977" s="8"/>
       <c r="P977" s="8"/>
     </row>
     <row r="978" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A978" s="62"/>
-      <c r="E978" s="62"/>
+      <c r="A978" s="50"/>
+      <c r="E978" s="50"/>
       <c r="N978" s="8"/>
       <c r="P978" s="8"/>
     </row>
     <row r="979" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A979" s="62"/>
-      <c r="E979" s="62"/>
+      <c r="A979" s="50"/>
+      <c r="E979" s="50"/>
       <c r="N979" s="8"/>
       <c r="P979" s="8"/>
     </row>
     <row r="980" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A980" s="62"/>
-      <c r="E980" s="62"/>
+      <c r="A980" s="50"/>
+      <c r="E980" s="50"/>
       <c r="N980" s="8"/>
       <c r="P980" s="8"/>
     </row>
     <row r="981" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A981" s="62"/>
-      <c r="E981" s="62"/>
+      <c r="A981" s="50"/>
+      <c r="E981" s="50"/>
       <c r="N981" s="8"/>
       <c r="P981" s="8"/>
     </row>
     <row r="982" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A982" s="62"/>
-      <c r="E982" s="62"/>
+      <c r="A982" s="50"/>
+      <c r="E982" s="50"/>
       <c r="N982" s="8"/>
       <c r="P982" s="8"/>
     </row>
     <row r="983" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A983" s="62"/>
-      <c r="E983" s="62"/>
+      <c r="A983" s="50"/>
+      <c r="E983" s="50"/>
       <c r="N983" s="8"/>
       <c r="P983" s="8"/>
     </row>
     <row r="984" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A984" s="62"/>
-      <c r="E984" s="62"/>
+      <c r="A984" s="50"/>
+      <c r="E984" s="50"/>
       <c r="N984" s="8"/>
       <c r="P984" s="8"/>
     </row>
     <row r="985" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A985" s="62"/>
-      <c r="E985" s="62"/>
+      <c r="A985" s="50"/>
+      <c r="E985" s="50"/>
       <c r="N985" s="8"/>
       <c r="P985" s="8"/>
     </row>
     <row r="986" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A986" s="62"/>
-      <c r="E986" s="62"/>
+      <c r="A986" s="50"/>
+      <c r="E986" s="50"/>
       <c r="N986" s="8"/>
       <c r="P986" s="8"/>
     </row>
     <row r="987" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A987" s="62"/>
-      <c r="E987" s="62"/>
+      <c r="A987" s="50"/>
+      <c r="E987" s="50"/>
       <c r="N987" s="8"/>
       <c r="P987" s="8"/>
     </row>
     <row r="988" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A988" s="62"/>
-      <c r="E988" s="62"/>
+      <c r="A988" s="50"/>
+      <c r="E988" s="50"/>
       <c r="N988" s="8"/>
       <c r="P988" s="8"/>
     </row>
     <row r="989" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A989" s="62"/>
-      <c r="E989" s="62"/>
+      <c r="A989" s="50"/>
+      <c r="E989" s="50"/>
       <c r="N989" s="8"/>
       <c r="P989" s="8"/>
     </row>
     <row r="990" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A990" s="62"/>
-      <c r="E990" s="62"/>
+      <c r="A990" s="50"/>
+      <c r="E990" s="50"/>
       <c r="N990" s="8"/>
       <c r="P990" s="8"/>
     </row>
     <row r="991" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A991" s="62"/>
-      <c r="E991" s="62"/>
+      <c r="A991" s="50"/>
+      <c r="E991" s="50"/>
       <c r="N991" s="8"/>
       <c r="P991" s="8"/>
     </row>
     <row r="992" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A992" s="62"/>
-      <c r="E992" s="62"/>
+      <c r="A992" s="50"/>
+      <c r="E992" s="50"/>
       <c r="N992" s="8"/>
       <c r="P992" s="8"/>
     </row>
     <row r="993" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A993" s="62"/>
-      <c r="E993" s="62"/>
+      <c r="A993" s="50"/>
+      <c r="E993" s="50"/>
       <c r="N993" s="8"/>
       <c r="P993" s="8"/>
     </row>
     <row r="994" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A994" s="62"/>
-      <c r="E994" s="62"/>
+      <c r="A994" s="50"/>
+      <c r="E994" s="50"/>
       <c r="N994" s="8"/>
       <c r="P994" s="8"/>
     </row>
     <row r="995" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A995" s="62"/>
-      <c r="E995" s="62"/>
+      <c r="A995" s="50"/>
+      <c r="E995" s="50"/>
       <c r="N995" s="8"/>
       <c r="P995" s="8"/>
     </row>
     <row r="996" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A996" s="62"/>
-      <c r="E996" s="62"/>
+      <c r="A996" s="50"/>
+      <c r="E996" s="50"/>
       <c r="N996" s="8"/>
       <c r="P996" s="8"/>
     </row>
     <row r="997" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A997" s="62"/>
-      <c r="E997" s="62"/>
+      <c r="A997" s="50"/>
+      <c r="E997" s="50"/>
       <c r="N997" s="8"/>
       <c r="P997" s="8"/>
     </row>
     <row r="998" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A998" s="62"/>
-      <c r="E998" s="62"/>
+      <c r="A998" s="50"/>
+      <c r="E998" s="50"/>
       <c r="N998" s="8"/>
       <c r="P998" s="8"/>
     </row>
     <row r="999" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A999" s="62"/>
-      <c r="E999" s="62"/>
+      <c r="A999" s="50"/>
+      <c r="E999" s="50"/>
       <c r="N999" s="8"/>
       <c r="P999" s="8"/>
     </row>
     <row r="1000" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1000" s="62"/>
-      <c r="E1000" s="62"/>
+      <c r="A1000" s="50"/>
+      <c r="E1000" s="50"/>
       <c r="N1000" s="8"/>
       <c r="P1000" s="8"/>
     </row>
     <row r="1001" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1001" s="62"/>
-      <c r="E1001" s="62"/>
+      <c r="A1001" s="50"/>
+      <c r="E1001" s="50"/>
       <c r="N1001" s="8"/>
       <c r="P1001" s="8"/>
     </row>
     <row r="1002" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1002" s="62"/>
-      <c r="E1002" s="62"/>
+      <c r="A1002" s="50"/>
+      <c r="E1002" s="50"/>
       <c r="N1002" s="8"/>
       <c r="P1002" s="8"/>
     </row>
     <row r="1003" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1003" s="62"/>
-      <c r="E1003" s="62"/>
+      <c r="A1003" s="50"/>
+      <c r="E1003" s="50"/>
       <c r="N1003" s="8"/>
       <c r="P1003" s="8"/>
     </row>
     <row r="1004" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1004" s="62"/>
-      <c r="E1004" s="62"/>
+      <c r="A1004" s="50"/>
+      <c r="E1004" s="50"/>
       <c r="N1004" s="8"/>
       <c r="P1004" s="8"/>
     </row>
     <row r="1005" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1005" s="62"/>
-      <c r="E1005" s="62"/>
+      <c r="A1005" s="50"/>
+      <c r="E1005" s="50"/>
       <c r="N1005" s="8"/>
       <c r="P1005" s="8"/>
     </row>
     <row r="1006" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1006" s="62"/>
-      <c r="E1006" s="62"/>
+      <c r="A1006" s="50"/>
+      <c r="E1006" s="50"/>
       <c r="N1006" s="8"/>
       <c r="P1006" s="8"/>
     </row>
     <row r="1007" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1007" s="62"/>
-      <c r="E1007" s="62"/>
+      <c r="A1007" s="50"/>
+      <c r="E1007" s="50"/>
       <c r="N1007" s="8"/>
       <c r="P1007" s="8"/>
     </row>
     <row r="1008" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1008" s="62"/>
-      <c r="E1008" s="62"/>
+      <c r="A1008" s="50"/>
+      <c r="E1008" s="50"/>
       <c r="N1008" s="8"/>
       <c r="P1008" s="8"/>
     </row>
     <row r="1009" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1009" s="62"/>
-      <c r="E1009" s="62"/>
+      <c r="A1009" s="50"/>
+      <c r="E1009" s="50"/>
       <c r="N1009" s="8"/>
       <c r="P1009" s="8"/>
     </row>
     <row r="1010" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1010" s="62"/>
-      <c r="E1010" s="62"/>
+      <c r="A1010" s="50"/>
+      <c r="E1010" s="50"/>
       <c r="N1010" s="8"/>
       <c r="P1010" s="8"/>
     </row>
     <row r="1011" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1011" s="62"/>
-      <c r="E1011" s="62"/>
+      <c r="A1011" s="50"/>
+      <c r="E1011" s="50"/>
       <c r="N1011" s="8"/>
       <c r="P1011" s="8"/>
     </row>
     <row r="1012" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1012" s="62"/>
-      <c r="E1012" s="62"/>
+      <c r="A1012" s="50"/>
+      <c r="E1012" s="50"/>
       <c r="N1012" s="8"/>
       <c r="P1012" s="8"/>
     </row>
     <row r="1013" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1013" s="62"/>
-      <c r="E1013" s="62"/>
+      <c r="A1013" s="50"/>
+      <c r="E1013" s="50"/>
       <c r="N1013" s="8"/>
       <c r="P1013" s="8"/>
     </row>
     <row r="1014" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1014" s="62"/>
-      <c r="E1014" s="62"/>
+      <c r="A1014" s="50"/>
+      <c r="E1014" s="50"/>
       <c r="N1014" s="8"/>
       <c r="P1014" s="8"/>
     </row>
     <row r="1015" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1015" s="62"/>
-      <c r="E1015" s="62"/>
+      <c r="A1015" s="50"/>
+      <c r="E1015" s="50"/>
       <c r="N1015" s="8"/>
       <c r="P1015" s="8"/>
     </row>
     <row r="1016" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1016" s="62"/>
-      <c r="E1016" s="62"/>
+      <c r="A1016" s="50"/>
+      <c r="E1016" s="50"/>
       <c r="N1016" s="8"/>
       <c r="P1016" s="8"/>
     </row>
     <row r="1017" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1017" s="62"/>
-      <c r="E1017" s="62"/>
+      <c r="A1017" s="50"/>
+      <c r="E1017" s="50"/>
       <c r="N1017" s="8"/>
       <c r="P1017" s="8"/>
     </row>
     <row r="1018" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1018" s="62"/>
-      <c r="E1018" s="62"/>
+      <c r="A1018" s="50"/>
+      <c r="E1018" s="50"/>
       <c r="N1018" s="8"/>
       <c r="P1018" s="8"/>
     </row>
     <row r="1019" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1019" s="62"/>
-      <c r="E1019" s="62"/>
+      <c r="A1019" s="50"/>
+      <c r="E1019" s="50"/>
       <c r="N1019" s="8"/>
       <c r="P1019" s="8"/>
     </row>
     <row r="1020" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1020" s="62"/>
-      <c r="E1020" s="62"/>
+      <c r="A1020" s="50"/>
+      <c r="E1020" s="50"/>
       <c r="N1020" s="8"/>
       <c r="P1020" s="8"/>
     </row>
     <row r="1021" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1021" s="62"/>
-      <c r="E1021" s="62"/>
+      <c r="A1021" s="50"/>
+      <c r="E1021" s="50"/>
       <c r="N1021" s="8"/>
       <c r="P1021" s="8"/>
     </row>
     <row r="1022" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1022" s="62"/>
-      <c r="E1022" s="62"/>
+      <c r="A1022" s="50"/>
+      <c r="E1022" s="50"/>
       <c r="N1022" s="8"/>
       <c r="P1022" s="8"/>
     </row>
     <row r="1023" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1023" s="62"/>
-      <c r="E1023" s="62"/>
+      <c r="A1023" s="50"/>
+      <c r="E1023" s="50"/>
       <c r="N1023" s="8"/>
       <c r="P1023" s="8"/>
     </row>
     <row r="1024" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1024" s="62"/>
-      <c r="E1024" s="62"/>
+      <c r="A1024" s="50"/>
+      <c r="E1024" s="50"/>
       <c r="N1024" s="8"/>
       <c r="P1024" s="8"/>
     </row>
     <row r="1025" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1025" s="62"/>
-      <c r="E1025" s="62"/>
+      <c r="A1025" s="50"/>
+      <c r="E1025" s="50"/>
       <c r="N1025" s="8"/>
       <c r="P1025" s="8"/>
     </row>
     <row r="1026" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1026" s="62"/>
-      <c r="E1026" s="62"/>
+      <c r="A1026" s="50"/>
+      <c r="E1026" s="50"/>
       <c r="N1026" s="8"/>
       <c r="P1026" s="8"/>
     </row>
     <row r="1027" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1027" s="62"/>
-      <c r="E1027" s="62"/>
+      <c r="A1027" s="50"/>
+      <c r="E1027" s="50"/>
       <c r="N1027" s="8"/>
       <c r="P1027" s="8"/>
     </row>
     <row r="1028" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1028" s="62"/>
-      <c r="E1028" s="62"/>
+      <c r="A1028" s="50"/>
+      <c r="E1028" s="50"/>
       <c r="N1028" s="8"/>
       <c r="P1028" s="8"/>
     </row>
     <row r="1029" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1029" s="62"/>
-      <c r="E1029" s="62"/>
+      <c r="A1029" s="50"/>
+      <c r="E1029" s="50"/>
       <c r="N1029" s="8"/>
       <c r="P1029" s="8"/>
     </row>
     <row r="1030" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1030" s="62"/>
-      <c r="E1030" s="62"/>
+      <c r="A1030" s="50"/>
+      <c r="E1030" s="50"/>
       <c r="N1030" s="8"/>
       <c r="P1030" s="8"/>
     </row>
     <row r="1031" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1031" s="62"/>
-      <c r="E1031" s="62"/>
+      <c r="A1031" s="50"/>
+      <c r="E1031" s="50"/>
       <c r="N1031" s="8"/>
       <c r="P1031" s="8"/>
     </row>
     <row r="1032" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1032" s="62"/>
-      <c r="E1032" s="62"/>
+      <c r="A1032" s="50"/>
+      <c r="E1032" s="50"/>
       <c r="N1032" s="8"/>
       <c r="P1032" s="8"/>
     </row>
     <row r="1033" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1033" s="62"/>
-      <c r="E1033" s="62"/>
+      <c r="A1033" s="50"/>
+      <c r="E1033" s="50"/>
       <c r="N1033" s="8"/>
       <c r="P1033" s="8"/>
     </row>
     <row r="1034" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1034" s="62"/>
-      <c r="E1034" s="62"/>
+      <c r="A1034" s="50"/>
+      <c r="E1034" s="50"/>
       <c r="N1034" s="8"/>
       <c r="P1034" s="8"/>
     </row>
     <row r="1035" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1035" s="62"/>
-      <c r="E1035" s="62"/>
+      <c r="A1035" s="50"/>
+      <c r="E1035" s="50"/>
       <c r="N1035" s="8"/>
       <c r="P1035" s="8"/>
     </row>
     <row r="1036" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1036" s="62"/>
-      <c r="E1036" s="62"/>
+      <c r="A1036" s="50"/>
+      <c r="E1036" s="50"/>
       <c r="N1036" s="8"/>
       <c r="P1036" s="8"/>
     </row>
     <row r="1037" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1037" s="62"/>
-      <c r="E1037" s="62"/>
+      <c r="A1037" s="50"/>
+      <c r="E1037" s="50"/>
       <c r="N1037" s="8"/>
       <c r="P1037" s="8"/>
     </row>
     <row r="1038" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1038" s="62"/>
-      <c r="E1038" s="62"/>
+      <c r="A1038" s="50"/>
+      <c r="E1038" s="50"/>
       <c r="N1038" s="8"/>
       <c r="P1038" s="8"/>
     </row>
     <row r="1039" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1039" s="62"/>
-      <c r="E1039" s="62"/>
+      <c r="A1039" s="50"/>
+      <c r="E1039" s="50"/>
       <c r="N1039" s="8"/>
       <c r="P1039" s="8"/>
     </row>
     <row r="1040" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1040" s="62"/>
-      <c r="E1040" s="62"/>
+      <c r="A1040" s="50"/>
+      <c r="E1040" s="50"/>
       <c r="N1040" s="8"/>
       <c r="P1040" s="8"/>
     </row>
     <row r="1041" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1041" s="62"/>
-      <c r="E1041" s="62"/>
+      <c r="A1041" s="50"/>
+      <c r="E1041" s="50"/>
       <c r="N1041" s="8"/>
       <c r="P1041" s="8"/>
     </row>
     <row r="1042" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1042" s="62"/>
-      <c r="E1042" s="62"/>
+      <c r="A1042" s="50"/>
+      <c r="E1042" s="50"/>
       <c r="N1042" s="8"/>
       <c r="P1042" s="8"/>
     </row>
     <row r="1043" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1043" s="62"/>
-      <c r="E1043" s="62"/>
+      <c r="A1043" s="50"/>
+      <c r="E1043" s="50"/>
       <c r="N1043" s="8"/>
       <c r="P1043" s="8"/>
     </row>
     <row r="1044" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1044" s="62"/>
-      <c r="E1044" s="62"/>
+      <c r="A1044" s="50"/>
+      <c r="E1044" s="50"/>
       <c r="N1044" s="8"/>
       <c r="P1044" s="8"/>
     </row>
     <row r="1045" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1045" s="62"/>
-      <c r="E1045" s="62"/>
+      <c r="A1045" s="50"/>
+      <c r="E1045" s="50"/>
       <c r="N1045" s="8"/>
       <c r="P1045" s="8"/>
     </row>
     <row r="1046" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1046" s="62"/>
-      <c r="E1046" s="62"/>
+      <c r="A1046" s="50"/>
+      <c r="E1046" s="50"/>
       <c r="N1046" s="8"/>
       <c r="P1046" s="8"/>
     </row>
     <row r="1047" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1047" s="62"/>
-      <c r="E1047" s="62"/>
+      <c r="A1047" s="50"/>
+      <c r="E1047" s="50"/>
       <c r="N1047" s="8"/>
       <c r="P1047" s="8"/>
     </row>
     <row r="1048" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1048" s="62"/>
-      <c r="E1048" s="62"/>
+      <c r="A1048" s="50"/>
+      <c r="E1048" s="50"/>
       <c r="N1048" s="8"/>
       <c r="P1048" s="8"/>
     </row>
     <row r="1049" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1049" s="62"/>
-      <c r="E1049" s="62"/>
+      <c r="A1049" s="50"/>
+      <c r="E1049" s="50"/>
       <c r="N1049" s="8"/>
       <c r="P1049" s="8"/>
     </row>
     <row r="1050" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1050" s="62"/>
-      <c r="E1050" s="62"/>
+      <c r="A1050" s="50"/>
+      <c r="E1050" s="50"/>
       <c r="N1050" s="8"/>
       <c r="P1050" s="8"/>
     </row>
     <row r="1051" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1051" s="62"/>
-      <c r="E1051" s="62"/>
+      <c r="A1051" s="50"/>
+      <c r="E1051" s="50"/>
       <c r="N1051" s="8"/>
       <c r="P1051" s="8"/>
     </row>
     <row r="1052" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1052" s="62"/>
-      <c r="E1052" s="62"/>
+      <c r="A1052" s="50"/>
+      <c r="E1052" s="50"/>
       <c r="N1052" s="8"/>
       <c r="P1052" s="8"/>
     </row>
     <row r="1053" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1053" s="62"/>
-      <c r="E1053" s="62"/>
+      <c r="A1053" s="50"/>
+      <c r="E1053" s="50"/>
       <c r="N1053" s="8"/>
       <c r="P1053" s="8"/>
     </row>
     <row r="1054" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1054" s="62"/>
-      <c r="E1054" s="62"/>
+      <c r="A1054" s="50"/>
+      <c r="E1054" s="50"/>
       <c r="N1054" s="8"/>
       <c r="P1054" s="8"/>
     </row>
     <row r="1055" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1055" s="62"/>
-      <c r="E1055" s="62"/>
+      <c r="A1055" s="50"/>
+      <c r="E1055" s="50"/>
       <c r="N1055" s="8"/>
       <c r="P1055" s="8"/>
     </row>
     <row r="1056" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1056" s="62"/>
-      <c r="E1056" s="62"/>
+      <c r="A1056" s="50"/>
+      <c r="E1056" s="50"/>
       <c r="N1056" s="8"/>
       <c r="P1056" s="8"/>
     </row>
     <row r="1057" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1057" s="62"/>
-      <c r="E1057" s="62"/>
+      <c r="A1057" s="50"/>
+      <c r="E1057" s="50"/>
       <c r="N1057" s="8"/>
       <c r="P1057" s="8"/>
     </row>
     <row r="1058" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1058" s="62"/>
-      <c r="E1058" s="62"/>
+      <c r="A1058" s="50"/>
+      <c r="E1058" s="50"/>
       <c r="N1058" s="8"/>
       <c r="P1058" s="8"/>
     </row>
     <row r="1059" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1059" s="62"/>
-      <c r="E1059" s="62"/>
+      <c r="A1059" s="50"/>
+      <c r="E1059" s="50"/>
       <c r="N1059" s="8"/>
       <c r="P1059" s="8"/>
     </row>
     <row r="1060" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1060" s="62"/>
-      <c r="E1060" s="62"/>
+      <c r="A1060" s="50"/>
+      <c r="E1060" s="50"/>
       <c r="N1060" s="8"/>
       <c r="P1060" s="8"/>
     </row>
     <row r="1061" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1061" s="62"/>
-      <c r="E1061" s="62"/>
+      <c r="A1061" s="50"/>
+      <c r="E1061" s="50"/>
       <c r="N1061" s="8"/>
       <c r="P1061" s="8"/>
     </row>
     <row r="1062" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1062" s="62"/>
-      <c r="E1062" s="62"/>
+      <c r="A1062" s="50"/>
+      <c r="E1062" s="50"/>
       <c r="N1062" s="8"/>
       <c r="P1062" s="8"/>
     </row>
     <row r="1063" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1063" s="62"/>
-      <c r="E1063" s="62"/>
+      <c r="A1063" s="50"/>
+      <c r="E1063" s="50"/>
       <c r="N1063" s="8"/>
       <c r="P1063" s="8"/>
     </row>
     <row r="1064" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1064" s="62"/>
-      <c r="E1064" s="62"/>
+      <c r="A1064" s="50"/>
+      <c r="E1064" s="50"/>
       <c r="N1064" s="8"/>
       <c r="P1064" s="8"/>
     </row>
     <row r="1065" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1065" s="62"/>
-      <c r="E1065" s="62"/>
+      <c r="A1065" s="50"/>
+      <c r="E1065" s="50"/>
       <c r="N1065" s="8"/>
       <c r="P1065" s="8"/>
     </row>
     <row r="1066" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1066" s="62"/>
-      <c r="E1066" s="62"/>
+      <c r="A1066" s="50"/>
+      <c r="E1066" s="50"/>
       <c r="N1066" s="8"/>
       <c r="P1066" s="8"/>
     </row>
     <row r="1067" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1067" s="62"/>
-      <c r="E1067" s="62"/>
+      <c r="A1067" s="50"/>
+      <c r="E1067" s="50"/>
       <c r="N1067" s="8"/>
       <c r="P1067" s="8"/>
     </row>
     <row r="1068" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1068" s="62"/>
-      <c r="E1068" s="62"/>
+      <c r="A1068" s="50"/>
+      <c r="E1068" s="50"/>
       <c r="N1068" s="8"/>
       <c r="P1068" s="8"/>
     </row>
     <row r="1069" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1069" s="62"/>
-      <c r="E1069" s="62"/>
+      <c r="A1069" s="50"/>
+      <c r="E1069" s="50"/>
       <c r="N1069" s="8"/>
       <c r="P1069" s="8"/>
     </row>
     <row r="1070" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1070" s="62"/>
-      <c r="E1070" s="62"/>
+      <c r="A1070" s="50"/>
+      <c r="E1070" s="50"/>
       <c r="N1070" s="8"/>
       <c r="P1070" s="8"/>
     </row>
     <row r="1071" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1071" s="62"/>
-      <c r="E1071" s="62"/>
+      <c r="A1071" s="50"/>
+      <c r="E1071" s="50"/>
       <c r="N1071" s="8"/>
       <c r="P1071" s="8"/>
     </row>
     <row r="1072" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1072" s="62"/>
-      <c r="E1072" s="62"/>
+      <c r="A1072" s="50"/>
+      <c r="E1072" s="50"/>
       <c r="N1072" s="8"/>
       <c r="P1072" s="8"/>
     </row>
     <row r="1073" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1073" s="62"/>
-      <c r="E1073" s="62"/>
+      <c r="A1073" s="50"/>
+      <c r="E1073" s="50"/>
       <c r="N1073" s="8"/>
       <c r="P1073" s="8"/>
     </row>
     <row r="1074" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1074" s="62"/>
-      <c r="E1074" s="62"/>
+      <c r="A1074" s="50"/>
+      <c r="E1074" s="50"/>
       <c r="N1074" s="8"/>
       <c r="P1074" s="8"/>
     </row>
     <row r="1075" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1075" s="62"/>
-      <c r="E1075" s="62"/>
+      <c r="A1075" s="50"/>
+      <c r="E1075" s="50"/>
       <c r="N1075" s="8"/>
       <c r="P1075" s="8"/>
     </row>
     <row r="1076" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1076" s="62"/>
-      <c r="E1076" s="62"/>
+      <c r="A1076" s="50"/>
+      <c r="E1076" s="50"/>
       <c r="N1076" s="8"/>
       <c r="P1076" s="8"/>
     </row>
     <row r="1077" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1077" s="62"/>
-      <c r="E1077" s="62"/>
+      <c r="A1077" s="50"/>
+      <c r="E1077" s="50"/>
       <c r="N1077" s="8"/>
       <c r="P1077" s="8"/>
     </row>
     <row r="1078" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1078" s="62"/>
-      <c r="E1078" s="62"/>
+      <c r="A1078" s="50"/>
+      <c r="E1078" s="50"/>
       <c r="N1078" s="8"/>
       <c r="P1078" s="8"/>
     </row>
     <row r="1079" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1079" s="62"/>
-      <c r="E1079" s="62"/>
+      <c r="A1079" s="50"/>
+      <c r="E1079" s="50"/>
       <c r="N1079" s="8"/>
       <c r="P1079" s="8"/>
     </row>
     <row r="1080" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1080" s="62"/>
-      <c r="E1080" s="62"/>
+      <c r="A1080" s="50"/>
+      <c r="E1080" s="50"/>
       <c r="N1080" s="8"/>
       <c r="P1080" s="8"/>
     </row>
     <row r="1081" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1081" s="62"/>
-      <c r="E1081" s="62"/>
+      <c r="A1081" s="50"/>
+      <c r="E1081" s="50"/>
       <c r="N1081" s="8"/>
       <c r="P1081" s="8"/>
     </row>
     <row r="1082" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1082" s="62"/>
-      <c r="E1082" s="62"/>
+      <c r="A1082" s="50"/>
+      <c r="E1082" s="50"/>
       <c r="N1082" s="8"/>
       <c r="P1082" s="8"/>
     </row>
     <row r="1083" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1083" s="62"/>
-      <c r="E1083" s="62"/>
+      <c r="A1083" s="50"/>
+      <c r="E1083" s="50"/>
       <c r="N1083" s="8"/>
       <c r="P1083" s="8"/>
     </row>
     <row r="1084" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1084" s="62"/>
-      <c r="E1084" s="62"/>
+      <c r="A1084" s="50"/>
+      <c r="E1084" s="50"/>
       <c r="N1084" s="8"/>
       <c r="P1084" s="8"/>
     </row>
     <row r="1085" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1085" s="62"/>
-      <c r="E1085" s="62"/>
+      <c r="A1085" s="50"/>
+      <c r="E1085" s="50"/>
       <c r="N1085" s="8"/>
       <c r="P1085" s="8"/>
     </row>
+    <row r="1086" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1086" s="50"/>
+      <c r="E1086" s="50"/>
+      <c r="N1086" s="8"/>
+      <c r="P1086" s="8"/>
+    </row>
+    <row r="1087" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1087" s="50"/>
+      <c r="E1087" s="50"/>
+      <c r="N1087" s="8"/>
+      <c r="P1087" s="8"/>
+    </row>
+    <row r="1088" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1088" s="50"/>
+      <c r="E1088" s="50"/>
+      <c r="N1088" s="8"/>
+      <c r="P1088" s="8"/>
+    </row>
+    <row r="1089" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1089" s="50"/>
+      <c r="E1089" s="50"/>
+      <c r="N1089" s="8"/>
+      <c r="P1089" s="8"/>
+    </row>
+    <row r="1090" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1090" s="50"/>
+      <c r="E1090" s="50"/>
+      <c r="N1090" s="8"/>
+      <c r="P1090" s="8"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P549"/>
+  <autoFilter ref="A1:P557"/>
   <dataValidations count="5">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="N2 N4:N5 N10:N11 N13:N15 N18:N23 N25 N28:N29 N31:N34 N36 N39:N50 N52:N58 N60:N66 N68 N71 N73 N75:N76 N78:N83 N87 N91:N94 N96 N98:N99 N101:N110 N113:N114 N116:N117 N119:N121 N124:N125 N127 N129:N131 N133:N141 N143:N144 N148:N151 N153 N159 N161:N162 N170 N173:N174 N177:N180 N183:N185 N191:N192 N195 N208 N216 N229:N230 N232 N235:N236 N248 N253:N254 N256:N258 N263:N265 N273 N276 N279 N284:N285 N296 N315:N317 N326 N328 N330 N333:N335 N359 N369 N376 N380:N381 N394:N395 N415 N428 N434 N478 N499:N500" type="list">
       <formula1>"CENTRO,NAÇÕES,ESTADOS,MUNICIPIOS,N. ESPERANÇA,PIONEIROS,PONTAL NORTE,ARIRIBA,BARRA,VILA REAL,Barra Sul,São J. Tadeu"</formula1>
